--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -11,9 +11,9 @@
     <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Лист1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -107,6 +107,199 @@
         </r>
       </text>
     </comment>
+    <comment ref="P20" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Дубликат ключей</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P24" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Левомеколь</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вино
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J25" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Газпром</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Росатом Энергосбыт</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Галстук + Брюки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P26" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Торт Мишутка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+УК Эталон</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -313,11 +506,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,6 +611,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -939,23 +1145,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>27</v>
       </c>
@@ -983,7 +1189,7 @@
       <c r="W1" s="37"/>
       <c r="X1" s="37"/>
     </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
+    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1285,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>5</v>
       </c>
@@ -1127,7 +1333,7 @@
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -1163,7 +1369,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -1203,7 +1409,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -1241,7 +1447,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -1280,7 +1486,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -1319,7 +1525,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -1354,7 +1560,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -1389,7 +1595,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -1431,7 +1637,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -1476,7 +1682,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -1514,7 +1720,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -1549,7 +1755,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -1582,7 +1788,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -1621,7 +1827,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -1657,7 +1863,7 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>20</v>
       </c>
@@ -1698,7 +1904,7 @@
       </c>
       <c r="X18" s="36"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -1738,7 +1944,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -1776,7 +1982,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -1811,7 +2017,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -1850,17 +2056,22 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>25</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="7"/>
+      <c r="C23" s="7">
+        <v>935</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="F23" s="7">
+        <f>1118+770</f>
+        <v>1888</v>
+      </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -1869,23 +2080,29 @@
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7">
-        <v>360</v>
+        <f>360+381</f>
+        <v>741</v>
       </c>
       <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <v>100</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
+      <c r="S23" s="7">
+        <f>100+650</f>
+        <v>750</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="8">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>4414</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -1894,7 +2111,9 @@
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="E24" s="10">
+        <v>611</v>
+      </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1903,9 +2122,14 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
+      <c r="N24" s="10">
+        <f>400+344</f>
+        <v>744</v>
+      </c>
       <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
+      <c r="P24" s="10">
+        <v>214</v>
+      </c>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
@@ -1913,12 +2137,12 @@
       <c r="U24" s="10"/>
       <c r="V24" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1569</v>
       </c>
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -1928,50 +2152,74 @@
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="F25" s="7">
+        <v>700</v>
+      </c>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7">
+        <v>1239.99</v>
+      </c>
       <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
+      <c r="J25" s="7">
+        <v>3974.41</v>
+      </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="N25" s="7">
+        <f>349+254+607+400</f>
+        <v>1610</v>
+      </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
+      <c r="U25" s="7">
+        <f>1100+1090+350</f>
+        <v>2540</v>
+      </c>
       <c r="V25" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10064.4</v>
       </c>
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>28</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10">
+        <v>1577.82</v>
+      </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="J26" s="10">
+        <v>3990.69</v>
+      </c>
       <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
+      <c r="L26" s="10">
+        <f>1896+3633</f>
+        <v>5529</v>
+      </c>
       <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
+      <c r="N26" s="10">
+        <f>233+539</f>
+        <v>772</v>
+      </c>
       <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
+      <c r="P26" s="10">
+        <v>2400</v>
+      </c>
       <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
       <c r="S26" s="10"/>
@@ -1979,12 +2227,12 @@
       <c r="U26" s="10"/>
       <c r="V26" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14269.51</v>
       </c>
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -1998,7 +2246,9 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
+      <c r="J27" s="10">
+        <v>1711.25</v>
+      </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
@@ -2012,12 +2262,12 @@
       <c r="U27" s="10"/>
       <c r="V27" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1711.25</v>
       </c>
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -2050,7 +2300,7 @@
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2083,91 +2333,70 @@
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>4</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="14">
-        <f>15000-SUM(C19:C29)</f>
-        <v>11851</v>
-      </c>
-      <c r="D30" s="14">
-        <f>12000-SUM(D19:D29)</f>
-        <v>12000</v>
-      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="14">
-        <f>4200-SUM(G19:G29)</f>
-        <v>65</v>
-      </c>
+      <c r="G30" s="14"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
-      <c r="J30" s="14">
-        <f>8000-SUM(J19:J29)</f>
-        <v>8000</v>
-      </c>
+      <c r="J30" s="14"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
-      <c r="N30" s="14">
-        <f>3500-SUM(N19:N29)</f>
-        <v>2162</v>
-      </c>
+      <c r="N30" s="14"/>
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
       <c r="Q30" s="10"/>
-      <c r="R30" s="14">
-        <f>2000-SUM(R19:R29)</f>
-        <v>2000</v>
-      </c>
-      <c r="S30" s="14">
-        <f>5000-SUM(S19:S29)</f>
-        <v>5000</v>
-      </c>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
       <c r="T30" s="10"/>
       <c r="U30" s="10"/>
       <c r="V30" s="11">
         <f t="shared" si="1"/>
-        <v>41078</v>
+        <v>0</v>
       </c>
       <c r="W30" s="12"/>
       <c r="X30" s="25">
         <f>W18+W21-SUM(V18:V30)</f>
-        <v>-3205.4799999999959</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
+        <v>6204.3600000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
         <v>20</v>
       </c>
       <c r="B31" s="38"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
-        <v>29330.45</v>
+        <v>19992.27</v>
       </c>
       <c r="D31" s="13">
         <f t="shared" ref="D31:U31" si="2">SUM(D3:D30)</f>
-        <v>23194</v>
+        <v>11194</v>
       </c>
       <c r="E31" s="13">
         <f t="shared" si="2"/>
-        <v>4516.4799999999996</v>
+        <v>5127.4799999999996</v>
       </c>
       <c r="F31" s="13">
         <f>SUM(F3:F30)</f>
-        <v>939</v>
+        <v>3527</v>
       </c>
       <c r="G31" s="13">
         <f t="shared" si="2"/>
-        <v>8610</v>
+        <v>8545</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1239.99</v>
       </c>
       <c r="I31" s="13">
         <f t="shared" si="2"/>
@@ -2175,7 +2404,7 @@
       </c>
       <c r="J31" s="13">
         <f t="shared" si="2"/>
-        <v>8450</v>
+        <v>10126.35</v>
       </c>
       <c r="K31" s="13">
         <f t="shared" si="2"/>
@@ -2183,7 +2412,7 @@
       </c>
       <c r="L31" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5529</v>
       </c>
       <c r="M31" s="13">
         <f t="shared" si="2"/>
@@ -2191,7 +2420,7 @@
       </c>
       <c r="N31" s="13">
         <f t="shared" si="2"/>
-        <v>8866</v>
+        <v>10211</v>
       </c>
       <c r="O31" s="13">
         <f t="shared" si="2"/>
@@ -2199,7 +2428,7 @@
       </c>
       <c r="P31" s="13">
         <f t="shared" si="2"/>
-        <v>6337</v>
+        <v>9051</v>
       </c>
       <c r="Q31" s="13">
         <f t="shared" si="2"/>
@@ -2207,11 +2436,11 @@
       </c>
       <c r="R31" s="13">
         <f t="shared" si="2"/>
-        <v>2499</v>
+        <v>499</v>
       </c>
       <c r="S31" s="13">
         <f t="shared" si="2"/>
-        <v>11055</v>
+        <v>6805</v>
       </c>
       <c r="T31" s="13">
         <f t="shared" si="2"/>
@@ -2219,11 +2448,11 @@
       </c>
       <c r="U31" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2540</v>
       </c>
       <c r="V31" s="13">
         <f t="shared" ref="V31:W31" si="3">SUM(V3:V26)</f>
-        <v>79276.929999999993</v>
+        <v>109233.83999999998</v>
       </c>
       <c r="W31" s="13">
         <f t="shared" si="3"/>
@@ -2231,7 +2460,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -2254,16 +2483,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="23" width="20.7109375" style="2" customWidth="1"/>
     <col min="24" max="35" width="12.7109375" style="2" customWidth="1"/>
     <col min="36" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="60.75" customHeight="1">
+    <row r="1" spans="1:45" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2519,7 @@
       <c r="V1" s="40"/>
       <c r="W1" s="40"/>
     </row>
-    <row r="2" spans="1:45" ht="45" customHeight="1">
+    <row r="2" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2612,7 @@
       <c r="AR2" s="1"/>
       <c r="AS2" s="1"/>
     </row>
-    <row r="3" spans="1:45">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>5</v>
       </c>
@@ -2418,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>6</v>
       </c>
@@ -2450,7 +2679,7 @@
       <c r="V4" s="30"/>
       <c r="W4" s="41"/>
     </row>
-    <row r="5" spans="1:45">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>7</v>
       </c>
@@ -2482,7 +2711,7 @@
       <c r="V5" s="30"/>
       <c r="W5" s="41"/>
     </row>
-    <row r="6" spans="1:45">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>8</v>
       </c>
@@ -2514,7 +2743,7 @@
       <c r="V6" s="30"/>
       <c r="W6" s="41"/>
     </row>
-    <row r="7" spans="1:45">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>9</v>
       </c>
@@ -2546,7 +2775,7 @@
       <c r="V7" s="30"/>
       <c r="W7" s="41"/>
     </row>
-    <row r="8" spans="1:45">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>10</v>
       </c>
@@ -2578,7 +2807,7 @@
       <c r="V8" s="30"/>
       <c r="W8" s="41"/>
     </row>
-    <row r="9" spans="1:45">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>11</v>
       </c>
@@ -2610,7 +2839,7 @@
       <c r="V9" s="30"/>
       <c r="W9" s="41"/>
     </row>
-    <row r="10" spans="1:45">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>12</v>
       </c>
@@ -2642,7 +2871,7 @@
       <c r="V10" s="30"/>
       <c r="W10" s="41"/>
     </row>
-    <row r="11" spans="1:45">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>13</v>
       </c>
@@ -2674,7 +2903,7 @@
       <c r="V11" s="30"/>
       <c r="W11" s="41"/>
     </row>
-    <row r="12" spans="1:45">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>14</v>
       </c>
@@ -2706,7 +2935,7 @@
       <c r="V12" s="30"/>
       <c r="W12" s="41"/>
     </row>
-    <row r="13" spans="1:45">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>15</v>
       </c>
@@ -2738,7 +2967,7 @@
       <c r="V13" s="30"/>
       <c r="W13" s="41"/>
     </row>
-    <row r="14" spans="1:45">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>16</v>
       </c>
@@ -2770,7 +2999,7 @@
       <c r="V14" s="30"/>
       <c r="W14" s="41"/>
     </row>
-    <row r="15" spans="1:45">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
         <v>17</v>
       </c>
@@ -2802,7 +3031,7 @@
       <c r="V15" s="30"/>
       <c r="W15" s="41"/>
     </row>
-    <row r="16" spans="1:45">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
         <v>18</v>
       </c>
@@ -2834,7 +3063,7 @@
       <c r="V16" s="30"/>
       <c r="W16" s="41"/>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
         <v>19</v>
       </c>
@@ -2866,7 +3095,7 @@
       <c r="V17" s="30"/>
       <c r="W17" s="41"/>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="28">
         <v>20</v>
       </c>
@@ -2898,7 +3127,7 @@
       <c r="V18" s="30"/>
       <c r="W18" s="41"/>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
         <v>21</v>
       </c>
@@ -2930,7 +3159,7 @@
       <c r="V19" s="30"/>
       <c r="W19" s="41"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <v>22</v>
       </c>
@@ -2962,7 +3191,7 @@
       <c r="V20" s="30"/>
       <c r="W20" s="41"/>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <v>23</v>
       </c>
@@ -2994,7 +3223,7 @@
       <c r="V21" s="30"/>
       <c r="W21" s="41"/>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <v>24</v>
       </c>
@@ -3026,7 +3255,7 @@
       <c r="V22" s="30"/>
       <c r="W22" s="41"/>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <v>25</v>
       </c>
@@ -3058,7 +3287,7 @@
       <c r="V23" s="30"/>
       <c r="W23" s="41"/>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="28">
         <v>26</v>
       </c>
@@ -3090,7 +3319,7 @@
       <c r="V24" s="30"/>
       <c r="W24" s="41"/>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="28">
         <v>27</v>
       </c>
@@ -3122,7 +3351,7 @@
       <c r="V25" s="30"/>
       <c r="W25" s="41"/>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="28">
         <v>28</v>
       </c>
@@ -3154,7 +3383,7 @@
       <c r="V26" s="30"/>
       <c r="W26" s="41"/>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
@@ -3179,7 +3408,7 @@
       <c r="V27" s="30"/>
       <c r="W27" s="41"/>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="28"/>
       <c r="C28" s="29"/>
@@ -3204,7 +3433,7 @@
       <c r="V28" s="30"/>
       <c r="W28" s="41"/>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="28"/>
       <c r="C29" s="29"/>
@@ -3229,7 +3458,7 @@
       <c r="V29" s="30"/>
       <c r="W29" s="41"/>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>20</v>
       </c>
@@ -3310,7 +3539,7 @@
       </c>
       <c r="W30" s="41"/>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -3332,9 +3561,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -3349,7 +3578,7 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>49</v>
       </c>
@@ -3365,7 +3594,7 @@
       <c r="J1" s="42"/>
       <c r="K1" s="42"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3397,7 +3626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -3431,7 +3660,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -3465,7 +3694,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -3499,7 +3728,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -3533,7 +3762,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -3567,7 +3796,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -3595,7 +3824,7 @@
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -3616,7 +3845,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -3637,7 +3866,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -3658,7 +3887,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -3679,7 +3908,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -3700,7 +3929,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -3721,7 +3950,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -3742,7 +3971,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -3763,7 +3992,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -3784,7 +4013,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -3802,7 +4031,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -3820,7 +4049,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -3838,7 +4067,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -3856,7 +4085,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -3874,7 +4103,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -3892,7 +4121,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
         <v>61</v>
       </c>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Февраль 2026" sheetId="3" r:id="rId1"/>
     <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Лист1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -155,7 +155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -304,8 +304,44 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="R3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+На ВПН</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
   <si>
     <t>Число</t>
   </si>
@@ -501,16 +537,22 @@
   </si>
   <si>
     <t>Столовая (обед)</t>
+  </si>
+  <si>
+    <t>Доходы - Расходы Март 2026</t>
+  </si>
+  <si>
+    <t>Обед</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,13 +642,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9" tint="0.39997558519241921"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -625,8 +660,24 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,7 +734,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,16 +804,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="9" tint="0.39997558519241921"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="9" tint="0.39997558519241921"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="9" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="9" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -752,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -814,16 +883,6 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -846,13 +905,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -863,6 +916,51 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,51 +1243,51 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+      <c r="A1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1285,55 +1383,55 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A3" s="31">
+    <row r="3" spans="1:46">
+      <c r="A3" s="27">
         <v>5</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="29">
         <f>183+2168</f>
         <v>2351</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <v>3131</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29">
         <v>450</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33">
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29">
         <v>40</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33">
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29">
         <v>14418</v>
       </c>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33">
+      <c r="R3" s="29"/>
+      <c r="S3" s="29">
         <v>5000</v>
       </c>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="34">
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="30">
         <f>SUM(C3:U3)</f>
         <v>25390</v>
       </c>
-      <c r="W3" s="35">
+      <c r="W3" s="31">
         <v>53739.4</v>
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -1369,7 +1467,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -1409,7 +1507,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -1447,7 +1545,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -1486,7 +1584,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -1525,7 +1623,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -1560,7 +1658,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -1595,7 +1693,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -1637,7 +1735,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -1682,7 +1780,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -1720,7 +1818,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -1755,7 +1853,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -1788,7 +1886,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -1827,7 +1925,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -1863,48 +1961,48 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+      <c r="A18" s="27">
         <v>20</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="33">
+      <c r="C18" s="29"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29">
         <v>1300</v>
       </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33">
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29">
         <f>1587+618</f>
         <v>2205</v>
       </c>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
-      <c r="V18" s="34">
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="30">
         <f>SUM(C18:U18)</f>
         <v>3505</v>
       </c>
-      <c r="W18" s="35">
+      <c r="W18" s="31">
         <f>30304+16451</f>
         <v>46755</v>
       </c>
-      <c r="X18" s="36"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X18" s="32"/>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -1944,7 +2042,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -1982,7 +2080,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -2017,7 +2115,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -2056,7 +2154,7 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -2102,7 +2200,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -2142,7 +2240,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -2187,7 +2285,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26" s="5">
         <v>28</v>
       </c>
@@ -2232,7 +2330,7 @@
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2240,7 +2338,9 @@
         <v>6</v>
       </c>
       <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="D27" s="10">
+        <v>1294</v>
+      </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -2252,22 +2352,27 @@
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
+      <c r="N27" s="10">
+        <v>133</v>
+      </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
+      <c r="S27" s="10">
+        <f>414+449</f>
+        <v>863</v>
+      </c>
       <c r="T27" s="10"/>
       <c r="U27" s="10"/>
       <c r="V27" s="8">
         <f t="shared" si="1"/>
-        <v>1711.25</v>
+        <v>4001.25</v>
       </c>
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -2277,7 +2382,10 @@
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="10">
+        <f>350+1510</f>
+        <v>1860</v>
+      </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
@@ -2285,22 +2393,26 @@
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
+      <c r="N28" s="10">
+        <v>277</v>
+      </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
+      <c r="R28" s="10">
+        <v>700</v>
+      </c>
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
       <c r="U28" s="10"/>
       <c r="V28" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2837</v>
       </c>
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2322,18 +2434,20 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+      <c r="R29" s="10">
+        <v>799</v>
+      </c>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
       <c r="U29" s="10"/>
       <c r="V29" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -2366,21 +2480,21 @@
       <c r="W30" s="12"/>
       <c r="X30" s="25">
         <f>W18+W21-SUM(V18:V30)</f>
-        <v>6204.3600000000006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
+        <v>278.36000000000058</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="38"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
       </c>
       <c r="D31" s="13">
         <f t="shared" ref="D31:U31" si="2">SUM(D3:D30)</f>
-        <v>11194</v>
+        <v>12488</v>
       </c>
       <c r="E31" s="13">
         <f t="shared" si="2"/>
@@ -2388,7 +2502,7 @@
       </c>
       <c r="F31" s="13">
         <f>SUM(F3:F30)</f>
-        <v>3527</v>
+        <v>5387</v>
       </c>
       <c r="G31" s="13">
         <f t="shared" si="2"/>
@@ -2420,7 +2534,7 @@
       </c>
       <c r="N31" s="13">
         <f t="shared" si="2"/>
-        <v>10211</v>
+        <v>10621</v>
       </c>
       <c r="O31" s="13">
         <f t="shared" si="2"/>
@@ -2436,11 +2550,11 @@
       </c>
       <c r="R31" s="13">
         <f t="shared" si="2"/>
-        <v>499</v>
+        <v>1998</v>
       </c>
       <c r="S31" s="13">
         <f t="shared" si="2"/>
-        <v>6805</v>
+        <v>7668</v>
       </c>
       <c r="T31" s="13">
         <f t="shared" si="2"/>
@@ -2460,7 +2574,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -2483,113 +2597,116 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AS34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AT34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="23" width="20.7109375" style="2" customWidth="1"/>
-    <col min="24" max="35" width="12.7109375" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
+    <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-    </row>
-    <row r="2" spans="1:45" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="27" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="H2" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="I2" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -2611,935 +2728,1015 @@
       <c r="AQ2" s="1"/>
       <c r="AR2" s="1"/>
       <c r="AS2" s="1"/>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+      <c r="AT2" s="1"/>
+    </row>
+    <row r="3" spans="1:46">
+      <c r="A3" s="46">
         <v>5</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29">
-        <f t="shared" ref="U3:U26" si="0">SUM(C3:T3)</f>
-        <v>0</v>
-      </c>
-      <c r="V3" s="30"/>
-      <c r="W3" s="41">
-        <f>V30-U30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="55">
+        <v>8000</v>
+      </c>
+      <c r="R3" s="55">
+        <v>1000</v>
+      </c>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47">
+        <f>SUM(C3:U3)</f>
+        <v>9000</v>
+      </c>
+      <c r="W3" s="48">
+        <v>43724</v>
+      </c>
+      <c r="X3" s="49"/>
+    </row>
+    <row r="4" spans="1:46">
+      <c r="A4" s="39">
         <v>6</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V4" s="30"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40">
+        <f t="shared" ref="V4:V29" si="0">SUM(C4:U4)</f>
+        <v>0</v>
+      </c>
       <c r="W4" s="41"/>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+      <c r="X4" s="45"/>
+    </row>
+    <row r="5" spans="1:46">
+      <c r="A5" s="39">
         <v>7</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V5" s="30"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W5" s="41"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="X5" s="45"/>
+    </row>
+    <row r="6" spans="1:46">
+      <c r="A6" s="39">
         <v>8</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="30"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W6" s="41"/>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="X6" s="45"/>
+    </row>
+    <row r="7" spans="1:46">
+      <c r="A7" s="39">
         <v>9</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V7" s="30"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W7" s="41"/>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="X7" s="45"/>
+    </row>
+    <row r="8" spans="1:46">
+      <c r="A8" s="39">
         <v>10</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V8" s="30"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W8" s="41"/>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="X8" s="45"/>
+    </row>
+    <row r="9" spans="1:46">
+      <c r="A9" s="39">
         <v>11</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="30"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W9" s="41"/>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="X9" s="45"/>
+    </row>
+    <row r="10" spans="1:46">
+      <c r="A10" s="39">
         <v>12</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="30"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W10" s="41"/>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
+      <c r="X10" s="45"/>
+    </row>
+    <row r="11" spans="1:46">
+      <c r="A11" s="39">
         <v>13</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="30"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W11" s="41"/>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="X11" s="45"/>
+    </row>
+    <row r="12" spans="1:46">
+      <c r="A12" s="39">
         <v>14</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="30"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W12" s="41"/>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
+      <c r="X12" s="45"/>
+    </row>
+    <row r="13" spans="1:46">
+      <c r="A13" s="39">
         <v>15</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="30"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W13" s="41"/>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="X13" s="45"/>
+    </row>
+    <row r="14" spans="1:46">
+      <c r="A14" s="39">
         <v>16</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="30"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W14" s="41"/>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
+      <c r="X14" s="45"/>
+    </row>
+    <row r="15" spans="1:46">
+      <c r="A15" s="39">
         <v>17</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="30"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W15" s="41"/>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="X15" s="45"/>
+    </row>
+    <row r="16" spans="1:46">
+      <c r="A16" s="39">
         <v>18</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="30"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W16" s="41"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
+      <c r="X16" s="45"/>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" s="39">
         <v>19</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="30"/>
+      <c r="C17" s="55">
+        <f>14500-SUM(C3:C16)</f>
+        <v>14500</v>
+      </c>
+      <c r="D17" s="40"/>
+      <c r="E17" s="55">
+        <f>12000-SUM(E3:E16)</f>
+        <v>12000</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="55">
+        <f>4400-SUM(G3:G16)</f>
+        <v>4400</v>
+      </c>
+      <c r="H17" s="55">
+        <f>1300-SUM(H3:H16)</f>
+        <v>1300</v>
+      </c>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="55">
+        <f>3200-SUM(N3:N16)</f>
+        <v>3200</v>
+      </c>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40">
+        <f t="shared" si="0"/>
+        <v>35400</v>
+      </c>
       <c r="W17" s="41"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="X17" s="54">
+        <f>SUM(W3:W17)-SUM(V3:V17)</f>
+        <v>-676</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" s="50">
         <v>20</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="30"/>
-      <c r="W18" s="41"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="51"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="51"/>
+      <c r="V18" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="52"/>
+      <c r="X18" s="53"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="39">
         <v>21</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="30"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W19" s="41"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="X19" s="45"/>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20" s="39">
         <v>22</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="30"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W20" s="41"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="28">
+      <c r="X20" s="45"/>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" s="39">
         <v>23</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="30"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W21" s="41"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="X21" s="45"/>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" s="39">
         <v>24</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="30"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W22" s="41"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="28">
+      <c r="X22" s="45"/>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" s="39">
         <v>25</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="30"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W23" s="41"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
+      <c r="X23" s="45"/>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="39">
         <v>26</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="30"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="40"/>
+      <c r="S24" s="40"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W24" s="41"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="28">
+      <c r="X24" s="45"/>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25" s="39">
         <v>27</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="30"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W25" s="41"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+      <c r="X25" s="45"/>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26" s="39">
         <v>28</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="30"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W26" s="41"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="30"/>
+      <c r="X26" s="45"/>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27" s="39">
+        <v>29</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W27" s="41"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="30"/>
+      <c r="X27" s="45"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" s="39">
+        <v>30</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="40"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W28" s="41"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="30"/>
+      <c r="X28" s="45"/>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29" s="39">
+        <v>31</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W29" s="41"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+      <c r="X29" s="45"/>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="30">
-        <f t="shared" ref="C30:V30" si="1">SUM(C3:C26)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30">
+      <c r="B30" s="42"/>
+      <c r="C30" s="41">
+        <f>SUM(C3:C29)</f>
+        <v>14500</v>
+      </c>
+      <c r="D30" s="41">
+        <f t="shared" ref="D30:V30" si="1">SUM(D3:D29)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="30">
+        <v>12000</v>
+      </c>
+      <c r="F30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30">
+      <c r="G30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="30">
+        <v>4400</v>
+      </c>
+      <c r="H30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="30">
+        <v>1300</v>
+      </c>
+      <c r="I30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="30">
+      <c r="J30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="30">
+      <c r="K30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M30" s="30">
+      <c r="L30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="30">
+      <c r="M30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O30" s="30">
+      <c r="N30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="30">
+        <v>3200</v>
+      </c>
+      <c r="O30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="30">
+      <c r="P30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R30" s="30">
+      <c r="Q30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="30">
+        <v>8000</v>
+      </c>
+      <c r="R30" s="41">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="30">
+        <v>1000</v>
+      </c>
+      <c r="S30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U30" s="30">
+      <c r="T30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V30" s="30">
+      <c r="U30" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W30" s="41"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="V30" s="43">
+        <f t="shared" si="1"/>
+        <v>44400</v>
+      </c>
+      <c r="W30" s="41">
+        <f>SUM(W3:W29)</f>
+        <v>43724</v>
+      </c>
+      <c r="X30" s="45"/>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -3548,22 +3745,23 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="W3:W30"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -3578,23 +3776,23 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="G1" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3626,7 +3824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -3660,7 +3858,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -3694,7 +3892,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -3728,7 +3926,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -3762,7 +3960,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -3796,7 +3994,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -3813,18 +4011,18 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -3845,7 +4043,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -3866,7 +4064,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -3887,7 +4085,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -3908,7 +4106,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -3929,7 +4127,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -3950,7 +4148,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -3971,7 +4169,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -3992,7 +4190,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -4013,7 +4211,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -4031,7 +4229,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -4049,7 +4247,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -4067,7 +4265,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -4085,7 +4283,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -4103,7 +4301,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -4121,13 +4319,13 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -333,6 +333,55 @@
           </rPr>
           <t xml:space="preserve">
 На ВПН</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Лапшичка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вк музыка
+</t>
         </r>
       </text>
     </comment>
@@ -899,24 +948,6 @@
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -924,9 +955,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -961,6 +989,27 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1243,7 +1292,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1260,32 +1309,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -2484,10 +2533,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -2607,104 +2656,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="44" t="s">
+      <c r="O2" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="44" t="s">
+      <c r="P2" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="44" t="s">
+      <c r="Q2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="44" t="s">
+      <c r="R2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="S2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="T2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="44" t="s">
+      <c r="U2" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="44" t="s">
+      <c r="V2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="44" t="s">
+      <c r="W2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="44" t="s">
+      <c r="X2" s="37" t="s">
         <v>21</v>
       </c>
       <c r="Y2" s="1"/>
@@ -2731,1010 +2780,1024 @@
       <c r="AT2" s="1"/>
     </row>
     <row r="3" spans="1:46">
-      <c r="A3" s="46">
+      <c r="A3" s="39">
         <v>5</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="55">
+      <c r="C3" s="40">
+        <f>2497.35+200</f>
+        <v>2697.35</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40">
+        <v>312</v>
+      </c>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40">
+        <v>990</v>
+      </c>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40">
+        <f>SUM(C3:U3)</f>
+        <v>3999.35</v>
+      </c>
+      <c r="W3" s="41">
+        <v>43724</v>
+      </c>
+      <c r="X3" s="42"/>
+    </row>
+    <row r="4" spans="1:46">
+      <c r="A4" s="33">
+        <v>6</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34">
+        <v>1610</v>
+      </c>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34">
+        <v>387</v>
+      </c>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34">
+        <v>199</v>
+      </c>
+      <c r="S4" s="34">
+        <f>2411.96/2+116.97+2148/2+729</f>
+        <v>3125.95</v>
+      </c>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34">
+        <f t="shared" ref="V4:V29" si="0">SUM(C4:U4)</f>
+        <v>5321.95</v>
+      </c>
+      <c r="W4" s="35"/>
+      <c r="X4" s="38"/>
+    </row>
+    <row r="5" spans="1:46">
+      <c r="A5" s="33">
+        <v>7</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W5" s="35"/>
+      <c r="X5" s="38"/>
+    </row>
+    <row r="6" spans="1:46">
+      <c r="A6" s="33">
+        <v>8</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="48">
         <v>8000</v>
       </c>
-      <c r="R3" s="55">
-        <v>1000</v>
-      </c>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47">
-        <f>SUM(C3:U3)</f>
-        <v>9000</v>
-      </c>
-      <c r="W3" s="48">
-        <v>43724</v>
-      </c>
-      <c r="X3" s="49"/>
-    </row>
-    <row r="4" spans="1:46">
-      <c r="A4" s="39">
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="34">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="W6" s="35"/>
+      <c r="X6" s="38"/>
+    </row>
+    <row r="7" spans="1:46">
+      <c r="A7" s="33">
+        <v>9</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="35"/>
+      <c r="X7" s="38"/>
+    </row>
+    <row r="8" spans="1:46">
+      <c r="A8" s="33">
+        <v>10</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="35"/>
+      <c r="X8" s="38"/>
+    </row>
+    <row r="9" spans="1:46">
+      <c r="A9" s="33">
+        <v>11</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="35"/>
+      <c r="X9" s="38"/>
+    </row>
+    <row r="10" spans="1:46">
+      <c r="A10" s="33">
+        <v>12</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="35"/>
+      <c r="X10" s="38"/>
+    </row>
+    <row r="11" spans="1:46">
+      <c r="A11" s="33">
+        <v>13</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="35"/>
+      <c r="X11" s="38"/>
+    </row>
+    <row r="12" spans="1:46">
+      <c r="A12" s="33">
+        <v>14</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="35"/>
+      <c r="X12" s="38"/>
+    </row>
+    <row r="13" spans="1:46">
+      <c r="A13" s="33">
+        <v>15</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40">
-        <f t="shared" ref="V4:V29" si="0">SUM(C4:U4)</f>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="34">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W4" s="41"/>
-      <c r="X4" s="45"/>
-    </row>
-    <row r="5" spans="1:46">
-      <c r="A5" s="39">
+      <c r="W13" s="35"/>
+      <c r="X13" s="38"/>
+    </row>
+    <row r="14" spans="1:46">
+      <c r="A14" s="33">
+        <v>16</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40">
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W5" s="41"/>
-      <c r="X5" s="45"/>
-    </row>
-    <row r="6" spans="1:46">
-      <c r="A6" s="39">
+      <c r="W14" s="35"/>
+      <c r="X14" s="38"/>
+    </row>
+    <row r="15" spans="1:46">
+      <c r="A15" s="33">
+        <v>17</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40">
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W6" s="41"/>
-      <c r="X6" s="45"/>
-    </row>
-    <row r="7" spans="1:46">
-      <c r="A7" s="39">
-        <v>9</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40">
+      <c r="W15" s="35"/>
+      <c r="X15" s="38"/>
+    </row>
+    <row r="16" spans="1:46">
+      <c r="A16" s="33">
+        <v>18</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W7" s="41"/>
-      <c r="X7" s="45"/>
-    </row>
-    <row r="8" spans="1:46">
-      <c r="A8" s="39">
-        <v>10</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="41"/>
-      <c r="X8" s="45"/>
-    </row>
-    <row r="9" spans="1:46">
-      <c r="A9" s="39">
-        <v>11</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="41"/>
-      <c r="X9" s="45"/>
-    </row>
-    <row r="10" spans="1:46">
-      <c r="A10" s="39">
-        <v>12</v>
-      </c>
-      <c r="B10" s="39" t="s">
+      <c r="W16" s="35"/>
+      <c r="X16" s="38"/>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" s="33">
+        <v>19</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="41"/>
-      <c r="X10" s="45"/>
-    </row>
-    <row r="11" spans="1:46">
-      <c r="A11" s="39">
-        <v>13</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="41"/>
-      <c r="X11" s="45"/>
-    </row>
-    <row r="12" spans="1:46">
-      <c r="A12" s="39">
-        <v>14</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="41"/>
-      <c r="X12" s="45"/>
-    </row>
-    <row r="13" spans="1:46">
-      <c r="A13" s="39">
-        <v>15</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="40"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="41"/>
-      <c r="X13" s="45"/>
-    </row>
-    <row r="14" spans="1:46">
-      <c r="A14" s="39">
-        <v>16</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="41"/>
-      <c r="X14" s="45"/>
-    </row>
-    <row r="15" spans="1:46">
-      <c r="A15" s="39">
-        <v>17</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="40"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="40"/>
-      <c r="U15" s="40"/>
-      <c r="V15" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="41"/>
-      <c r="X15" s="45"/>
-    </row>
-    <row r="16" spans="1:46">
-      <c r="A16" s="39">
-        <v>18</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="41"/>
-      <c r="X16" s="45"/>
-    </row>
-    <row r="17" spans="1:24">
-      <c r="A17" s="39">
-        <v>19</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="55">
+      <c r="C17" s="48">
         <f>14500-SUM(C3:C16)</f>
-        <v>14500</v>
-      </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="55">
+        <v>11802.65</v>
+      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="48">
         <f>12000-SUM(E3:E16)</f>
         <v>12000</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="55">
+      <c r="F17" s="34"/>
+      <c r="G17" s="48">
         <f>4400-SUM(G3:G16)</f>
         <v>4400</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="48">
         <f>1300-SUM(H3:H16)</f>
         <v>1300</v>
       </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="55">
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="48">
         <f>3200-SUM(N3:N16)</f>
-        <v>3200</v>
-      </c>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="40"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40">
-        <f t="shared" si="0"/>
-        <v>35400</v>
-      </c>
-      <c r="W17" s="41"/>
-      <c r="X17" s="54">
+        <v>2501</v>
+      </c>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34">
+        <f t="shared" si="0"/>
+        <v>32003.65</v>
+      </c>
+      <c r="W17" s="35"/>
+      <c r="X17" s="47">
         <f>SUM(W3:W17)-SUM(V3:V17)</f>
-        <v>-676</v>
+        <v>-5600.9499999999971</v>
       </c>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="50">
+      <c r="A18" s="43">
         <v>20</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="51">
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W18" s="52"/>
-      <c r="X18" s="53"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="46"/>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="39">
+      <c r="A19" s="33">
         <v>21</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
-      <c r="V19" s="40">
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W19" s="41"/>
-      <c r="X19" s="45"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="38"/>
     </row>
     <row r="20" spans="1:24">
-      <c r="A20" s="39">
+      <c r="A20" s="33">
         <v>22</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="40"/>
-      <c r="U20" s="40"/>
-      <c r="V20" s="40">
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W20" s="41"/>
-      <c r="X20" s="45"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="38"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="39">
+      <c r="A21" s="33">
         <v>23</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="40"/>
-      <c r="U21" s="40"/>
-      <c r="V21" s="40">
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W21" s="41"/>
-      <c r="X21" s="45"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="38"/>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" s="39">
+      <c r="A22" s="33">
         <v>24</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="40">
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W22" s="41"/>
-      <c r="X22" s="45"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="38"/>
     </row>
     <row r="23" spans="1:24">
-      <c r="A23" s="39">
+      <c r="A23" s="33">
         <v>25</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="40">
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W23" s="41"/>
-      <c r="X23" s="45"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="38"/>
     </row>
     <row r="24" spans="1:24">
-      <c r="A24" s="39">
+      <c r="A24" s="33">
         <v>26</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40">
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W24" s="41"/>
-      <c r="X24" s="45"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="38"/>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" s="39">
+      <c r="A25" s="33">
         <v>27</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="40"/>
-      <c r="U25" s="40"/>
-      <c r="V25" s="40">
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W25" s="41"/>
-      <c r="X25" s="45"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="38"/>
     </row>
     <row r="26" spans="1:24">
-      <c r="A26" s="39">
+      <c r="A26" s="33">
         <v>28</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40">
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W26" s="41"/>
-      <c r="X26" s="45"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="38"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="39">
+      <c r="A27" s="33">
         <v>29</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="40">
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="41"/>
-      <c r="X27" s="45"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="38"/>
     </row>
     <row r="28" spans="1:24">
-      <c r="A28" s="39">
+      <c r="A28" s="33">
         <v>30</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="40"/>
-      <c r="U28" s="40"/>
-      <c r="V28" s="40">
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W28" s="41"/>
-      <c r="X28" s="45"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="38"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" s="39">
+      <c r="A29" s="33">
         <v>31</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
-      <c r="V29" s="40">
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W29" s="41"/>
-      <c r="X29" s="45"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="38"/>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="41">
+      <c r="B30" s="51"/>
+      <c r="C30" s="35">
         <f>SUM(C3:C29)</f>
         <v>14500</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="35">
         <f t="shared" ref="D30:V30" si="1">SUM(D3:D29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="35">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="35">
+        <f t="shared" si="1"/>
+        <v>1610</v>
+      </c>
+      <c r="G30" s="35">
+        <f t="shared" si="1"/>
+        <v>4400</v>
+      </c>
+      <c r="H30" s="35">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="I30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G30" s="41">
-        <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="H30" s="41">
-        <f t="shared" si="1"/>
-        <v>1300</v>
-      </c>
-      <c r="I30" s="41">
+      <c r="J30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="41">
+      <c r="K30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="41">
+      <c r="L30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="41">
+      <c r="M30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M30" s="41">
+      <c r="N30" s="35">
+        <f t="shared" si="1"/>
+        <v>3200</v>
+      </c>
+      <c r="O30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="41">
-        <f t="shared" si="1"/>
-        <v>3200</v>
-      </c>
-      <c r="O30" s="41">
+      <c r="P30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P30" s="41">
+      <c r="Q30" s="35">
+        <f>SUM(Q4:Q29)</f>
+        <v>8000</v>
+      </c>
+      <c r="R30" s="35">
+        <f t="shared" si="1"/>
+        <v>1189</v>
+      </c>
+      <c r="S30" s="35">
+        <f t="shared" si="1"/>
+        <v>3125.95</v>
+      </c>
+      <c r="T30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="41">
-        <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-      <c r="R30" s="41">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="S30" s="41">
+      <c r="U30" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T30" s="41">
+      <c r="V30" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="41">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="43">
-        <f t="shared" si="1"/>
-        <v>44400</v>
-      </c>
-      <c r="W30" s="41">
+        <v>49324.95</v>
+      </c>
+      <c r="W30" s="35">
         <f>SUM(W3:W29)</f>
         <v>43724</v>
       </c>
-      <c r="X30" s="45"/>
+      <c r="X30" s="38"/>
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="6"/>
@@ -3777,20 +3840,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="G1" s="36" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="G1" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -4011,12 +4074,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -4320,12 +4383,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
@@ -11,9 +11,9 @@
     <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Лист1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -155,7 +155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -252,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -310,7 +310,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -360,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -385,6 +385,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Покупки на работе, связанные с 8 марта</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок маме на 8 марта</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -597,11 +645,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1292,23 +1340,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>27</v>
       </c>
@@ -1336,7 +1384,7 @@
       <c r="W1" s="49"/>
       <c r="X1" s="49"/>
     </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
+    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1480,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>5</v>
       </c>
@@ -1480,7 +1528,7 @@
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -1516,7 +1564,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -1556,7 +1604,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -1594,7 +1642,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -1633,7 +1681,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -1672,7 +1720,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -1707,7 +1755,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -1742,7 +1790,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -1784,7 +1832,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -1829,7 +1877,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -1867,7 +1915,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -1902,7 +1950,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -1935,7 +1983,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -1974,7 +2022,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -2010,7 +2058,7 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>20</v>
       </c>
@@ -2051,7 +2099,7 @@
       </c>
       <c r="X18" s="32"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -2091,7 +2139,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -2129,7 +2177,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -2164,7 +2212,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -2203,7 +2251,7 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -2249,7 +2297,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -2289,7 +2337,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -2334,7 +2382,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>28</v>
       </c>
@@ -2379,7 +2427,7 @@
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2421,7 +2469,7 @@
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -2461,7 +2509,7 @@
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2496,7 +2544,7 @@
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -2532,7 +2580,7 @@
         <v>278.36000000000058</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="50" t="s">
         <v>20</v>
       </c>
@@ -2623,7 +2671,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -2646,16 +2694,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>65</v>
       </c>
@@ -2683,7 +2731,7 @@
       <c r="W1" s="52"/>
       <c r="X1" s="52"/>
     </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
+    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -2779,7 +2827,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="39">
         <v>5</v>
       </c>
@@ -2821,7 +2869,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>6</v>
       </c>
@@ -2842,7 +2890,8 @@
       <c r="L4" s="34"/>
       <c r="M4" s="34"/>
       <c r="N4" s="34">
-        <v>387</v>
+        <f>387+364</f>
+        <v>751</v>
       </c>
       <c r="O4" s="34"/>
       <c r="P4" s="34"/>
@@ -2854,16 +2903,18 @@
         <f>2411.96/2+116.97+2148/2+729</f>
         <v>3125.95</v>
       </c>
-      <c r="T4" s="34"/>
+      <c r="T4" s="34">
+        <v>6000</v>
+      </c>
       <c r="U4" s="34"/>
       <c r="V4" s="34">
         <f t="shared" ref="V4:V29" si="0">SUM(C4:U4)</f>
-        <v>5321.95</v>
+        <v>11685.95</v>
       </c>
       <c r="W4" s="35"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>7</v>
       </c>
@@ -2883,7 +2934,9 @@
       <c r="M5" s="34"/>
       <c r="N5" s="34"/>
       <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
+      <c r="P5" s="48">
+        <v>10000</v>
+      </c>
       <c r="Q5" s="34"/>
       <c r="R5" s="34"/>
       <c r="S5" s="34"/>
@@ -2891,12 +2944,12 @@
       <c r="U5" s="34"/>
       <c r="V5" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W5" s="35"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>8</v>
       </c>
@@ -2917,21 +2970,19 @@
       <c r="N6" s="34"/>
       <c r="O6" s="34"/>
       <c r="P6" s="34"/>
-      <c r="Q6" s="48">
-        <v>8000</v>
-      </c>
+      <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
       <c r="S6" s="34"/>
       <c r="T6" s="34"/>
       <c r="U6" s="34"/>
       <c r="V6" s="34">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="W6" s="35"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>9</v>
       </c>
@@ -2964,7 +3015,7 @@
       <c r="W7" s="35"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>10</v>
       </c>
@@ -2997,7 +3048,7 @@
       <c r="W8" s="35"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>11</v>
       </c>
@@ -3030,7 +3081,7 @@
       <c r="W9" s="35"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>12</v>
       </c>
@@ -3063,7 +3114,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>13</v>
       </c>
@@ -3096,7 +3147,7 @@
       <c r="W11" s="35"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>14</v>
       </c>
@@ -3129,7 +3180,7 @@
       <c r="W12" s="35"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>15</v>
       </c>
@@ -3162,7 +3213,7 @@
       <c r="W13" s="35"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>16</v>
       </c>
@@ -3195,7 +3246,7 @@
       <c r="W14" s="35"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>17</v>
       </c>
@@ -3228,7 +3279,7 @@
       <c r="W15" s="35"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="33">
         <v>18</v>
       </c>
@@ -3261,7 +3312,7 @@
       <c r="W16" s="35"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>19</v>
       </c>
@@ -3269,13 +3320,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="48">
-        <f>14500-SUM(C3:C16)</f>
-        <v>11802.65</v>
+        <f>(14500-SUM(C3:C16))  /2</f>
+        <v>5901.3249999999998</v>
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="48">
-        <f>12000-SUM(E3:E16)</f>
-        <v>12000</v>
+        <f>(12000-SUM(E3:E16))/2</f>
+        <v>6000</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="48">
@@ -3293,7 +3344,7 @@
       <c r="M17" s="34"/>
       <c r="N17" s="48">
         <f>3200-SUM(N3:N16)</f>
-        <v>2501</v>
+        <v>2137</v>
       </c>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
@@ -3304,15 +3355,15 @@
       <c r="U17" s="34"/>
       <c r="V17" s="34">
         <f t="shared" si="0"/>
-        <v>32003.65</v>
+        <v>19738.325000000001</v>
       </c>
       <c r="W17" s="35"/>
       <c r="X17" s="47">
         <f>SUM(W3:W17)-SUM(V3:V17)</f>
-        <v>-5600.9499999999971</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
+        <v>-1699.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>20</v>
       </c>
@@ -3345,7 +3396,7 @@
       <c r="W18" s="45"/>
       <c r="X18" s="46"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>21</v>
       </c>
@@ -3366,19 +3417,21 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
+      <c r="Q19" s="48">
+        <v>8000</v>
+      </c>
       <c r="R19" s="34"/>
       <c r="S19" s="34"/>
       <c r="T19" s="34"/>
       <c r="U19" s="34"/>
       <c r="V19" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W19" s="35"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>22</v>
       </c>
@@ -3411,7 +3464,7 @@
       <c r="W20" s="35"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>23</v>
       </c>
@@ -3444,7 +3497,7 @@
       <c r="W21" s="35"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>24</v>
       </c>
@@ -3477,7 +3530,7 @@
       <c r="W22" s="35"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>25</v>
       </c>
@@ -3510,7 +3563,7 @@
       <c r="W23" s="35"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>26</v>
       </c>
@@ -3543,7 +3596,7 @@
       <c r="W24" s="35"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>27</v>
       </c>
@@ -3576,7 +3629,7 @@
       <c r="W25" s="35"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>28</v>
       </c>
@@ -3609,7 +3662,7 @@
       <c r="W26" s="35"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>29</v>
       </c>
@@ -3642,7 +3695,7 @@
       <c r="W27" s="35"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>30</v>
       </c>
@@ -3675,7 +3728,7 @@
       <c r="W28" s="35"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>31</v>
       </c>
@@ -3708,14 +3761,14 @@
       <c r="W29" s="35"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="51"/>
       <c r="C30" s="35">
         <f>SUM(C3:C29)</f>
-        <v>14500</v>
+        <v>8598.6749999999993</v>
       </c>
       <c r="D30" s="35">
         <f t="shared" ref="D30:V30" si="1">SUM(D3:D29)</f>
@@ -3723,7 +3776,7 @@
       </c>
       <c r="E30" s="35">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F30" s="35">
         <f t="shared" si="1"/>
@@ -3767,7 +3820,7 @@
       </c>
       <c r="P30" s="35">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Q30" s="35">
         <f>SUM(Q4:Q29)</f>
@@ -3783,7 +3836,7 @@
       </c>
       <c r="T30" s="35">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U30" s="35">
         <f t="shared" si="1"/>
@@ -3791,7 +3844,7 @@
       </c>
       <c r="V30" s="36">
         <f t="shared" si="1"/>
-        <v>49324.95</v>
+        <v>53423.625</v>
       </c>
       <c r="W30" s="35">
         <f>SUM(W3:W29)</f>
@@ -3799,7 +3852,7 @@
       </c>
       <c r="X30" s="38"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -3822,9 +3875,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -3839,7 +3892,7 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
@@ -3855,7 +3908,7 @@
       <c r="J1" s="53"/>
       <c r="K1" s="53"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3887,7 +3940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -3921,7 +3974,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -3955,7 +4008,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -3989,7 +4042,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -4023,7 +4076,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -4057,7 +4110,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -4085,7 +4138,7 @@
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -4106,7 +4159,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -4127,7 +4180,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -4148,7 +4201,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -4169,7 +4222,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -4190,7 +4243,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -4211,7 +4264,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -4232,7 +4285,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -4253,7 +4306,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -4274,7 +4327,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -4292,7 +4345,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -4310,7 +4363,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -4328,7 +4381,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -4346,7 +4399,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -4364,7 +4417,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -4382,7 +4435,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="54" t="s">
         <v>61</v>
       </c>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -430,6 +430,54 @@
           </rPr>
           <t xml:space="preserve">
 Подарок маме на 8 марта</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Брекфаст бенд</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок на 8 марта</t>
         </r>
       </text>
     </comment>
@@ -1128,7 +1176,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1163,7 +1211,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2925,26 +2973,34 @@
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="G5" s="34">
+        <f>3080+328</f>
+        <v>3408</v>
+      </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="34"/>
       <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
+      <c r="N5" s="34">
+        <v>268</v>
+      </c>
       <c r="O5" s="34"/>
-      <c r="P5" s="48">
-        <v>10000</v>
+      <c r="P5" s="34">
+        <v>8428</v>
       </c>
       <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
+      <c r="R5" s="34">
+        <f>255+547</f>
+        <v>802</v>
+      </c>
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
       <c r="U5" s="34"/>
       <c r="V5" s="34">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>12906</v>
       </c>
       <c r="W5" s="35"/>
       <c r="X5" s="38"/>
@@ -3331,7 +3387,7 @@
       <c r="F17" s="34"/>
       <c r="G17" s="48">
         <f>4400-SUM(G3:G16)</f>
-        <v>4400</v>
+        <v>992</v>
       </c>
       <c r="H17" s="48">
         <f>1300-SUM(H3:H16)</f>
@@ -3344,7 +3400,7 @@
       <c r="M17" s="34"/>
       <c r="N17" s="48">
         <f>3200-SUM(N3:N16)</f>
-        <v>2137</v>
+        <v>1869</v>
       </c>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
@@ -3355,12 +3411,12 @@
       <c r="U17" s="34"/>
       <c r="V17" s="34">
         <f t="shared" si="0"/>
-        <v>19738.325000000001</v>
+        <v>16062.325000000001</v>
       </c>
       <c r="W17" s="35"/>
       <c r="X17" s="47">
         <f>SUM(W3:W17)-SUM(V3:V17)</f>
-        <v>-1699.625</v>
+        <v>-929.625</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -3820,7 +3876,7 @@
       </c>
       <c r="P30" s="35">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>8428</v>
       </c>
       <c r="Q30" s="35">
         <f>SUM(Q4:Q29)</f>
@@ -3828,7 +3884,7 @@
       </c>
       <c r="R30" s="35">
         <f t="shared" si="1"/>
-        <v>1189</v>
+        <v>1991</v>
       </c>
       <c r="S30" s="35">
         <f t="shared" si="1"/>
@@ -3844,7 +3900,7 @@
       </c>
       <c r="V30" s="36">
         <f t="shared" si="1"/>
-        <v>53423.625</v>
+        <v>52653.625</v>
       </c>
       <c r="W30" s="35">
         <f>SUM(W3:W29)</f>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
@@ -11,9 +11,9 @@
     <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
     <sheet name="Лист1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -124,14 +125,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Дубликат ключей</t>
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -139,7 +141,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -148,14 +151,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Левомеколь</t>
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +167,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -172,7 +177,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Вино
@@ -180,7 +186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +194,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -197,14 +204,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Газпром</t>
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +220,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -221,14 +230,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Росатом Энергосбыт</t>
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -236,7 +246,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -245,14 +256,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Галстук + Брюки</t>
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +272,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -269,14 +282,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Торт Мишутка</t>
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -284,7 +298,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -293,7 +308,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 УК Эталон</t>
@@ -310,7 +326,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -344,7 +360,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -353,14 +370,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Лапшичка</t>
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -368,7 +386,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -377,7 +396,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Вк музыка
@@ -385,7 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -393,7 +413,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -402,14 +423,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Покупки на работе, связанные с 8 марта</t>
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -417,7 +439,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -426,14 +449,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Подарок маме на 8 марта</t>
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -441,7 +465,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -450,14 +475,15 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Брекфаст бенд</t>
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -465,7 +491,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -474,10 +501,222 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Подарок на 8 марта</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Цветы на 8 марта
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Лампочки в ванную</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В этот день по сути деньги закончились</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Влажные салфетки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Интернет
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Постельное белье</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарки Климу и Адольфу на др</t>
         </r>
       </text>
     </comment>
@@ -486,7 +725,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="67">
   <si>
     <t>Число</t>
   </si>
@@ -693,11 +932,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,36 +1032,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Arial Black"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -885,19 +1102,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFF4B79E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1054,20 +1265,10 @@
     <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1079,12 +1280,6 @@
     <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1107,6 +1302,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1115,6 +1320,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF4B79E"/>
       <color rgb="FF062D4E"/>
       <color rgb="FF094679"/>
       <color rgb="FF7BB7E9"/>
@@ -1176,7 +1382,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1211,7 +1417,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1388,51 +1594,51 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+      <c r="A1" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1528,7 +1734,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46">
       <c r="A3" s="27">
         <v>5</v>
       </c>
@@ -1576,7 +1782,7 @@
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -1612,7 +1818,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -1652,7 +1858,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -1690,7 +1896,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -1729,7 +1935,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -1768,7 +1974,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -1803,7 +2009,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -1838,7 +2044,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -1880,7 +2086,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -1925,7 +2131,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -1963,7 +2169,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -1998,7 +2204,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -2031,7 +2237,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -2070,7 +2276,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -2106,7 +2312,7 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1">
       <c r="A18" s="27">
         <v>20</v>
       </c>
@@ -2147,7 +2353,7 @@
       </c>
       <c r="X18" s="32"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -2187,7 +2393,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -2225,7 +2431,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -2260,7 +2466,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -2299,7 +2505,7 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -2345,7 +2551,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -2385,7 +2591,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -2430,7 +2636,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26" s="5">
         <v>28</v>
       </c>
@@ -2475,7 +2681,7 @@
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2517,7 +2723,7 @@
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -2557,7 +2763,7 @@
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2592,7 +2798,7 @@
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -2628,11 +2834,11 @@
         <v>278.36000000000058</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+    <row r="31" spans="1:24">
+      <c r="A31" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="50"/>
+      <c r="B31" s="44"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -2719,7 +2925,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -2742,44 +2948,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AT36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
+      <c r="A1" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -2875,7 +3081,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46">
       <c r="A3" s="39">
         <v>5</v>
       </c>
@@ -2917,7 +3123,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46">
       <c r="A4" s="33">
         <v>6</v>
       </c>
@@ -2956,13 +3162,13 @@
       </c>
       <c r="U4" s="34"/>
       <c r="V4" s="34">
-        <f t="shared" ref="V4:V29" si="0">SUM(C4:U4)</f>
+        <f t="shared" ref="V4:V31" si="0">SUM(C4:U4)</f>
         <v>11685.95</v>
       </c>
       <c r="W4" s="35"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46">
       <c r="A5" s="33">
         <v>7</v>
       </c>
@@ -3005,27 +3211,36 @@
       <c r="W5" s="35"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46">
       <c r="A6" s="33">
         <v>8</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="34">
+        <f>284+995</f>
+        <v>1279</v>
+      </c>
       <c r="D6" s="34"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
       <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
+      <c r="H6" s="34">
+        <v>1117</v>
+      </c>
       <c r="I6" s="34"/>
       <c r="J6" s="34"/>
       <c r="K6" s="34"/>
       <c r="L6" s="34"/>
       <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
+      <c r="N6" s="34">
+        <v>400</v>
+      </c>
       <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
+      <c r="P6" s="34">
+        <v>1330</v>
+      </c>
       <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
       <c r="S6" s="34"/>
@@ -3033,19 +3248,21 @@
       <c r="U6" s="34"/>
       <c r="V6" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="W6" s="35"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46">
       <c r="A7" s="33">
         <v>9</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="34">
+        <v>769</v>
+      </c>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
@@ -3066,12 +3283,12 @@
       <c r="U7" s="34"/>
       <c r="V7" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="W7" s="35"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46">
       <c r="A8" s="33">
         <v>10</v>
       </c>
@@ -3090,7 +3307,9 @@
       <c r="L8" s="34"/>
       <c r="M8" s="34"/>
       <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
+      <c r="O8" s="34">
+        <v>302</v>
+      </c>
       <c r="P8" s="34"/>
       <c r="Q8" s="34"/>
       <c r="R8" s="34"/>
@@ -3099,12 +3318,12 @@
       <c r="U8" s="34"/>
       <c r="V8" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="W8" s="35"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46">
       <c r="A9" s="33">
         <v>11</v>
       </c>
@@ -3112,9 +3331,14 @@
         <v>2</v>
       </c>
       <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="34">
+        <v>1191</v>
+      </c>
       <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="F9" s="34">
+        <f>1070+109</f>
+        <v>1179</v>
+      </c>
       <c r="G9" s="34"/>
       <c r="H9" s="34"/>
       <c r="I9" s="34"/>
@@ -3122,8 +3346,12 @@
       <c r="K9" s="34"/>
       <c r="L9" s="34"/>
       <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
+      <c r="N9" s="34">
+        <v>400</v>
+      </c>
+      <c r="O9" s="34">
+        <v>277</v>
+      </c>
       <c r="P9" s="34"/>
       <c r="Q9" s="34"/>
       <c r="R9" s="34"/>
@@ -3132,12 +3360,12 @@
       <c r="U9" s="34"/>
       <c r="V9" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3047</v>
       </c>
       <c r="W9" s="35"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46">
       <c r="A10" s="33">
         <v>12</v>
       </c>
@@ -3147,63 +3375,80 @@
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="F10" s="34">
+        <f>420+700</f>
+        <v>1120</v>
+      </c>
+      <c r="G10" s="34">
+        <f>1421+331</f>
+        <v>1752</v>
+      </c>
       <c r="H10" s="34"/>
       <c r="I10" s="34"/>
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
+      <c r="N10" s="34">
+        <v>294</v>
+      </c>
       <c r="O10" s="34"/>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
+      <c r="S10" s="34">
+        <f>387+864</f>
+        <v>1251</v>
+      </c>
       <c r="T10" s="34"/>
       <c r="U10" s="34"/>
       <c r="V10" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4417</v>
       </c>
       <c r="W10" s="35"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A11" s="33">
+    <row r="11" spans="1:46">
+      <c r="A11" s="50">
         <v>13</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="35"/>
-      <c r="X11" s="38"/>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51">
+        <f>1070+60</f>
+        <v>1130</v>
+      </c>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51">
+        <f>251+328+262</f>
+        <v>841</v>
+      </c>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>1971</v>
+      </c>
+      <c r="W11" s="52"/>
+      <c r="X11" s="53"/>
+    </row>
+    <row r="12" spans="1:46">
       <c r="A12" s="33">
         <v>14</v>
       </c>
@@ -3214,7 +3459,9 @@
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
+      <c r="G12" s="51">
+        <v>3605</v>
+      </c>
       <c r="H12" s="34"/>
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
@@ -3231,19 +3478,22 @@
       <c r="U12" s="34"/>
       <c r="V12" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3605</v>
       </c>
       <c r="W12" s="35"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46">
       <c r="A13" s="33">
         <v>15</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="51">
+        <f>318+2115</f>
+        <v>2433</v>
+      </c>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -3264,12 +3514,12 @@
       <c r="U13" s="34"/>
       <c r="V13" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="W13" s="35"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46">
       <c r="A14" s="33">
         <v>16</v>
       </c>
@@ -3279,7 +3529,10 @@
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
+      <c r="F14" s="51">
+        <f>350</f>
+        <v>350</v>
+      </c>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
@@ -3288,7 +3541,9 @@
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
       <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
+      <c r="O14" s="51">
+        <v>291</v>
+      </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="34"/>
@@ -3297,12 +3552,12 @@
       <c r="U14" s="34"/>
       <c r="V14" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="W14" s="35"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46">
       <c r="A15" s="33">
         <v>17</v>
       </c>
@@ -3312,7 +3567,9 @@
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
+      <c r="F15" s="51">
+        <v>350</v>
+      </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
@@ -3321,7 +3578,9 @@
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
       <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
+      <c r="O15" s="51">
+        <v>1000</v>
+      </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="34"/>
@@ -3330,12 +3589,12 @@
       <c r="U15" s="34"/>
       <c r="V15" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="W15" s="35"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46">
       <c r="A16" s="33">
         <v>18</v>
       </c>
@@ -3345,7 +3604,10 @@
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
+      <c r="F16" s="51">
+        <f>1080+109+350</f>
+        <v>1539</v>
+      </c>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
       <c r="I16" s="34"/>
@@ -3353,7 +3615,9 @@
       <c r="K16" s="34"/>
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
+      <c r="N16" s="51">
+        <v>400</v>
+      </c>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
@@ -3363,44 +3627,32 @@
       <c r="U16" s="34"/>
       <c r="V16" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1939</v>
       </c>
       <c r="W16" s="35"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17" s="33">
         <v>19</v>
       </c>
       <c r="B17" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="48">
-        <f>(14500-SUM(C3:C16))  /2</f>
-        <v>5901.3249999999998</v>
-      </c>
+      <c r="C17" s="34"/>
       <c r="D17" s="34"/>
-      <c r="E17" s="48">
-        <f>(12000-SUM(E3:E16))/2</f>
-        <v>6000</v>
-      </c>
+      <c r="E17" s="34"/>
       <c r="F17" s="34"/>
-      <c r="G17" s="48">
-        <f>4400-SUM(G3:G16)</f>
-        <v>992</v>
-      </c>
-      <c r="H17" s="48">
-        <f>1300-SUM(H3:H16)</f>
-        <v>1300</v>
-      </c>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="34"/>
       <c r="J17" s="34"/>
       <c r="K17" s="34"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
-      <c r="N17" s="48">
-        <f>3200-SUM(N3:N16)</f>
-        <v>1869</v>
+      <c r="N17" s="51">
+        <f>159+358</f>
+        <v>517</v>
       </c>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
@@ -3411,55 +3663,64 @@
       <c r="U17" s="34"/>
       <c r="V17" s="34">
         <f t="shared" si="0"/>
-        <v>16062.325000000001</v>
+        <v>517</v>
       </c>
       <c r="W17" s="35"/>
-      <c r="X17" s="47">
-        <f>SUM(W3:W17)-SUM(V3:V17)</f>
-        <v>-929.625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="X17" s="38"/>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" s="39">
         <v>20</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="45"/>
-      <c r="X18" s="46"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C18" s="40">
+        <f>220+2225+135</f>
+        <v>2580</v>
+      </c>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40">
+        <v>499</v>
+      </c>
+      <c r="S18" s="40">
+        <v>130</v>
+      </c>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40">
+        <f t="shared" si="0"/>
+        <v>3209</v>
+      </c>
+      <c r="W18" s="41">
+        <v>24676</v>
+      </c>
+      <c r="X18" s="42"/>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="33">
         <v>21</v>
       </c>
       <c r="B19" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="34">
+        <f>780+65</f>
+        <v>845</v>
+      </c>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -3473,28 +3734,36 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="48">
-        <v>8000</v>
-      </c>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34">
+        <f>570+120</f>
+        <v>690</v>
+      </c>
+      <c r="S19" s="34">
+        <v>4661</v>
+      </c>
+      <c r="T19" s="34">
+        <v>1200</v>
+      </c>
       <c r="U19" s="34"/>
       <c r="V19" s="34">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>7396</v>
       </c>
       <c r="W19" s="35"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20" s="33">
         <v>22</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="34">
+        <f>5500-2600</f>
+        <v>2900</v>
+      </c>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -3510,17 +3779,19 @@
       <c r="P20" s="34"/>
       <c r="Q20" s="34"/>
       <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
+      <c r="S20" s="34">
+        <v>2600</v>
+      </c>
       <c r="T20" s="34"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="W20" s="35"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21" s="33">
         <v>23</v>
       </c>
@@ -3553,7 +3824,7 @@
       <c r="W21" s="35"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22" s="33">
         <v>24</v>
       </c>
@@ -3586,7 +3857,7 @@
       <c r="W22" s="35"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23" s="33">
         <v>25</v>
       </c>
@@ -3619,7 +3890,7 @@
       <c r="W23" s="35"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24" s="33">
         <v>26</v>
       </c>
@@ -3652,7 +3923,7 @@
       <c r="W24" s="35"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25" s="33">
         <v>27</v>
       </c>
@@ -3685,7 +3956,7 @@
       <c r="W25" s="35"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26" s="33">
         <v>28</v>
       </c>
@@ -3718,7 +3989,7 @@
       <c r="W26" s="35"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27" s="33">
         <v>29</v>
       </c>
@@ -3751,7 +4022,7 @@
       <c r="W27" s="35"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28" s="33">
         <v>30</v>
       </c>
@@ -3784,7 +4055,7 @@
       <c r="W28" s="35"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29" s="33">
         <v>31</v>
       </c>
@@ -3817,111 +4088,180 @@
       <c r="W29" s="35"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="51" t="s">
+    <row r="30" spans="1:24">
+      <c r="A30" s="33">
+        <v>1</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="35"/>
+      <c r="X30" s="38"/>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" s="33">
+        <v>2</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="35"/>
+      <c r="X31" s="38"/>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="A32" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="35">
-        <f>SUM(C3:C29)</f>
-        <v>8598.6749999999993</v>
-      </c>
-      <c r="D30" s="35">
-        <f t="shared" ref="D30:V30" si="1">SUM(D3:D29)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="35">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="F30" s="35">
-        <f t="shared" si="1"/>
-        <v>1610</v>
-      </c>
-      <c r="G30" s="35">
-        <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="H30" s="35">
-        <f t="shared" si="1"/>
-        <v>1300</v>
-      </c>
-      <c r="I30" s="35">
+      <c r="B32" s="45"/>
+      <c r="C32" s="35">
+        <f>SUM(C3:C31)</f>
+        <v>13503.35</v>
+      </c>
+      <c r="D32" s="35">
+        <f t="shared" ref="D32:U32" si="1">SUM(D3:D31)</f>
+        <v>1191</v>
+      </c>
+      <c r="E32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="35">
+      <c r="F32" s="35">
+        <f t="shared" si="1"/>
+        <v>7278</v>
+      </c>
+      <c r="G32" s="35">
+        <f t="shared" si="1"/>
+        <v>8765</v>
+      </c>
+      <c r="H32" s="35">
+        <f t="shared" si="1"/>
+        <v>1117</v>
+      </c>
+      <c r="I32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="35">
+      <c r="J32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="35">
+      <c r="K32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M30" s="35">
+      <c r="L32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="35">
-        <f t="shared" si="1"/>
-        <v>3200</v>
-      </c>
-      <c r="O30" s="35">
+      <c r="M32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P30" s="35">
+      <c r="N32" s="35">
         <f t="shared" si="1"/>
-        <v>8428</v>
-      </c>
-      <c r="Q30" s="35">
-        <f>SUM(Q4:Q29)</f>
-        <v>8000</v>
-      </c>
-      <c r="R30" s="35">
+        <v>4183</v>
+      </c>
+      <c r="O32" s="35">
         <f t="shared" si="1"/>
-        <v>1991</v>
-      </c>
-      <c r="S30" s="35">
+        <v>1870</v>
+      </c>
+      <c r="P32" s="35">
         <f t="shared" si="1"/>
-        <v>3125.95</v>
-      </c>
-      <c r="T30" s="35">
-        <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-      <c r="U30" s="35">
+        <v>9758</v>
+      </c>
+      <c r="Q32" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V30" s="36">
+      <c r="R32" s="35">
         <f t="shared" si="1"/>
-        <v>52653.625</v>
-      </c>
-      <c r="W30" s="35">
+        <v>3180</v>
+      </c>
+      <c r="S32" s="35">
+        <f t="shared" si="1"/>
+        <v>11767.95</v>
+      </c>
+      <c r="T32" s="35">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+      <c r="U32" s="35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="36">
+        <f>SUM(V3:V31)</f>
+        <v>69813.3</v>
+      </c>
+      <c r="W32" s="35">
         <f>SUM(W3:W29)</f>
-        <v>43724</v>
-      </c>
-      <c r="X30" s="38"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
+        <v>68400</v>
+      </c>
+      <c r="X32" s="38">
+        <f>W32-V32</f>
+        <v>-1413.3000000000029</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3931,9 +4271,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -3948,23 +4288,23 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="G1" s="53" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="G1" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3996,7 +4336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -4030,7 +4370,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -4064,7 +4404,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -4098,7 +4438,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -4132,7 +4472,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -4166,7 +4506,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -4183,18 +4523,18 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -4215,7 +4555,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -4236,7 +4576,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -4257,7 +4597,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -4278,7 +4618,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -4299,7 +4639,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -4320,7 +4660,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -4341,7 +4681,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -4362,7 +4702,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -4383,7 +4723,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -4401,7 +4741,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -4419,7 +4759,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -4437,7 +4777,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -4455,7 +4795,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -4473,7 +4813,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -4491,13 +4831,13 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="54" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1281,6 +1281,16 @@
     <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1301,16 +1311,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1594,7 +1594,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1611,32 +1611,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -2835,10 +2835,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="44"/>
+      <c r="B31" s="48"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -2958,32 +2958,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -3410,43 +3410,43 @@
       <c r="X10" s="38"/>
     </row>
     <row r="11" spans="1:46">
-      <c r="A11" s="50">
+      <c r="A11" s="43">
         <v>13</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51">
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44">
         <f>1070+60</f>
         <v>1130</v>
       </c>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51">
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44">
         <f>251+328+262</f>
         <v>841</v>
       </c>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51">
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44">
         <f t="shared" si="0"/>
         <v>1971</v>
       </c>
-      <c r="W11" s="52"/>
-      <c r="X11" s="53"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="46"/>
     </row>
     <row r="12" spans="1:46">
       <c r="A12" s="33">
@@ -3459,7 +3459,7 @@
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
-      <c r="G12" s="51">
+      <c r="G12" s="44">
         <v>3605</v>
       </c>
       <c r="H12" s="34"/>
@@ -3490,7 +3490,7 @@
       <c r="B13" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="44">
         <f>318+2115</f>
         <v>2433</v>
       </c>
@@ -3529,7 +3529,7 @@
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
-      <c r="F14" s="51">
+      <c r="F14" s="44">
         <f>350</f>
         <v>350</v>
       </c>
@@ -3541,7 +3541,7 @@
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
       <c r="N14" s="34"/>
-      <c r="O14" s="51">
+      <c r="O14" s="44">
         <v>291</v>
       </c>
       <c r="P14" s="34"/>
@@ -3567,7 +3567,7 @@
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
-      <c r="F15" s="51">
+      <c r="F15" s="44">
         <v>350</v>
       </c>
       <c r="G15" s="34"/>
@@ -3578,7 +3578,7 @@
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
       <c r="N15" s="34"/>
-      <c r="O15" s="51">
+      <c r="O15" s="44">
         <v>1000</v>
       </c>
       <c r="P15" s="34"/>
@@ -3604,7 +3604,7 @@
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
-      <c r="F16" s="51">
+      <c r="F16" s="44">
         <f>1080+109+350</f>
         <v>1539</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="K16" s="34"/>
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
-      <c r="N16" s="51">
+      <c r="N16" s="44">
         <v>400</v>
       </c>
       <c r="O16" s="34"/>
@@ -3650,7 +3650,7 @@
       <c r="K17" s="34"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
-      <c r="N17" s="51">
+      <c r="N17" s="44">
         <f>159+358</f>
         <v>517</v>
       </c>
@@ -3864,10 +3864,16 @@
       <c r="B23" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="34"/>
+      <c r="C23" s="34">
+        <f>633</f>
+        <v>633</v>
+      </c>
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
+      <c r="F23" s="34">
+        <f>392+352</f>
+        <v>744</v>
+      </c>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
       <c r="I23" s="34"/>
@@ -3875,7 +3881,10 @@
       <c r="K23" s="34"/>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
+      <c r="N23" s="34">
+        <f>204+188+400</f>
+        <v>792</v>
+      </c>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
@@ -3885,7 +3894,7 @@
       <c r="U23" s="34"/>
       <c r="V23" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2169</v>
       </c>
       <c r="W23" s="35"/>
       <c r="X23" s="38"/>
@@ -4155,13 +4164,13 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="45"/>
+      <c r="B32" s="49"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
-        <v>13503.35</v>
+        <v>14136.35</v>
       </c>
       <c r="D32" s="35">
         <f t="shared" ref="D32:U32" si="1">SUM(D3:D31)</f>
@@ -4173,7 +4182,7 @@
       </c>
       <c r="F32" s="35">
         <f t="shared" si="1"/>
-        <v>7278</v>
+        <v>8022</v>
       </c>
       <c r="G32" s="35">
         <f t="shared" si="1"/>
@@ -4205,7 +4214,7 @@
       </c>
       <c r="N32" s="35">
         <f t="shared" si="1"/>
-        <v>4183</v>
+        <v>4975</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="1"/>
@@ -4237,7 +4246,7 @@
       </c>
       <c r="V32" s="36">
         <f>SUM(V3:V31)</f>
-        <v>69813.3</v>
+        <v>71982.3</v>
       </c>
       <c r="W32" s="35">
         <f>SUM(W3:W29)</f>
@@ -4245,7 +4254,7 @@
       </c>
       <c r="X32" s="38">
         <f>W32-V32</f>
-        <v>-1413.3000000000029</v>
+        <v>-3582.3000000000029</v>
       </c>
     </row>
     <row r="36" spans="2:10">
@@ -4289,20 +4298,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="G1" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -4523,12 +4532,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="G8" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -4832,12 +4841,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Февраль 2026" sheetId="3" r:id="rId1"/>
     <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
-    <sheet name="Лист1" sheetId="2" r:id="rId3"/>
+    <sheet name="Апрель 2026" sheetId="4" r:id="rId3"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -720,12 +721,119 @@
         </r>
       </text>
     </comment>
+    <comment ref="T20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Наташе на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарочные пакеты</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Аптека</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Долг маме + штрафы за парковку
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="68">
   <si>
     <t>Число</t>
   </si>
@@ -927,6 +1035,9 @@
   </si>
   <si>
     <t>Обед</t>
+  </si>
+  <si>
+    <t>Синабон</t>
   </si>
 </sst>
 </file>
@@ -936,7 +1047,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1038,8 +1149,21 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1112,6 +1236,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1177,7 +1313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1311,6 +1447,25 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1594,7 +1749,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3782,11 +3937,13 @@
       <c r="S20" s="34">
         <v>2600</v>
       </c>
-      <c r="T20" s="34"/>
+      <c r="T20" s="34">
+        <v>600</v>
+      </c>
       <c r="U20" s="34"/>
       <c r="V20" s="34">
         <f t="shared" si="0"/>
-        <v>5500</v>
+        <v>6100</v>
       </c>
       <c r="W20" s="35"/>
       <c r="X20" s="38"/>
@@ -3810,7 +3967,9 @@
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
+      <c r="O21" s="34">
+        <v>311</v>
+      </c>
       <c r="P21" s="34"/>
       <c r="Q21" s="34"/>
       <c r="R21" s="34"/>
@@ -3819,7 +3978,7 @@
       <c r="U21" s="34"/>
       <c r="V21" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="W21" s="35"/>
       <c r="X21" s="38"/>
@@ -3843,16 +4002,20 @@
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
       <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
+      <c r="O22" s="34">
+        <v>295</v>
+      </c>
       <c r="P22" s="34"/>
       <c r="Q22" s="34"/>
       <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
+      <c r="S22" s="34">
+        <v>900</v>
+      </c>
       <c r="T22" s="34"/>
       <c r="U22" s="34"/>
       <c r="V22" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="W22" s="35"/>
       <c r="X22" s="38"/>
@@ -3939,8 +4102,12 @@
       <c r="B25" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
+      <c r="C25" s="34">
+        <v>1104</v>
+      </c>
+      <c r="D25" s="34">
+        <v>856</v>
+      </c>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
       <c r="G25" s="34"/>
@@ -3950,7 +4117,10 @@
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
       <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
+      <c r="N25" s="34">
+        <f>201+182</f>
+        <v>383</v>
+      </c>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
@@ -3960,7 +4130,7 @@
       <c r="U25" s="34"/>
       <c r="V25" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="W25" s="35"/>
       <c r="X25" s="38"/>
@@ -3973,7 +4143,9 @@
         <v>5</v>
       </c>
       <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="34">
+        <v>1067</v>
+      </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
       <c r="G26" s="34"/>
@@ -3988,12 +4160,14 @@
       <c r="P26" s="34"/>
       <c r="Q26" s="34"/>
       <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
+      <c r="S26" s="34">
+        <v>132</v>
+      </c>
       <c r="T26" s="34"/>
       <c r="U26" s="34"/>
       <c r="V26" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="W26" s="35"/>
       <c r="X26" s="38"/>
@@ -4005,7 +4179,10 @@
       <c r="B27" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="34"/>
+      <c r="C27" s="44">
+        <f>735+868</f>
+        <v>1603</v>
+      </c>
       <c r="D27" s="34"/>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
@@ -4016,7 +4193,10 @@
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
+      <c r="N27" s="34">
+        <f>322+198</f>
+        <v>520</v>
+      </c>
       <c r="O27" s="34"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="34"/>
@@ -4026,7 +4206,7 @@
       <c r="U27" s="34"/>
       <c r="V27" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="W27" s="35"/>
       <c r="X27" s="38"/>
@@ -4041,7 +4221,10 @@
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
       <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
+      <c r="F28" s="44">
+        <f>350</f>
+        <v>350</v>
+      </c>
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
@@ -4049,7 +4232,9 @@
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
       <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
+      <c r="N28" s="44">
+        <v>228</v>
+      </c>
       <c r="O28" s="34"/>
       <c r="P28" s="34"/>
       <c r="Q28" s="34"/>
@@ -4059,7 +4244,7 @@
       <c r="U28" s="34"/>
       <c r="V28" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="W28" s="35"/>
       <c r="X28" s="38"/>
@@ -4170,11 +4355,11 @@
       <c r="B32" s="49"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
-        <v>14136.35</v>
+        <v>16843.349999999999</v>
       </c>
       <c r="D32" s="35">
         <f t="shared" ref="D32:U32" si="1">SUM(D3:D31)</f>
-        <v>1191</v>
+        <v>3114</v>
       </c>
       <c r="E32" s="35">
         <f t="shared" si="1"/>
@@ -4182,7 +4367,7 @@
       </c>
       <c r="F32" s="35">
         <f t="shared" si="1"/>
-        <v>8022</v>
+        <v>8372</v>
       </c>
       <c r="G32" s="35">
         <f t="shared" si="1"/>
@@ -4214,11 +4399,11 @@
       </c>
       <c r="N32" s="35">
         <f t="shared" si="1"/>
-        <v>4975</v>
+        <v>6106</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="1"/>
-        <v>1870</v>
+        <v>2476</v>
       </c>
       <c r="P32" s="35">
         <f t="shared" si="1"/>
@@ -4234,11 +4419,11 @@
       </c>
       <c r="S32" s="35">
         <f t="shared" si="1"/>
-        <v>11767.95</v>
+        <v>12799.95</v>
       </c>
       <c r="T32" s="35">
         <f t="shared" si="1"/>
-        <v>7200</v>
+        <v>7800</v>
       </c>
       <c r="U32" s="35">
         <f t="shared" si="1"/>
@@ -4246,7 +4431,7 @@
       </c>
       <c r="V32" s="36">
         <f>SUM(V3:V31)</f>
-        <v>71982.3</v>
+        <v>80331.3</v>
       </c>
       <c r="W32" s="35">
         <f>SUM(W3:W29)</f>
@@ -4254,7 +4439,7 @@
       </c>
       <c r="X32" s="38">
         <f>W32-V32</f>
-        <v>-3582.3000000000029</v>
+        <v>-11931.300000000003</v>
       </c>
     </row>
     <row r="36" spans="2:10">
@@ -4280,6 +4465,1387 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AU39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" ht="60.75" customHeight="1">
+      <c r="A1" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+    </row>
+    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+    </row>
+    <row r="3" spans="1:47">
+      <c r="A3" s="39">
+        <v>3</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="60">
+        <v>44000</v>
+      </c>
+      <c r="R3" s="60">
+        <v>10000</v>
+      </c>
+      <c r="S3" s="60">
+        <v>4660</v>
+      </c>
+      <c r="T3" s="60">
+        <v>7000</v>
+      </c>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40">
+        <f>SUM(C3:V3)</f>
+        <v>65660</v>
+      </c>
+      <c r="X3" s="41">
+        <v>80000</v>
+      </c>
+      <c r="Y3" s="42"/>
+    </row>
+    <row r="4" spans="1:47">
+      <c r="A4" s="54">
+        <v>4</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="60">
+        <v>5000</v>
+      </c>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="60">
+        <v>2000</v>
+      </c>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55">
+        <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
+        <v>7000</v>
+      </c>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="57"/>
+    </row>
+    <row r="5" spans="1:47">
+      <c r="A5" s="54">
+        <v>5</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="57"/>
+    </row>
+    <row r="6" spans="1:47">
+      <c r="A6" s="54">
+        <v>6</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="55"/>
+      <c r="U6" s="55"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="57"/>
+    </row>
+    <row r="7" spans="1:47">
+      <c r="A7" s="54">
+        <v>7</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="57"/>
+    </row>
+    <row r="8" spans="1:47">
+      <c r="A8" s="54">
+        <v>8</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="55"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="57"/>
+    </row>
+    <row r="9" spans="1:47">
+      <c r="A9" s="54">
+        <v>9</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="55"/>
+      <c r="W9" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="57"/>
+    </row>
+    <row r="10" spans="1:47">
+      <c r="A10" s="54">
+        <v>10</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="60">
+        <v>10000</v>
+      </c>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="55"/>
+      <c r="U10" s="55"/>
+      <c r="V10" s="55"/>
+      <c r="W10" s="55">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="57"/>
+    </row>
+    <row r="11" spans="1:47">
+      <c r="A11" s="54">
+        <v>11</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="55"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="57"/>
+    </row>
+    <row r="12" spans="1:47">
+      <c r="A12" s="54">
+        <v>12</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="57"/>
+    </row>
+    <row r="13" spans="1:47">
+      <c r="A13" s="54">
+        <v>13</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="57"/>
+    </row>
+    <row r="14" spans="1:47">
+      <c r="A14" s="54">
+        <v>14</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="55"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="55"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="55"/>
+      <c r="W14" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="57"/>
+    </row>
+    <row r="15" spans="1:47">
+      <c r="A15" s="54">
+        <v>15</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="55"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="55"/>
+      <c r="U15" s="55"/>
+      <c r="V15" s="55"/>
+      <c r="W15" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="57"/>
+    </row>
+    <row r="16" spans="1:47">
+      <c r="A16" s="54">
+        <v>16</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="55"/>
+      <c r="P16" s="55"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="55"/>
+      <c r="T16" s="55"/>
+      <c r="U16" s="55"/>
+      <c r="V16" s="55"/>
+      <c r="W16" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="57"/>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="54">
+        <v>17</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="55"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="55"/>
+      <c r="V17" s="55"/>
+      <c r="W17" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="57"/>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="54">
+        <v>18</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="55"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="55"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="55"/>
+      <c r="T18" s="55"/>
+      <c r="U18" s="55"/>
+      <c r="V18" s="55"/>
+      <c r="W18" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="56"/>
+      <c r="Y18" s="57"/>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="54">
+        <v>19</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="60">
+        <f>10000-SUM(C3:C18)</f>
+        <v>10000</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="60">
+        <f>7300-SUM(F3:F18)</f>
+        <v>7300</v>
+      </c>
+      <c r="G19" s="55"/>
+      <c r="H19" s="60">
+        <f>8700-SUM(H3:H18)</f>
+        <v>8700</v>
+      </c>
+      <c r="I19" s="60">
+        <f>2000-SUM(I3:I18)</f>
+        <v>2000</v>
+      </c>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="60">
+        <f>4000-SUM(O3:O18)</f>
+        <v>4000</v>
+      </c>
+      <c r="P19" s="55"/>
+      <c r="Q19" s="55"/>
+      <c r="R19" s="55"/>
+      <c r="S19" s="55"/>
+      <c r="T19" s="55"/>
+      <c r="U19" s="55"/>
+      <c r="V19" s="55"/>
+      <c r="W19" s="55">
+        <f t="shared" si="0"/>
+        <v>32000</v>
+      </c>
+      <c r="X19" s="56"/>
+      <c r="Y19" s="57">
+        <f>X3-SUM(W3:W19)</f>
+        <v>-34660</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="39">
+        <v>20</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="42"/>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="54">
+        <v>21</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="55"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="55"/>
+      <c r="T21" s="55"/>
+      <c r="U21" s="55"/>
+      <c r="V21" s="55"/>
+      <c r="W21" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="56"/>
+      <c r="Y21" s="57"/>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="54">
+        <v>22</v>
+      </c>
+      <c r="B22" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="55"/>
+      <c r="Q22" s="55"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="55"/>
+      <c r="T22" s="55"/>
+      <c r="U22" s="55"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="56"/>
+      <c r="Y22" s="57"/>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="54">
+        <v>23</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="55"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="55"/>
+      <c r="R23" s="55"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="55"/>
+      <c r="U23" s="55"/>
+      <c r="V23" s="55"/>
+      <c r="W23" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="56"/>
+      <c r="Y23" s="57"/>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="54">
+        <v>24</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="55"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55"/>
+      <c r="S24" s="55"/>
+      <c r="T24" s="55"/>
+      <c r="U24" s="55"/>
+      <c r="V24" s="55"/>
+      <c r="W24" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="56"/>
+      <c r="Y24" s="57"/>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="54">
+        <v>25</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="55"/>
+      <c r="W25" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="56"/>
+      <c r="Y25" s="57"/>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="54">
+        <v>26</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="55"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="55"/>
+      <c r="S26" s="55"/>
+      <c r="T26" s="55"/>
+      <c r="U26" s="55"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="56"/>
+      <c r="Y26" s="57"/>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="54">
+        <v>27</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="55"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="56"/>
+      <c r="Y27" s="57"/>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="54">
+        <v>28</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="55"/>
+      <c r="S28" s="55"/>
+      <c r="T28" s="55"/>
+      <c r="U28" s="55"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="56"/>
+      <c r="Y28" s="57"/>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="54">
+        <v>29</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="55"/>
+      <c r="S29" s="55"/>
+      <c r="T29" s="55"/>
+      <c r="U29" s="55"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="56"/>
+      <c r="Y29" s="57"/>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="54">
+        <v>30</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="55"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="56"/>
+      <c r="Y30" s="57"/>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="54">
+        <v>1</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="55"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="56"/>
+      <c r="Y31" s="57"/>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="54">
+        <v>2</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="55"/>
+      <c r="U32" s="55"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="56"/>
+      <c r="Y32" s="57"/>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" s="54">
+        <v>3</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="55"/>
+      <c r="S33" s="55"/>
+      <c r="T33" s="55"/>
+      <c r="U33" s="55"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="56"/>
+      <c r="Y33" s="57"/>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" s="54">
+        <v>4</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="55"/>
+      <c r="R34" s="55"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="55"/>
+      <c r="U34" s="55"/>
+      <c r="V34" s="55"/>
+      <c r="W34" s="55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="56"/>
+      <c r="Y34" s="57"/>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="58"/>
+      <c r="C35" s="59">
+        <f>SUM(C3:C34)</f>
+        <v>10000</v>
+      </c>
+      <c r="D35" s="59">
+        <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="59">
+        <f t="shared" si="1"/>
+        <v>7300</v>
+      </c>
+      <c r="G35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="59">
+        <f t="shared" si="1"/>
+        <v>8700</v>
+      </c>
+      <c r="I35" s="59">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="J35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="59">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="L35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="59">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="O35" s="59">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="P35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="59">
+        <f t="shared" si="1"/>
+        <v>44000</v>
+      </c>
+      <c r="R35" s="59">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="S35" s="59">
+        <f t="shared" si="1"/>
+        <v>6660</v>
+      </c>
+      <c r="T35" s="59">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="U35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="59">
+        <f t="shared" si="1"/>
+        <v>114660</v>
+      </c>
+      <c r="X35" s="56">
+        <f>SUM(X3:X29)</f>
+        <v>80000</v>
+      </c>
+      <c r="Y35" s="57">
+        <f>X35-W35</f>
+        <v>-34660</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A35:B35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -803,6 +803,30 @@
     <author>Автор</author>
   </authors>
   <commentList>
+    <comment ref="Q3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На пальто</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="T3" authorId="0">
       <text>
         <r>
@@ -1313,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1427,6 +1451,22 @@
     <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1439,6 +1479,9 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1448,25 +1491,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1749,7 +1774,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1766,32 +1791,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -2990,10 +3015,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="48"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3113,32 +3138,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -4349,10 +4374,10 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="49"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -4475,33 +4500,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -4623,598 +4648,599 @@
       <c r="N3" s="40"/>
       <c r="O3" s="40"/>
       <c r="P3" s="40"/>
-      <c r="Q3" s="60">
-        <v>44000</v>
-      </c>
-      <c r="R3" s="60">
+      <c r="Q3" s="48">
+        <v>22000</v>
+      </c>
+      <c r="R3" s="52">
         <v>10000</v>
       </c>
-      <c r="S3" s="60">
-        <v>4660</v>
-      </c>
-      <c r="T3" s="60">
+      <c r="S3" s="48">
+        <f>4660+702</f>
+        <v>5362</v>
+      </c>
+      <c r="T3" s="48">
         <v>7000</v>
       </c>
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
       <c r="W3" s="40">
         <f>SUM(C3:V3)</f>
-        <v>65660</v>
+        <v>44362</v>
       </c>
       <c r="X3" s="41">
-        <v>80000</v>
+        <v>100688</v>
       </c>
       <c r="Y3" s="42"/>
     </row>
     <row r="4" spans="1:47">
-      <c r="A4" s="54">
+      <c r="A4" s="47">
         <v>4</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="60">
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="52">
         <v>5000</v>
       </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="60">
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="52">
         <v>2000</v>
       </c>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55">
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48">
         <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
         <v>7000</v>
       </c>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="57"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="50"/>
     </row>
     <row r="5" spans="1:47">
-      <c r="A5" s="54">
+      <c r="A5" s="47">
         <v>5</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55">
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="57"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="50"/>
     </row>
     <row r="6" spans="1:47">
-      <c r="A6" s="54">
+      <c r="A6" s="47">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55">
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="57"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="50"/>
     </row>
     <row r="7" spans="1:47">
-      <c r="A7" s="54">
+      <c r="A7" s="47">
         <v>7</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55">
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="57"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="50"/>
     </row>
     <row r="8" spans="1:47">
-      <c r="A8" s="54">
+      <c r="A8" s="47">
         <v>8</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55">
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="57"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="50"/>
     </row>
     <row r="9" spans="1:47">
-      <c r="A9" s="54">
+      <c r="A9" s="47">
         <v>9</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55">
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X9" s="56"/>
-      <c r="Y9" s="57"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="50"/>
     </row>
     <row r="10" spans="1:47">
-      <c r="A10" s="54">
+      <c r="A10" s="47">
         <v>10</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="60">
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="52">
         <v>10000</v>
       </c>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55">
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="48">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="57"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="50"/>
     </row>
     <row r="11" spans="1:47">
-      <c r="A11" s="54">
+      <c r="A11" s="47">
         <v>11</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="55"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55">
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="57"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="50"/>
     </row>
     <row r="12" spans="1:47">
-      <c r="A12" s="54">
+      <c r="A12" s="47">
         <v>12</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55">
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="57"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="50"/>
     </row>
     <row r="13" spans="1:47">
-      <c r="A13" s="54">
+      <c r="A13" s="47">
         <v>13</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55">
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="57"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="50"/>
     </row>
     <row r="14" spans="1:47">
-      <c r="A14" s="54">
+      <c r="A14" s="47">
         <v>14</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55">
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
+      <c r="W14" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X14" s="56"/>
-      <c r="Y14" s="57"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="50"/>
     </row>
     <row r="15" spans="1:47">
-      <c r="A15" s="54">
+      <c r="A15" s="47">
         <v>15</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="55"/>
-      <c r="V15" s="55"/>
-      <c r="W15" s="55">
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="57"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="50"/>
     </row>
     <row r="16" spans="1:47">
-      <c r="A16" s="54">
+      <c r="A16" s="47">
         <v>16</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="55"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="55"/>
-      <c r="U16" s="55"/>
-      <c r="V16" s="55"/>
-      <c r="W16" s="55">
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X16" s="56"/>
-      <c r="Y16" s="57"/>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" s="54">
+      <c r="X16" s="49"/>
+      <c r="Y16" s="50"/>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="47">
         <v>17</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="55"/>
-      <c r="V17" s="55"/>
-      <c r="W17" s="55">
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X17" s="56"/>
-      <c r="Y17" s="57"/>
-    </row>
-    <row r="18" spans="1:25">
-      <c r="A18" s="54">
+      <c r="X17" s="49"/>
+      <c r="Y17" s="50"/>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="47">
         <v>18</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="55"/>
-      <c r="V18" s="55"/>
-      <c r="W18" s="55">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X18" s="56"/>
-      <c r="Y18" s="57"/>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" s="54">
+      <c r="X18" s="49"/>
+      <c r="Y18" s="50"/>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19" s="47">
         <v>19</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="60">
+      <c r="C19" s="52">
         <f>10000-SUM(C3:C18)</f>
         <v>10000</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="60">
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="52">
         <f>7300-SUM(F3:F18)</f>
         <v>7300</v>
       </c>
-      <c r="G19" s="55"/>
-      <c r="H19" s="60">
+      <c r="G19" s="48"/>
+      <c r="H19" s="52">
         <f>8700-SUM(H3:H18)</f>
         <v>8700</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I19" s="52">
         <f>2000-SUM(I3:I18)</f>
         <v>2000</v>
       </c>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="60">
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="52">
         <f>4000-SUM(O3:O18)</f>
         <v>4000</v>
       </c>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="55"/>
-      <c r="W19" s="55">
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48">
         <f t="shared" si="0"/>
         <v>32000</v>
       </c>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="57">
+      <c r="X19" s="49"/>
+      <c r="Y19" s="50">
         <f>X3-SUM(W3:W19)</f>
-        <v>-34660</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>7326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="39">
         <v>20</v>
       </c>
@@ -5248,578 +5274,579 @@
       <c r="X20" s="41"/>
       <c r="Y20" s="42"/>
     </row>
-    <row r="21" spans="1:25">
-      <c r="A21" s="54">
+    <row r="21" spans="1:27">
+      <c r="A21" s="47">
         <v>21</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="55"/>
-      <c r="V21" s="55"/>
-      <c r="W21" s="55">
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X21" s="56"/>
-      <c r="Y21" s="57"/>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" s="54">
+      <c r="X21" s="49"/>
+      <c r="Y21" s="50"/>
+      <c r="AA21" s="61"/>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22" s="47">
         <v>22</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="55"/>
-      <c r="W22" s="55">
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X22" s="56"/>
-      <c r="Y22" s="57"/>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" s="54">
+      <c r="X22" s="49"/>
+      <c r="Y22" s="50"/>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="A23" s="47">
         <v>23</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="55"/>
-      <c r="V23" s="55"/>
-      <c r="W23" s="55">
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X23" s="56"/>
-      <c r="Y23" s="57"/>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="54">
+      <c r="X23" s="49"/>
+      <c r="Y23" s="50"/>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="A24" s="47">
         <v>24</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="55"/>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55"/>
-      <c r="W24" s="55">
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X24" s="56"/>
-      <c r="Y24" s="57"/>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" s="54">
+      <c r="X24" s="49"/>
+      <c r="Y24" s="50"/>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="A25" s="47">
         <v>25</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55">
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="48"/>
+      <c r="V25" s="48"/>
+      <c r="W25" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X25" s="56"/>
-      <c r="Y25" s="57"/>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="54">
+      <c r="X25" s="49"/>
+      <c r="Y25" s="50"/>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="A26" s="47">
         <v>26</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="55"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="55">
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="57"/>
-    </row>
-    <row r="27" spans="1:25">
-      <c r="A27" s="54">
+      <c r="X26" s="49"/>
+      <c r="Y26" s="50"/>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="47">
         <v>27</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="55"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="55"/>
-      <c r="U27" s="55"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="55">
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="57"/>
-    </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="54">
+      <c r="X27" s="49"/>
+      <c r="Y27" s="50"/>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="47">
         <v>28</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="55">
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X28" s="56"/>
-      <c r="Y28" s="57"/>
-    </row>
-    <row r="29" spans="1:25">
-      <c r="A29" s="54">
+      <c r="X28" s="49"/>
+      <c r="Y28" s="50"/>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="47">
         <v>29</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="55">
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X29" s="56"/>
-      <c r="Y29" s="57"/>
-    </row>
-    <row r="30" spans="1:25">
-      <c r="A30" s="54">
+      <c r="X29" s="49"/>
+      <c r="Y29" s="50"/>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="47">
         <v>30</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="55"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="55">
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="48"/>
+      <c r="V30" s="48"/>
+      <c r="W30" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X30" s="56"/>
-      <c r="Y30" s="57"/>
-    </row>
-    <row r="31" spans="1:25">
-      <c r="A31" s="54">
+      <c r="X30" s="49"/>
+      <c r="Y30" s="50"/>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="47">
         <v>1</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="55"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="55"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="55">
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X31" s="56"/>
-      <c r="Y31" s="57"/>
-    </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="54">
+      <c r="X31" s="49"/>
+      <c r="Y31" s="50"/>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="47">
         <v>2</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="55"/>
-      <c r="Q32" s="55"/>
-      <c r="R32" s="55"/>
-      <c r="S32" s="55"/>
-      <c r="T32" s="55"/>
-      <c r="U32" s="55"/>
-      <c r="V32" s="55"/>
-      <c r="W32" s="55">
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="48"/>
+      <c r="S32" s="48"/>
+      <c r="T32" s="48"/>
+      <c r="U32" s="48"/>
+      <c r="V32" s="48"/>
+      <c r="W32" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X32" s="56"/>
-      <c r="Y32" s="57"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="50"/>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="54">
+      <c r="A33" s="47">
         <v>3</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="55"/>
-      <c r="Q33" s="55"/>
-      <c r="R33" s="55"/>
-      <c r="S33" s="55"/>
-      <c r="T33" s="55"/>
-      <c r="U33" s="55"/>
-      <c r="V33" s="55"/>
-      <c r="W33" s="55">
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="48"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="48"/>
+      <c r="V33" s="48"/>
+      <c r="W33" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X33" s="56"/>
-      <c r="Y33" s="57"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="50"/>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="54">
+      <c r="A34" s="47">
         <v>4</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="55"/>
-      <c r="K34" s="55"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="55"/>
-      <c r="N34" s="55"/>
-      <c r="O34" s="55"/>
-      <c r="P34" s="55"/>
-      <c r="Q34" s="55"/>
-      <c r="R34" s="55"/>
-      <c r="S34" s="55"/>
-      <c r="T34" s="55"/>
-      <c r="U34" s="55"/>
-      <c r="V34" s="55"/>
-      <c r="W34" s="55">
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="48"/>
+      <c r="V34" s="48"/>
+      <c r="W34" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X34" s="56"/>
-      <c r="Y34" s="57"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="50"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="58" t="s">
+      <c r="A35" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="59">
+      <c r="B35" s="57"/>
+      <c r="C35" s="51">
         <f>SUM(C3:C34)</f>
         <v>10000</v>
       </c>
-      <c r="D35" s="59">
+      <c r="D35" s="51">
         <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="59">
+      <c r="E35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F35" s="59">
+      <c r="F35" s="51">
         <f t="shared" si="1"/>
         <v>7300</v>
       </c>
-      <c r="G35" s="59">
+      <c r="G35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="59">
+      <c r="H35" s="51">
         <f t="shared" si="1"/>
         <v>8700</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="51">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="J35" s="59">
+      <c r="J35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K35" s="59">
+      <c r="K35" s="51">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-      <c r="L35" s="59">
+      <c r="L35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M35" s="59">
+      <c r="M35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N35" s="59">
+      <c r="N35" s="51">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="O35" s="59">
+      <c r="O35" s="51">
         <f t="shared" si="1"/>
         <v>4000</v>
       </c>
-      <c r="P35" s="59">
+      <c r="P35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="59">
+      <c r="Q35" s="51">
         <f t="shared" si="1"/>
-        <v>44000</v>
-      </c>
-      <c r="R35" s="59">
+        <v>22000</v>
+      </c>
+      <c r="R35" s="51">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-      <c r="S35" s="59">
+      <c r="S35" s="51">
         <f t="shared" si="1"/>
-        <v>6660</v>
-      </c>
-      <c r="T35" s="59">
+        <v>7362</v>
+      </c>
+      <c r="T35" s="51">
         <f t="shared" si="1"/>
         <v>7000</v>
       </c>
-      <c r="U35" s="59">
+      <c r="U35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V35" s="59">
+      <c r="V35" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W35" s="59">
+      <c r="W35" s="51">
         <f t="shared" si="1"/>
-        <v>114660</v>
-      </c>
-      <c r="X35" s="56">
+        <v>93362</v>
+      </c>
+      <c r="X35" s="49">
         <f>SUM(X3:X29)</f>
-        <v>80000</v>
-      </c>
-      <c r="Y35" s="57">
+        <v>100688</v>
+      </c>
+      <c r="Y35" s="50">
         <f>X35-W35</f>
-        <v>-34660</v>
+        <v>7326</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -5864,20 +5891,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="G1" s="51" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="G1" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -6098,12 +6125,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -6407,12 +6434,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
@@ -12,9 +12,9 @@
     <sheet name="Апрель 2026" sheetId="4" r:id="rId3"/>
     <sheet name="Лист1" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -27,7 +27,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -187,7 +187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -265,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +327,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -353,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -379,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -406,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -432,7 +432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -458,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -484,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -510,7 +510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -537,7 +537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -563,7 +563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -589,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -616,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -642,7 +642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -695,7 +695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -721,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -745,7 +745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -769,7 +769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -803,7 +803,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -813,21 +813,37 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-На пальто</t>
+          <t>Автор
+Пальто + Цветы</t>
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Белье + сотовая связь + яндекс плюс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -849,6 +865,175 @@
           <t xml:space="preserve">
 Долг маме + штрафы за парковку
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Проиграл маме в теннис</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Брекфаст бенд</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+за УК Эталон</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Уролог</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Сдек за пальто
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На сотовую связь</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Поход в кино</t>
         </r>
       </text>
     </comment>
@@ -1067,11 +1252,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1467,6 +1652,7 @@
     <xf numFmtId="164" fontId="12" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1491,7 +1677,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1774,51 +1959,51 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1914,7 +2099,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>5</v>
       </c>
@@ -1962,7 +2147,7 @@
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -1998,7 +2183,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -2038,7 +2223,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -2076,7 +2261,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -2115,7 +2300,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -2154,7 +2339,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -2189,7 +2374,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -2224,7 +2409,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -2266,7 +2451,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -2311,7 +2496,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -2349,7 +2534,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -2384,7 +2569,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -2417,7 +2602,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -2456,7 +2641,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -2492,7 +2677,7 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>20</v>
       </c>
@@ -2533,7 +2718,7 @@
       </c>
       <c r="X18" s="32"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -2573,7 +2758,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -2611,7 +2796,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -2646,7 +2831,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -2685,7 +2870,7 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -2731,7 +2916,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -2771,7 +2956,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -2816,7 +3001,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>28</v>
       </c>
@@ -2861,7 +3046,7 @@
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2903,7 +3088,7 @@
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -2943,7 +3128,7 @@
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2978,7 +3163,7 @@
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -3014,11 +3199,11 @@
         <v>278.36000000000058</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
-      <c r="A31" s="54" t="s">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="54"/>
+      <c r="B31" s="55"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3105,7 +3290,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -3128,44 +3313,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-    </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+    </row>
+    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -3261,7 +3446,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="39">
         <v>5</v>
       </c>
@@ -3303,7 +3488,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>6</v>
       </c>
@@ -3348,7 +3533,7 @@
       <c r="W4" s="35"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>7</v>
       </c>
@@ -3391,7 +3576,7 @@
       <c r="W5" s="35"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>8</v>
       </c>
@@ -3433,7 +3618,7 @@
       <c r="W6" s="35"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>9</v>
       </c>
@@ -3468,7 +3653,7 @@
       <c r="W7" s="35"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>10</v>
       </c>
@@ -3503,7 +3688,7 @@
       <c r="W8" s="35"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>11</v>
       </c>
@@ -3545,7 +3730,7 @@
       <c r="W9" s="35"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>12</v>
       </c>
@@ -3589,7 +3774,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="43">
         <v>13</v>
       </c>
@@ -3628,7 +3813,7 @@
       <c r="W11" s="45"/>
       <c r="X11" s="46"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>14</v>
       </c>
@@ -3663,7 +3848,7 @@
       <c r="W12" s="35"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>15</v>
       </c>
@@ -3699,7 +3884,7 @@
       <c r="W13" s="35"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>16</v>
       </c>
@@ -3737,7 +3922,7 @@
       <c r="W14" s="35"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>17</v>
       </c>
@@ -3774,7 +3959,7 @@
       <c r="W15" s="35"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="33">
         <v>18</v>
       </c>
@@ -3812,7 +3997,7 @@
       <c r="W16" s="35"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>19</v>
       </c>
@@ -3848,7 +4033,7 @@
       <c r="W17" s="35"/>
       <c r="X17" s="38"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>20</v>
       </c>
@@ -3890,7 +4075,7 @@
       </c>
       <c r="X18" s="42"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>21</v>
       </c>
@@ -3933,7 +4118,7 @@
       <c r="W19" s="35"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>22</v>
       </c>
@@ -3973,7 +4158,7 @@
       <c r="W20" s="35"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>23</v>
       </c>
@@ -4008,7 +4193,7 @@
       <c r="W21" s="35"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>24</v>
       </c>
@@ -4045,7 +4230,7 @@
       <c r="W22" s="35"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>25</v>
       </c>
@@ -4087,7 +4272,7 @@
       <c r="W23" s="35"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>26</v>
       </c>
@@ -4120,7 +4305,7 @@
       <c r="W24" s="35"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>27</v>
       </c>
@@ -4160,7 +4345,7 @@
       <c r="W25" s="35"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>28</v>
       </c>
@@ -4197,7 +4382,7 @@
       <c r="W26" s="35"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>29</v>
       </c>
@@ -4236,7 +4421,7 @@
       <c r="W27" s="35"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>30</v>
       </c>
@@ -4274,7 +4459,7 @@
       <c r="W28" s="35"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>31</v>
       </c>
@@ -4307,7 +4492,7 @@
       <c r="W29" s="35"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>1</v>
       </c>
@@ -4340,7 +4525,7 @@
       <c r="W30" s="35"/>
       <c r="X30" s="38"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>2</v>
       </c>
@@ -4373,11 +4558,11 @@
       <c r="W31" s="35"/>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24">
-      <c r="A32" s="55" t="s">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="55"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -4467,7 +4652,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -4490,45 +4675,45 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
     <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:47" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-    </row>
-    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+    </row>
+    <row r="2" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4627,7 +4812,7 @@
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
     </row>
-    <row r="3" spans="1:47">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="39">
         <v>3</v>
       </c>
@@ -4649,68 +4834,80 @@
       <c r="O3" s="40"/>
       <c r="P3" s="40"/>
       <c r="Q3" s="48">
-        <v>22000</v>
-      </c>
-      <c r="R3" s="52">
-        <v>10000</v>
-      </c>
+        <f>22000+3500</f>
+        <v>25500</v>
+      </c>
+      <c r="R3" s="48"/>
       <c r="S3" s="48">
-        <f>4660+702</f>
-        <v>5362</v>
+        <f>4660+702+799</f>
+        <v>6161</v>
       </c>
       <c r="T3" s="48">
         <v>7000</v>
       </c>
-      <c r="U3" s="40"/>
+      <c r="U3" s="40">
+        <v>750</v>
+      </c>
       <c r="V3" s="40"/>
       <c r="W3" s="40">
         <f>SUM(C3:V3)</f>
-        <v>44362</v>
+        <v>39411</v>
       </c>
       <c r="X3" s="41">
         <v>100688</v>
       </c>
       <c r="Y3" s="42"/>
     </row>
-    <row r="4" spans="1:47">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="48"/>
+      <c r="C4" s="48">
+        <v>100</v>
+      </c>
       <c r="D4" s="48"/>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
       <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+      <c r="H4" s="48">
+        <v>2320</v>
+      </c>
       <c r="I4" s="48"/>
       <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+      <c r="K4" s="48">
+        <v>3663.22</v>
+      </c>
       <c r="L4" s="48"/>
       <c r="M4" s="48"/>
-      <c r="N4" s="52">
-        <v>5000</v>
+      <c r="N4" s="48">
+        <v>5350</v>
       </c>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="48">
+        <v>1025</v>
+      </c>
       <c r="R4" s="48"/>
-      <c r="S4" s="52">
-        <v>2000</v>
+      <c r="S4" s="48">
+        <v>100</v>
       </c>
       <c r="T4" s="48"/>
       <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
+      <c r="V4" s="48">
+        <f>1320+1330+210</f>
+        <v>2860</v>
+      </c>
       <c r="W4" s="48">
         <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
-        <v>7000</v>
+        <v>15418.22</v>
       </c>
       <c r="X4" s="49"/>
       <c r="Y4" s="50"/>
     </row>
-    <row r="5" spans="1:47">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="47">
         <v>5</v>
       </c>
@@ -4744,7 +4941,7 @@
       <c r="X5" s="49"/>
       <c r="Y5" s="50"/>
     </row>
-    <row r="6" spans="1:47">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="47">
         <v>6</v>
       </c>
@@ -4766,19 +4963,21 @@
       <c r="O6" s="48"/>
       <c r="P6" s="48"/>
       <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
+      <c r="R6" s="52">
+        <v>10000</v>
+      </c>
       <c r="S6" s="48"/>
       <c r="T6" s="48"/>
       <c r="U6" s="48"/>
       <c r="V6" s="48"/>
       <c r="W6" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X6" s="49"/>
       <c r="Y6" s="50"/>
     </row>
-    <row r="7" spans="1:47">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
         <v>7</v>
       </c>
@@ -4812,7 +5011,7 @@
       <c r="X7" s="49"/>
       <c r="Y7" s="50"/>
     </row>
-    <row r="8" spans="1:47">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>8</v>
       </c>
@@ -4846,7 +5045,7 @@
       <c r="X8" s="49"/>
       <c r="Y8" s="50"/>
     </row>
-    <row r="9" spans="1:47">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="47">
         <v>9</v>
       </c>
@@ -4880,7 +5079,7 @@
       <c r="X9" s="49"/>
       <c r="Y9" s="50"/>
     </row>
-    <row r="10" spans="1:47">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>10</v>
       </c>
@@ -4916,7 +5115,7 @@
       <c r="X10" s="49"/>
       <c r="Y10" s="50"/>
     </row>
-    <row r="11" spans="1:47">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="47">
         <v>11</v>
       </c>
@@ -4950,7 +5149,7 @@
       <c r="X11" s="49"/>
       <c r="Y11" s="50"/>
     </row>
-    <row r="12" spans="1:47">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>12</v>
       </c>
@@ -4984,7 +5183,7 @@
       <c r="X12" s="49"/>
       <c r="Y12" s="50"/>
     </row>
-    <row r="13" spans="1:47">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="47">
         <v>13</v>
       </c>
@@ -5018,7 +5217,7 @@
       <c r="X13" s="49"/>
       <c r="Y13" s="50"/>
     </row>
-    <row r="14" spans="1:47">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>14</v>
       </c>
@@ -5052,7 +5251,7 @@
       <c r="X14" s="49"/>
       <c r="Y14" s="50"/>
     </row>
-    <row r="15" spans="1:47">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
         <v>15</v>
       </c>
@@ -5086,7 +5285,7 @@
       <c r="X15" s="49"/>
       <c r="Y15" s="50"/>
     </row>
-    <row r="16" spans="1:47">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
         <v>16</v>
       </c>
@@ -5120,7 +5319,7 @@
       <c r="X16" s="49"/>
       <c r="Y16" s="50"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
         <v>17</v>
       </c>
@@ -5154,7 +5353,7 @@
       <c r="X17" s="49"/>
       <c r="Y17" s="50"/>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="47">
         <v>18</v>
       </c>
@@ -5188,7 +5387,7 @@
       <c r="X18" s="49"/>
       <c r="Y18" s="50"/>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="47">
         <v>19</v>
       </c>
@@ -5197,7 +5396,7 @@
       </c>
       <c r="C19" s="52">
         <f>10000-SUM(C3:C18)</f>
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -5208,7 +5407,7 @@
       <c r="G19" s="48"/>
       <c r="H19" s="52">
         <f>8700-SUM(H3:H18)</f>
-        <v>8700</v>
+        <v>6380</v>
       </c>
       <c r="I19" s="52">
         <f>2000-SUM(I3:I18)</f>
@@ -5232,15 +5431,15 @@
       <c r="V19" s="48"/>
       <c r="W19" s="48">
         <f t="shared" si="0"/>
-        <v>32000</v>
+        <v>29580</v>
       </c>
       <c r="X19" s="49"/>
       <c r="Y19" s="50">
         <f>X3-SUM(W3:W19)</f>
-        <v>7326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27">
+        <v>-3721.2200000000012</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>20</v>
       </c>
@@ -5274,7 +5473,7 @@
       <c r="X20" s="41"/>
       <c r="Y20" s="42"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="47">
         <v>21</v>
       </c>
@@ -5307,9 +5506,9 @@
       </c>
       <c r="X21" s="49"/>
       <c r="Y21" s="50"/>
-      <c r="AA21" s="61"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AA21" s="53"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="47">
         <v>22</v>
       </c>
@@ -5343,7 +5542,7 @@
       <c r="X22" s="49"/>
       <c r="Y22" s="50"/>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="47">
         <v>23</v>
       </c>
@@ -5377,7 +5576,7 @@
       <c r="X23" s="49"/>
       <c r="Y23" s="50"/>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="47">
         <v>24</v>
       </c>
@@ -5411,7 +5610,7 @@
       <c r="X24" s="49"/>
       <c r="Y24" s="50"/>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="47">
         <v>25</v>
       </c>
@@ -5445,7 +5644,7 @@
       <c r="X25" s="49"/>
       <c r="Y25" s="50"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="47">
         <v>26</v>
       </c>
@@ -5479,7 +5678,7 @@
       <c r="X26" s="49"/>
       <c r="Y26" s="50"/>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="47">
         <v>27</v>
       </c>
@@ -5513,7 +5712,7 @@
       <c r="X27" s="49"/>
       <c r="Y27" s="50"/>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="47">
         <v>28</v>
       </c>
@@ -5547,7 +5746,7 @@
       <c r="X28" s="49"/>
       <c r="Y28" s="50"/>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="47">
         <v>29</v>
       </c>
@@ -5581,7 +5780,7 @@
       <c r="X29" s="49"/>
       <c r="Y29" s="50"/>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="47">
         <v>30</v>
       </c>
@@ -5615,7 +5814,7 @@
       <c r="X30" s="49"/>
       <c r="Y30" s="50"/>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="47">
         <v>1</v>
       </c>
@@ -5649,7 +5848,7 @@
       <c r="X31" s="49"/>
       <c r="Y31" s="50"/>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="47">
         <v>2</v>
       </c>
@@ -5683,7 +5882,7 @@
       <c r="X32" s="49"/>
       <c r="Y32" s="50"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="47">
         <v>3</v>
       </c>
@@ -5717,7 +5916,7 @@
       <c r="X33" s="49"/>
       <c r="Y33" s="50"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="47">
         <v>4</v>
       </c>
@@ -5751,11 +5950,11 @@
       <c r="X34" s="49"/>
       <c r="Y34" s="50"/>
     </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="57" t="s">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="57"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="51">
         <f>SUM(C3:C34)</f>
         <v>10000</v>
@@ -5790,7 +5989,7 @@
       </c>
       <c r="K35" s="51">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>13663.22</v>
       </c>
       <c r="L35" s="51">
         <f t="shared" si="1"/>
@@ -5802,7 +6001,7 @@
       </c>
       <c r="N35" s="51">
         <f t="shared" si="1"/>
-        <v>5000</v>
+        <v>5350</v>
       </c>
       <c r="O35" s="51">
         <f t="shared" si="1"/>
@@ -5814,15 +6013,15 @@
       </c>
       <c r="Q35" s="51">
         <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>26525</v>
       </c>
       <c r="R35" s="51">
-        <f t="shared" si="1"/>
+        <f>SUM(R4:R34)</f>
         <v>10000</v>
       </c>
       <c r="S35" s="51">
         <f t="shared" si="1"/>
-        <v>7362</v>
+        <v>6261</v>
       </c>
       <c r="T35" s="51">
         <f t="shared" si="1"/>
@@ -5830,15 +6029,15 @@
       </c>
       <c r="U35" s="51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="V35" s="51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2860</v>
       </c>
       <c r="W35" s="51">
         <f t="shared" si="1"/>
-        <v>93362</v>
+        <v>104409.22</v>
       </c>
       <c r="X35" s="49">
         <f>SUM(X3:X29)</f>
@@ -5846,10 +6045,10 @@
       </c>
       <c r="Y35" s="50">
         <f>X35-W35</f>
-        <v>7326</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
+        <v>-3721.2200000000012</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -5873,9 +6072,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -5890,23 +6089,23 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="G1" s="58" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="G1" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -5938,7 +6137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -5972,7 +6171,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -6006,7 +6205,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -6040,7 +6239,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -6074,7 +6273,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -6108,7 +6307,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -6125,18 +6324,18 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G8" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -6157,7 +6356,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -6178,7 +6377,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -6199,7 +6398,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -6220,7 +6419,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -6241,7 +6440,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -6262,7 +6461,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -6283,7 +6482,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -6304,7 +6503,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -6325,7 +6524,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -6343,7 +6542,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -6361,7 +6560,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -6379,7 +6578,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -6397,7 +6596,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -6415,7 +6614,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -6433,13 +6632,13 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="59" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -912,7 +912,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Брекфаст бенд</t>
+Брекфаст бенд и макдак</t>
         </r>
       </text>
     </comment>
@@ -1009,7 +1009,33 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-На сотовую связь</t>
+На сотовую связь
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Плата за 2sub на 3 месяца
+</t>
         </r>
       </text>
     </comment>
@@ -1034,6 +1060,55 @@
           </rPr>
           <t xml:space="preserve">
 Поход в кино</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вино
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+вк музыка</t>
         </r>
       </text>
     </comment>
@@ -1747,7 +1822,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1782,7 +1857,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4866,14 +4941,18 @@
         <v>5</v>
       </c>
       <c r="C4" s="48">
-        <v>100</v>
-      </c>
-      <c r="D4" s="48"/>
+        <f>100+422+585</f>
+        <v>1107</v>
+      </c>
+      <c r="D4" s="48">
+        <v>3679</v>
+      </c>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
       <c r="G4" s="48"/>
       <c r="H4" s="48">
-        <v>2320</v>
+        <f>2320+1728</f>
+        <v>4048</v>
       </c>
       <c r="I4" s="48"/>
       <c r="J4" s="48"/>
@@ -4895,14 +4974,16 @@
         <v>100</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
+      <c r="U4" s="48">
+        <v>990</v>
+      </c>
       <c r="V4" s="48">
         <f>1320+1330+210</f>
         <v>2860</v>
       </c>
       <c r="W4" s="48">
         <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
-        <v>15418.22</v>
+        <v>22822.22</v>
       </c>
       <c r="X4" s="49"/>
       <c r="Y4" s="50"/>
@@ -4914,13 +4995,18 @@
       <c r="B5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="48"/>
+      <c r="C5" s="48">
+        <f>3116+382</f>
+        <v>3498</v>
+      </c>
       <c r="D5" s="48"/>
       <c r="E5" s="48"/>
       <c r="F5" s="48"/>
       <c r="G5" s="48"/>
       <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
+      <c r="I5" s="48">
+        <v>1500</v>
+      </c>
       <c r="J5" s="48"/>
       <c r="K5" s="48"/>
       <c r="L5" s="48"/>
@@ -4929,14 +5015,18 @@
       <c r="O5" s="48"/>
       <c r="P5" s="48"/>
       <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
+      <c r="R5" s="48">
+        <v>9373</v>
+      </c>
+      <c r="S5" s="48">
+        <v>199</v>
+      </c>
       <c r="T5" s="48"/>
       <c r="U5" s="48"/>
       <c r="V5" s="48"/>
       <c r="W5" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14570</v>
       </c>
       <c r="X5" s="49"/>
       <c r="Y5" s="50"/>
@@ -4963,16 +5053,14 @@
       <c r="O6" s="48"/>
       <c r="P6" s="48"/>
       <c r="Q6" s="48"/>
-      <c r="R6" s="52">
-        <v>10000</v>
-      </c>
+      <c r="R6" s="48"/>
       <c r="S6" s="48"/>
       <c r="T6" s="48"/>
       <c r="U6" s="48"/>
       <c r="V6" s="48"/>
       <c r="W6" s="48">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X6" s="49"/>
       <c r="Y6" s="50"/>
@@ -5396,7 +5484,7 @@
       </c>
       <c r="C19" s="52">
         <f>10000-SUM(C3:C18)</f>
-        <v>9900</v>
+        <v>5395</v>
       </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
@@ -5407,11 +5495,11 @@
       <c r="G19" s="48"/>
       <c r="H19" s="52">
         <f>8700-SUM(H3:H18)</f>
-        <v>6380</v>
+        <v>4652</v>
       </c>
       <c r="I19" s="52">
         <f>2000-SUM(I3:I18)</f>
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J19" s="48"/>
       <c r="K19" s="48"/>
@@ -5431,12 +5519,12 @@
       <c r="V19" s="48"/>
       <c r="W19" s="48">
         <f t="shared" si="0"/>
-        <v>29580</v>
+        <v>21847</v>
       </c>
       <c r="X19" s="49"/>
       <c r="Y19" s="50">
         <f>X3-SUM(W3:W19)</f>
-        <v>-3721.2200000000012</v>
+        <v>-7962.2200000000012</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
@@ -5961,7 +6049,7 @@
       </c>
       <c r="D35" s="51">
         <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
-        <v>0</v>
+        <v>3679</v>
       </c>
       <c r="E35" s="51">
         <f t="shared" si="1"/>
@@ -6017,11 +6105,11 @@
       </c>
       <c r="R35" s="51">
         <f>SUM(R4:R34)</f>
-        <v>10000</v>
+        <v>9373</v>
       </c>
       <c r="S35" s="51">
         <f t="shared" si="1"/>
-        <v>6261</v>
+        <v>6460</v>
       </c>
       <c r="T35" s="51">
         <f t="shared" si="1"/>
@@ -6029,7 +6117,7 @@
       </c>
       <c r="U35" s="51">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>1740</v>
       </c>
       <c r="V35" s="51">
         <f t="shared" si="1"/>
@@ -6037,7 +6125,7 @@
       </c>
       <c r="W35" s="51">
         <f t="shared" si="1"/>
-        <v>104409.22</v>
+        <v>108650.22</v>
       </c>
       <c r="X35" s="49">
         <f>SUM(X3:X29)</f>
@@ -6045,7 +6133,7 @@
       </c>
       <c r="Y35" s="50">
         <f>X35-W35</f>
-        <v>-3721.2200000000012</v>
+        <v>-7962.2200000000012</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
@@ -12,9 +12,9 @@
     <sheet name="Апрель 2026" sheetId="4" r:id="rId3"/>
     <sheet name="Лист1" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -27,7 +27,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -187,7 +187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -213,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -239,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -265,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +327,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -353,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -379,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -406,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -432,7 +432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -458,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -484,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -510,7 +510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -537,7 +537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -563,7 +563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -589,7 +589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -616,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -642,7 +642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -695,7 +695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -721,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -745,7 +745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -769,7 +769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -803,7 +803,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -818,7 +818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -843,7 +843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -868,7 +868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -892,7 +892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -916,7 +916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -940,7 +940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -964,7 +964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -989,7 +989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1014,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1039,7 +1039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1063,7 +1063,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1088,7 +1088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1109,6 +1109,199 @@
           </rPr>
           <t xml:space="preserve">
 вк музыка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вода и мусор
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+ВПН
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">круасан в пекарне
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Додо пицца
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама дала в долг
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок от мамы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ВАФЕЛ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Гель для душа и журнал
+</t>
         </r>
       </text>
     </comment>
@@ -1327,11 +1520,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1822,7 +2015,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1857,7 +2050,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2034,23 +2227,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
       <c r="A1" s="54" t="s">
         <v>27</v>
       </c>
@@ -2078,7 +2271,7 @@
       <c r="W1" s="54"/>
       <c r="X1" s="54"/>
     </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2174,7 +2367,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46">
       <c r="A3" s="27">
         <v>5</v>
       </c>
@@ -2222,7 +2415,7 @@
       </c>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46">
       <c r="A4" s="5">
         <v>6</v>
       </c>
@@ -2258,7 +2451,7 @@
       <c r="W4" s="12"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46">
       <c r="A5" s="4">
         <v>7</v>
       </c>
@@ -2298,7 +2491,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46">
       <c r="A6" s="5">
         <v>8</v>
       </c>
@@ -2336,7 +2529,7 @@
       <c r="W6" s="12"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46">
       <c r="A7" s="4">
         <v>9</v>
       </c>
@@ -2375,7 +2568,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46">
       <c r="A8" s="5">
         <v>10</v>
       </c>
@@ -2414,7 +2607,7 @@
       <c r="W8" s="12"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46">
       <c r="A9" s="4">
         <v>11</v>
       </c>
@@ -2449,7 +2642,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46">
       <c r="A10" s="5">
         <v>12</v>
       </c>
@@ -2484,7 +2677,7 @@
       <c r="W10" s="12"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -2526,7 +2719,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46">
       <c r="A12" s="5">
         <v>14</v>
       </c>
@@ -2571,7 +2764,7 @@
       <c r="W12" s="12"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46">
       <c r="A13" s="4">
         <v>15</v>
       </c>
@@ -2609,7 +2802,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46">
       <c r="A14" s="5">
         <v>16</v>
       </c>
@@ -2644,7 +2837,7 @@
       <c r="W14" s="12"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46">
       <c r="A15" s="4">
         <v>17</v>
       </c>
@@ -2677,7 +2870,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46">
       <c r="A16" s="5">
         <v>18</v>
       </c>
@@ -2716,7 +2909,7 @@
       <c r="W16" s="12"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17" s="4">
         <v>19</v>
       </c>
@@ -2752,7 +2945,7 @@
         <v>-6655.0499999999956</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1">
       <c r="A18" s="27">
         <v>20</v>
       </c>
@@ -2793,7 +2986,7 @@
       </c>
       <c r="X18" s="32"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19" s="4">
         <v>21</v>
       </c>
@@ -2833,7 +3026,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20" s="5">
         <v>22</v>
       </c>
@@ -2871,7 +3064,7 @@
       <c r="W20" s="12"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -2906,7 +3099,7 @@
       </c>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22" s="5">
         <v>24</v>
       </c>
@@ -2945,7 +3138,7 @@
       <c r="W22" s="12"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23" s="4">
         <v>25</v>
       </c>
@@ -2991,7 +3184,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24" s="5">
         <v>26</v>
       </c>
@@ -3031,7 +3224,7 @@
       <c r="W24" s="12"/>
       <c r="X24" s="25"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25" s="4">
         <v>27</v>
       </c>
@@ -3076,7 +3269,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26" s="5">
         <v>28</v>
       </c>
@@ -3121,7 +3314,7 @@
       <c r="W26" s="12"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -3163,7 +3356,7 @@
       <c r="W27" s="12"/>
       <c r="X27" s="25"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28" s="5">
         <v>2</v>
       </c>
@@ -3203,7 +3396,7 @@
       <c r="W28" s="12"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -3238,7 +3431,7 @@
       <c r="W29" s="12"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -3274,7 +3467,7 @@
         <v>278.36000000000058</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="A31" s="55" t="s">
         <v>20</v>
       </c>
@@ -3365,7 +3558,7 @@
       </c>
       <c r="X31" s="26"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10">
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -3388,16 +3581,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="24" width="20.7109375" style="2" customWidth="1"/>
     <col min="25" max="36" width="12.7109375" style="2" customWidth="1"/>
     <col min="37" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="60.75" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>65</v>
       </c>
@@ -3425,7 +3618,7 @@
       <c r="W1" s="57"/>
       <c r="X1" s="57"/>
     </row>
-    <row r="2" spans="1:46" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -3521,7 +3714,7 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46">
       <c r="A3" s="39">
         <v>5</v>
       </c>
@@ -3563,7 +3756,7 @@
       </c>
       <c r="X3" s="42"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46">
       <c r="A4" s="33">
         <v>6</v>
       </c>
@@ -3608,7 +3801,7 @@
       <c r="W4" s="35"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46">
       <c r="A5" s="33">
         <v>7</v>
       </c>
@@ -3651,7 +3844,7 @@
       <c r="W5" s="35"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46">
       <c r="A6" s="33">
         <v>8</v>
       </c>
@@ -3693,7 +3886,7 @@
       <c r="W6" s="35"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46">
       <c r="A7" s="33">
         <v>9</v>
       </c>
@@ -3728,7 +3921,7 @@
       <c r="W7" s="35"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46">
       <c r="A8" s="33">
         <v>10</v>
       </c>
@@ -3763,7 +3956,7 @@
       <c r="W8" s="35"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46">
       <c r="A9" s="33">
         <v>11</v>
       </c>
@@ -3805,7 +3998,7 @@
       <c r="W9" s="35"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46">
       <c r="A10" s="33">
         <v>12</v>
       </c>
@@ -3849,7 +4042,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46">
       <c r="A11" s="43">
         <v>13</v>
       </c>
@@ -3888,7 +4081,7 @@
       <c r="W11" s="45"/>
       <c r="X11" s="46"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46">
       <c r="A12" s="33">
         <v>14</v>
       </c>
@@ -3923,7 +4116,7 @@
       <c r="W12" s="35"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46">
       <c r="A13" s="33">
         <v>15</v>
       </c>
@@ -3959,7 +4152,7 @@
       <c r="W13" s="35"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46">
       <c r="A14" s="33">
         <v>16</v>
       </c>
@@ -3997,7 +4190,7 @@
       <c r="W14" s="35"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46">
       <c r="A15" s="33">
         <v>17</v>
       </c>
@@ -4034,7 +4227,7 @@
       <c r="W15" s="35"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46">
       <c r="A16" s="33">
         <v>18</v>
       </c>
@@ -4072,7 +4265,7 @@
       <c r="W16" s="35"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17" s="33">
         <v>19</v>
       </c>
@@ -4108,7 +4301,7 @@
       <c r="W17" s="35"/>
       <c r="X17" s="38"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18" s="39">
         <v>20</v>
       </c>
@@ -4150,7 +4343,7 @@
       </c>
       <c r="X18" s="42"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19" s="33">
         <v>21</v>
       </c>
@@ -4193,7 +4386,7 @@
       <c r="W19" s="35"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20" s="33">
         <v>22</v>
       </c>
@@ -4233,7 +4426,7 @@
       <c r="W20" s="35"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21" s="33">
         <v>23</v>
       </c>
@@ -4268,7 +4461,7 @@
       <c r="W21" s="35"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22" s="33">
         <v>24</v>
       </c>
@@ -4305,7 +4498,7 @@
       <c r="W22" s="35"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23" s="33">
         <v>25</v>
       </c>
@@ -4347,7 +4540,7 @@
       <c r="W23" s="35"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24" s="33">
         <v>26</v>
       </c>
@@ -4380,7 +4573,7 @@
       <c r="W24" s="35"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25" s="33">
         <v>27</v>
       </c>
@@ -4420,7 +4613,7 @@
       <c r="W25" s="35"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26" s="33">
         <v>28</v>
       </c>
@@ -4457,7 +4650,7 @@
       <c r="W26" s="35"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27" s="33">
         <v>29</v>
       </c>
@@ -4496,7 +4689,7 @@
       <c r="W27" s="35"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28" s="33">
         <v>30</v>
       </c>
@@ -4534,7 +4727,7 @@
       <c r="W28" s="35"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29" s="33">
         <v>31</v>
       </c>
@@ -4567,7 +4760,7 @@
       <c r="W29" s="35"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="A30" s="33">
         <v>1</v>
       </c>
@@ -4600,7 +4793,7 @@
       <c r="W30" s="35"/>
       <c r="X30" s="38"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="A31" s="33">
         <v>2</v>
       </c>
@@ -4633,7 +4826,7 @@
       <c r="W31" s="35"/>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="A32" s="56" t="s">
         <v>20</v>
       </c>
@@ -4727,7 +4920,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10">
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -4750,16 +4943,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
     <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" ht="60.75" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>65</v>
       </c>
@@ -4788,7 +4981,7 @@
       <c r="X1" s="57"/>
       <c r="Y1" s="57"/>
     </row>
-    <row r="2" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
@@ -4887,7 +5080,7 @@
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47">
       <c r="A3" s="39">
         <v>3</v>
       </c>
@@ -4933,7 +5126,7 @@
       </c>
       <c r="Y3" s="42"/>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47">
       <c r="A4" s="47">
         <v>4</v>
       </c>
@@ -4988,7 +5181,7 @@
       <c r="X4" s="49"/>
       <c r="Y4" s="50"/>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47">
       <c r="A5" s="47">
         <v>5</v>
       </c>
@@ -5031,41 +5224,52 @@
       <c r="X5" s="49"/>
       <c r="Y5" s="50"/>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47">
       <c r="A6" s="47">
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="C6" s="48">
+        <v>918</v>
+      </c>
+      <c r="D6" s="48">
+        <v>994</v>
+      </c>
       <c r="E6" s="48"/>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
       <c r="H6" s="48"/>
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="K6" s="48">
+        <v>3464</v>
+      </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="48"/>
       <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
+      <c r="P6" s="48">
+        <f>500+288</f>
+        <v>788</v>
+      </c>
       <c r="Q6" s="48"/>
       <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
+      <c r="S6" s="48">
+        <v>990</v>
+      </c>
       <c r="T6" s="48"/>
       <c r="U6" s="48"/>
       <c r="V6" s="48"/>
       <c r="W6" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7154</v>
       </c>
       <c r="X6" s="49"/>
       <c r="Y6" s="50"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47">
       <c r="A7" s="47">
         <v>7</v>
       </c>
@@ -5073,7 +5277,9 @@
         <v>8</v>
       </c>
       <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
+      <c r="D7" s="48">
+        <v>714</v>
+      </c>
       <c r="E7" s="48"/>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
@@ -5085,7 +5291,10 @@
       <c r="M7" s="48"/>
       <c r="N7" s="48"/>
       <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
+      <c r="P7" s="48">
+        <f>500+280</f>
+        <v>780</v>
+      </c>
       <c r="Q7" s="48"/>
       <c r="R7" s="48"/>
       <c r="S7" s="48"/>
@@ -5094,12 +5303,12 @@
       <c r="V7" s="48"/>
       <c r="W7" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="X7" s="49"/>
       <c r="Y7" s="50"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47">
       <c r="A8" s="47">
         <v>8</v>
       </c>
@@ -5109,9 +5318,15 @@
       <c r="C8" s="48"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
+      <c r="F8" s="48">
+        <v>420</v>
+      </c>
+      <c r="G8" s="48">
+        <v>835</v>
+      </c>
+      <c r="H8" s="48">
+        <v>285</v>
+      </c>
       <c r="I8" s="48"/>
       <c r="J8" s="48"/>
       <c r="K8" s="48"/>
@@ -5128,20 +5343,24 @@
       <c r="V8" s="48"/>
       <c r="W8" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1540</v>
       </c>
       <c r="X8" s="49"/>
       <c r="Y8" s="50"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47">
       <c r="A9" s="47">
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
+      <c r="C9" s="48">
+        <v>863</v>
+      </c>
+      <c r="D9" s="48">
+        <v>710</v>
+      </c>
       <c r="E9" s="48"/>
       <c r="F9" s="48"/>
       <c r="G9" s="48"/>
@@ -5152,7 +5371,9 @@
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
       <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
+      <c r="O9" s="48">
+        <v>409</v>
+      </c>
       <c r="P9" s="48"/>
       <c r="Q9" s="48"/>
       <c r="R9" s="48"/>
@@ -5162,33 +5383,43 @@
       <c r="V9" s="48"/>
       <c r="W9" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1982</v>
       </c>
       <c r="X9" s="49"/>
       <c r="Y9" s="50"/>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47">
       <c r="A10" s="47">
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
+      <c r="C10" s="48">
+        <v>319</v>
+      </c>
+      <c r="D10" s="48">
+        <v>940</v>
+      </c>
+      <c r="E10" s="48">
+        <v>1895</v>
+      </c>
       <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
+      <c r="G10" s="48">
+        <v>835</v>
+      </c>
       <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
+      <c r="I10" s="48">
+        <v>1034</v>
+      </c>
       <c r="J10" s="48"/>
-      <c r="K10" s="52">
-        <v>10000</v>
-      </c>
+      <c r="K10" s="48"/>
       <c r="L10" s="48"/>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
+      <c r="O10" s="48">
+        <v>275</v>
+      </c>
       <c r="P10" s="48"/>
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
@@ -5198,20 +5429,25 @@
       <c r="V10" s="48"/>
       <c r="W10" s="48">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>5298</v>
       </c>
       <c r="X10" s="49"/>
       <c r="Y10" s="50"/>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47">
       <c r="A11" s="47">
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
+      <c r="C11" s="48">
+        <f>790+282</f>
+        <v>1072</v>
+      </c>
+      <c r="D11" s="48">
+        <v>1311</v>
+      </c>
       <c r="E11" s="48"/>
       <c r="F11" s="48"/>
       <c r="G11" s="48"/>
@@ -5221,8 +5457,14 @@
       <c r="K11" s="48"/>
       <c r="L11" s="48"/>
       <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
+      <c r="N11" s="48">
+        <f>1500+1900</f>
+        <v>3400</v>
+      </c>
+      <c r="O11" s="48">
+        <f>302+243</f>
+        <v>545</v>
+      </c>
       <c r="P11" s="48"/>
       <c r="Q11" s="48"/>
       <c r="R11" s="48"/>
@@ -5232,19 +5474,24 @@
       <c r="V11" s="48"/>
       <c r="W11" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="49"/>
+        <v>6328</v>
+      </c>
+      <c r="X11" s="49">
+        <v>5000</v>
+      </c>
       <c r="Y11" s="50"/>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47">
       <c r="A12" s="47">
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="48"/>
+      <c r="C12" s="48">
+        <f>69+603</f>
+        <v>672</v>
+      </c>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
       <c r="F12" s="48"/>
@@ -5266,12 +5513,14 @@
       <c r="V12" s="48"/>
       <c r="W12" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="49"/>
+        <v>672</v>
+      </c>
+      <c r="X12" s="49">
+        <v>10000</v>
+      </c>
       <c r="Y12" s="50"/>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47">
       <c r="A13" s="47">
         <v>13</v>
       </c>
@@ -5305,26 +5554,36 @@
       <c r="X13" s="49"/>
       <c r="Y13" s="50"/>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47">
       <c r="A14" s="47">
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="48"/>
+      <c r="C14" s="48">
+        <v>879</v>
+      </c>
       <c r="D14" s="48"/>
       <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
+      <c r="F14" s="48">
+        <v>1080</v>
+      </c>
+      <c r="G14" s="48">
+        <v>580</v>
+      </c>
+      <c r="H14" s="48">
+        <v>1261</v>
+      </c>
       <c r="I14" s="48"/>
       <c r="J14" s="48"/>
       <c r="K14" s="48"/>
       <c r="L14" s="48"/>
       <c r="M14" s="48"/>
       <c r="N14" s="48"/>
-      <c r="O14" s="48"/>
+      <c r="O14" s="48">
+        <v>305</v>
+      </c>
       <c r="P14" s="48"/>
       <c r="Q14" s="48"/>
       <c r="R14" s="48"/>
@@ -5334,46 +5593,56 @@
       <c r="V14" s="48"/>
       <c r="W14" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4105</v>
       </c>
       <c r="X14" s="49"/>
       <c r="Y14" s="50"/>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47">
       <c r="A15" s="47">
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="48"/>
+      <c r="C15" s="48">
+        <v>700</v>
+      </c>
       <c r="D15" s="48"/>
       <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
+      <c r="F15" s="48">
+        <v>990</v>
+      </c>
       <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
+      <c r="H15" s="48">
+        <v>2200</v>
+      </c>
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48"/>
       <c r="L15" s="48"/>
       <c r="M15" s="48"/>
       <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
+      <c r="O15" s="48">
+        <v>369</v>
+      </c>
       <c r="P15" s="48"/>
       <c r="Q15" s="48"/>
       <c r="R15" s="48"/>
       <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
+      <c r="T15" s="48">
+        <v>1400</v>
+      </c>
       <c r="U15" s="48"/>
       <c r="V15" s="48"/>
       <c r="W15" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5659</v>
       </c>
       <c r="X15" s="49"/>
       <c r="Y15" s="50"/>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47">
       <c r="A16" s="47">
         <v>16</v>
       </c>
@@ -5407,7 +5676,7 @@
       <c r="X16" s="49"/>
       <c r="Y16" s="50"/>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27">
       <c r="A17" s="47">
         <v>17</v>
       </c>
@@ -5441,7 +5710,7 @@
       <c r="X17" s="49"/>
       <c r="Y17" s="50"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27">
       <c r="A18" s="47">
         <v>18</v>
       </c>
@@ -5475,41 +5744,26 @@
       <c r="X18" s="49"/>
       <c r="Y18" s="50"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27">
       <c r="A19" s="47">
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="52">
-        <f>10000-SUM(C3:C18)</f>
-        <v>5395</v>
-      </c>
+      <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
-      <c r="F19" s="52">
-        <f>7300-SUM(F3:F18)</f>
-        <v>7300</v>
-      </c>
+      <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="52">
-        <f>8700-SUM(H3:H18)</f>
-        <v>4652</v>
-      </c>
-      <c r="I19" s="52">
-        <f>2000-SUM(I3:I18)</f>
-        <v>500</v>
-      </c>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48"/>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="N19" s="48"/>
-      <c r="O19" s="52">
-        <f>4000-SUM(O3:O18)</f>
-        <v>4000</v>
-      </c>
+      <c r="O19" s="48"/>
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
       <c r="R19" s="48"/>
@@ -5519,15 +5773,15 @@
       <c r="V19" s="48"/>
       <c r="W19" s="48">
         <f t="shared" si="0"/>
-        <v>21847</v>
+        <v>0</v>
       </c>
       <c r="X19" s="49"/>
       <c r="Y19" s="50">
-        <f>X3-SUM(W3:W19)</f>
-        <v>-7962.2200000000012</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+        <f>SUM(X3:X19)-SUM(W3:W19)</f>
+        <v>4652.7799999999988</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="39">
         <v>20</v>
       </c>
@@ -5561,7 +5815,7 @@
       <c r="X20" s="41"/>
       <c r="Y20" s="42"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27">
       <c r="A21" s="47">
         <v>21</v>
       </c>
@@ -5596,7 +5850,7 @@
       <c r="Y21" s="50"/>
       <c r="AA21" s="53"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27">
       <c r="A22" s="47">
         <v>22</v>
       </c>
@@ -5630,7 +5884,7 @@
       <c r="X22" s="49"/>
       <c r="Y22" s="50"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27">
       <c r="A23" s="47">
         <v>23</v>
       </c>
@@ -5664,7 +5918,7 @@
       <c r="X23" s="49"/>
       <c r="Y23" s="50"/>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27">
       <c r="A24" s="47">
         <v>24</v>
       </c>
@@ -5698,7 +5952,7 @@
       <c r="X24" s="49"/>
       <c r="Y24" s="50"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27">
       <c r="A25" s="47">
         <v>25</v>
       </c>
@@ -5732,7 +5986,7 @@
       <c r="X25" s="49"/>
       <c r="Y25" s="50"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27">
       <c r="A26" s="47">
         <v>26</v>
       </c>
@@ -5766,7 +6020,7 @@
       <c r="X26" s="49"/>
       <c r="Y26" s="50"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27">
       <c r="A27" s="47">
         <v>27</v>
       </c>
@@ -5800,7 +6054,7 @@
       <c r="X27" s="49"/>
       <c r="Y27" s="50"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27">
       <c r="A28" s="47">
         <v>28</v>
       </c>
@@ -5834,7 +6088,7 @@
       <c r="X28" s="49"/>
       <c r="Y28" s="50"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27">
       <c r="A29" s="47">
         <v>29</v>
       </c>
@@ -5868,7 +6122,7 @@
       <c r="X29" s="49"/>
       <c r="Y29" s="50"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27">
       <c r="A30" s="47">
         <v>30</v>
       </c>
@@ -5902,7 +6156,7 @@
       <c r="X30" s="49"/>
       <c r="Y30" s="50"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27">
       <c r="A31" s="47">
         <v>1</v>
       </c>
@@ -5936,7 +6190,7 @@
       <c r="X31" s="49"/>
       <c r="Y31" s="50"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27">
       <c r="A32" s="47">
         <v>2</v>
       </c>
@@ -5970,7 +6224,7 @@
       <c r="X32" s="49"/>
       <c r="Y32" s="50"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25">
       <c r="A33" s="47">
         <v>3</v>
       </c>
@@ -6004,27 +6258,56 @@
       <c r="X33" s="49"/>
       <c r="Y33" s="50"/>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25">
       <c r="A34" s="47">
         <v>4</v>
       </c>
       <c r="B34" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
+      <c r="C34" s="52">
+        <v>8850</v>
+      </c>
+      <c r="D34" s="52">
+        <f>SUM(D3:D19)/17*15</f>
+        <v>7365.8823529411766</v>
+      </c>
+      <c r="E34" s="52">
+        <f t="shared" ref="E34:V34" si="1">SUM(E3:E19)/17*15</f>
+        <v>1672.0588235294117</v>
+      </c>
+      <c r="F34" s="52">
+        <f t="shared" si="1"/>
+        <v>2197.0588235294117</v>
+      </c>
+      <c r="G34" s="52">
+        <f t="shared" si="1"/>
+        <v>1985.2941176470588</v>
+      </c>
+      <c r="H34" s="52">
+        <f t="shared" si="1"/>
+        <v>6877.0588235294126</v>
+      </c>
+      <c r="I34" s="52">
+        <f t="shared" si="1"/>
+        <v>2235.8823529411766</v>
+      </c>
       <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
+      <c r="K34" s="52">
+        <f t="shared" si="1"/>
+        <v>6288.7235294117636</v>
+      </c>
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
       <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
+      <c r="O34" s="52">
+        <f t="shared" si="1"/>
+        <v>1679.1176470588234</v>
+      </c>
+      <c r="P34" s="52">
+        <f t="shared" si="1"/>
+        <v>1383.5294117647059</v>
+      </c>
       <c r="Q34" s="48"/>
       <c r="R34" s="48"/>
       <c r="S34" s="48"/>
@@ -6032,75 +6315,75 @@
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(C34:V34)</f>
+        <v>40534.605882352946</v>
       </c>
       <c r="X34" s="49"/>
       <c r="Y34" s="50"/>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25">
       <c r="A35" s="58" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="58"/>
       <c r="C35" s="51">
         <f>SUM(C3:C34)</f>
-        <v>10000</v>
+        <v>18878</v>
       </c>
       <c r="D35" s="51">
-        <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
-        <v>3679</v>
+        <f t="shared" ref="D35:W35" si="2">SUM(D3:D34)</f>
+        <v>15713.882352941177</v>
       </c>
       <c r="E35" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>3567.0588235294117</v>
+      </c>
+      <c r="F35" s="51">
+        <f t="shared" si="2"/>
+        <v>4687.0588235294117</v>
+      </c>
+      <c r="G35" s="51">
+        <f t="shared" si="2"/>
+        <v>4235.2941176470586</v>
+      </c>
+      <c r="H35" s="51">
+        <f t="shared" si="2"/>
+        <v>14671.058823529413</v>
+      </c>
+      <c r="I35" s="51">
+        <f t="shared" si="2"/>
+        <v>4769.8823529411766</v>
+      </c>
+      <c r="J35" s="51">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F35" s="51">
-        <f t="shared" si="1"/>
-        <v>7300</v>
-      </c>
-      <c r="G35" s="51">
-        <f t="shared" si="1"/>
+      <c r="K35" s="51">
+        <f t="shared" si="2"/>
+        <v>13415.943529411763</v>
+      </c>
+      <c r="L35" s="51">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H35" s="51">
-        <f t="shared" si="1"/>
-        <v>8700</v>
-      </c>
-      <c r="I35" s="51">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="J35" s="51">
-        <f t="shared" si="1"/>
+      <c r="M35" s="51">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="51">
-        <f t="shared" si="1"/>
-        <v>13663.22</v>
-      </c>
-      <c r="L35" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="N35" s="51">
-        <f t="shared" si="1"/>
-        <v>5350</v>
+        <f t="shared" si="2"/>
+        <v>8750</v>
       </c>
       <c r="O35" s="51">
-        <f t="shared" si="1"/>
-        <v>4000</v>
+        <f t="shared" si="2"/>
+        <v>3582.1176470588234</v>
       </c>
       <c r="P35" s="51">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2951.5294117647059</v>
       </c>
       <c r="Q35" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26525</v>
       </c>
       <c r="R35" s="51">
@@ -6108,35 +6391,35 @@
         <v>9373</v>
       </c>
       <c r="S35" s="51">
-        <f t="shared" si="1"/>
-        <v>6460</v>
+        <f t="shared" si="2"/>
+        <v>7450</v>
       </c>
       <c r="T35" s="51">
-        <f t="shared" si="1"/>
-        <v>7000</v>
+        <f t="shared" si="2"/>
+        <v>8400</v>
       </c>
       <c r="U35" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1740</v>
       </c>
       <c r="V35" s="51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2860</v>
       </c>
       <c r="W35" s="51">
-        <f t="shared" si="1"/>
-        <v>108650.22</v>
+        <f t="shared" si="2"/>
+        <v>151569.82588235295</v>
       </c>
       <c r="X35" s="49">
         <f>SUM(X3:X29)</f>
-        <v>100688</v>
+        <v>115688</v>
       </c>
       <c r="Y35" s="50">
         <f>X35-W35</f>
-        <v>-7962.2200000000012</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-35881.825882352947</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -6160,9 +6443,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
     <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
@@ -6177,7 +6460,7 @@
     <col min="12" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="59" t="s">
         <v>49</v>
       </c>
@@ -6193,7 +6476,7 @@
       <c r="J1" s="59"/>
       <c r="K1" s="59"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -6225,7 +6508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="18">
         <v>1</v>
       </c>
@@ -6259,7 +6542,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -6293,7 +6576,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -6327,7 +6610,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="18">
         <v>4</v>
       </c>
@@ -6361,7 +6644,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="18">
         <v>5</v>
       </c>
@@ -6395,7 +6678,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="18">
         <v>6</v>
       </c>
@@ -6423,7 +6706,7 @@
         <v>4873</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="18">
         <v>7</v>
       </c>
@@ -6444,7 +6727,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="18">
         <v>8</v>
       </c>
@@ -6465,7 +6748,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="18">
         <v>9</v>
       </c>
@@ -6486,7 +6769,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="18">
         <v>10</v>
       </c>
@@ -6507,7 +6790,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="18">
         <v>11</v>
       </c>
@@ -6528,7 +6811,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="18">
         <v>12</v>
       </c>
@@ -6549,7 +6832,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="18">
         <v>13</v>
       </c>
@@ -6570,7 +6853,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="18">
         <v>14</v>
       </c>
@@ -6591,7 +6874,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="18">
         <v>15</v>
       </c>
@@ -6612,7 +6895,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="18">
         <v>16</v>
       </c>
@@ -6630,7 +6913,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="18">
         <v>17</v>
       </c>
@@ -6648,7 +6931,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="18">
         <v>18</v>
       </c>
@@ -6666,7 +6949,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="18">
         <v>19</v>
       </c>
@@ -6684,7 +6967,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="18">
         <v>20</v>
       </c>
@@ -6702,7 +6985,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="18">
         <v>15</v>
       </c>
@@ -6720,7 +7003,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" s="60" t="s">
         <v>61</v>
       </c>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1302,6 +1302,78 @@
           </rPr>
           <t xml:space="preserve">Гель для душа и журнал
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Додо пицца</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На роллы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Интернет</t>
         </r>
       </text>
     </comment>
@@ -1640,7 +1712,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1719,12 +1791,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1790,7 +1856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1916,9 +1982,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2227,7 +2290,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2244,32 +2307,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -3468,10 +3531,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="55"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3591,32 +3654,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -4827,10 +4890,10 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="56"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -4953,33 +5016,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -5101,16 +5164,16 @@
       <c r="N3" s="40"/>
       <c r="O3" s="40"/>
       <c r="P3" s="40"/>
-      <c r="Q3" s="48">
+      <c r="Q3" s="40">
         <f>22000+3500</f>
         <v>25500</v>
       </c>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48">
+      <c r="R3" s="40"/>
+      <c r="S3" s="40">
         <f>4660+702+799</f>
         <v>6161</v>
       </c>
-      <c r="T3" s="48">
+      <c r="T3" s="40">
         <v>7000</v>
       </c>
       <c r="U3" s="40">
@@ -5175,7 +5238,7 @@
         <v>2860</v>
       </c>
       <c r="W4" s="48">
-        <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
+        <f t="shared" ref="W4:W33" si="0">SUM(C4:V4)</f>
         <v>22822.22</v>
       </c>
       <c r="X4" s="49"/>
@@ -5649,7 +5712,10 @@
       <c r="B16" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="48"/>
+      <c r="C16" s="48">
+        <f>160+263</f>
+        <v>423</v>
+      </c>
       <c r="D16" s="48"/>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
@@ -5666,12 +5732,14 @@
       <c r="Q16" s="48"/>
       <c r="R16" s="48"/>
       <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
+      <c r="T16" s="48">
+        <v>450</v>
+      </c>
       <c r="U16" s="48"/>
       <c r="V16" s="48"/>
       <c r="W16" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>873</v>
       </c>
       <c r="X16" s="49"/>
       <c r="Y16" s="50"/>
@@ -5685,7 +5753,9 @@
       </c>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
+      <c r="E17" s="48">
+        <v>1116</v>
+      </c>
       <c r="F17" s="48"/>
       <c r="G17" s="48"/>
       <c r="H17" s="48"/>
@@ -5695,9 +5765,13 @@
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
       <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
+      <c r="O17" s="48">
+        <v>307</v>
+      </c>
       <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
+      <c r="Q17" s="48">
+        <v>800</v>
+      </c>
       <c r="R17" s="48"/>
       <c r="S17" s="48"/>
       <c r="T17" s="48"/>
@@ -5705,7 +5779,7 @@
       <c r="V17" s="48"/>
       <c r="W17" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2223</v>
       </c>
       <c r="X17" s="49"/>
       <c r="Y17" s="50"/>
@@ -5717,7 +5791,10 @@
       <c r="B18" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="48"/>
+      <c r="C18" s="48">
+        <f>1357.83+470</f>
+        <v>1827.83</v>
+      </c>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
@@ -5729,7 +5806,9 @@
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
-      <c r="O18" s="48"/>
+      <c r="O18" s="48">
+        <v>187</v>
+      </c>
       <c r="P18" s="48"/>
       <c r="Q18" s="48"/>
       <c r="R18" s="48"/>
@@ -5739,7 +5818,7 @@
       <c r="V18" s="48"/>
       <c r="W18" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2014.83</v>
       </c>
       <c r="X18" s="49"/>
       <c r="Y18" s="50"/>
@@ -5767,18 +5846,20 @@
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
       <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
+      <c r="S19" s="48">
+        <v>700</v>
+      </c>
       <c r="T19" s="48"/>
       <c r="U19" s="48"/>
       <c r="V19" s="48"/>
       <c r="W19" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="X19" s="49"/>
       <c r="Y19" s="50">
         <f>SUM(X3:X19)-SUM(W3:W19)</f>
-        <v>4652.7799999999988</v>
+        <v>-1158.0500000000029</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -5848,7 +5929,7 @@
       </c>
       <c r="X21" s="49"/>
       <c r="Y21" s="50"/>
-      <c r="AA21" s="53"/>
+      <c r="AA21" s="52"/>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="47">
@@ -6265,49 +6346,20 @@
       <c r="B34" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="52">
-        <v>8850</v>
-      </c>
-      <c r="D34" s="52">
-        <f>SUM(D3:D19)/17*15</f>
-        <v>7365.8823529411766</v>
-      </c>
-      <c r="E34" s="52">
-        <f t="shared" ref="E34:V34" si="1">SUM(E3:E19)/17*15</f>
-        <v>1672.0588235294117</v>
-      </c>
-      <c r="F34" s="52">
-        <f t="shared" si="1"/>
-        <v>2197.0588235294117</v>
-      </c>
-      <c r="G34" s="52">
-        <f t="shared" si="1"/>
-        <v>1985.2941176470588</v>
-      </c>
-      <c r="H34" s="52">
-        <f t="shared" si="1"/>
-        <v>6877.0588235294126</v>
-      </c>
-      <c r="I34" s="52">
-        <f t="shared" si="1"/>
-        <v>2235.8823529411766</v>
-      </c>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
       <c r="J34" s="48"/>
-      <c r="K34" s="52">
-        <f t="shared" si="1"/>
-        <v>6288.7235294117636</v>
-      </c>
+      <c r="K34" s="48"/>
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
       <c r="N34" s="48"/>
-      <c r="O34" s="52">
-        <f t="shared" si="1"/>
-        <v>1679.1176470588234</v>
-      </c>
-      <c r="P34" s="52">
-        <f t="shared" si="1"/>
-        <v>1383.5294117647059</v>
-      </c>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
       <c r="R34" s="48"/>
       <c r="S34" s="48"/>
@@ -6316,99 +6368,99 @@
       <c r="V34" s="48"/>
       <c r="W34" s="48">
         <f>SUM(C34:V34)</f>
-        <v>40534.605882352946</v>
+        <v>0</v>
       </c>
       <c r="X34" s="49"/>
       <c r="Y34" s="50"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="58" t="s">
+      <c r="A35" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="58"/>
+      <c r="B35" s="57"/>
       <c r="C35" s="51">
         <f>SUM(C3:C34)</f>
-        <v>18878</v>
+        <v>12278.83</v>
       </c>
       <c r="D35" s="51">
-        <f t="shared" ref="D35:W35" si="2">SUM(D3:D34)</f>
-        <v>15713.882352941177</v>
+        <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
+        <v>8348</v>
       </c>
       <c r="E35" s="51">
-        <f t="shared" si="2"/>
-        <v>3567.0588235294117</v>
+        <f t="shared" si="1"/>
+        <v>3011</v>
       </c>
       <c r="F35" s="51">
-        <f t="shared" si="2"/>
-        <v>4687.0588235294117</v>
+        <f t="shared" si="1"/>
+        <v>2490</v>
       </c>
       <c r="G35" s="51">
-        <f t="shared" si="2"/>
-        <v>4235.2941176470586</v>
+        <f t="shared" si="1"/>
+        <v>2250</v>
       </c>
       <c r="H35" s="51">
-        <f t="shared" si="2"/>
-        <v>14671.058823529413</v>
+        <f t="shared" si="1"/>
+        <v>7794</v>
       </c>
       <c r="I35" s="51">
-        <f t="shared" si="2"/>
-        <v>4769.8823529411766</v>
+        <f t="shared" si="1"/>
+        <v>2534</v>
       </c>
       <c r="J35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K35" s="51">
-        <f t="shared" si="2"/>
-        <v>13415.943529411763</v>
+        <f t="shared" si="1"/>
+        <v>7127.2199999999993</v>
       </c>
       <c r="L35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8750</v>
       </c>
       <c r="O35" s="51">
-        <f t="shared" si="2"/>
-        <v>3582.1176470588234</v>
+        <f t="shared" si="1"/>
+        <v>2397</v>
       </c>
       <c r="P35" s="51">
-        <f t="shared" si="2"/>
-        <v>2951.5294117647059</v>
+        <f t="shared" si="1"/>
+        <v>1568</v>
       </c>
       <c r="Q35" s="51">
-        <f t="shared" si="2"/>
-        <v>26525</v>
+        <f t="shared" si="1"/>
+        <v>27325</v>
       </c>
       <c r="R35" s="51">
         <f>SUM(R4:R34)</f>
         <v>9373</v>
       </c>
       <c r="S35" s="51">
-        <f t="shared" si="2"/>
-        <v>7450</v>
+        <f t="shared" si="1"/>
+        <v>8150</v>
       </c>
       <c r="T35" s="51">
-        <f t="shared" si="2"/>
-        <v>8400</v>
+        <f t="shared" si="1"/>
+        <v>8850</v>
       </c>
       <c r="U35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1740</v>
       </c>
       <c r="V35" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2860</v>
       </c>
       <c r="W35" s="51">
-        <f t="shared" si="2"/>
-        <v>151569.82588235295</v>
+        <f t="shared" si="1"/>
+        <v>116846.05</v>
       </c>
       <c r="X35" s="49">
         <f>SUM(X3:X29)</f>
@@ -6416,7 +6468,7 @@
       </c>
       <c r="Y35" s="50">
         <f>X35-W35</f>
-        <v>-35881.825882352947</v>
+        <v>-1158.0500000000029</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -6461,20 +6513,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="G1" s="59" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="G1" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -6695,12 +6747,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -7004,12 +7056,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -729,7 +729,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -738,7 +739,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Наташе на ДР</t>
@@ -753,7 +755,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -762,7 +765,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Подарочные пакеты</t>
@@ -777,7 +781,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -786,7 +791,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Аптека</t>
@@ -811,7 +817,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор
 Пальто + Цветы</t>
@@ -826,7 +833,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -835,7 +843,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Белье + сотовая связь + яндекс плюс
@@ -851,7 +860,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -860,7 +870,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Долг маме + штрафы за парковку
@@ -876,7 +887,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -885,7 +897,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Проиграл маме в теннис</t>
@@ -900,7 +913,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -909,7 +923,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Брекфаст бенд и макдак</t>
@@ -924,7 +939,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -933,7 +949,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 за УК Эталон</t>
@@ -948,7 +965,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -957,7 +975,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Уролог</t>
@@ -972,7 +991,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -981,7 +1001,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Сдек за пальто
@@ -997,7 +1018,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1006,7 +1028,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 На сотовую связь
@@ -1022,7 +1045,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1031,7 +1055,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Плата за 2sub на 3 месяца
@@ -1047,7 +1072,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1056,7 +1082,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Поход в кино</t>
@@ -1071,7 +1098,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1080,7 +1108,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Вино
@@ -1096,7 +1125,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1105,7 +1135,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 вк музыка</t>
@@ -1120,7 +1151,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1129,7 +1161,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Вода и мусор
@@ -1145,7 +1178,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1154,7 +1188,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 ВПН
@@ -1170,7 +1205,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">круасан в пекарне
 </t>
@@ -1185,7 +1221,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1194,7 +1231,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Додо пицца
@@ -1210,7 +1248,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1219,7 +1258,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Мама дала в долг
@@ -1235,7 +1275,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1244,7 +1285,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Подарок от мамы</t>
@@ -1259,7 +1301,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1268,7 +1311,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 КФЦ
@@ -1284,7 +1328,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">ВАФЕЛ
 </t>
@@ -1298,7 +1343,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Гель для душа и журнал
 </t>
@@ -1313,7 +1359,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1322,7 +1369,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Додо пицца</t>
@@ -1337,7 +1385,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1346,7 +1395,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 На роллы</t>
@@ -1361,7 +1411,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1370,10 +1421,91 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Интернет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Белье + сотовая связь
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Книга про стиль</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Журналы ЧТИВО
+</t>
         </r>
       </text>
     </comment>
@@ -1382,7 +1514,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="71">
   <si>
     <t>Число</t>
   </si>
@@ -1588,6 +1720,15 @@
   <si>
     <t>Синабон</t>
   </si>
+  <si>
+    <t>Итоги по ЗП:</t>
+  </si>
+  <si>
+    <t>Итого по Авансу:</t>
+  </si>
+  <si>
+    <t>ИТОГО по месяцу:</t>
+  </si>
 </sst>
 </file>
 
@@ -1699,20 +1840,25 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1791,8 +1937,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1852,11 +2016,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1980,9 +2170,6 @@
     <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1996,9 +2183,6 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2007,6 +2191,28 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2290,7 +2496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2307,32 +2513,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -3531,10 +3737,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="54"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3654,32 +3860,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -4890,10 +5096,10 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="55" t="s">
+      <c r="A32" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="55"/>
+      <c r="B32" s="54"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -5007,7 +5213,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU39"/>
+  <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
@@ -5016,33 +5222,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -5238,7 +5444,7 @@
         <v>2860</v>
       </c>
       <c r="W4" s="48">
-        <f t="shared" ref="W4:W33" si="0">SUM(C4:V4)</f>
+        <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
         <v>22822.22</v>
       </c>
       <c r="X4" s="49"/>
@@ -5857,122 +6063,204 @@
         <v>700</v>
       </c>
       <c r="X19" s="49"/>
-      <c r="Y19" s="50">
-        <f>SUM(X3:X19)-SUM(W3:W19)</f>
+      <c r="Y19" s="50"/>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="60"/>
+      <c r="C20" s="61">
+        <f>SUM(C3:C19)</f>
+        <v>12278.83</v>
+      </c>
+      <c r="D20" s="61">
+        <f t="shared" ref="D20:V20" si="1">SUM(D3:D19)</f>
+        <v>8348</v>
+      </c>
+      <c r="E20" s="61">
+        <f t="shared" si="1"/>
+        <v>3011</v>
+      </c>
+      <c r="F20" s="61">
+        <f t="shared" si="1"/>
+        <v>2490</v>
+      </c>
+      <c r="G20" s="61">
+        <f t="shared" si="1"/>
+        <v>2250</v>
+      </c>
+      <c r="H20" s="61">
+        <f t="shared" si="1"/>
+        <v>7794</v>
+      </c>
+      <c r="I20" s="61">
+        <f t="shared" si="1"/>
+        <v>2534</v>
+      </c>
+      <c r="J20" s="61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="61">
+        <f t="shared" si="1"/>
+        <v>7127.2199999999993</v>
+      </c>
+      <c r="L20" s="61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="61">
+        <f t="shared" si="1"/>
+        <v>8750</v>
+      </c>
+      <c r="O20" s="61">
+        <f t="shared" si="1"/>
+        <v>2397</v>
+      </c>
+      <c r="P20" s="61">
+        <f t="shared" si="1"/>
+        <v>1568</v>
+      </c>
+      <c r="Q20" s="61">
+        <f t="shared" si="1"/>
+        <v>27325</v>
+      </c>
+      <c r="R20" s="61">
+        <f t="shared" si="1"/>
+        <v>9373</v>
+      </c>
+      <c r="S20" s="61">
+        <f t="shared" si="1"/>
+        <v>8150</v>
+      </c>
+      <c r="T20" s="61">
+        <f t="shared" si="1"/>
+        <v>8850</v>
+      </c>
+      <c r="U20" s="61">
+        <f t="shared" si="1"/>
+        <v>1740</v>
+      </c>
+      <c r="V20" s="61">
+        <f t="shared" si="1"/>
+        <v>2860</v>
+      </c>
+      <c r="W20" s="61">
+        <f>SUM(W3:W19)</f>
+        <v>116846.05</v>
+      </c>
+      <c r="X20" s="62">
+        <f>SUM(X3:X19)</f>
+        <v>115688</v>
+      </c>
+      <c r="Y20" s="63">
+        <f>X20-W20</f>
         <v>-1158.0500000000029</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
-      <c r="A20" s="39">
+    <row r="21" spans="1:27">
+      <c r="A21" s="39">
         <v>20</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B21" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="40"/>
-      <c r="U20" s="40"/>
-      <c r="V20" s="40"/>
-      <c r="W20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="42"/>
-    </row>
-    <row r="21" spans="1:27">
-      <c r="A21" s="47">
-        <v>21</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="48"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="48"/>
-      <c r="R21" s="48"/>
-      <c r="S21" s="48"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48"/>
-      <c r="V21" s="48"/>
-      <c r="W21" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="50"/>
-      <c r="AA21" s="52"/>
+      <c r="C21" s="66">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="40">
+        <v>299</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="66">
+        <f>4660+700</f>
+        <v>5360</v>
+      </c>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40">
+        <f t="shared" si="0"/>
+        <v>6659</v>
+      </c>
+      <c r="X21" s="41">
+        <v>36010</v>
+      </c>
+      <c r="Y21" s="42"/>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="47">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="48"/>
+        <v>8</v>
+      </c>
+      <c r="C22" s="66">
+        <v>1000</v>
+      </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48"/>
       <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
+      <c r="G22" s="66">
+        <v>700</v>
+      </c>
       <c r="H22" s="48"/>
       <c r="I22" s="48"/>
       <c r="J22" s="48"/>
       <c r="K22" s="48"/>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
+      <c r="N22" s="66">
+        <v>6000</v>
+      </c>
       <c r="O22" s="48"/>
       <c r="P22" s="48"/>
       <c r="Q22" s="48"/>
       <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48"/>
+      <c r="S22" s="66">
+        <v>500</v>
+      </c>
+      <c r="T22" s="66">
+        <v>1600</v>
+      </c>
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="X22" s="49"/>
       <c r="Y22" s="50"/>
+      <c r="AA22" s="51"/>
     </row>
     <row r="23" spans="1:27">
       <c r="A23" s="47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="48"/>
+        <v>2</v>
+      </c>
+      <c r="C23" s="66">
+        <v>1000</v>
+      </c>
       <c r="D23" s="48"/>
       <c r="E23" s="48"/>
       <c r="F23" s="48"/>
@@ -5984,29 +6272,35 @@
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
       <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
+      <c r="O23" s="66">
+        <v>409</v>
+      </c>
       <c r="P23" s="48"/>
       <c r="Q23" s="48"/>
       <c r="R23" s="48"/>
       <c r="S23" s="48"/>
-      <c r="T23" s="48"/>
+      <c r="T23" s="66">
+        <v>1600</v>
+      </c>
       <c r="U23" s="48"/>
       <c r="V23" s="48"/>
       <c r="W23" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3009</v>
       </c>
       <c r="X23" s="49"/>
       <c r="Y23" s="50"/>
     </row>
     <row r="24" spans="1:27">
       <c r="A24" s="47">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="48"/>
+        <v>3</v>
+      </c>
+      <c r="C24" s="66">
+        <v>1000</v>
+      </c>
       <c r="D24" s="48"/>
       <c r="E24" s="48"/>
       <c r="F24" s="48"/>
@@ -6018,7 +6312,9 @@
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
       <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
+      <c r="O24" s="66">
+        <v>275</v>
+      </c>
       <c r="P24" s="48"/>
       <c r="Q24" s="48"/>
       <c r="R24" s="48"/>
@@ -6028,23 +6324,27 @@
       <c r="V24" s="48"/>
       <c r="W24" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="X24" s="49"/>
       <c r="Y24" s="50"/>
     </row>
     <row r="25" spans="1:27">
       <c r="A25" s="47">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="48"/>
+        <v>4</v>
+      </c>
+      <c r="C25" s="66">
+        <v>1000</v>
+      </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
       <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
+      <c r="G25" s="66">
+        <v>700</v>
+      </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="48"/>
@@ -6052,41 +6352,56 @@
       <c r="L25" s="48"/>
       <c r="M25" s="48"/>
       <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
+      <c r="O25" s="66">
+        <f>302+243</f>
+        <v>545</v>
+      </c>
       <c r="P25" s="48"/>
       <c r="Q25" s="48"/>
       <c r="R25" s="48"/>
-      <c r="S25" s="48"/>
+      <c r="S25" s="66">
+        <v>1000</v>
+      </c>
       <c r="T25" s="48"/>
       <c r="U25" s="48"/>
       <c r="V25" s="48"/>
       <c r="W25" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3245</v>
       </c>
       <c r="X25" s="49"/>
       <c r="Y25" s="50"/>
     </row>
     <row r="26" spans="1:27">
       <c r="A26" s="47">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="48"/>
+        <v>5</v>
+      </c>
+      <c r="C26" s="66">
+        <v>1000</v>
+      </c>
       <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
+      <c r="E26" s="66">
+        <v>2500</v>
+      </c>
       <c r="F26" s="48"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
+      <c r="I26" s="66">
+        <v>1200</v>
+      </c>
       <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
+      <c r="K26" s="66">
+        <v>5000</v>
+      </c>
       <c r="L26" s="48"/>
       <c r="M26" s="48"/>
       <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
+      <c r="O26" s="66">
+        <v>409</v>
+      </c>
       <c r="P26" s="48"/>
       <c r="Q26" s="48"/>
       <c r="R26" s="48"/>
@@ -6096,19 +6411,21 @@
       <c r="V26" s="48"/>
       <c r="W26" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10109</v>
       </c>
       <c r="X26" s="49"/>
       <c r="Y26" s="50"/>
     </row>
     <row r="27" spans="1:27">
       <c r="A27" s="47">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="48"/>
+        <v>6</v>
+      </c>
+      <c r="C27" s="66">
+        <v>1000</v>
+      </c>
       <c r="D27" s="48"/>
       <c r="E27" s="48"/>
       <c r="F27" s="48"/>
@@ -6120,7 +6437,9 @@
       <c r="L27" s="48"/>
       <c r="M27" s="48"/>
       <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
+      <c r="O27" s="66">
+        <v>275</v>
+      </c>
       <c r="P27" s="48"/>
       <c r="Q27" s="48"/>
       <c r="R27" s="48"/>
@@ -6130,19 +6449,21 @@
       <c r="V27" s="48"/>
       <c r="W27" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="X27" s="49"/>
       <c r="Y27" s="50"/>
     </row>
     <row r="28" spans="1:27">
       <c r="A28" s="47">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="48"/>
+        <v>7</v>
+      </c>
+      <c r="C28" s="66">
+        <v>1000</v>
+      </c>
       <c r="D28" s="48"/>
       <c r="E28" s="48"/>
       <c r="F28" s="48"/>
@@ -6154,7 +6475,10 @@
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
+      <c r="O28" s="66">
+        <f>302+243</f>
+        <v>545</v>
+      </c>
       <c r="P28" s="48"/>
       <c r="Q28" s="48"/>
       <c r="R28" s="48"/>
@@ -6164,23 +6488,27 @@
       <c r="V28" s="48"/>
       <c r="W28" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1545</v>
       </c>
       <c r="X28" s="49"/>
       <c r="Y28" s="50"/>
     </row>
     <row r="29" spans="1:27">
       <c r="A29" s="47">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="48"/>
+        <v>8</v>
+      </c>
+      <c r="C29" s="66">
+        <v>1000</v>
+      </c>
       <c r="D29" s="48"/>
       <c r="E29" s="48"/>
       <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
+      <c r="G29" s="66">
+        <v>700</v>
+      </c>
       <c r="H29" s="48"/>
       <c r="I29" s="48"/>
       <c r="J29" s="48"/>
@@ -6189,7 +6517,9 @@
       <c r="M29" s="48"/>
       <c r="N29" s="48"/>
       <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
+      <c r="P29" s="66">
+        <v>1000</v>
+      </c>
       <c r="Q29" s="48"/>
       <c r="R29" s="48"/>
       <c r="S29" s="48"/>
@@ -6198,19 +6528,21 @@
       <c r="V29" s="48"/>
       <c r="W29" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="X29" s="49"/>
       <c r="Y29" s="50"/>
     </row>
     <row r="30" spans="1:27">
       <c r="A30" s="47">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="48"/>
+        <v>2</v>
+      </c>
+      <c r="C30" s="66">
+        <v>1000</v>
+      </c>
       <c r="D30" s="48"/>
       <c r="E30" s="48"/>
       <c r="F30" s="48"/>
@@ -6232,19 +6564,21 @@
       <c r="V30" s="48"/>
       <c r="W30" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X30" s="49"/>
       <c r="Y30" s="50"/>
     </row>
     <row r="31" spans="1:27">
       <c r="A31" s="47">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="48"/>
+        <v>3</v>
+      </c>
+      <c r="C31" s="66">
+        <v>1000</v>
+      </c>
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="48"/>
@@ -6256,7 +6590,9 @@
       <c r="L31" s="48"/>
       <c r="M31" s="48"/>
       <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
+      <c r="O31" s="66">
+        <v>305</v>
+      </c>
       <c r="P31" s="48"/>
       <c r="Q31" s="48"/>
       <c r="R31" s="48"/>
@@ -6266,23 +6602,27 @@
       <c r="V31" s="48"/>
       <c r="W31" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="X31" s="49"/>
       <c r="Y31" s="50"/>
     </row>
     <row r="32" spans="1:27">
       <c r="A32" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="48"/>
+        <v>4</v>
+      </c>
+      <c r="C32" s="66">
+        <v>1000</v>
+      </c>
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
+      <c r="G32" s="66">
+        <v>700</v>
+      </c>
       <c r="H32" s="48"/>
       <c r="I32" s="48"/>
       <c r="J32" s="48"/>
@@ -6290,7 +6630,9 @@
       <c r="L32" s="48"/>
       <c r="M32" s="48"/>
       <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
+      <c r="O32" s="66">
+        <v>369</v>
+      </c>
       <c r="P32" s="48"/>
       <c r="Q32" s="48"/>
       <c r="R32" s="48"/>
@@ -6300,25 +6642,31 @@
       <c r="V32" s="48"/>
       <c r="W32" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2069</v>
       </c>
       <c r="X32" s="49"/>
       <c r="Y32" s="50"/>
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="48"/>
+        <v>5</v>
+      </c>
+      <c r="C33" s="66">
+        <v>1000</v>
+      </c>
       <c r="D33" s="48"/>
       <c r="E33" s="48"/>
       <c r="F33" s="48"/>
       <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
+      <c r="H33" s="66">
+        <v>4000</v>
+      </c>
+      <c r="I33" s="66">
+        <v>1200</v>
+      </c>
       <c r="J33" s="48"/>
       <c r="K33" s="48"/>
       <c r="L33" s="48"/>
@@ -6334,19 +6682,21 @@
       <c r="V33" s="48"/>
       <c r="W33" s="48">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="X33" s="49"/>
       <c r="Y33" s="50"/>
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="48"/>
+        <v>6</v>
+      </c>
+      <c r="C34" s="66">
+        <v>1000</v>
+      </c>
       <c r="D34" s="48"/>
       <c r="E34" s="48"/>
       <c r="F34" s="48"/>
@@ -6358,7 +6708,9 @@
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
       <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
+      <c r="O34" s="66">
+        <v>307</v>
+      </c>
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
       <c r="R34" s="48"/>
@@ -6367,126 +6719,264 @@
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48">
-        <f>SUM(C34:V34)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1307</v>
       </c>
       <c r="X34" s="49"/>
       <c r="Y34" s="50"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="57"/>
-      <c r="C35" s="51">
-        <f>SUM(C3:C34)</f>
-        <v>12278.83</v>
-      </c>
-      <c r="D35" s="51">
-        <f t="shared" ref="D35:W35" si="1">SUM(D3:D34)</f>
-        <v>8348</v>
-      </c>
-      <c r="E35" s="51">
-        <f t="shared" si="1"/>
-        <v>3011</v>
-      </c>
-      <c r="F35" s="51">
-        <f t="shared" si="1"/>
+      <c r="A35" s="47">
+        <v>4</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="66">
+        <v>1000</v>
+      </c>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="66">
+        <v>187</v>
+      </c>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="48"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="48"/>
+      <c r="U35" s="48"/>
+      <c r="V35" s="48"/>
+      <c r="W35" s="48">
+        <f>SUM(C35:V35)</f>
+        <v>1187</v>
+      </c>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="50"/>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="60"/>
+      <c r="C36" s="61">
+        <f>SUM(C21:C35)</f>
+        <v>15000</v>
+      </c>
+      <c r="D36" s="61">
+        <f t="shared" ref="D36:V36" si="2">SUM(D21:D35)</f>
+        <v>299</v>
+      </c>
+      <c r="E36" s="61">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
+      <c r="F36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="61">
+        <f t="shared" si="2"/>
+        <v>2800</v>
+      </c>
+      <c r="H36" s="61">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
+      <c r="I36" s="61">
+        <f t="shared" si="2"/>
+        <v>2400</v>
+      </c>
+      <c r="J36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="61">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="L36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="61">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="O36" s="61">
+        <f t="shared" si="2"/>
+        <v>3626</v>
+      </c>
+      <c r="P36" s="61">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="Q36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="61">
+        <f t="shared" si="2"/>
+        <v>6860</v>
+      </c>
+      <c r="T36" s="61">
+        <f t="shared" si="2"/>
+        <v>3200</v>
+      </c>
+      <c r="U36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="61">
+        <f>SUM(W21:W35)</f>
+        <v>52685</v>
+      </c>
+      <c r="X36" s="62">
+        <f>SUM(X21:X35)</f>
+        <v>36010</v>
+      </c>
+      <c r="Y36" s="63">
+        <f>X36-W36</f>
+        <v>-16675</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="31.5" customHeight="1">
+      <c r="A37" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="64"/>
+      <c r="C37" s="65">
+        <f>SUM(C20,C36)</f>
+        <v>27278.83</v>
+      </c>
+      <c r="D37" s="65">
+        <f t="shared" ref="D37:V37" si="3">SUM(D20,D36)</f>
+        <v>8647</v>
+      </c>
+      <c r="E37" s="65">
+        <f t="shared" si="3"/>
+        <v>5511</v>
+      </c>
+      <c r="F37" s="65">
+        <f t="shared" si="3"/>
         <v>2490</v>
       </c>
-      <c r="G35" s="51">
-        <f t="shared" si="1"/>
-        <v>2250</v>
-      </c>
-      <c r="H35" s="51">
-        <f t="shared" si="1"/>
-        <v>7794</v>
-      </c>
-      <c r="I35" s="51">
-        <f t="shared" si="1"/>
-        <v>2534</v>
-      </c>
-      <c r="J35" s="51">
-        <f t="shared" si="1"/>
+      <c r="G37" s="65">
+        <f t="shared" si="3"/>
+        <v>5050</v>
+      </c>
+      <c r="H37" s="65">
+        <f t="shared" si="3"/>
+        <v>11794</v>
+      </c>
+      <c r="I37" s="65">
+        <f t="shared" si="3"/>
+        <v>4934</v>
+      </c>
+      <c r="J37" s="65">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="51">
-        <f t="shared" si="1"/>
-        <v>7127.2199999999993</v>
-      </c>
-      <c r="L35" s="51">
-        <f t="shared" si="1"/>
+      <c r="K37" s="65">
+        <f t="shared" si="3"/>
+        <v>12127.22</v>
+      </c>
+      <c r="L37" s="65">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="51">
-        <f t="shared" si="1"/>
+      <c r="M37" s="65">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="51">
-        <f t="shared" si="1"/>
-        <v>8750</v>
-      </c>
-      <c r="O35" s="51">
-        <f t="shared" si="1"/>
-        <v>2397</v>
-      </c>
-      <c r="P35" s="51">
-        <f t="shared" si="1"/>
-        <v>1568</v>
-      </c>
-      <c r="Q35" s="51">
-        <f t="shared" si="1"/>
+      <c r="N37" s="65">
+        <f t="shared" si="3"/>
+        <v>14750</v>
+      </c>
+      <c r="O37" s="65">
+        <f t="shared" si="3"/>
+        <v>6023</v>
+      </c>
+      <c r="P37" s="65">
+        <f t="shared" si="3"/>
+        <v>2568</v>
+      </c>
+      <c r="Q37" s="65">
+        <f t="shared" si="3"/>
         <v>27325</v>
       </c>
-      <c r="R35" s="51">
-        <f>SUM(R4:R34)</f>
+      <c r="R37" s="65">
+        <f t="shared" si="3"/>
         <v>9373</v>
       </c>
-      <c r="S35" s="51">
-        <f t="shared" si="1"/>
-        <v>8150</v>
-      </c>
-      <c r="T35" s="51">
-        <f t="shared" si="1"/>
-        <v>8850</v>
-      </c>
-      <c r="U35" s="51">
-        <f t="shared" si="1"/>
+      <c r="S37" s="65">
+        <f t="shared" si="3"/>
+        <v>15010</v>
+      </c>
+      <c r="T37" s="65">
+        <f t="shared" si="3"/>
+        <v>12050</v>
+      </c>
+      <c r="U37" s="65">
+        <f t="shared" si="3"/>
         <v>1740</v>
       </c>
-      <c r="V35" s="51">
-        <f t="shared" si="1"/>
+      <c r="V37" s="65">
+        <f t="shared" si="3"/>
         <v>2860</v>
       </c>
-      <c r="W35" s="51">
-        <f t="shared" si="1"/>
-        <v>116846.05</v>
-      </c>
-      <c r="X35" s="49">
-        <f>SUM(X3:X29)</f>
-        <v>115688</v>
-      </c>
-      <c r="Y35" s="50">
-        <f>X35-W35</f>
-        <v>-1158.0500000000029</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="W37" s="65">
+        <f t="shared" ref="W37" si="4">SUM(W20,W36)</f>
+        <v>169531.05</v>
+      </c>
+      <c r="X37" s="65">
+        <f>SUM(X20,X36)</f>
+        <v>151698</v>
+      </c>
+      <c r="Y37" s="65">
+        <f>SUM(Y20,Y36)</f>
+        <v>-17833.050000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6513,20 +7003,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="G1" s="58" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="G1" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -6747,12 +7237,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G8" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -7056,12 +7546,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="59" t="s">
+      <c r="A24" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1456,7 +1456,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2171,6 +2171,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2183,6 +2196,15 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2191,28 +2213,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2496,7 +2496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2513,32 +2513,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -3737,10 +3737,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="53"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3860,32 +3860,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -5096,10 +5096,10 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="54"/>
+      <c r="B32" s="59"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -5222,33 +5222,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -6066,99 +6066,99 @@
       <c r="Y19" s="50"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="61">
+      <c r="B20" s="63"/>
+      <c r="C20" s="52">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="52">
         <f t="shared" ref="D20:V20" si="1">SUM(D3:D19)</f>
         <v>8348</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="52">
         <f t="shared" si="1"/>
         <v>3011</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="52">
         <f t="shared" si="1"/>
         <v>2490</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="52">
         <f t="shared" si="1"/>
         <v>2250</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="52">
         <f t="shared" si="1"/>
         <v>7794</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="52">
         <f t="shared" si="1"/>
         <v>2534</v>
       </c>
-      <c r="J20" s="61">
+      <c r="J20" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="61">
+      <c r="K20" s="52">
         <f t="shared" si="1"/>
         <v>7127.2199999999993</v>
       </c>
-      <c r="L20" s="61">
+      <c r="L20" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="61">
+      <c r="M20" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="61">
+      <c r="N20" s="52">
         <f t="shared" si="1"/>
         <v>8750</v>
       </c>
-      <c r="O20" s="61">
+      <c r="O20" s="52">
         <f t="shared" si="1"/>
         <v>2397</v>
       </c>
-      <c r="P20" s="61">
+      <c r="P20" s="52">
         <f t="shared" si="1"/>
         <v>1568</v>
       </c>
-      <c r="Q20" s="61">
+      <c r="Q20" s="52">
         <f t="shared" si="1"/>
         <v>27325</v>
       </c>
-      <c r="R20" s="61">
+      <c r="R20" s="52">
         <f t="shared" si="1"/>
         <v>9373</v>
       </c>
-      <c r="S20" s="61">
+      <c r="S20" s="52">
         <f t="shared" si="1"/>
         <v>8150</v>
       </c>
-      <c r="T20" s="61">
+      <c r="T20" s="52">
         <f t="shared" si="1"/>
         <v>8850</v>
       </c>
-      <c r="U20" s="61">
+      <c r="U20" s="52">
         <f t="shared" si="1"/>
         <v>1740</v>
       </c>
-      <c r="V20" s="61">
+      <c r="V20" s="52">
         <f t="shared" si="1"/>
         <v>2860</v>
       </c>
-      <c r="W20" s="61">
+      <c r="W20" s="52">
         <f>SUM(W3:W19)</f>
         <v>116846.05</v>
       </c>
-      <c r="X20" s="62">
+      <c r="X20" s="53">
         <f>SUM(X3:X19)</f>
         <v>115688</v>
       </c>
-      <c r="Y20" s="63">
+      <c r="Y20" s="54">
         <f>X20-W20</f>
         <v>-1158.0500000000029</v>
       </c>
@@ -6170,7 +6170,7 @@
       <c r="B21" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="56">
         <v>1000</v>
       </c>
       <c r="D21" s="40">
@@ -6190,16 +6190,18 @@
       <c r="P21" s="40"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="40"/>
-      <c r="S21" s="66">
-        <f>4660+700</f>
-        <v>5360</v>
-      </c>
-      <c r="T21" s="40"/>
+      <c r="S21" s="40">
+        <f>4660</f>
+        <v>4660</v>
+      </c>
+      <c r="T21" s="40">
+        <v>1634</v>
+      </c>
       <c r="U21" s="40"/>
       <c r="V21" s="40"/>
       <c r="W21" s="40">
         <f t="shared" si="0"/>
-        <v>6659</v>
+        <v>7593</v>
       </c>
       <c r="X21" s="41">
         <v>36010</v>
@@ -6213,13 +6215,13 @@
       <c r="B22" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="56">
         <v>1000</v>
       </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48"/>
       <c r="F22" s="48"/>
-      <c r="G22" s="66">
+      <c r="G22" s="56">
         <v>700</v>
       </c>
       <c r="H22" s="48"/>
@@ -6228,24 +6230,22 @@
       <c r="K22" s="48"/>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
-      <c r="N22" s="66">
+      <c r="N22" s="56">
         <v>6000</v>
       </c>
       <c r="O22" s="48"/>
       <c r="P22" s="48"/>
       <c r="Q22" s="48"/>
       <c r="R22" s="48"/>
-      <c r="S22" s="66">
+      <c r="S22" s="56">
         <v>500</v>
       </c>
-      <c r="T22" s="66">
-        <v>1600</v>
-      </c>
+      <c r="T22" s="48"/>
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="48">
         <f t="shared" si="0"/>
-        <v>9800</v>
+        <v>8200</v>
       </c>
       <c r="X22" s="49"/>
       <c r="Y22" s="50"/>
@@ -6258,7 +6258,7 @@
       <c r="B23" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="66">
+      <c r="C23" s="56">
         <v>1000</v>
       </c>
       <c r="D23" s="48"/>
@@ -6272,14 +6272,14 @@
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
       <c r="N23" s="48"/>
-      <c r="O23" s="66">
+      <c r="O23" s="56">
         <v>409</v>
       </c>
       <c r="P23" s="48"/>
       <c r="Q23" s="48"/>
       <c r="R23" s="48"/>
       <c r="S23" s="48"/>
-      <c r="T23" s="66">
+      <c r="T23" s="56">
         <v>1600</v>
       </c>
       <c r="U23" s="48"/>
@@ -6298,7 +6298,7 @@
       <c r="B24" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="56">
         <v>1000</v>
       </c>
       <c r="D24" s="48"/>
@@ -6312,7 +6312,7 @@
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
       <c r="N24" s="48"/>
-      <c r="O24" s="66">
+      <c r="O24" s="56">
         <v>275</v>
       </c>
       <c r="P24" s="48"/>
@@ -6336,13 +6336,13 @@
       <c r="B25" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="66">
+      <c r="C25" s="56">
         <v>1000</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
       <c r="F25" s="48"/>
-      <c r="G25" s="66">
+      <c r="G25" s="56">
         <v>700</v>
       </c>
       <c r="H25" s="48"/>
@@ -6352,14 +6352,14 @@
       <c r="L25" s="48"/>
       <c r="M25" s="48"/>
       <c r="N25" s="48"/>
-      <c r="O25" s="66">
+      <c r="O25" s="56">
         <f>302+243</f>
         <v>545</v>
       </c>
       <c r="P25" s="48"/>
       <c r="Q25" s="48"/>
       <c r="R25" s="48"/>
-      <c r="S25" s="66">
+      <c r="S25" s="56">
         <v>1000</v>
       </c>
       <c r="T25" s="48"/>
@@ -6379,27 +6379,27 @@
       <c r="B26" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="66">
+      <c r="C26" s="56">
         <v>1000</v>
       </c>
       <c r="D26" s="48"/>
-      <c r="E26" s="66">
+      <c r="E26" s="56">
         <v>2500</v>
       </c>
       <c r="F26" s="48"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
-      <c r="I26" s="66">
+      <c r="I26" s="56">
         <v>1200</v>
       </c>
       <c r="J26" s="48"/>
-      <c r="K26" s="66">
+      <c r="K26" s="56">
         <v>5000</v>
       </c>
       <c r="L26" s="48"/>
       <c r="M26" s="48"/>
       <c r="N26" s="48"/>
-      <c r="O26" s="66">
+      <c r="O26" s="56">
         <v>409</v>
       </c>
       <c r="P26" s="48"/>
@@ -6423,7 +6423,7 @@
       <c r="B27" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="66">
+      <c r="C27" s="56">
         <v>1000</v>
       </c>
       <c r="D27" s="48"/>
@@ -6437,7 +6437,7 @@
       <c r="L27" s="48"/>
       <c r="M27" s="48"/>
       <c r="N27" s="48"/>
-      <c r="O27" s="66">
+      <c r="O27" s="56">
         <v>275</v>
       </c>
       <c r="P27" s="48"/>
@@ -6461,7 +6461,7 @@
       <c r="B28" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="66">
+      <c r="C28" s="56">
         <v>1000</v>
       </c>
       <c r="D28" s="48"/>
@@ -6475,7 +6475,7 @@
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
-      <c r="O28" s="66">
+      <c r="O28" s="56">
         <f>302+243</f>
         <v>545</v>
       </c>
@@ -6500,13 +6500,13 @@
       <c r="B29" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="66">
+      <c r="C29" s="56">
         <v>1000</v>
       </c>
       <c r="D29" s="48"/>
       <c r="E29" s="48"/>
       <c r="F29" s="48"/>
-      <c r="G29" s="66">
+      <c r="G29" s="56">
         <v>700</v>
       </c>
       <c r="H29" s="48"/>
@@ -6517,7 +6517,7 @@
       <c r="M29" s="48"/>
       <c r="N29" s="48"/>
       <c r="O29" s="48"/>
-      <c r="P29" s="66">
+      <c r="P29" s="56">
         <v>1000</v>
       </c>
       <c r="Q29" s="48"/>
@@ -6540,7 +6540,7 @@
       <c r="B30" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="66">
+      <c r="C30" s="56">
         <v>1000</v>
       </c>
       <c r="D30" s="48"/>
@@ -6576,7 +6576,7 @@
       <c r="B31" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="66">
+      <c r="C31" s="56">
         <v>1000</v>
       </c>
       <c r="D31" s="48"/>
@@ -6590,7 +6590,7 @@
       <c r="L31" s="48"/>
       <c r="M31" s="48"/>
       <c r="N31" s="48"/>
-      <c r="O31" s="66">
+      <c r="O31" s="56">
         <v>305</v>
       </c>
       <c r="P31" s="48"/>
@@ -6614,13 +6614,13 @@
       <c r="B32" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="66">
+      <c r="C32" s="56">
         <v>1000</v>
       </c>
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="48"/>
-      <c r="G32" s="66">
+      <c r="G32" s="56">
         <v>700</v>
       </c>
       <c r="H32" s="48"/>
@@ -6630,7 +6630,7 @@
       <c r="L32" s="48"/>
       <c r="M32" s="48"/>
       <c r="N32" s="48"/>
-      <c r="O32" s="66">
+      <c r="O32" s="56">
         <v>369</v>
       </c>
       <c r="P32" s="48"/>
@@ -6654,17 +6654,17 @@
       <c r="B33" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="66">
+      <c r="C33" s="56">
         <v>1000</v>
       </c>
       <c r="D33" s="48"/>
       <c r="E33" s="48"/>
       <c r="F33" s="48"/>
       <c r="G33" s="48"/>
-      <c r="H33" s="66">
+      <c r="H33" s="56">
         <v>4000</v>
       </c>
-      <c r="I33" s="66">
+      <c r="I33" s="56">
         <v>1200</v>
       </c>
       <c r="J33" s="48"/>
@@ -6694,7 +6694,7 @@
       <c r="B34" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="66">
+      <c r="C34" s="56">
         <v>1000</v>
       </c>
       <c r="D34" s="48"/>
@@ -6708,7 +6708,7 @@
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
       <c r="N34" s="48"/>
-      <c r="O34" s="66">
+      <c r="O34" s="56">
         <v>307</v>
       </c>
       <c r="P34" s="48"/>
@@ -6732,7 +6732,7 @@
       <c r="B35" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="66">
+      <c r="C35" s="56">
         <v>1000</v>
       </c>
       <c r="D35" s="48"/>
@@ -6746,7 +6746,7 @@
       <c r="L35" s="48"/>
       <c r="M35" s="48"/>
       <c r="N35" s="48"/>
-      <c r="O35" s="66">
+      <c r="O35" s="56">
         <v>187</v>
       </c>
       <c r="P35" s="48"/>
@@ -6764,199 +6764,199 @@
       <c r="Y35" s="50"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="59" t="s">
+      <c r="A36" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="60"/>
-      <c r="C36" s="61">
+      <c r="B36" s="63"/>
+      <c r="C36" s="52">
         <f>SUM(C21:C35)</f>
         <v>15000</v>
       </c>
-      <c r="D36" s="61">
+      <c r="D36" s="52">
         <f t="shared" ref="D36:V36" si="2">SUM(D21:D35)</f>
         <v>299</v>
       </c>
-      <c r="E36" s="61">
+      <c r="E36" s="52">
         <f t="shared" si="2"/>
         <v>2500</v>
       </c>
-      <c r="F36" s="61">
+      <c r="F36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G36" s="61">
+      <c r="G36" s="52">
         <f t="shared" si="2"/>
         <v>2800</v>
       </c>
-      <c r="H36" s="61">
+      <c r="H36" s="52">
         <f t="shared" si="2"/>
         <v>4000</v>
       </c>
-      <c r="I36" s="61">
+      <c r="I36" s="52">
         <f t="shared" si="2"/>
         <v>2400</v>
       </c>
-      <c r="J36" s="61">
+      <c r="J36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="61">
+      <c r="K36" s="52">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="L36" s="61">
+      <c r="L36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M36" s="61">
+      <c r="M36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N36" s="61">
+      <c r="N36" s="52">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="O36" s="61">
+      <c r="O36" s="52">
         <f t="shared" si="2"/>
         <v>3626</v>
       </c>
-      <c r="P36" s="61">
+      <c r="P36" s="52">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="Q36" s="61">
+      <c r="Q36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R36" s="61">
+      <c r="R36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S36" s="61">
+      <c r="S36" s="52">
         <f t="shared" si="2"/>
-        <v>6860</v>
-      </c>
-      <c r="T36" s="61">
-        <f t="shared" si="2"/>
-        <v>3200</v>
-      </c>
-      <c r="U36" s="61">
+        <v>6160</v>
+      </c>
+      <c r="T36" s="52">
+        <f>SUM(T21:T35)</f>
+        <v>3234</v>
+      </c>
+      <c r="U36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V36" s="61">
+      <c r="V36" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W36" s="61">
+      <c r="W36" s="52">
         <f>SUM(W21:W35)</f>
-        <v>52685</v>
-      </c>
-      <c r="X36" s="62">
+        <v>52019</v>
+      </c>
+      <c r="X36" s="53">
         <f>SUM(X21:X35)</f>
         <v>36010</v>
       </c>
-      <c r="Y36" s="63">
+      <c r="Y36" s="54">
         <f>X36-W36</f>
-        <v>-16675</v>
+        <v>-16009</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="64" t="s">
+      <c r="A37" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65">
+      <c r="B37" s="61"/>
+      <c r="C37" s="55">
         <f>SUM(C20,C36)</f>
         <v>27278.83</v>
       </c>
-      <c r="D37" s="65">
+      <c r="D37" s="55">
         <f t="shared" ref="D37:V37" si="3">SUM(D20,D36)</f>
         <v>8647</v>
       </c>
-      <c r="E37" s="65">
+      <c r="E37" s="55">
         <f t="shared" si="3"/>
         <v>5511</v>
       </c>
-      <c r="F37" s="65">
+      <c r="F37" s="55">
         <f t="shared" si="3"/>
         <v>2490</v>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="55">
         <f t="shared" si="3"/>
         <v>5050</v>
       </c>
-      <c r="H37" s="65">
+      <c r="H37" s="55">
         <f t="shared" si="3"/>
         <v>11794</v>
       </c>
-      <c r="I37" s="65">
+      <c r="I37" s="55">
         <f t="shared" si="3"/>
         <v>4934</v>
       </c>
-      <c r="J37" s="65">
+      <c r="J37" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="65">
+      <c r="K37" s="55">
         <f t="shared" si="3"/>
         <v>12127.22</v>
       </c>
-      <c r="L37" s="65">
+      <c r="L37" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M37" s="65">
+      <c r="M37" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N37" s="65">
+      <c r="N37" s="55">
         <f t="shared" si="3"/>
         <v>14750</v>
       </c>
-      <c r="O37" s="65">
+      <c r="O37" s="55">
         <f t="shared" si="3"/>
         <v>6023</v>
       </c>
-      <c r="P37" s="65">
+      <c r="P37" s="55">
         <f t="shared" si="3"/>
         <v>2568</v>
       </c>
-      <c r="Q37" s="65">
+      <c r="Q37" s="55">
         <f t="shared" si="3"/>
         <v>27325</v>
       </c>
-      <c r="R37" s="65">
+      <c r="R37" s="55">
         <f t="shared" si="3"/>
         <v>9373</v>
       </c>
-      <c r="S37" s="65">
+      <c r="S37" s="55">
         <f t="shared" si="3"/>
-        <v>15010</v>
-      </c>
-      <c r="T37" s="65">
+        <v>14310</v>
+      </c>
+      <c r="T37" s="55">
         <f t="shared" si="3"/>
-        <v>12050</v>
-      </c>
-      <c r="U37" s="65">
+        <v>12084</v>
+      </c>
+      <c r="U37" s="55">
         <f t="shared" si="3"/>
         <v>1740</v>
       </c>
-      <c r="V37" s="65">
+      <c r="V37" s="55">
         <f t="shared" si="3"/>
         <v>2860</v>
       </c>
-      <c r="W37" s="65">
+      <c r="W37" s="55">
         <f t="shared" ref="W37" si="4">SUM(W20,W36)</f>
-        <v>169531.05</v>
-      </c>
-      <c r="X37" s="65">
+        <v>168865.05</v>
+      </c>
+      <c r="X37" s="55">
         <f>SUM(X20,X36)</f>
         <v>151698</v>
       </c>
-      <c r="Y37" s="65">
+      <c r="Y37" s="55">
         <f>SUM(Y20,Y36)</f>
-        <v>-17833.050000000003</v>
+        <v>-17167.050000000003</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -7003,20 +7003,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="G1" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -7237,12 +7237,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -7546,12 +7546,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1482,7 +1482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T23" authorId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1504,8 +1504,210 @@
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
-Журналы ЧТИВО
+Промясо</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Журналы Чтиво и Книга про вино</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Поке
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Поке
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+До-до пицца
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Лапшичка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
         </r>
       </text>
     </comment>
@@ -1737,7 +1939,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1857,8 +2059,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1946,12 +2154,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2046,7 +2248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2179,9 +2381,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2496,7 +2695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2513,32 +2712,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -3737,10 +3936,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="58" t="s">
+      <c r="A31" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="57"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -3860,32 +4059,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -5096,10 +5295,10 @@
       <c r="X31" s="38"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="59"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="35">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -5222,33 +5421,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="37" t="s">
@@ -6066,10 +6265,10 @@
       <c r="Y19" s="50"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="63"/>
+      <c r="B20" s="62"/>
       <c r="C20" s="52">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -6170,8 +6369,8 @@
       <c r="B21" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="56">
-        <v>1000</v>
+      <c r="C21" s="40">
+        <v>2409</v>
       </c>
       <c r="D21" s="40">
         <v>299</v>
@@ -6186,7 +6385,9 @@
       <c r="L21" s="40"/>
       <c r="M21" s="40"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
+      <c r="O21" s="40">
+        <v>187</v>
+      </c>
       <c r="P21" s="40"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="40"/>
@@ -6201,7 +6402,7 @@
       <c r="V21" s="40"/>
       <c r="W21" s="40">
         <f t="shared" si="0"/>
-        <v>7593</v>
+        <v>9189</v>
       </c>
       <c r="X21" s="41">
         <v>36010</v>
@@ -6215,37 +6416,39 @@
       <c r="B22" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="56">
-        <v>1000</v>
+      <c r="C22" s="48">
+        <v>374</v>
       </c>
       <c r="D22" s="48"/>
       <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="56">
-        <v>700</v>
-      </c>
-      <c r="H22" s="48"/>
+      <c r="F22" s="48">
+        <v>1080</v>
+      </c>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48">
+        <v>572</v>
+      </c>
       <c r="I22" s="48"/>
       <c r="J22" s="48"/>
       <c r="K22" s="48"/>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
-      <c r="N22" s="56">
-        <v>6000</v>
-      </c>
-      <c r="O22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48">
+        <v>215</v>
+      </c>
       <c r="P22" s="48"/>
       <c r="Q22" s="48"/>
       <c r="R22" s="48"/>
-      <c r="S22" s="56">
-        <v>500</v>
-      </c>
-      <c r="T22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48">
+        <v>3700</v>
+      </c>
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="48">
         <f t="shared" si="0"/>
-        <v>8200</v>
+        <v>5941</v>
       </c>
       <c r="X22" s="49"/>
       <c r="Y22" s="50"/>
@@ -6258,13 +6461,15 @@
       <c r="B23" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="56">
-        <v>1000</v>
+      <c r="C23" s="48">
+        <v>1027.8900000000001</v>
       </c>
       <c r="D23" s="48"/>
       <c r="E23" s="48"/>
       <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
+      <c r="G23" s="48">
+        <v>835</v>
+      </c>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
       <c r="J23" s="48"/>
@@ -6272,21 +6477,19 @@
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
       <c r="N23" s="48"/>
-      <c r="O23" s="56">
-        <v>409</v>
+      <c r="O23" s="48">
+        <v>265</v>
       </c>
       <c r="P23" s="48"/>
       <c r="Q23" s="48"/>
       <c r="R23" s="48"/>
       <c r="S23" s="48"/>
-      <c r="T23" s="56">
-        <v>1600</v>
-      </c>
+      <c r="T23" s="48"/>
       <c r="U23" s="48"/>
       <c r="V23" s="48"/>
       <c r="W23" s="48">
         <f t="shared" si="0"/>
-        <v>3009</v>
+        <v>2127.8900000000003</v>
       </c>
       <c r="X23" s="49"/>
       <c r="Y23" s="50"/>
@@ -6298,11 +6501,11 @@
       <c r="B24" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C24" s="48"/>
       <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
+      <c r="E24" s="48">
+        <v>1344</v>
+      </c>
       <c r="F24" s="48"/>
       <c r="G24" s="48"/>
       <c r="H24" s="48"/>
@@ -6312,11 +6515,13 @@
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
       <c r="N24" s="48"/>
-      <c r="O24" s="56">
-        <v>275</v>
+      <c r="O24" s="48">
+        <v>349</v>
       </c>
       <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
+      <c r="Q24" s="48">
+        <v>1000</v>
+      </c>
       <c r="R24" s="48"/>
       <c r="S24" s="48"/>
       <c r="T24" s="48"/>
@@ -6324,7 +6529,7 @@
       <c r="V24" s="48"/>
       <c r="W24" s="48">
         <f t="shared" si="0"/>
-        <v>1275</v>
+        <v>2693</v>
       </c>
       <c r="X24" s="49"/>
       <c r="Y24" s="50"/>
@@ -6336,15 +6541,15 @@
       <c r="B25" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="56">
-        <v>1000</v>
+      <c r="C25" s="48">
+        <v>1755</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="56">
-        <v>700</v>
-      </c>
+      <c r="F25" s="48">
+        <v>1331</v>
+      </c>
+      <c r="G25" s="48"/>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="48"/>
@@ -6352,22 +6557,21 @@
       <c r="L25" s="48"/>
       <c r="M25" s="48"/>
       <c r="N25" s="48"/>
-      <c r="O25" s="56">
-        <f>302+243</f>
-        <v>545</v>
+      <c r="O25" s="48">
+        <v>180</v>
       </c>
       <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
+      <c r="Q25" s="48">
+        <v>500</v>
+      </c>
       <c r="R25" s="48"/>
-      <c r="S25" s="56">
-        <v>1000</v>
-      </c>
+      <c r="S25" s="48"/>
       <c r="T25" s="48"/>
       <c r="U25" s="48"/>
       <c r="V25" s="48"/>
       <c r="W25" s="48">
         <f t="shared" si="0"/>
-        <v>3245</v>
+        <v>3766</v>
       </c>
       <c r="X25" s="49"/>
       <c r="Y25" s="50"/>
@@ -6379,31 +6583,29 @@
       <c r="B26" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="56">
-        <v>2500</v>
-      </c>
+      <c r="C26" s="48">
+        <v>525</v>
+      </c>
+      <c r="D26" s="48">
+        <v>1326</v>
+      </c>
+      <c r="E26" s="48"/>
       <c r="F26" s="48"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
-      <c r="I26" s="56">
-        <v>1200</v>
-      </c>
+      <c r="I26" s="48"/>
       <c r="J26" s="48"/>
-      <c r="K26" s="56">
-        <v>5000</v>
-      </c>
+      <c r="K26" s="48"/>
       <c r="L26" s="48"/>
       <c r="M26" s="48"/>
       <c r="N26" s="48"/>
-      <c r="O26" s="56">
-        <v>409</v>
+      <c r="O26" s="48">
+        <v>251</v>
       </c>
       <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
+      <c r="Q26" s="48">
+        <v>300</v>
+      </c>
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
       <c r="T26" s="48"/>
@@ -6411,7 +6613,7 @@
       <c r="V26" s="48"/>
       <c r="W26" s="48">
         <f t="shared" si="0"/>
-        <v>10109</v>
+        <v>2402</v>
       </c>
       <c r="X26" s="49"/>
       <c r="Y26" s="50"/>
@@ -6423,11 +6625,13 @@
       <c r="B27" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48">
+        <v>2161</v>
+      </c>
+      <c r="E27" s="48">
+        <v>1336</v>
+      </c>
       <c r="F27" s="48"/>
       <c r="G27" s="48"/>
       <c r="H27" s="48"/>
@@ -6437,11 +6641,11 @@
       <c r="L27" s="48"/>
       <c r="M27" s="48"/>
       <c r="N27" s="48"/>
-      <c r="O27" s="56">
-        <v>275</v>
-      </c>
+      <c r="O27" s="48"/>
       <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
+      <c r="Q27" s="48">
+        <v>151</v>
+      </c>
       <c r="R27" s="48"/>
       <c r="S27" s="48"/>
       <c r="T27" s="48"/>
@@ -6449,7 +6653,7 @@
       <c r="V27" s="48"/>
       <c r="W27" s="48">
         <f t="shared" si="0"/>
-        <v>1275</v>
+        <v>3648</v>
       </c>
       <c r="X27" s="49"/>
       <c r="Y27" s="50"/>
@@ -6461,10 +6665,10 @@
       <c r="B28" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48">
+        <v>1417</v>
+      </c>
       <c r="E28" s="48"/>
       <c r="F28" s="48"/>
       <c r="G28" s="48"/>
@@ -6475,9 +6679,9 @@
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
       <c r="N28" s="48"/>
-      <c r="O28" s="56">
-        <f>302+243</f>
-        <v>545</v>
+      <c r="O28" s="48">
+        <f>677+345</f>
+        <v>1022</v>
       </c>
       <c r="P28" s="48"/>
       <c r="Q28" s="48"/>
@@ -6488,7 +6692,7 @@
       <c r="V28" s="48"/>
       <c r="W28" s="48">
         <f t="shared" si="0"/>
-        <v>1545</v>
+        <v>2439</v>
       </c>
       <c r="X28" s="49"/>
       <c r="Y28" s="50"/>
@@ -6500,35 +6704,40 @@
       <c r="B29" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48">
+        <v>1796</v>
+      </c>
       <c r="E29" s="48"/>
       <c r="F29" s="48"/>
-      <c r="G29" s="56">
-        <v>700</v>
-      </c>
-      <c r="H29" s="48"/>
+      <c r="G29" s="48">
+        <v>485</v>
+      </c>
+      <c r="H29" s="48">
+        <v>1360</v>
+      </c>
       <c r="I29" s="48"/>
       <c r="J29" s="48"/>
       <c r="K29" s="48"/>
       <c r="L29" s="48"/>
       <c r="M29" s="48"/>
       <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="56">
-        <v>1000</v>
-      </c>
+      <c r="O29" s="48">
+        <f>319+442</f>
+        <v>761</v>
+      </c>
+      <c r="P29" s="48"/>
       <c r="Q29" s="48"/>
       <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
+      <c r="S29" s="48">
+        <v>249</v>
+      </c>
       <c r="T29" s="48"/>
       <c r="U29" s="48"/>
       <c r="V29" s="48"/>
       <c r="W29" s="48">
         <f t="shared" si="0"/>
-        <v>2700</v>
+        <v>4651</v>
       </c>
       <c r="X29" s="49"/>
       <c r="Y29" s="50"/>
@@ -6540,12 +6749,12 @@
       <c r="B30" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C30" s="48"/>
       <c r="D30" s="48"/>
       <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
+      <c r="F30" s="48">
+        <v>614</v>
+      </c>
       <c r="G30" s="48"/>
       <c r="H30" s="48"/>
       <c r="I30" s="48"/>
@@ -6554,7 +6763,9 @@
       <c r="L30" s="48"/>
       <c r="M30" s="48"/>
       <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
+      <c r="O30" s="48">
+        <v>207</v>
+      </c>
       <c r="P30" s="48"/>
       <c r="Q30" s="48"/>
       <c r="R30" s="48"/>
@@ -6564,7 +6775,7 @@
       <c r="V30" s="48"/>
       <c r="W30" s="48">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>821</v>
       </c>
       <c r="X30" s="49"/>
       <c r="Y30" s="50"/>
@@ -6576,9 +6787,7 @@
       <c r="B31" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C31" s="48"/>
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="48"/>
@@ -6590,9 +6799,7 @@
       <c r="L31" s="48"/>
       <c r="M31" s="48"/>
       <c r="N31" s="48"/>
-      <c r="O31" s="56">
-        <v>305</v>
-      </c>
+      <c r="O31" s="48"/>
       <c r="P31" s="48"/>
       <c r="Q31" s="48"/>
       <c r="R31" s="48"/>
@@ -6602,7 +6809,7 @@
       <c r="V31" s="48"/>
       <c r="W31" s="48">
         <f t="shared" si="0"/>
-        <v>1305</v>
+        <v>0</v>
       </c>
       <c r="X31" s="49"/>
       <c r="Y31" s="50"/>
@@ -6614,15 +6821,11 @@
       <c r="B32" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C32" s="48"/>
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="48"/>
-      <c r="G32" s="56">
-        <v>700</v>
-      </c>
+      <c r="G32" s="48"/>
       <c r="H32" s="48"/>
       <c r="I32" s="48"/>
       <c r="J32" s="48"/>
@@ -6630,9 +6833,7 @@
       <c r="L32" s="48"/>
       <c r="M32" s="48"/>
       <c r="N32" s="48"/>
-      <c r="O32" s="56">
-        <v>369</v>
-      </c>
+      <c r="O32" s="48"/>
       <c r="P32" s="48"/>
       <c r="Q32" s="48"/>
       <c r="R32" s="48"/>
@@ -6642,7 +6843,7 @@
       <c r="V32" s="48"/>
       <c r="W32" s="48">
         <f t="shared" si="0"/>
-        <v>2069</v>
+        <v>0</v>
       </c>
       <c r="X32" s="49"/>
       <c r="Y32" s="50"/>
@@ -6654,19 +6855,13 @@
       <c r="B33" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C33" s="48"/>
       <c r="D33" s="48"/>
       <c r="E33" s="48"/>
       <c r="F33" s="48"/>
       <c r="G33" s="48"/>
-      <c r="H33" s="56">
-        <v>4000</v>
-      </c>
-      <c r="I33" s="56">
-        <v>1200</v>
-      </c>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
       <c r="J33" s="48"/>
       <c r="K33" s="48"/>
       <c r="L33" s="48"/>
@@ -6682,7 +6877,7 @@
       <c r="V33" s="48"/>
       <c r="W33" s="48">
         <f t="shared" si="0"/>
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="X33" s="49"/>
       <c r="Y33" s="50"/>
@@ -6694,9 +6889,7 @@
       <c r="B34" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C34" s="48"/>
       <c r="D34" s="48"/>
       <c r="E34" s="48"/>
       <c r="F34" s="48"/>
@@ -6708,9 +6901,7 @@
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
       <c r="N34" s="48"/>
-      <c r="O34" s="56">
-        <v>307</v>
-      </c>
+      <c r="O34" s="48"/>
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
       <c r="R34" s="48"/>
@@ -6720,7 +6911,7 @@
       <c r="V34" s="48"/>
       <c r="W34" s="48">
         <f t="shared" si="0"/>
-        <v>1307</v>
+        <v>0</v>
       </c>
       <c r="X34" s="49"/>
       <c r="Y34" s="50"/>
@@ -6732,9 +6923,7 @@
       <c r="B35" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="56">
-        <v>1000</v>
-      </c>
+      <c r="C35" s="48"/>
       <c r="D35" s="48"/>
       <c r="E35" s="48"/>
       <c r="F35" s="48"/>
@@ -6746,9 +6935,7 @@
       <c r="L35" s="48"/>
       <c r="M35" s="48"/>
       <c r="N35" s="48"/>
-      <c r="O35" s="56">
-        <v>187</v>
-      </c>
+      <c r="O35" s="48"/>
       <c r="P35" s="48"/>
       <c r="Q35" s="48"/>
       <c r="R35" s="48"/>
@@ -6758,43 +6945,43 @@
       <c r="V35" s="48"/>
       <c r="W35" s="48">
         <f>SUM(C35:V35)</f>
-        <v>1187</v>
+        <v>0</v>
       </c>
       <c r="X35" s="49"/>
       <c r="Y35" s="50"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="63"/>
+      <c r="B36" s="62"/>
       <c r="C36" s="52">
         <f>SUM(C21:C35)</f>
-        <v>15000</v>
+        <v>6090.89</v>
       </c>
       <c r="D36" s="52">
         <f t="shared" ref="D36:V36" si="2">SUM(D21:D35)</f>
-        <v>299</v>
+        <v>6999</v>
       </c>
       <c r="E36" s="52">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>2680</v>
       </c>
       <c r="F36" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3025</v>
       </c>
       <c r="G36" s="52">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>1320</v>
       </c>
       <c r="H36" s="52">
         <f t="shared" si="2"/>
-        <v>4000</v>
+        <v>1932</v>
       </c>
       <c r="I36" s="52">
         <f t="shared" si="2"/>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J36" s="52">
         <f t="shared" si="2"/>
@@ -6802,7 +6989,7 @@
       </c>
       <c r="K36" s="52">
         <f t="shared" si="2"/>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L36" s="52">
         <f t="shared" si="2"/>
@@ -6814,19 +7001,19 @@
       </c>
       <c r="N36" s="52">
         <f t="shared" si="2"/>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="O36" s="52">
         <f t="shared" si="2"/>
-        <v>3626</v>
+        <v>3437</v>
       </c>
       <c r="P36" s="52">
         <f t="shared" si="2"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1951</v>
       </c>
       <c r="R36" s="52">
         <f t="shared" si="2"/>
@@ -6834,11 +7021,11 @@
       </c>
       <c r="S36" s="52">
         <f t="shared" si="2"/>
-        <v>6160</v>
+        <v>4909</v>
       </c>
       <c r="T36" s="52">
         <f>SUM(T21:T35)</f>
-        <v>3234</v>
+        <v>5334</v>
       </c>
       <c r="U36" s="52">
         <f t="shared" si="2"/>
@@ -6850,7 +7037,7 @@
       </c>
       <c r="W36" s="52">
         <f>SUM(W21:W35)</f>
-        <v>52019</v>
+        <v>37677.89</v>
       </c>
       <c r="X36" s="53">
         <f>SUM(X21:X35)</f>
@@ -6858,41 +7045,41 @@
       </c>
       <c r="Y36" s="54">
         <f>X36-W36</f>
-        <v>-16009</v>
+        <v>-1667.8899999999994</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="61" t="s">
+      <c r="A37" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="61"/>
+      <c r="B37" s="60"/>
       <c r="C37" s="55">
         <f>SUM(C20,C36)</f>
-        <v>27278.83</v>
+        <v>18369.72</v>
       </c>
       <c r="D37" s="55">
         <f t="shared" ref="D37:V37" si="3">SUM(D20,D36)</f>
-        <v>8647</v>
+        <v>15347</v>
       </c>
       <c r="E37" s="55">
         <f t="shared" si="3"/>
-        <v>5511</v>
+        <v>5691</v>
       </c>
       <c r="F37" s="55">
         <f t="shared" si="3"/>
-        <v>2490</v>
+        <v>5515</v>
       </c>
       <c r="G37" s="55">
         <f t="shared" si="3"/>
-        <v>5050</v>
+        <v>3570</v>
       </c>
       <c r="H37" s="55">
         <f t="shared" si="3"/>
-        <v>11794</v>
+        <v>9726</v>
       </c>
       <c r="I37" s="55">
         <f t="shared" si="3"/>
-        <v>4934</v>
+        <v>2534</v>
       </c>
       <c r="J37" s="55">
         <f t="shared" si="3"/>
@@ -6900,7 +7087,7 @@
       </c>
       <c r="K37" s="55">
         <f t="shared" si="3"/>
-        <v>12127.22</v>
+        <v>7127.2199999999993</v>
       </c>
       <c r="L37" s="55">
         <f t="shared" si="3"/>
@@ -6912,31 +7099,31 @@
       </c>
       <c r="N37" s="55">
         <f t="shared" si="3"/>
-        <v>14750</v>
+        <v>8750</v>
       </c>
       <c r="O37" s="55">
         <f t="shared" si="3"/>
-        <v>6023</v>
+        <v>5834</v>
       </c>
       <c r="P37" s="55">
         <f t="shared" si="3"/>
-        <v>2568</v>
+        <v>1568</v>
       </c>
       <c r="Q37" s="55">
         <f t="shared" si="3"/>
-        <v>27325</v>
+        <v>29276</v>
       </c>
       <c r="R37" s="55">
         <f t="shared" si="3"/>
         <v>9373</v>
       </c>
       <c r="S37" s="55">
-        <f t="shared" si="3"/>
-        <v>14310</v>
+        <f>SUM(S20,S36)</f>
+        <v>13059</v>
       </c>
       <c r="T37" s="55">
         <f t="shared" si="3"/>
-        <v>12084</v>
+        <v>14184</v>
       </c>
       <c r="U37" s="55">
         <f t="shared" si="3"/>
@@ -6948,7 +7135,7 @@
       </c>
       <c r="W37" s="55">
         <f t="shared" ref="W37" si="4">SUM(W20,W36)</f>
-        <v>168865.05</v>
+        <v>154523.94</v>
       </c>
       <c r="X37" s="55">
         <f>SUM(X20,X36)</f>
@@ -6956,7 +7143,7 @@
       </c>
       <c r="Y37" s="55">
         <f>SUM(Y20,Y36)</f>
-        <v>-17167.050000000003</v>
+        <v>-2825.9400000000023</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -7003,20 +7190,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="G1" s="64" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="G1" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
@@ -7237,12 +7424,12 @@
         <f t="shared" si="0"/>
         <v>193</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
       <c r="K8" s="20">
         <f>SUM(K3:K7)</f>
         <v>4873</v>
@@ -7546,12 +7733,12 @@
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
       <c r="E24" s="20">
         <f>SUM(E3:E23)</f>
         <v>6908</v>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Февраль 2026" sheetId="3" r:id="rId1"/>
-    <sheet name="Март 2026" sheetId="1" r:id="rId2"/>
-    <sheet name="Апрель 2026" sheetId="4" r:id="rId3"/>
-    <sheet name="Лист1" sheetId="2" r:id="rId4"/>
+    <sheet name="Сводная" sheetId="5" r:id="rId1"/>
+    <sheet name="Февраль 2026" sheetId="3" r:id="rId2"/>
+    <sheet name="Март 2026" sheetId="1" r:id="rId3"/>
+    <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
+    <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -1711,12 +1712,171 @@
         </r>
       </text>
     </comment>
+    <comment ref="X30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+В долг у бати</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Брэкфаст бенд</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+в долг у мамы</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="S3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вк музыка, белье, сотовая связь</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Долг маме
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="57">
   <si>
     <t>Число</t>
   </si>
@@ -1803,106 +1963,7 @@
     <t>Доходы - Расходы Февраль 2026</t>
   </si>
   <si>
-    <t>Наименование</t>
-  </si>
-  <si>
-    <t>Количество</t>
-  </si>
-  <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>Всего по позиции</t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Курица</t>
-  </si>
-  <si>
-    <t>Яйца</t>
-  </si>
-  <si>
-    <t>Пшено</t>
-  </si>
-  <si>
-    <t>Йогурт</t>
-  </si>
-  <si>
-    <t>Ветчина</t>
-  </si>
-  <si>
-    <t>Авокадо</t>
-  </si>
-  <si>
-    <t>Хлеб</t>
-  </si>
-  <si>
-    <t>Сливки</t>
-  </si>
-  <si>
-    <t>Сыр Пармезан</t>
-  </si>
-  <si>
-    <t>Сыр Чеддер</t>
-  </si>
-  <si>
-    <t>Томаты в собственном соку</t>
-  </si>
-  <si>
-    <t>Булгур</t>
-  </si>
-  <si>
-    <t>Рис</t>
-  </si>
-  <si>
-    <t>Макароны</t>
-  </si>
-  <si>
-    <t>Киноа</t>
-  </si>
-  <si>
-    <t>Сыр творожный</t>
-  </si>
-  <si>
-    <t>Базовая корзина (на 3 дня)</t>
-  </si>
-  <si>
-    <t>Доп. корзина  (на 7 дней)</t>
-  </si>
-  <si>
-    <t>Булдак</t>
-  </si>
-  <si>
-    <t>Непредвиденные</t>
-  </si>
-  <si>
-    <t>Молоко</t>
-  </si>
-  <si>
-    <t>Масло</t>
-  </si>
-  <si>
-    <t>Лимон</t>
-  </si>
-  <si>
-    <t>Вино</t>
-  </si>
-  <si>
-    <t>Мишутка</t>
-  </si>
-  <si>
-    <t>Шоколадка</t>
-  </si>
-  <si>
-    <t>Вода</t>
-  </si>
-  <si>
     <t>Аня</t>
-  </si>
-  <si>
-    <t>Итого</t>
   </si>
   <si>
     <t>Вкус Вилл</t>
@@ -1931,6 +1992,63 @@
   <si>
     <t>ИТОГО по месяцу:</t>
   </si>
+  <si>
+    <t>Доходы - Расходы Апрель 2026</t>
+  </si>
+  <si>
+    <t>ЗП</t>
+  </si>
+  <si>
+    <t>Занял</t>
+  </si>
+  <si>
+    <t>Расходы</t>
+  </si>
+  <si>
+    <t>Месяц</t>
+  </si>
+  <si>
+    <t>Январь</t>
+  </si>
+  <si>
+    <t>Февраль</t>
+  </si>
+  <si>
+    <t>Март</t>
+  </si>
+  <si>
+    <t>Апрель</t>
+  </si>
+  <si>
+    <t>Май</t>
+  </si>
+  <si>
+    <t>Июнь</t>
+  </si>
+  <si>
+    <t>Июль</t>
+  </si>
+  <si>
+    <t>Август</t>
+  </si>
+  <si>
+    <t>Сентябрь</t>
+  </si>
+  <si>
+    <t>Октябрь</t>
+  </si>
+  <si>
+    <t>Ноябрь</t>
+  </si>
+  <si>
+    <t>Декабрь</t>
+  </si>
+  <si>
+    <t>Подарили</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
@@ -1939,7 +2057,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2005,15 +2123,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="2" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -2065,8 +2174,80 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Antique Olive"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFC00000"/>
+      <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Antique Olive Compact"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2157,8 +2338,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2244,11 +2437,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFEC1606"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFEC1606"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEC1606"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2285,23 +2564,10 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2326,62 +2592,121 @@
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2389,38 +2714,103 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEC1606"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEC1606"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF57B418"/>
+      <color rgb="FFFF8585"/>
+      <color rgb="FF6C0000"/>
+      <color rgb="FFEC1606"/>
       <color rgb="FFF4B79E"/>
       <color rgb="FF062D4E"/>
       <color rgb="FF094679"/>
@@ -2695,13 +3085,243 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="C3:H17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="49"/>
+    <col min="3" max="3" width="11.7109375" style="49" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="49" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="49" customWidth="1"/>
+    <col min="6" max="6" width="20" style="49" customWidth="1"/>
+    <col min="7" max="8" width="21.7109375" style="49" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="49"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:8" ht="15.75" thickBot="1"/>
+    <row r="4" spans="3:8" ht="45" customHeight="1">
+      <c r="C4" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" ht="16.5">
+      <c r="C5" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" ht="16.5">
+      <c r="C6" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="51">
+        <v>100494.39999999999</v>
+      </c>
+      <c r="E6" s="51">
+        <v>10000</v>
+      </c>
+      <c r="F6" s="51">
+        <v>0</v>
+      </c>
+      <c r="G6" s="51">
+        <v>109233.84</v>
+      </c>
+      <c r="H6" s="51">
+        <f>SUM(D6:F6)-G6</f>
+        <v>1260.5599999999977</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" ht="16.5">
+      <c r="C7" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="51">
+        <v>68400</v>
+      </c>
+      <c r="E7" s="51">
+        <v>0</v>
+      </c>
+      <c r="F7" s="51">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51">
+        <v>80331.3</v>
+      </c>
+      <c r="H7" s="51">
+        <f t="shared" ref="H7:H8" si="0">SUM(D7:F7)-G7</f>
+        <v>-11931.300000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" ht="16.5">
+      <c r="C8" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="51">
+        <v>136698</v>
+      </c>
+      <c r="E8" s="51">
+        <v>10000</v>
+      </c>
+      <c r="F8" s="51">
+        <v>17000</v>
+      </c>
+      <c r="G8" s="51">
+        <v>163638.94</v>
+      </c>
+      <c r="H8" s="51">
+        <f t="shared" si="0"/>
+        <v>59.059999999997672</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" ht="16.5">
+      <c r="C9" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+    </row>
+    <row r="10" spans="3:8" ht="16.5">
+      <c r="C10" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+    </row>
+    <row r="11" spans="3:8" ht="16.5">
+      <c r="C11" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+    </row>
+    <row r="12" spans="3:8" ht="16.5">
+      <c r="C12" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+    </row>
+    <row r="13" spans="3:8" ht="16.5">
+      <c r="C13" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+    </row>
+    <row r="14" spans="3:8" ht="16.5">
+      <c r="C14" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+    </row>
+    <row r="15" spans="3:8" ht="16.5">
+      <c r="C15" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="16" spans="3:8" ht="17.25" thickBot="1">
+      <c r="C16" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+    </row>
+    <row r="17" spans="3:8" ht="17.25" thickBot="1">
+      <c r="C17" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H5:H16">
+    <cfRule type="expression" dxfId="11" priority="4">
+      <formula>H5&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="3">
+      <formula>H5&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>H17&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>H17&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2712,32 +3332,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -2753,16 +3373,16 @@
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>12</v>
@@ -2786,7 +3406,7 @@
         <v>16</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>17</v>
@@ -2836,52 +3456,52 @@
       <c r="AT2" s="1"/>
     </row>
     <row r="3" spans="1:46">
-      <c r="A3" s="27">
+      <c r="A3" s="20">
         <v>5</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="22">
         <f>183+2168</f>
         <v>2351</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="22">
         <v>3131</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29">
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22">
         <v>450</v>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29">
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22">
         <v>40</v>
       </c>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29">
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
         <v>14418</v>
       </c>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29">
+      <c r="R3" s="22"/>
+      <c r="S3" s="22">
         <v>5000</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="30">
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="23">
         <f>SUM(C3:U3)</f>
         <v>25390</v>
       </c>
-      <c r="W3" s="31">
+      <c r="W3" s="24">
         <v>53739.4</v>
       </c>
-      <c r="X3" s="25"/>
+      <c r="X3" s="18"/>
     </row>
     <row r="4" spans="1:46">
       <c r="A4" s="5">
@@ -2901,7 +3521,7 @@
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
-      <c r="N4" s="23">
+      <c r="N4" s="16">
         <f>131+247</f>
         <v>378</v>
       </c>
@@ -2917,7 +3537,7 @@
         <v>378</v>
       </c>
       <c r="W4" s="12"/>
-      <c r="X4" s="25"/>
+      <c r="X4" s="18"/>
     </row>
     <row r="5" spans="1:46">
       <c r="A5" s="4">
@@ -2927,11 +3547,11 @@
         <v>5</v>
       </c>
       <c r="C5" s="15"/>
-      <c r="D5" s="24">
+      <c r="D5" s="17">
         <v>1110</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="7">
@@ -2957,7 +3577,7 @@
         <v>2406</v>
       </c>
       <c r="W5" s="9"/>
-      <c r="X5" s="25"/>
+      <c r="X5" s="18"/>
     </row>
     <row r="6" spans="1:46">
       <c r="A6" s="5">
@@ -2966,7 +3586,7 @@
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="16">
         <v>1006</v>
       </c>
       <c r="D6" s="14"/>
@@ -2979,7 +3599,7 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="23">
+      <c r="N6" s="16">
         <f>221+171</f>
         <v>392</v>
       </c>
@@ -2995,7 +3615,7 @@
         <v>1398</v>
       </c>
       <c r="W6" s="12"/>
-      <c r="X6" s="25"/>
+      <c r="X6" s="18"/>
     </row>
     <row r="7" spans="1:46">
       <c r="A7" s="4">
@@ -3004,7 +3624,7 @@
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="17">
         <v>1819</v>
       </c>
       <c r="D7" s="15"/>
@@ -3034,7 +3654,7 @@
         <v>3098</v>
       </c>
       <c r="W7" s="9"/>
-      <c r="X7" s="25"/>
+      <c r="X7" s="18"/>
     </row>
     <row r="8" spans="1:46">
       <c r="A8" s="5">
@@ -3073,7 +3693,7 @@
         <v>2783.9</v>
       </c>
       <c r="W8" s="12"/>
-      <c r="X8" s="25"/>
+      <c r="X8" s="18"/>
     </row>
     <row r="9" spans="1:46">
       <c r="A9" s="4">
@@ -3108,7 +3728,7 @@
         <v>1403.84</v>
       </c>
       <c r="W9" s="9"/>
-      <c r="X9" s="25"/>
+      <c r="X9" s="18"/>
     </row>
     <row r="10" spans="1:46">
       <c r="A10" s="5">
@@ -3143,7 +3763,7 @@
         <v>959</v>
       </c>
       <c r="W10" s="12"/>
-      <c r="X10" s="25"/>
+      <c r="X10" s="18"/>
     </row>
     <row r="11" spans="1:46">
       <c r="A11" s="4">
@@ -3185,7 +3805,7 @@
         <v>10553.970000000001</v>
       </c>
       <c r="W11" s="9"/>
-      <c r="X11" s="25"/>
+      <c r="X11" s="18"/>
     </row>
     <row r="12" spans="1:46">
       <c r="A12" s="5">
@@ -3230,7 +3850,7 @@
         <v>8049.95</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="X12" s="25"/>
+      <c r="X12" s="18"/>
     </row>
     <row r="13" spans="1:46">
       <c r="A13" s="4">
@@ -3268,7 +3888,7 @@
         <v>1704.79</v>
       </c>
       <c r="W13" s="9"/>
-      <c r="X13" s="25"/>
+      <c r="X13" s="18"/>
     </row>
     <row r="14" spans="1:46">
       <c r="A14" s="5">
@@ -3303,7 +3923,7 @@
         <v>1170</v>
       </c>
       <c r="W14" s="12"/>
-      <c r="X14" s="25"/>
+      <c r="X14" s="18"/>
     </row>
     <row r="15" spans="1:46">
       <c r="A15" s="4">
@@ -3336,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W15" s="9"/>
-      <c r="X15" s="25"/>
+      <c r="X15" s="18"/>
     </row>
     <row r="16" spans="1:46">
       <c r="A16" s="5">
@@ -3375,7 +3995,7 @@
         <v>1099</v>
       </c>
       <c r="W16" s="12"/>
-      <c r="X16" s="25"/>
+      <c r="X16" s="18"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="4">
@@ -3408,51 +4028,51 @@
         <v>0</v>
       </c>
       <c r="W17" s="9"/>
-      <c r="X17" s="25">
+      <c r="X17" s="18">
         <f>W3-SUM(V3:V16)</f>
         <v>-6655.0499999999956</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="14.25" customHeight="1">
-      <c r="A18" s="27">
+      <c r="A18" s="20">
         <v>20</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="29">
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22">
         <v>1300</v>
       </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29">
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22">
         <f>1587+618</f>
         <v>2205</v>
       </c>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="30">
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="23">
         <f>SUM(C18:U18)</f>
         <v>3505</v>
       </c>
-      <c r="W18" s="31">
+      <c r="W18" s="24">
         <f>30304+16451</f>
         <v>46755</v>
       </c>
-      <c r="X18" s="32"/>
+      <c r="X18" s="25"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="4">
@@ -3492,7 +4112,7 @@
         <v>7531.48</v>
       </c>
       <c r="W19" s="9"/>
-      <c r="X19" s="25"/>
+      <c r="X19" s="18"/>
     </row>
     <row r="20" spans="1:24">
       <c r="A20" s="5">
@@ -3530,7 +4150,7 @@
         <v>4449</v>
       </c>
       <c r="W20" s="12"/>
-      <c r="X20" s="25"/>
+      <c r="X20" s="18"/>
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="4">
@@ -3565,7 +4185,7 @@
       <c r="W21" s="9">
         <v>10000</v>
       </c>
-      <c r="X21" s="25"/>
+      <c r="X21" s="18"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="5">
@@ -3604,7 +4224,7 @@
         <v>3037</v>
       </c>
       <c r="W22" s="12"/>
-      <c r="X22" s="25"/>
+      <c r="X22" s="18"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="4">
@@ -3650,7 +4270,7 @@
         <v>4414</v>
       </c>
       <c r="W23" s="9"/>
-      <c r="X23" s="25"/>
+      <c r="X23" s="18"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="5">
@@ -3690,7 +4310,7 @@
         <v>1569</v>
       </c>
       <c r="W24" s="12"/>
-      <c r="X24" s="25"/>
+      <c r="X24" s="18"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="4">
@@ -3735,7 +4355,7 @@
         <v>10064.4</v>
       </c>
       <c r="W25" s="9"/>
-      <c r="X25" s="25"/>
+      <c r="X25" s="18"/>
     </row>
     <row r="26" spans="1:24">
       <c r="A26" s="5">
@@ -3780,7 +4400,7 @@
         <v>14269.51</v>
       </c>
       <c r="W26" s="12"/>
-      <c r="X26" s="25"/>
+      <c r="X26" s="18"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="5">
@@ -3822,7 +4442,7 @@
         <v>4001.25</v>
       </c>
       <c r="W27" s="12"/>
-      <c r="X27" s="25"/>
+      <c r="X27" s="18"/>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="5">
@@ -3862,7 +4482,7 @@
         <v>2837</v>
       </c>
       <c r="W28" s="12"/>
-      <c r="X28" s="25"/>
+      <c r="X28" s="18"/>
     </row>
     <row r="29" spans="1:24">
       <c r="A29" s="5">
@@ -3897,7 +4517,7 @@
         <v>799</v>
       </c>
       <c r="W29" s="12"/>
-      <c r="X29" s="25"/>
+      <c r="X29" s="18"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="5">
@@ -3930,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="W30" s="12"/>
-      <c r="X30" s="25">
+      <c r="X30" s="18">
         <f>W18+W21-SUM(V18:V30)</f>
         <v>278.36000000000058</v>
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="57"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -4024,7 +4644,10 @@
         <f t="shared" si="3"/>
         <v>110494.39999999999</v>
       </c>
-      <c r="X31" s="26"/>
+      <c r="X31" s="19">
+        <f>W31-V31</f>
+        <v>1260.5600000000122</v>
+      </c>
     </row>
     <row r="35" spans="2:10">
       <c r="B35" s="6"/>
@@ -4048,7 +4671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4059,104 +4682,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
+      <c r="A1" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37" t="s">
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="37" t="s">
+      <c r="D2" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="37" t="s">
+      <c r="F2" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="37" t="s">
+      <c r="H2" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="37" t="s">
+      <c r="M2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q2" s="37" t="s">
+      <c r="P2" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="R2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="S2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="T2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="U2" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="30" t="s">
         <v>21</v>
       </c>
       <c r="Y2" s="1"/>
@@ -4183,1207 +4806,1207 @@
       <c r="AT2" s="1"/>
     </row>
     <row r="3" spans="1:46">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>5</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="33">
         <f>2497.35+200</f>
         <v>2697.35</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33">
         <v>312</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40">
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33">
         <v>990</v>
       </c>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40">
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33">
         <f>SUM(C3:U3)</f>
         <v>3999.35</v>
       </c>
-      <c r="W3" s="41">
+      <c r="W3" s="34">
         <v>43724</v>
       </c>
-      <c r="X3" s="42"/>
+      <c r="X3" s="35"/>
     </row>
     <row r="4" spans="1:46">
-      <c r="A4" s="33">
+      <c r="A4" s="26">
         <v>6</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27">
         <v>1610</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27">
         <f>387+364</f>
         <v>751</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27">
         <v>199</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="27">
         <f>2411.96/2+116.97+2148/2+729</f>
         <v>3125.95</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="27">
         <v>6000</v>
       </c>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34">
+      <c r="U4" s="27"/>
+      <c r="V4" s="27">
         <f t="shared" ref="V4:V31" si="0">SUM(C4:U4)</f>
         <v>11685.95</v>
       </c>
-      <c r="W4" s="35"/>
-      <c r="X4" s="38"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="31"/>
     </row>
     <row r="5" spans="1:46">
-      <c r="A5" s="33">
+      <c r="A5" s="26">
         <v>7</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27">
         <f>3080+328</f>
         <v>3408</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27">
         <v>268</v>
       </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34">
+      <c r="O5" s="27"/>
+      <c r="P5" s="27">
         <v>8428</v>
       </c>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27">
         <f>255+547</f>
         <v>802</v>
       </c>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34">
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27">
         <f t="shared" si="0"/>
         <v>12906</v>
       </c>
-      <c r="W5" s="35"/>
-      <c r="X5" s="38"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="31"/>
     </row>
     <row r="6" spans="1:46">
-      <c r="A6" s="33">
+      <c r="A6" s="26">
         <v>8</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="27">
         <f>284+995</f>
         <v>1279</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34">
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>1117</v>
       </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34">
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27">
         <v>400</v>
       </c>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34">
+      <c r="O6" s="27"/>
+      <c r="P6" s="27">
         <v>1330</v>
       </c>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34">
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27">
         <f t="shared" si="0"/>
         <v>4126</v>
       </c>
-      <c r="W6" s="35"/>
-      <c r="X6" s="38"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="31"/>
     </row>
     <row r="7" spans="1:46">
-      <c r="A7" s="33">
+      <c r="A7" s="26">
         <v>9</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="27">
         <v>769</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34">
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27">
         <f t="shared" si="0"/>
         <v>769</v>
       </c>
-      <c r="W7" s="35"/>
-      <c r="X7" s="38"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="31"/>
     </row>
     <row r="8" spans="1:46">
-      <c r="A8" s="33">
+      <c r="A8" s="26">
         <v>10</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27">
         <v>302</v>
       </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34">
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27">
         <f t="shared" si="0"/>
         <v>302</v>
       </c>
-      <c r="W8" s="35"/>
-      <c r="X8" s="38"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="31"/>
     </row>
     <row r="9" spans="1:46">
-      <c r="A9" s="33">
+      <c r="A9" s="26">
         <v>11</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34">
+      <c r="C9" s="27"/>
+      <c r="D9" s="27">
         <v>1191</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34">
+      <c r="E9" s="27"/>
+      <c r="F9" s="27">
         <f>1070+109</f>
         <v>1179</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27">
         <v>400</v>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="27">
         <v>277</v>
       </c>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34">
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27">
         <f t="shared" si="0"/>
         <v>3047</v>
       </c>
-      <c r="W9" s="35"/>
-      <c r="X9" s="38"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="31"/>
     </row>
     <row r="10" spans="1:46">
-      <c r="A10" s="33">
+      <c r="A10" s="26">
         <v>12</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27">
         <f>420+700</f>
         <v>1120</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="27">
         <f>1421+331</f>
         <v>1752</v>
       </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34">
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27">
         <v>294</v>
       </c>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34">
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27">
         <f>387+864</f>
         <v>1251</v>
       </c>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34">
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27">
         <f t="shared" si="0"/>
         <v>4417</v>
       </c>
-      <c r="W10" s="35"/>
-      <c r="X10" s="38"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="31"/>
     </row>
     <row r="11" spans="1:46">
-      <c r="A11" s="43">
+      <c r="A11" s="36">
         <v>13</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44">
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37">
         <f>1070+60</f>
         <v>1130</v>
       </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44">
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37">
         <f>251+328+262</f>
         <v>841</v>
       </c>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44">
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37">
         <f t="shared" si="0"/>
         <v>1971</v>
       </c>
-      <c r="W11" s="45"/>
-      <c r="X11" s="46"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="39"/>
     </row>
     <row r="12" spans="1:46">
-      <c r="A12" s="33">
+      <c r="A12" s="26">
         <v>14</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="44">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="37">
         <v>3605</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34">
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27">
         <f t="shared" si="0"/>
         <v>3605</v>
       </c>
-      <c r="W12" s="35"/>
-      <c r="X12" s="38"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="31"/>
     </row>
     <row r="13" spans="1:46">
-      <c r="A13" s="33">
+      <c r="A13" s="26">
         <v>15</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="37">
         <f>318+2115</f>
         <v>2433</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27">
         <f t="shared" si="0"/>
         <v>2433</v>
       </c>
-      <c r="W13" s="35"/>
-      <c r="X13" s="38"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="31"/>
     </row>
     <row r="14" spans="1:46">
-      <c r="A14" s="33">
+      <c r="A14" s="26">
         <v>16</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="44">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="37">
         <f>350</f>
         <v>350</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="44">
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="37">
         <v>291</v>
       </c>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34">
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27">
         <f t="shared" si="0"/>
         <v>641</v>
       </c>
-      <c r="W14" s="35"/>
-      <c r="X14" s="38"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="31"/>
     </row>
     <row r="15" spans="1:46">
-      <c r="A15" s="33">
+      <c r="A15" s="26">
         <v>17</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="44">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="37">
         <v>350</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="44">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="37">
         <v>1000</v>
       </c>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34">
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27">
         <f t="shared" si="0"/>
         <v>1350</v>
       </c>
-      <c r="W15" s="35"/>
-      <c r="X15" s="38"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="31"/>
     </row>
     <row r="16" spans="1:46">
-      <c r="A16" s="33">
+      <c r="A16" s="26">
         <v>18</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="44">
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="37">
         <f>1080+109+350</f>
         <v>1539</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="44">
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="37">
         <v>400</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34">
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27">
         <f t="shared" si="0"/>
         <v>1939</v>
       </c>
-      <c r="W16" s="35"/>
-      <c r="X16" s="38"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="31"/>
     </row>
     <row r="17" spans="1:24">
-      <c r="A17" s="33">
+      <c r="A17" s="26">
         <v>19</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="44">
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="37">
         <f>159+358</f>
         <v>517</v>
       </c>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34">
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27">
         <f t="shared" si="0"/>
         <v>517</v>
       </c>
-      <c r="W17" s="35"/>
-      <c r="X17" s="38"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="31"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="39">
+      <c r="A18" s="32">
         <v>20</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="33">
         <f>220+2225+135</f>
         <v>2580</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40">
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33">
         <v>499</v>
       </c>
-      <c r="S18" s="40">
+      <c r="S18" s="33">
         <v>130</v>
       </c>
-      <c r="T18" s="40"/>
-      <c r="U18" s="40"/>
-      <c r="V18" s="40">
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33">
         <f t="shared" si="0"/>
         <v>3209</v>
       </c>
-      <c r="W18" s="41">
+      <c r="W18" s="34">
         <v>24676</v>
       </c>
-      <c r="X18" s="42"/>
+      <c r="X18" s="35"/>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="33">
+      <c r="A19" s="26">
         <v>21</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="27">
         <f>780+65</f>
         <v>845</v>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34">
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27">
         <f>570+120</f>
         <v>690</v>
       </c>
-      <c r="S19" s="34">
+      <c r="S19" s="27">
         <v>4661</v>
       </c>
-      <c r="T19" s="34">
+      <c r="T19" s="27">
         <v>1200</v>
       </c>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34">
+      <c r="U19" s="27"/>
+      <c r="V19" s="27">
         <f t="shared" si="0"/>
         <v>7396</v>
       </c>
-      <c r="W19" s="35"/>
-      <c r="X19" s="38"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="31"/>
     </row>
     <row r="20" spans="1:24">
-      <c r="A20" s="33">
+      <c r="A20" s="26">
         <v>22</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="27">
         <f>5500-2600</f>
         <v>2900</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34">
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27">
         <v>2600</v>
       </c>
-      <c r="T20" s="34">
+      <c r="T20" s="27">
         <v>600</v>
       </c>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34">
+      <c r="U20" s="27"/>
+      <c r="V20" s="27">
         <f t="shared" si="0"/>
         <v>6100</v>
       </c>
-      <c r="W20" s="35"/>
-      <c r="X20" s="38"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="31"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="33">
+      <c r="A21" s="26">
         <v>23</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34">
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27">
         <v>311</v>
       </c>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34">
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27">
         <f t="shared" si="0"/>
         <v>311</v>
       </c>
-      <c r="W21" s="35"/>
-      <c r="X21" s="38"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="31"/>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" s="33">
+      <c r="A22" s="26">
         <v>24</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34">
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27">
         <v>295</v>
       </c>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34">
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27">
         <v>900</v>
       </c>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34">
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27">
         <f t="shared" si="0"/>
         <v>1195</v>
       </c>
-      <c r="W22" s="35"/>
-      <c r="X22" s="38"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="31"/>
     </row>
     <row r="23" spans="1:24">
-      <c r="A23" s="33">
+      <c r="A23" s="26">
         <v>25</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="27">
         <f>633</f>
         <v>633</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34">
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27">
         <f>392+352</f>
         <v>744</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34">
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27">
         <f>204+188+400</f>
         <v>792</v>
       </c>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34">
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27">
         <f t="shared" si="0"/>
         <v>2169</v>
       </c>
-      <c r="W23" s="35"/>
-      <c r="X23" s="38"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="31"/>
     </row>
     <row r="24" spans="1:24">
-      <c r="A24" s="33">
+      <c r="A24" s="26">
         <v>26</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34">
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W24" s="35"/>
-      <c r="X24" s="38"/>
+      <c r="W24" s="28"/>
+      <c r="X24" s="31"/>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" s="33">
+      <c r="A25" s="26">
         <v>27</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="27">
         <v>1104</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="27">
         <v>856</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27">
         <f>201+182</f>
         <v>383</v>
       </c>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34">
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27">
         <f t="shared" si="0"/>
         <v>2343</v>
       </c>
-      <c r="W25" s="35"/>
-      <c r="X25" s="38"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="31"/>
     </row>
     <row r="26" spans="1:24">
-      <c r="A26" s="33">
+      <c r="A26" s="26">
         <v>28</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27">
         <v>1067</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27">
         <v>132</v>
       </c>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34">
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27">
         <f t="shared" si="0"/>
         <v>1199</v>
       </c>
-      <c r="W26" s="35"/>
-      <c r="X26" s="38"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="31"/>
     </row>
     <row r="27" spans="1:24">
-      <c r="A27" s="33">
+      <c r="A27" s="26">
         <v>29</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="37">
         <f>735+868</f>
         <v>1603</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34">
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27">
         <f>322+198</f>
         <v>520</v>
       </c>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34">
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27">
         <f t="shared" si="0"/>
         <v>2123</v>
       </c>
-      <c r="W27" s="35"/>
-      <c r="X27" s="38"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="31"/>
     </row>
     <row r="28" spans="1:24">
-      <c r="A28" s="33">
+      <c r="A28" s="26">
         <v>30</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="44">
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="37">
         <f>350</f>
         <v>350</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="44">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="37">
         <v>228</v>
       </c>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34">
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27">
         <f t="shared" si="0"/>
         <v>578</v>
       </c>
-      <c r="W28" s="35"/>
-      <c r="X28" s="38"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="31"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" s="33">
+      <c r="A29" s="26">
         <v>31</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34">
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W29" s="35"/>
-      <c r="X29" s="38"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="31"/>
     </row>
     <row r="30" spans="1:24">
-      <c r="A30" s="33">
+      <c r="A30" s="26">
         <v>1</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="34">
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W30" s="35"/>
-      <c r="X30" s="38"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="31"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="33">
+      <c r="A31" s="26">
         <v>2</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34">
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W31" s="35"/>
-      <c r="X31" s="38"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="58" t="s">
+      <c r="A32" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="35">
+      <c r="B32" s="78"/>
+      <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="28">
         <f t="shared" ref="D32:U32" si="1">SUM(D3:D31)</f>
         <v>3114</v>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="28">
         <f t="shared" si="1"/>
         <v>8372</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="28">
         <f t="shared" si="1"/>
         <v>8765</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="28">
         <f t="shared" si="1"/>
         <v>1117</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M32" s="35">
+      <c r="M32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="35">
+      <c r="N32" s="28">
         <f t="shared" si="1"/>
         <v>6106</v>
       </c>
-      <c r="O32" s="35">
+      <c r="O32" s="28">
         <f t="shared" si="1"/>
         <v>2476</v>
       </c>
-      <c r="P32" s="35">
+      <c r="P32" s="28">
         <f t="shared" si="1"/>
         <v>9758</v>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R32" s="35">
+      <c r="R32" s="28">
         <f t="shared" si="1"/>
         <v>3180</v>
       </c>
-      <c r="S32" s="35">
+      <c r="S32" s="28">
         <f t="shared" si="1"/>
         <v>12799.95</v>
       </c>
-      <c r="T32" s="35">
+      <c r="T32" s="28">
         <f t="shared" si="1"/>
         <v>7800</v>
       </c>
-      <c r="U32" s="35">
+      <c r="U32" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V32" s="36">
+      <c r="V32" s="29">
         <f>SUM(V3:V31)</f>
         <v>80331.3</v>
       </c>
-      <c r="W32" s="35">
+      <c r="W32" s="28">
         <f>SUM(W3:W29)</f>
         <v>68400</v>
       </c>
-      <c r="X32" s="38">
+      <c r="X32" s="31">
         <f>W32-V32</f>
         <v>-11931.300000000003</v>
       </c>
@@ -5410,7 +6033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5421,108 +6044,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
+      <c r="A1" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37" t="s">
+      <c r="A2" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="37" t="s">
+      <c r="D2" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="37" t="s">
+      <c r="F2" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="J2" s="37" t="s">
+      <c r="I2" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="37" t="s">
+      <c r="M2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="P2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" s="37" t="s">
+      <c r="Q2" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="S2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="T2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="U2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="Y2" s="30" t="s">
         <v>21</v>
       </c>
       <c r="Z2" s="1"/>
@@ -5549,1601 +6172,1638 @@
       <c r="AU2" s="1"/>
     </row>
     <row r="3" spans="1:47">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>3</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40">
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33">
         <f>22000+3500</f>
         <v>25500</v>
       </c>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40">
+      <c r="R3" s="33"/>
+      <c r="S3" s="33">
         <f>4660+702+799</f>
         <v>6161</v>
       </c>
-      <c r="T3" s="40">
+      <c r="T3" s="33">
         <v>7000</v>
       </c>
-      <c r="U3" s="40">
+      <c r="U3" s="33">
         <v>750</v>
       </c>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40">
+      <c r="V3" s="33"/>
+      <c r="W3" s="33">
         <f>SUM(C3:V3)</f>
         <v>39411</v>
       </c>
-      <c r="X3" s="41">
+      <c r="X3" s="34">
         <v>100688</v>
       </c>
-      <c r="Y3" s="42"/>
+      <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:47">
-      <c r="A4" s="47">
+      <c r="A4" s="40">
         <v>4</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="41">
         <f>100+422+585</f>
         <v>1107</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="41">
         <v>3679</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48">
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41">
         <f>2320+1728</f>
         <v>4048</v>
       </c>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48">
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41">
         <v>3663.22</v>
       </c>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48">
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41">
         <v>5350</v>
       </c>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48">
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41">
         <v>1025</v>
       </c>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48">
+      <c r="R4" s="41"/>
+      <c r="S4" s="41">
         <v>100</v>
       </c>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48">
+      <c r="T4" s="41"/>
+      <c r="U4" s="41">
         <v>990</v>
       </c>
-      <c r="V4" s="48">
+      <c r="V4" s="41">
         <f>1320+1330+210</f>
         <v>2860</v>
       </c>
-      <c r="W4" s="48">
+      <c r="W4" s="41">
         <f t="shared" ref="W4:W34" si="0">SUM(C4:V4)</f>
         <v>22822.22</v>
       </c>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="50"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="43"/>
     </row>
     <row r="5" spans="1:47">
-      <c r="A5" s="47">
+      <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="41">
         <f>3116+382</f>
         <v>3498</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48">
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41">
         <v>1500</v>
       </c>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48">
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41">
         <v>9373</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="41">
         <v>199</v>
       </c>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48">
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41">
         <f t="shared" si="0"/>
         <v>14570</v>
       </c>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="50"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="43"/>
     </row>
     <row r="6" spans="1:47">
-      <c r="A6" s="47">
+      <c r="A6" s="40">
         <v>6</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="41">
         <v>918</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="41">
         <v>994</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48">
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41">
         <v>3464</v>
       </c>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48">
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41">
         <f>500+288</f>
         <v>788</v>
       </c>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48">
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41">
         <v>990</v>
       </c>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48">
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41">
         <f t="shared" si="0"/>
         <v>7154</v>
       </c>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="50"/>
+      <c r="X6" s="42"/>
+      <c r="Y6" s="43"/>
     </row>
     <row r="7" spans="1:47">
-      <c r="A7" s="47">
+      <c r="A7" s="40">
         <v>7</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48">
+      <c r="C7" s="41"/>
+      <c r="D7" s="41">
         <v>714</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48">
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41">
         <f>500+280</f>
         <v>780</v>
       </c>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48">
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41">
         <f t="shared" si="0"/>
         <v>1494</v>
       </c>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="50"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="43"/>
     </row>
     <row r="8" spans="1:47">
-      <c r="A8" s="47">
+      <c r="A8" s="40">
         <v>8</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48">
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41">
         <v>420</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="41">
         <v>835</v>
       </c>
-      <c r="H8" s="48">
+      <c r="H8" s="41">
         <v>285</v>
       </c>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48">
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="41"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
+      <c r="W8" s="41">
         <f t="shared" si="0"/>
         <v>1540</v>
       </c>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="50"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="43"/>
     </row>
     <row r="9" spans="1:47">
-      <c r="A9" s="47">
+      <c r="A9" s="40">
         <v>9</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="41">
         <v>863</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="41">
         <v>710</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48">
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41">
         <v>409</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48">
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41">
         <f t="shared" si="0"/>
         <v>1982</v>
       </c>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="50"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="43"/>
     </row>
     <row r="10" spans="1:47">
-      <c r="A10" s="47">
+      <c r="A10" s="40">
         <v>10</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="41">
         <v>319</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="41">
         <v>940</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="41">
         <v>1895</v>
       </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48">
+      <c r="F10" s="41"/>
+      <c r="G10" s="41">
         <v>835</v>
       </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48">
+      <c r="H10" s="41"/>
+      <c r="I10" s="41">
         <v>1034</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48">
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41">
         <v>275</v>
       </c>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="48"/>
-      <c r="W10" s="48">
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41">
         <f t="shared" si="0"/>
         <v>5298</v>
       </c>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="50"/>
+      <c r="X10" s="42"/>
+      <c r="Y10" s="43"/>
     </row>
     <row r="11" spans="1:47">
-      <c r="A11" s="47">
+      <c r="A11" s="40">
         <v>11</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="41">
         <f>790+282</f>
         <v>1072</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="41">
         <v>1311</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48">
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41">
         <f>1500+1900</f>
         <v>3400</v>
       </c>
-      <c r="O11" s="48">
+      <c r="O11" s="41">
         <f>302+243</f>
         <v>545</v>
       </c>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="48">
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41">
         <f t="shared" si="0"/>
         <v>6328</v>
       </c>
-      <c r="X11" s="49">
+      <c r="X11" s="42">
         <v>5000</v>
       </c>
-      <c r="Y11" s="50"/>
+      <c r="Y11" s="43"/>
     </row>
     <row r="12" spans="1:47">
-      <c r="A12" s="47">
+      <c r="A12" s="40">
         <v>12</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="41">
         <f>69+603</f>
         <v>672</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48">
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41">
         <f t="shared" si="0"/>
         <v>672</v>
       </c>
-      <c r="X12" s="49">
+      <c r="X12" s="42">
         <v>10000</v>
       </c>
-      <c r="Y12" s="50"/>
+      <c r="Y12" s="43"/>
     </row>
     <row r="13" spans="1:47">
-      <c r="A13" s="47">
+      <c r="A13" s="40">
         <v>13</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="48"/>
-      <c r="W13" s="48">
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="41"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="41"/>
+      <c r="W13" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="50"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="43"/>
     </row>
     <row r="14" spans="1:47">
-      <c r="A14" s="47">
+      <c r="A14" s="40">
         <v>14</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="41">
         <v>879</v>
       </c>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48">
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41">
         <v>1080</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="41">
         <v>580</v>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="41">
         <v>1261</v>
       </c>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48">
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41">
         <v>305</v>
       </c>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="48"/>
-      <c r="S14" s="48"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="48"/>
-      <c r="V14" s="48"/>
-      <c r="W14" s="48">
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="41">
         <f t="shared" si="0"/>
         <v>4105</v>
       </c>
-      <c r="X14" s="49"/>
-      <c r="Y14" s="50"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="43"/>
     </row>
     <row r="15" spans="1:47">
-      <c r="A15" s="47">
+      <c r="A15" s="40">
         <v>15</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="41">
         <v>700</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48">
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41">
         <v>990</v>
       </c>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41">
         <v>2200</v>
       </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48">
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41">
         <v>369</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48">
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41">
         <v>1400</v>
       </c>
-      <c r="U15" s="48"/>
-      <c r="V15" s="48"/>
-      <c r="W15" s="48">
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41">
         <f t="shared" si="0"/>
         <v>5659</v>
       </c>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="50"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="43"/>
     </row>
     <row r="16" spans="1:47">
-      <c r="A16" s="47">
+      <c r="A16" s="40">
         <v>16</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="41">
         <f>160+263</f>
         <v>423</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48">
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41">
         <v>450</v>
       </c>
-      <c r="U16" s="48"/>
-      <c r="V16" s="48"/>
-      <c r="W16" s="48">
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41">
         <f t="shared" si="0"/>
         <v>873</v>
       </c>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="50"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="43"/>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="47">
+      <c r="A17" s="40">
         <v>17</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41">
         <v>1116</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48">
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41">
         <v>307</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48">
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41">
         <v>800</v>
       </c>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="48"/>
-      <c r="V17" s="48"/>
-      <c r="W17" s="48">
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="41">
         <f t="shared" si="0"/>
         <v>2223</v>
       </c>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="50"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="43"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="47">
+      <c r="A18" s="40">
         <v>18</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="41">
         <f>1357.83+470</f>
         <v>1827.83</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="48">
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41">
         <v>187</v>
       </c>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="48"/>
-      <c r="V18" s="48"/>
-      <c r="W18" s="48">
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="41">
         <f t="shared" si="0"/>
         <v>2014.83</v>
       </c>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="50"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="43"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="47">
+      <c r="A19" s="40">
         <v>19</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48">
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41">
         <v>700</v>
       </c>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48">
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
+      <c r="W19" s="41">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="50"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="52">
+      <c r="A20" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="82"/>
+      <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="45">
         <f t="shared" ref="D20:V20" si="1">SUM(D3:D19)</f>
         <v>8348</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="45">
         <f t="shared" si="1"/>
         <v>3011</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="45">
         <f t="shared" si="1"/>
         <v>2490</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="45">
         <f t="shared" si="1"/>
         <v>2250</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="45">
         <f t="shared" si="1"/>
         <v>7794</v>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="45">
         <f t="shared" si="1"/>
         <v>2534</v>
       </c>
-      <c r="J20" s="52">
+      <c r="J20" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="52">
+      <c r="K20" s="45">
         <f t="shared" si="1"/>
         <v>7127.2199999999993</v>
       </c>
-      <c r="L20" s="52">
+      <c r="L20" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="52">
+      <c r="M20" s="45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="52">
+      <c r="N20" s="45">
         <f t="shared" si="1"/>
         <v>8750</v>
       </c>
-      <c r="O20" s="52">
+      <c r="O20" s="45">
         <f t="shared" si="1"/>
         <v>2397</v>
       </c>
-      <c r="P20" s="52">
+      <c r="P20" s="45">
         <f t="shared" si="1"/>
         <v>1568</v>
       </c>
-      <c r="Q20" s="52">
+      <c r="Q20" s="45">
         <f t="shared" si="1"/>
         <v>27325</v>
       </c>
-      <c r="R20" s="52">
+      <c r="R20" s="45">
         <f t="shared" si="1"/>
         <v>9373</v>
       </c>
-      <c r="S20" s="52">
+      <c r="S20" s="45">
         <f t="shared" si="1"/>
         <v>8150</v>
       </c>
-      <c r="T20" s="52">
+      <c r="T20" s="45">
         <f t="shared" si="1"/>
         <v>8850</v>
       </c>
-      <c r="U20" s="52">
+      <c r="U20" s="45">
         <f t="shared" si="1"/>
         <v>1740</v>
       </c>
-      <c r="V20" s="52">
+      <c r="V20" s="45">
         <f t="shared" si="1"/>
         <v>2860</v>
       </c>
-      <c r="W20" s="52">
+      <c r="W20" s="45">
         <f>SUM(W3:W19)</f>
         <v>116846.05</v>
       </c>
-      <c r="X20" s="53">
+      <c r="X20" s="46">
         <f>SUM(X3:X19)</f>
         <v>115688</v>
       </c>
-      <c r="Y20" s="54">
+      <c r="Y20" s="47">
         <f>X20-W20</f>
         <v>-1158.0500000000029</v>
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="39">
+      <c r="A21" s="32">
         <v>20</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="33">
         <v>2409</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="33">
         <v>299</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40">
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33">
         <v>187</v>
       </c>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="40">
-        <f>4660</f>
-        <v>4660</v>
-      </c>
-      <c r="T21" s="40">
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33">
+        <f>4660+700</f>
+        <v>5360</v>
+      </c>
+      <c r="T21" s="33">
         <v>1634</v>
       </c>
-      <c r="U21" s="40"/>
-      <c r="V21" s="40"/>
-      <c r="W21" s="40">
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33">
         <f t="shared" si="0"/>
-        <v>9189</v>
-      </c>
-      <c r="X21" s="41">
+        <v>9889</v>
+      </c>
+      <c r="X21" s="34">
         <v>36010</v>
       </c>
-      <c r="Y21" s="42"/>
+      <c r="Y21" s="35"/>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="47">
+      <c r="A22" s="40">
         <v>21</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="41">
         <v>374</v>
       </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48">
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41">
         <v>1080</v>
       </c>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48">
+      <c r="G22" s="41"/>
+      <c r="H22" s="41">
         <v>572</v>
       </c>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48">
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41">
         <v>215</v>
       </c>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48">
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41">
         <v>3700</v>
       </c>
-      <c r="U22" s="48"/>
-      <c r="V22" s="48"/>
-      <c r="W22" s="48">
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41">
         <f t="shared" si="0"/>
         <v>5941</v>
       </c>
-      <c r="X22" s="49"/>
-      <c r="Y22" s="50"/>
-      <c r="AA22" s="51"/>
+      <c r="X22" s="42"/>
+      <c r="Y22" s="43"/>
+      <c r="AA22" s="44"/>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="47">
+      <c r="A23" s="40">
         <v>22</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="41">
         <v>1027.8900000000001</v>
       </c>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48">
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41">
         <v>835</v>
       </c>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48">
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41">
         <v>265</v>
       </c>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="48"/>
-      <c r="S23" s="48"/>
-      <c r="T23" s="48"/>
-      <c r="U23" s="48"/>
-      <c r="V23" s="48"/>
-      <c r="W23" s="48">
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="41">
         <f t="shared" si="0"/>
         <v>2127.8900000000003</v>
       </c>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="50"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="43"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="47">
+      <c r="A24" s="40">
         <v>23</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48">
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41">
         <v>1344</v>
       </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48">
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="41">
         <v>349</v>
       </c>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48">
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41">
         <v>1000</v>
       </c>
-      <c r="R24" s="48"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="48"/>
-      <c r="W24" s="48">
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41">
         <f t="shared" si="0"/>
         <v>2693</v>
       </c>
-      <c r="X24" s="49"/>
-      <c r="Y24" s="50"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="43"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="47">
+      <c r="A25" s="40">
         <v>24</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="41">
         <v>1755</v>
       </c>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48">
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41">
         <v>1331</v>
       </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48">
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41">
         <v>180</v>
       </c>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48">
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41">
         <v>500</v>
       </c>
-      <c r="R25" s="48"/>
-      <c r="S25" s="48"/>
-      <c r="T25" s="48"/>
-      <c r="U25" s="48"/>
-      <c r="V25" s="48"/>
-      <c r="W25" s="48">
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41">
         <f t="shared" si="0"/>
         <v>3766</v>
       </c>
-      <c r="X25" s="49"/>
-      <c r="Y25" s="50"/>
+      <c r="X25" s="42"/>
+      <c r="Y25" s="43"/>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="47">
+      <c r="A26" s="40">
         <v>25</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="41">
         <v>525</v>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="41">
         <v>1326</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48">
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41">
         <v>251</v>
       </c>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48">
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41">
         <v>300</v>
       </c>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48">
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41">
         <f t="shared" si="0"/>
         <v>2402</v>
       </c>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="50"/>
+      <c r="X26" s="42"/>
+      <c r="Y26" s="43"/>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="47">
+      <c r="A27" s="40">
         <v>26</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48">
+      <c r="C27" s="41"/>
+      <c r="D27" s="41">
         <v>2161</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="41">
         <v>1336</v>
       </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48">
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41">
         <v>151</v>
       </c>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48">
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41">
         <f t="shared" si="0"/>
         <v>3648</v>
       </c>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="50"/>
+      <c r="X27" s="42"/>
+      <c r="Y27" s="43"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="47">
+      <c r="A28" s="40">
         <v>27</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48">
+      <c r="C28" s="41"/>
+      <c r="D28" s="41">
         <v>1417</v>
       </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48">
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41">
         <f>677+345</f>
         <v>1022</v>
       </c>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48">
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41">
         <f t="shared" si="0"/>
         <v>2439</v>
       </c>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="50"/>
+      <c r="X28" s="42"/>
+      <c r="Y28" s="43"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="47">
+      <c r="A29" s="40">
         <v>28</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48">
+      <c r="C29" s="41"/>
+      <c r="D29" s="41">
         <v>1796</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48">
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41">
         <v>485</v>
       </c>
-      <c r="H29" s="48">
+      <c r="H29" s="41">
         <v>1360</v>
       </c>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48">
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41">
         <f>319+442</f>
         <v>761</v>
       </c>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48">
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41">
         <v>249</v>
       </c>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48">
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41">
         <f t="shared" si="0"/>
         <v>4651</v>
       </c>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="50"/>
+      <c r="X29" s="42"/>
+      <c r="Y29" s="43"/>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="47">
+      <c r="A30" s="40">
         <v>29</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48">
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41">
         <v>614</v>
       </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48">
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41">
         <v>207</v>
       </c>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="48">
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41">
         <f t="shared" si="0"/>
         <v>821</v>
       </c>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="50"/>
+      <c r="X30" s="42">
+        <v>10000</v>
+      </c>
+      <c r="Y30" s="43"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="47">
+      <c r="A31" s="40">
         <v>30</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="48">
+      <c r="C31" s="41">
+        <f>90</f>
+        <v>90</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41">
+        <f>1150+165</f>
+        <v>1315</v>
+      </c>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41">
+        <v>227</v>
+      </c>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="50"/>
+        <v>1632</v>
+      </c>
+      <c r="X31" s="42"/>
+      <c r="Y31" s="43"/>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="47">
+      <c r="A32" s="40">
         <v>1</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="48">
+      <c r="C32" s="41">
+        <f>1695+809</f>
+        <v>2504</v>
+      </c>
+      <c r="D32" s="41">
+        <v>464</v>
+      </c>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41">
+        <v>145</v>
+      </c>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="50"/>
+        <v>3113</v>
+      </c>
+      <c r="X32" s="42"/>
+      <c r="Y32" s="43"/>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="47">
+      <c r="A33" s="40">
         <v>2</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="48"/>
-      <c r="W33" s="48">
+      <c r="C33" s="41">
+        <f>85+547</f>
+        <v>632</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41">
+        <v>799</v>
+      </c>
+      <c r="T33" s="41">
+        <v>62</v>
+      </c>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="49"/>
-      <c r="Y33" s="50"/>
+        <v>1493</v>
+      </c>
+      <c r="X33" s="42"/>
+      <c r="Y33" s="43"/>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="47">
+      <c r="A34" s="40">
         <v>3</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="48"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="48"/>
-      <c r="W34" s="48">
+      <c r="C34" s="41">
+        <v>363</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41">
+        <v>20</v>
+      </c>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="49"/>
-      <c r="Y34" s="50"/>
+        <v>383</v>
+      </c>
+      <c r="X34" s="42"/>
+      <c r="Y34" s="43"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="47">
+      <c r="A35" s="40">
         <v>4</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="48"/>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48">
+      <c r="C35" s="41">
+        <f>47+1331</f>
+        <v>1378</v>
+      </c>
+      <c r="D35" s="41">
+        <v>89</v>
+      </c>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41">
+        <v>327</v>
+      </c>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41">
         <f>SUM(C35:V35)</f>
-        <v>0</v>
-      </c>
-      <c r="X35" s="49"/>
-      <c r="Y35" s="50"/>
+        <v>1794</v>
+      </c>
+      <c r="X35" s="42">
+        <v>2000</v>
+      </c>
+      <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="62"/>
-      <c r="C36" s="52">
+      <c r="A36" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="82"/>
+      <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
-        <v>6090.89</v>
-      </c>
-      <c r="D36" s="52">
+        <v>11057.89</v>
+      </c>
+      <c r="D36" s="45">
         <f t="shared" ref="D36:V36" si="2">SUM(D21:D35)</f>
-        <v>6999</v>
-      </c>
-      <c r="E36" s="52">
+        <v>7552</v>
+      </c>
+      <c r="E36" s="45">
         <f t="shared" si="2"/>
         <v>2680</v>
       </c>
-      <c r="F36" s="52">
+      <c r="F36" s="45">
         <f t="shared" si="2"/>
         <v>3025</v>
       </c>
-      <c r="G36" s="52">
+      <c r="G36" s="45">
         <f t="shared" si="2"/>
         <v>1320</v>
       </c>
-      <c r="H36" s="52">
+      <c r="H36" s="45">
         <f t="shared" si="2"/>
-        <v>1932</v>
-      </c>
-      <c r="I36" s="52">
+        <v>3247</v>
+      </c>
+      <c r="I36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J36" s="52">
+      <c r="J36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="52">
+      <c r="K36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="52">
+      <c r="L36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M36" s="52">
+      <c r="M36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N36" s="52">
+      <c r="N36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O36" s="52">
+      <c r="O36" s="45">
         <f t="shared" si="2"/>
         <v>3437</v>
       </c>
-      <c r="P36" s="52">
+      <c r="P36" s="45">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="52">
+        <v>554</v>
+      </c>
+      <c r="Q36" s="45">
         <f t="shared" si="2"/>
         <v>1951</v>
       </c>
-      <c r="R36" s="52">
+      <c r="R36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S36" s="52">
+      <c r="S36" s="45">
         <f t="shared" si="2"/>
-        <v>4909</v>
-      </c>
-      <c r="T36" s="52">
+        <v>6408</v>
+      </c>
+      <c r="T36" s="45">
         <f>SUM(T21:T35)</f>
-        <v>5334</v>
-      </c>
-      <c r="U36" s="52">
+        <v>5561</v>
+      </c>
+      <c r="U36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V36" s="52">
+      <c r="V36" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W36" s="52">
+      <c r="W36" s="45">
         <f>SUM(W21:W35)</f>
-        <v>37677.89</v>
-      </c>
-      <c r="X36" s="53">
+        <v>46792.89</v>
+      </c>
+      <c r="X36" s="46">
         <f>SUM(X21:X35)</f>
-        <v>36010</v>
-      </c>
-      <c r="Y36" s="54">
+        <v>48010</v>
+      </c>
+      <c r="Y36" s="47">
         <f>X36-W36</f>
-        <v>-1667.8899999999994</v>
+        <v>1217.1100000000006</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="55">
+      <c r="A37" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="80"/>
+      <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
-        <v>18369.72</v>
-      </c>
-      <c r="D37" s="55">
+        <v>23336.720000000001</v>
+      </c>
+      <c r="D37" s="48">
         <f t="shared" ref="D37:V37" si="3">SUM(D20,D36)</f>
-        <v>15347</v>
-      </c>
-      <c r="E37" s="55">
+        <v>15900</v>
+      </c>
+      <c r="E37" s="48">
         <f t="shared" si="3"/>
         <v>5691</v>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="48">
         <f t="shared" si="3"/>
         <v>5515</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="48">
         <f t="shared" si="3"/>
         <v>3570</v>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="48">
         <f t="shared" si="3"/>
-        <v>9726</v>
-      </c>
-      <c r="I37" s="55">
+        <v>11041</v>
+      </c>
+      <c r="I37" s="48">
         <f t="shared" si="3"/>
         <v>2534</v>
       </c>
-      <c r="J37" s="55">
+      <c r="J37" s="48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="55">
+      <c r="K37" s="48">
         <f t="shared" si="3"/>
         <v>7127.2199999999993</v>
       </c>
-      <c r="L37" s="55">
+      <c r="L37" s="48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M37" s="55">
+      <c r="M37" s="48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N37" s="55">
+      <c r="N37" s="48">
         <f t="shared" si="3"/>
         <v>8750</v>
       </c>
-      <c r="O37" s="55">
+      <c r="O37" s="48">
         <f t="shared" si="3"/>
         <v>5834</v>
       </c>
-      <c r="P37" s="55">
+      <c r="P37" s="48">
         <f t="shared" si="3"/>
-        <v>1568</v>
-      </c>
-      <c r="Q37" s="55">
+        <v>2122</v>
+      </c>
+      <c r="Q37" s="48">
         <f t="shared" si="3"/>
         <v>29276</v>
       </c>
-      <c r="R37" s="55">
+      <c r="R37" s="48">
         <f t="shared" si="3"/>
         <v>9373</v>
       </c>
-      <c r="S37" s="55">
+      <c r="S37" s="48">
         <f>SUM(S20,S36)</f>
-        <v>13059</v>
-      </c>
-      <c r="T37" s="55">
+        <v>14558</v>
+      </c>
+      <c r="T37" s="48">
         <f t="shared" si="3"/>
-        <v>14184</v>
-      </c>
-      <c r="U37" s="55">
+        <v>14411</v>
+      </c>
+      <c r="U37" s="48">
         <f t="shared" si="3"/>
         <v>1740</v>
       </c>
-      <c r="V37" s="55">
+      <c r="V37" s="48">
         <f t="shared" si="3"/>
         <v>2860</v>
       </c>
-      <c r="W37" s="55">
+      <c r="W37" s="48">
         <f t="shared" ref="W37" si="4">SUM(W20,W36)</f>
-        <v>154523.94</v>
-      </c>
-      <c r="X37" s="55">
+        <v>163638.94</v>
+      </c>
+      <c r="X37" s="48">
         <f>SUM(X20,X36)</f>
-        <v>151698</v>
-      </c>
-      <c r="Y37" s="55">
+        <v>163698</v>
+      </c>
+      <c r="Y37" s="48">
         <f>SUM(Y20,Y36)</f>
-        <v>-2825.9400000000023</v>
+        <v>59.059999999997672</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -7171,586 +7831,1482 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="19"/>
-    <col min="2" max="2" width="22.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="17" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="19"/>
-    <col min="8" max="8" width="18.42578125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" style="19" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="G1" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1" spans="1:47" ht="60.75" customHeight="1">
+      <c r="A1" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+    </row>
+    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="A2" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+      <c r="R2" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+    </row>
+    <row r="3" spans="1:47" ht="15.75">
+      <c r="A3" s="62">
+        <v>5</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71">
+        <f>178+110</f>
+        <v>288</v>
+      </c>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72">
+        <f>199+4660+700</f>
+        <v>5559</v>
+      </c>
+      <c r="T3" s="72">
+        <v>7000</v>
+      </c>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72">
+        <f>SUM(C3:V3)</f>
+        <v>12847</v>
+      </c>
+      <c r="X3" s="64">
+        <v>53970.91</v>
+      </c>
+      <c r="Y3" s="65"/>
+    </row>
+    <row r="4" spans="1:47" ht="15.75">
+      <c r="A4" s="66">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="74"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="74">
+        <f>SUM(C4:V4)</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="69"/>
+    </row>
+    <row r="5" spans="1:47" ht="15.75">
+      <c r="A5" s="62">
+        <v>7</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="72"/>
+      <c r="V5" s="72"/>
+      <c r="W5" s="72">
+        <f t="shared" ref="W5:W17" si="0">SUM(C5:V5)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="65"/>
+    </row>
+    <row r="6" spans="1:47" ht="15.75">
+      <c r="A6" s="66">
+        <v>8</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="74"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="74"/>
+      <c r="V6" s="74"/>
+      <c r="W6" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="69"/>
+    </row>
+    <row r="7" spans="1:47" ht="15.75">
+      <c r="A7" s="62">
+        <v>9</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="72"/>
+      <c r="V7" s="72"/>
+      <c r="W7" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="65"/>
+    </row>
+    <row r="8" spans="1:47" ht="15.75">
+      <c r="A8" s="66">
+        <v>10</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="74"/>
+      <c r="S8" s="74"/>
+      <c r="T8" s="74"/>
+      <c r="U8" s="74"/>
+      <c r="V8" s="74"/>
+      <c r="W8" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="69"/>
+    </row>
+    <row r="9" spans="1:47" ht="15.75">
+      <c r="A9" s="62">
+        <v>11</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="65"/>
+    </row>
+    <row r="10" spans="1:47" ht="15.75">
+      <c r="A10" s="66">
+        <v>12</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="74"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="74"/>
+      <c r="S10" s="74"/>
+      <c r="T10" s="74"/>
+      <c r="U10" s="74"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="69"/>
+    </row>
+    <row r="11" spans="1:47" ht="15.75">
+      <c r="A11" s="62">
+        <v>13</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="65"/>
+    </row>
+    <row r="12" spans="1:47" ht="15.75">
+      <c r="A12" s="66">
+        <v>14</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
+      <c r="T12" s="74"/>
+      <c r="U12" s="74"/>
+      <c r="V12" s="74"/>
+      <c r="W12" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="69"/>
+    </row>
+    <row r="13" spans="1:47" ht="15.75">
+      <c r="A13" s="62">
+        <v>15</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="72"/>
+      <c r="V13" s="72"/>
+      <c r="W13" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="65"/>
+    </row>
+    <row r="14" spans="1:47" ht="15.75">
+      <c r="A14" s="66">
+        <v>16</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="69"/>
+    </row>
+    <row r="15" spans="1:47" ht="15.75">
+      <c r="A15" s="62">
+        <v>17</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="65"/>
+    </row>
+    <row r="16" spans="1:47" ht="15.75">
+      <c r="A16" s="66">
+        <v>18</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="74"/>
+      <c r="U16" s="74"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="74">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="68"/>
+      <c r="Y16" s="69"/>
+    </row>
+    <row r="17" spans="1:27" ht="15.75">
+      <c r="A17" s="62">
+        <v>19</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="65"/>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="84"/>
+      <c r="C18" s="75">
+        <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="75">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="75">
+        <f t="shared" si="1"/>
+        <v>5559</v>
+      </c>
+      <c r="T18" s="75">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="U18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="75">
+        <f t="shared" si="1"/>
+        <v>12847</v>
+      </c>
+      <c r="X18" s="60">
+        <f t="shared" si="1"/>
+        <v>53970.91</v>
+      </c>
+      <c r="Y18" s="61">
+        <f>X18-W18</f>
+        <v>41123.910000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="15.75">
+      <c r="A19" s="62">
+        <v>20</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="72"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="65"/>
+    </row>
+    <row r="20" spans="1:27" ht="15.75">
+      <c r="A20" s="66">
+        <v>21</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="74"/>
+      <c r="P20" s="74"/>
+      <c r="Q20" s="74"/>
+      <c r="R20" s="74"/>
+      <c r="S20" s="74"/>
+      <c r="T20" s="74"/>
+      <c r="U20" s="74"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="74"/>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="69"/>
+      <c r="AA20" s="44"/>
+    </row>
+    <row r="21" spans="1:27" ht="15.75">
+      <c r="A21" s="62">
+        <v>22</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="72"/>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="65"/>
+    </row>
+    <row r="22" spans="1:27" ht="15.75">
+      <c r="A22" s="66">
+        <v>23</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="S22" s="74"/>
+      <c r="T22" s="74"/>
+      <c r="U22" s="74"/>
+      <c r="V22" s="74"/>
+      <c r="W22" s="74"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="69"/>
+    </row>
+    <row r="23" spans="1:27" ht="15.75">
+      <c r="A23" s="62">
+        <v>24</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="65"/>
+    </row>
+    <row r="24" spans="1:27" ht="15.75">
+      <c r="A24" s="66">
+        <v>25</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="S24" s="74"/>
+      <c r="T24" s="74"/>
+      <c r="U24" s="74"/>
+      <c r="V24" s="74"/>
+      <c r="W24" s="74"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="69"/>
+    </row>
+    <row r="25" spans="1:27" ht="15.75">
+      <c r="A25" s="62">
+        <v>26</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="72"/>
+      <c r="W25" s="72"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="65"/>
+    </row>
+    <row r="26" spans="1:27" ht="15.75">
+      <c r="A26" s="66">
+        <v>27</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="74"/>
+      <c r="W26" s="74"/>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="69"/>
+    </row>
+    <row r="27" spans="1:27" ht="15.75">
+      <c r="A27" s="62">
+        <v>28</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="72"/>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="72"/>
+      <c r="V27" s="72"/>
+      <c r="W27" s="72"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="65"/>
+    </row>
+    <row r="28" spans="1:27" ht="15.75">
+      <c r="A28" s="66">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B28" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="74"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="74"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="69"/>
+    </row>
+    <row r="29" spans="1:27" ht="15.75">
+      <c r="A29" s="62">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B29" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="72"/>
+      <c r="V29" s="72"/>
+      <c r="W29" s="72"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="65"/>
+    </row>
+    <row r="30" spans="1:27" ht="15.75">
+      <c r="A30" s="66">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="18">
+      <c r="B30" s="67"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
+      <c r="U30" s="74"/>
+      <c r="V30" s="74"/>
+      <c r="W30" s="74"/>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="69"/>
+    </row>
+    <row r="31" spans="1:27" ht="15.75">
+      <c r="A31" s="62">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>90</v>
-      </c>
-      <c r="E3" s="16">
-        <f>C3*D3</f>
-        <v>90</v>
-      </c>
-      <c r="G3" s="18">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="16">
-        <v>318</v>
-      </c>
-      <c r="K3" s="16">
-        <f>I3*J3</f>
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30">
-      <c r="A4" s="18">
+      <c r="B31" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="72"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="65"/>
+    </row>
+    <row r="32" spans="1:27" ht="15.75">
+      <c r="A32" s="66">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16">
-        <v>90</v>
-      </c>
-      <c r="E4" s="16">
-        <f t="shared" ref="E4:E22" si="0">C4*D4</f>
-        <v>90</v>
-      </c>
-      <c r="G4" s="18">
+      <c r="B32" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="74"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="74"/>
+      <c r="Q32" s="74"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
+      <c r="U32" s="74"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="74"/>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="69"/>
+    </row>
+    <row r="33" spans="1:25" ht="15.75">
+      <c r="A33" s="62">
+        <v>3</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
+      <c r="T33" s="72"/>
+      <c r="U33" s="72"/>
+      <c r="V33" s="72"/>
+      <c r="W33" s="72"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="65"/>
+    </row>
+    <row r="34" spans="1:25" ht="15.75">
+      <c r="A34" s="66">
+        <v>4</v>
+      </c>
+      <c r="B34" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="16">
-        <v>255</v>
-      </c>
-      <c r="K4" s="16">
-        <f>I4*J4</f>
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="18">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="16">
-        <v>90</v>
-      </c>
-      <c r="E5" s="16">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="G5" s="18">
-        <v>3</v>
-      </c>
-      <c r="H5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="16">
-        <v>1200</v>
-      </c>
-      <c r="K5" s="16">
-        <f t="shared" ref="K5:K7" si="1">I5*J5</f>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="18">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16">
-        <v>200</v>
-      </c>
-      <c r="E6" s="16">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="G6" s="18">
-        <v>4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="16">
-        <v>1100</v>
-      </c>
-      <c r="K6" s="16">
-        <f t="shared" si="1"/>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="18">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16">
-        <v>200</v>
-      </c>
-      <c r="E7" s="16">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="G7" s="18">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16">
-        <v>2000</v>
-      </c>
-      <c r="K7" s="16">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="18">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="16">
-        <v>193</v>
-      </c>
-      <c r="E8" s="16">
-        <f t="shared" si="0"/>
-        <v>193</v>
-      </c>
-      <c r="G8" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="20">
-        <f>SUM(K3:K7)</f>
-        <v>4873</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="18">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="74"/>
+      <c r="Q34" s="74"/>
+      <c r="R34" s="74"/>
+      <c r="S34" s="74"/>
+      <c r="T34" s="74"/>
+      <c r="U34" s="74"/>
+      <c r="V34" s="74"/>
+      <c r="W34" s="74"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="69"/>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9" s="16">
-        <v>90</v>
-      </c>
-      <c r="E9" s="16">
-        <f t="shared" si="0"/>
-        <v>540</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="18">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B35" s="84"/>
+      <c r="C35" s="75">
+        <f>SUM(C19:C34)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="75">
+        <f t="shared" ref="D35:V35" si="2">SUM(D19:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="75">
+        <f>SUM(T19:T34)</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="75">
+        <f>SUM(W19:W34)</f>
+        <v>0</v>
+      </c>
+      <c r="X35" s="60">
+        <f>SUM(X19:X34)</f>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="61">
+        <f>X35-W35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="31.5" customHeight="1">
+      <c r="A36" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16">
-        <v>350</v>
-      </c>
-      <c r="E10" s="16">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="G10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="18">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="16">
-        <v>250</v>
-      </c>
-      <c r="E11" s="16">
-        <f t="shared" si="0"/>
-        <v>250</v>
-      </c>
-      <c r="G11" s="21"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="18">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="16">
-        <v>500</v>
-      </c>
-      <c r="E12" s="16">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="18">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16">
-        <v>150</v>
-      </c>
-      <c r="E13" s="16">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="G13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="18">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="16">
-        <v>300</v>
-      </c>
-      <c r="E14" s="16">
-        <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="18">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="16">
-        <v>350</v>
-      </c>
-      <c r="E15" s="16">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="18">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="16">
-        <v>350</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="18">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" s="16">
-        <v>250</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="G17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="18">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" s="16">
-        <v>200</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="18">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" s="16">
-        <v>210</v>
-      </c>
-      <c r="E19" s="16">
-        <f t="shared" si="0"/>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="18">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="16">
-        <v>255</v>
-      </c>
-      <c r="E20" s="16">
-        <f t="shared" si="0"/>
-        <v>255</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="18">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16">
-        <v>350</v>
-      </c>
-      <c r="E21" s="16">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="18">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16">
-        <v>240</v>
-      </c>
-      <c r="E22" s="16">
-        <f t="shared" si="0"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="18">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23" s="16">
-        <v>500</v>
-      </c>
-      <c r="E23" s="16">
-        <f>C23*D23</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="20">
-        <f>SUM(E3:E23)</f>
-        <v>6908</v>
-      </c>
+      <c r="B36" s="85"/>
+      <c r="C36" s="70">
+        <f>SUM(C18,C35)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="70">
+        <f t="shared" ref="D36:W36" si="3">SUM(D18,D35)</f>
+        <v>288</v>
+      </c>
+      <c r="E36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="70">
+        <f>SUM(S18,S35)</f>
+        <v>5559</v>
+      </c>
+      <c r="T36" s="70">
+        <f t="shared" si="3"/>
+        <v>7000</v>
+      </c>
+      <c r="U36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="70">
+        <f t="shared" si="3"/>
+        <v>12847</v>
+      </c>
+      <c r="X36" s="70">
+        <f>SUM(X18,X35)</f>
+        <v>53970.91</v>
+      </c>
+      <c r="Y36" s="70">
+        <f>SUM(Y18,Y35)</f>
+        <v>41123.910000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
+  <conditionalFormatting sqref="Y18:Y36">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>Y18&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>Y18&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4"/>
   </bookViews>
@@ -13,9 +13,9 @@
     <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -82,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -214,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -328,7 +328,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -354,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -380,7 +380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -407,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -485,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -511,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -564,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -590,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -617,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -643,7 +643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -670,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -696,7 +696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -774,7 +774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -810,7 +810,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -826,7 +826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -880,7 +880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -906,7 +906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -932,7 +932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -958,7 +958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -984,7 +984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1011,7 +1011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1065,7 +1065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1091,7 +1091,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1118,7 +1118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1144,7 +1144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0">
+    <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1171,7 +1171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0">
+    <comment ref="S6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1198,7 +1198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0">
+    <comment ref="H8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1214,7 +1214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1241,7 +1241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0">
+    <comment ref="X11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1268,7 +1268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0">
+    <comment ref="X12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1294,7 +1294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1321,7 +1321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1337,7 +1337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0">
+    <comment ref="T15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1352,7 +1352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1378,7 +1378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1404,7 +1404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1430,7 +1430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1457,7 +1457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1483,7 +1483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1509,7 +1509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1534,7 +1534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0">
+    <comment ref="T22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1559,7 +1559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="E24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1585,7 +1585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0">
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1611,7 +1611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1637,7 +1637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0">
+    <comment ref="H29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1662,7 +1662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1687,7 +1687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1712,7 +1712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0">
+    <comment ref="X30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1736,7 +1736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1760,7 +1760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1786,7 +1786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0">
+    <comment ref="X35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1822,7 +1822,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1846,7 +1846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1868,6 +1868,212 @@
           <t xml:space="preserve">
 Долг маме
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Поход в гиннес на обед</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ВПН</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Друзья</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вода, мусор</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама перевела якобы за впн, кинопоиск и бензин</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+УК Эталон</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Электроэнергия</t>
         </r>
       </text>
     </comment>
@@ -2053,7 +2259,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -2247,7 +2453,7 @@
       <family val="5"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2347,6 +2553,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2527,7 +2739,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2693,13 +2905,7 @@
     <xf numFmtId="164" fontId="22" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2738,41 +2944,14 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -3085,14 +3264,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3126,7 +3305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="16.5">
+    <row r="5" spans="3:8" ht="15.75">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -3146,7 +3325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="16.5">
+    <row r="6" spans="3:8" ht="15.75">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -3167,7 +3346,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="16.5">
+    <row r="7" spans="3:8" ht="15.75">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -3188,7 +3367,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="16.5">
+    <row r="8" spans="3:8" ht="15.75">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -3209,7 +3388,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="16.5">
+    <row r="9" spans="3:8" ht="15.75">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -3219,7 +3398,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="16.5">
+    <row r="10" spans="3:8" ht="15.75">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -3229,7 +3408,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="16.5">
+    <row r="11" spans="3:8" ht="15.75">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -3239,7 +3418,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="16.5">
+    <row r="12" spans="3:8" ht="15.75">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -3249,7 +3428,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="16.5">
+    <row r="13" spans="3:8" ht="15.75">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -3259,7 +3438,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="16.5">
+    <row r="14" spans="3:8" ht="15.75">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -3269,7 +3448,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="16.5">
+    <row r="15" spans="3:8" ht="15.75">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -3279,7 +3458,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="17.25" thickBot="1">
+    <row r="16" spans="3:8" ht="16.5" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -3289,7 +3468,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="17.25" thickBot="1">
+    <row r="17" spans="3:8" ht="16.5" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -3301,18 +3480,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="11" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3322,7 +3501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3332,32 +3511,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -4556,10 +4735,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="77"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -4672,7 +4851,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4682,32 +4861,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -5918,10 +6097,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="78" t="s">
+      <c r="A32" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -6034,7 +6213,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6044,33 +6223,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
+      <c r="Y1" s="77"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -6888,10 +7067,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="82"/>
+      <c r="B20" s="80"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -7611,10 +7790,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="81" t="s">
+      <c r="A36" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -7709,10 +7888,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="80"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -7832,7 +8011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7842,33 +8021,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -7982,31 +8161,34 @@
         <v>288</v>
       </c>
       <c r="E3" s="71"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72">
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71">
+        <f>1000+281</f>
+        <v>1281</v>
+      </c>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71">
         <f>199+4660+700</f>
         <v>5559</v>
       </c>
-      <c r="T3" s="72">
+      <c r="T3" s="71">
         <v>7000</v>
       </c>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72">
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71">
         <f>SUM(C3:V3)</f>
-        <v>12847</v>
+        <v>14128</v>
       </c>
       <c r="X3" s="64">
         <v>53970.91</v>
@@ -8020,29 +8202,37 @@
       <c r="B4" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74">
+      <c r="C4" s="72"/>
+      <c r="D4" s="72">
+        <v>110</v>
+      </c>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72">
+        <f>2500+270</f>
+        <v>2770</v>
+      </c>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72">
+        <f>363+350</f>
+        <v>713</v>
+      </c>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72">
         <f>SUM(C4:V4)</f>
-        <v>0</v>
+        <v>3593</v>
       </c>
       <c r="X4" s="68"/>
       <c r="Y4" s="69"/>
@@ -8054,29 +8244,43 @@
       <c r="B5" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
+      <c r="C5" s="71">
+        <f>1497+707</f>
+        <v>2204</v>
+      </c>
+      <c r="D5" s="71">
+        <v>520</v>
+      </c>
       <c r="E5" s="71"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="72"/>
-      <c r="V5" s="72"/>
-      <c r="W5" s="72">
+      <c r="F5" s="71">
+        <f>189</f>
+        <v>189</v>
+      </c>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71">
+        <v>750</v>
+      </c>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71">
+        <v>245</v>
+      </c>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71">
+        <v>990</v>
+      </c>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71">
         <f t="shared" ref="W5:W17" si="0">SUM(C5:V5)</f>
-        <v>0</v>
+        <v>4898</v>
       </c>
       <c r="X5" s="64"/>
       <c r="Y5" s="65"/>
@@ -8088,29 +8292,36 @@
       <c r="B6" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
-      <c r="S6" s="74"/>
-      <c r="T6" s="74"/>
-      <c r="U6" s="74"/>
-      <c r="V6" s="74"/>
-      <c r="W6" s="74">
+      <c r="C6" s="72"/>
+      <c r="D6" s="72">
+        <v>2122</v>
+      </c>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72">
+        <v>3695</v>
+      </c>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72">
+        <f>350+407+249</f>
+        <v>1006</v>
+      </c>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6823</v>
       </c>
       <c r="X6" s="68"/>
       <c r="Y6" s="69"/>
@@ -8125,28 +8336,32 @@
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
       <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="72"/>
-      <c r="U7" s="72"/>
-      <c r="V7" s="72"/>
-      <c r="W7" s="72">
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71">
+        <v>1008.31</v>
+      </c>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X7" s="64"/>
+        <v>1008.31</v>
+      </c>
+      <c r="X7" s="64">
+        <v>3000</v>
+      </c>
       <c r="Y7" s="65"/>
     </row>
     <row r="8" spans="1:47" ht="15.75">
@@ -8156,29 +8371,33 @@
       <c r="B8" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74">
+      <c r="C8" s="84">
+        <v>2500</v>
+      </c>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72">
+        <v>1763.15</v>
+      </c>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4263.1499999999996</v>
       </c>
       <c r="X8" s="68"/>
       <c r="Y8" s="69"/>
@@ -8193,26 +8412,28 @@
       <c r="C9" s="71"/>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="72"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="72">
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71">
+        <v>2244.06</v>
+      </c>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2244.06</v>
       </c>
       <c r="X9" s="64"/>
       <c r="Y9" s="65"/>
@@ -8224,29 +8445,31 @@
       <c r="B10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="74"/>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="74"/>
-      <c r="S10" s="74"/>
-      <c r="T10" s="74"/>
-      <c r="U10" s="74"/>
-      <c r="V10" s="74"/>
-      <c r="W10" s="74">
+      <c r="C10" s="84">
+        <v>2500</v>
+      </c>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="X10" s="68"/>
       <c r="Y10" s="69"/>
@@ -8261,24 +8484,24 @@
       <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72">
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8292,29 +8515,31 @@
       <c r="B12" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="74"/>
-      <c r="S12" s="74"/>
-      <c r="T12" s="74"/>
-      <c r="U12" s="74"/>
-      <c r="V12" s="74"/>
-      <c r="W12" s="74">
+      <c r="C12" s="84">
+        <v>2500</v>
+      </c>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="X12" s="68"/>
       <c r="Y12" s="69"/>
@@ -8329,24 +8554,24 @@
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="72"/>
-      <c r="V13" s="72"/>
-      <c r="W13" s="72">
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8360,29 +8585,31 @@
       <c r="B14" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74">
+      <c r="C14" s="84">
+        <v>2500</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="X14" s="68"/>
       <c r="Y14" s="69"/>
@@ -8397,24 +8624,24 @@
       <c r="C15" s="71"/>
       <c r="D15" s="71"/>
       <c r="E15" s="71"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="72"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="72">
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8428,29 +8655,31 @@
       <c r="B16" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="74"/>
-      <c r="S16" s="74"/>
-      <c r="T16" s="74"/>
-      <c r="U16" s="74"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74">
+      <c r="C16" s="84">
+        <v>2500</v>
+      </c>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="X16" s="68"/>
       <c r="Y16" s="69"/>
@@ -8465,24 +8694,24 @@
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="72">
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8490,101 +8719,101 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="84"/>
-      <c r="C18" s="75">
+      <c r="B18" s="82"/>
+      <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="75">
+        <v>14704</v>
+      </c>
+      <c r="D18" s="73">
         <f t="shared" si="1"/>
-        <v>288</v>
-      </c>
-      <c r="E18" s="75">
+        <v>3040</v>
+      </c>
+      <c r="E18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="73">
+        <f t="shared" si="1"/>
+        <v>189</v>
+      </c>
+      <c r="G18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="75">
+      <c r="H18" s="73">
+        <f t="shared" si="1"/>
+        <v>6465</v>
+      </c>
+      <c r="I18" s="73">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="J18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="75">
+      <c r="K18" s="73">
+        <f t="shared" si="1"/>
+        <v>5015.5200000000004</v>
+      </c>
+      <c r="L18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="75">
+      <c r="M18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="75">
+      <c r="N18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="75">
+      <c r="O18" s="73">
+        <f t="shared" si="1"/>
+        <v>1964</v>
+      </c>
+      <c r="P18" s="73">
+        <f t="shared" si="1"/>
+        <v>1281</v>
+      </c>
+      <c r="Q18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="75">
+      <c r="R18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M18" s="75">
+      <c r="S18" s="73">
+        <f t="shared" si="1"/>
+        <v>6549</v>
+      </c>
+      <c r="T18" s="73">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="U18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="75">
+      <c r="V18" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O18" s="75">
+      <c r="W18" s="73">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="75">
-        <f t="shared" si="1"/>
-        <v>5559</v>
-      </c>
-      <c r="T18" s="75">
-        <f t="shared" si="1"/>
-        <v>7000</v>
-      </c>
-      <c r="U18" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="75">
-        <f t="shared" si="1"/>
-        <v>12847</v>
+        <v>46957.52</v>
       </c>
       <c r="X18" s="60">
         <f t="shared" si="1"/>
-        <v>53970.91</v>
+        <v>56970.91</v>
       </c>
       <c r="Y18" s="61">
         <f>X18-W18</f>
-        <v>41123.910000000003</v>
+        <v>10013.390000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15.75">
@@ -8594,27 +8823,27 @@
       <c r="B19" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="72"/>
-      <c r="V19" s="72"/>
-      <c r="W19" s="72"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="71"/>
       <c r="X19" s="64"/>
       <c r="Y19" s="65"/>
     </row>
@@ -8625,27 +8854,27 @@
       <c r="B20" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="74"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="74"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="74"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="72"/>
       <c r="X20" s="68"/>
       <c r="Y20" s="69"/>
       <c r="AA20" s="44"/>
@@ -8657,27 +8886,27 @@
       <c r="B21" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="72"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="72"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
+      <c r="U21" s="71"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="71"/>
       <c r="X21" s="64"/>
       <c r="Y21" s="65"/>
     </row>
@@ -8688,27 +8917,27 @@
       <c r="B22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="74"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
-      <c r="S22" s="74"/>
-      <c r="T22" s="74"/>
-      <c r="U22" s="74"/>
-      <c r="V22" s="74"/>
-      <c r="W22" s="74"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
       <c r="X22" s="68"/>
       <c r="Y22" s="69"/>
     </row>
@@ -8719,27 +8948,27 @@
       <c r="B23" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="72"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="71"/>
       <c r="X23" s="64"/>
       <c r="Y23" s="65"/>
     </row>
@@ -8750,27 +8979,27 @@
       <c r="B24" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="S24" s="74"/>
-      <c r="T24" s="74"/>
-      <c r="U24" s="74"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="74"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
       <c r="X24" s="68"/>
       <c r="Y24" s="69"/>
     </row>
@@ -8781,27 +9010,27 @@
       <c r="B25" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="72"/>
-      <c r="U25" s="72"/>
-      <c r="V25" s="72"/>
-      <c r="W25" s="72"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
+      <c r="U25" s="71"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="71"/>
       <c r="X25" s="64"/>
       <c r="Y25" s="65"/>
     </row>
@@ -8812,27 +9041,27 @@
       <c r="B26" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72"/>
       <c r="X26" s="68"/>
       <c r="Y26" s="69"/>
     </row>
@@ -8843,27 +9072,27 @@
       <c r="B27" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="72"/>
-      <c r="T27" s="72"/>
-      <c r="U27" s="72"/>
-      <c r="V27" s="72"/>
-      <c r="W27" s="72"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="71"/>
+      <c r="T27" s="71"/>
+      <c r="U27" s="71"/>
+      <c r="V27" s="71"/>
+      <c r="W27" s="71"/>
       <c r="X27" s="64"/>
       <c r="Y27" s="65"/>
     </row>
@@ -8874,27 +9103,27 @@
       <c r="B28" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="74"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="74"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="74"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
       <c r="X28" s="68"/>
       <c r="Y28" s="69"/>
     </row>
@@ -8905,27 +9134,27 @@
       <c r="B29" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="72"/>
-      <c r="T29" s="72"/>
-      <c r="U29" s="72"/>
-      <c r="V29" s="72"/>
-      <c r="W29" s="72"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+      <c r="T29" s="71"/>
+      <c r="U29" s="71"/>
+      <c r="V29" s="71"/>
+      <c r="W29" s="71"/>
       <c r="X29" s="64"/>
       <c r="Y29" s="65"/>
     </row>
@@ -8934,27 +9163,27 @@
         <v>31</v>
       </c>
       <c r="B30" s="67"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="74"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="74"/>
-      <c r="T30" s="74"/>
-      <c r="U30" s="74"/>
-      <c r="V30" s="74"/>
-      <c r="W30" s="74"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
       <c r="X30" s="68"/>
       <c r="Y30" s="69"/>
     </row>
@@ -8965,27 +9194,27 @@
       <c r="B31" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
-      <c r="T31" s="72"/>
-      <c r="U31" s="72"/>
-      <c r="V31" s="72"/>
-      <c r="W31" s="72"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="71"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="71"/>
+      <c r="W31" s="71"/>
       <c r="X31" s="64"/>
       <c r="Y31" s="65"/>
     </row>
@@ -8996,27 +9225,27 @@
       <c r="B32" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="74"/>
-      <c r="T32" s="74"/>
-      <c r="U32" s="74"/>
-      <c r="V32" s="74"/>
-      <c r="W32" s="74"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
       <c r="X32" s="68"/>
       <c r="Y32" s="69"/>
     </row>
@@ -9027,27 +9256,27 @@
       <c r="B33" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
-      <c r="Q33" s="72"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="72"/>
-      <c r="T33" s="72"/>
-      <c r="U33" s="72"/>
-      <c r="V33" s="72"/>
-      <c r="W33" s="72"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="71"/>
+      <c r="U33" s="71"/>
+      <c r="V33" s="71"/>
+      <c r="W33" s="71"/>
       <c r="X33" s="64"/>
       <c r="Y33" s="65"/>
     </row>
@@ -9058,116 +9287,116 @@
       <c r="B34" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="74"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="74"/>
-      <c r="O34" s="74"/>
-      <c r="P34" s="74"/>
-      <c r="Q34" s="74"/>
-      <c r="R34" s="74"/>
-      <c r="S34" s="74"/>
-      <c r="T34" s="74"/>
-      <c r="U34" s="74"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="74"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72"/>
       <c r="X34" s="68"/>
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="75">
+      <c r="B35" s="82"/>
+      <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="75">
+      <c r="D35" s="73">
         <f t="shared" ref="D35:V35" si="2">SUM(D19:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F35" s="75">
+      <c r="F35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G35" s="75">
+      <c r="G35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J35" s="75">
+      <c r="J35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="75">
+      <c r="K35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="75">
+      <c r="L35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M35" s="75">
+      <c r="M35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N35" s="75">
+      <c r="N35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O35" s="75">
+      <c r="O35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P35" s="75">
+      <c r="P35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="75">
+      <c r="Q35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R35" s="75">
+      <c r="R35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S35" s="75">
+      <c r="S35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T35" s="75">
+      <c r="T35" s="73">
         <f>SUM(T19:T34)</f>
         <v>0</v>
       </c>
-      <c r="U35" s="75">
+      <c r="U35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V35" s="75">
+      <c r="V35" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W35" s="75">
+      <c r="W35" s="73">
         <f>SUM(W19:W34)</f>
         <v>0</v>
       </c>
@@ -9181,17 +9410,17 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="85" t="s">
+      <c r="A36" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="85"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
-        <v>0</v>
+        <v>14704</v>
       </c>
       <c r="D36" s="70">
         <f t="shared" ref="D36:W36" si="3">SUM(D18,D35)</f>
-        <v>288</v>
+        <v>3040</v>
       </c>
       <c r="E36" s="70">
         <f t="shared" si="3"/>
@@ -9199,7 +9428,7 @@
       </c>
       <c r="F36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="G36" s="70">
         <f t="shared" si="3"/>
@@ -9207,11 +9436,11 @@
       </c>
       <c r="H36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6465</v>
       </c>
       <c r="I36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="J36" s="70">
         <f t="shared" si="3"/>
@@ -9219,7 +9448,7 @@
       </c>
       <c r="K36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5015.5200000000004</v>
       </c>
       <c r="L36" s="70">
         <f t="shared" si="3"/>
@@ -9235,11 +9464,11 @@
       </c>
       <c r="O36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1964</v>
       </c>
       <c r="P36" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1281</v>
       </c>
       <c r="Q36" s="70">
         <f t="shared" si="3"/>
@@ -9251,7 +9480,7 @@
       </c>
       <c r="S36" s="70">
         <f>SUM(S18,S35)</f>
-        <v>5559</v>
+        <v>6549</v>
       </c>
       <c r="T36" s="70">
         <f t="shared" si="3"/>
@@ -9267,15 +9496,15 @@
       </c>
       <c r="W36" s="70">
         <f t="shared" si="3"/>
-        <v>12847</v>
+        <v>46957.52</v>
       </c>
       <c r="X36" s="70">
         <f>SUM(X18,X35)</f>
-        <v>53970.91</v>
+        <v>56970.91</v>
       </c>
       <c r="Y36" s="70">
         <f>SUM(Y18,Y35)</f>
-        <v>41123.910000000003</v>
+        <v>10013.390000000007</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -9298,10 +9527,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4"/>
   </bookViews>
@@ -13,9 +13,9 @@
     <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -82,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -214,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -328,7 +328,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -354,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -380,7 +380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -407,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -485,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -511,7 +511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -564,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -590,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -617,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -643,7 +643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -670,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -696,7 +696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -748,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -774,7 +774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -810,7 +810,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -826,7 +826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -853,7 +853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -880,7 +880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -906,7 +906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -932,7 +932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -958,7 +958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -984,7 +984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1011,7 +1011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1065,7 +1065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1091,7 +1091,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1118,7 +1118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1144,7 +1144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="K6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1171,7 +1171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1198,7 +1198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1214,7 +1214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1241,7 +1241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1268,7 +1268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1294,7 +1294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1321,7 +1321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1337,7 +1337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1352,7 +1352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1378,7 +1378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1404,7 +1404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1430,7 +1430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1457,7 +1457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1483,7 +1483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1509,7 +1509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1534,7 +1534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1559,7 +1559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1585,7 +1585,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1611,7 +1611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1637,7 +1637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1662,7 +1662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1687,7 +1687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1712,7 +1712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0" shapeId="0">
+    <comment ref="X30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1736,7 +1736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1760,7 +1760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1786,7 +1786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
+    <comment ref="X35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1822,7 +1822,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1846,7 +1846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1871,7 +1871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1895,7 +1895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1921,7 +1921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1947,7 +1947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1973,7 +1973,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1999,7 +1999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2025,7 +2025,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2051,7 +2051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2074,6 +2074,274 @@
           </rPr>
           <t xml:space="preserve">
 Электроэнергия</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Про мясо
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Чикен хаус</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Сиги</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Интернет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+журнал Чтиво
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс + Мяуча</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+журнал ЧТИВО
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На бенз</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Рыбалка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Теле 2</t>
         </r>
       </text>
     </comment>
@@ -2082,7 +2350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
   <si>
     <t>Число</t>
   </si>
@@ -2255,11 +2523,14 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>Доходы - Расходы Май 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -2453,7 +2724,7 @@
       <family val="5"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2553,12 +2824,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2739,7 +3004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2942,9 +3207,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3264,14 +3526,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3305,7 +3567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="15.75">
+    <row r="5" spans="3:8" ht="16.5">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -3325,7 +3587,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="15.75">
+    <row r="6" spans="3:8" ht="16.5">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -3346,7 +3608,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="15.75">
+    <row r="7" spans="3:8" ht="16.5">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -3367,7 +3629,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="15.75">
+    <row r="8" spans="3:8" ht="16.5">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -3388,7 +3650,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="15.75">
+    <row r="9" spans="3:8" ht="16.5">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -3398,7 +3660,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="15.75">
+    <row r="10" spans="3:8" ht="16.5">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -3408,7 +3670,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="15.75">
+    <row r="11" spans="3:8" ht="16.5">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -3418,7 +3680,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="15.75">
+    <row r="12" spans="3:8" ht="16.5">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -3428,7 +3690,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="15.75">
+    <row r="13" spans="3:8" ht="16.5">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -3438,7 +3700,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="15.75">
+    <row r="14" spans="3:8" ht="16.5">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -3448,7 +3710,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="15.75">
+    <row r="15" spans="3:8" ht="16.5">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -3458,7 +3720,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="16.5" thickBot="1">
+    <row r="16" spans="3:8" ht="17.25" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -3468,7 +3730,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="16.5" thickBot="1">
+    <row r="17" spans="3:8" ht="17.25" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -3501,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4851,7 +5113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6213,7 +6475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8011,7 +8273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8022,7 +8284,7 @@
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
       <c r="A1" s="81" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -8371,10 +8633,10 @@
       <c r="B8" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="84">
-        <v>2500</v>
-      </c>
-      <c r="D8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72">
+        <v>2550.04</v>
+      </c>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="72"/>
@@ -8397,7 +8659,7 @@
       <c r="V8" s="72"/>
       <c r="W8" s="72">
         <f t="shared" si="0"/>
-        <v>4263.1499999999996</v>
+        <v>4313.1900000000005</v>
       </c>
       <c r="X8" s="68"/>
       <c r="Y8" s="69"/>
@@ -8409,8 +8671,14 @@
       <c r="B9" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
+      <c r="C9" s="71">
+        <f>3150.35+125</f>
+        <v>3275.35</v>
+      </c>
+      <c r="D9" s="71">
+        <f>264+1506</f>
+        <v>1770</v>
+      </c>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
       <c r="G9" s="71"/>
@@ -8424,16 +8692,21 @@
       <c r="M9" s="71"/>
       <c r="N9" s="71"/>
       <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
+      <c r="P9" s="71">
+        <v>1000</v>
+      </c>
       <c r="Q9" s="71"/>
       <c r="R9" s="71"/>
       <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
+      <c r="T9" s="71">
+        <f>100+100+400</f>
+        <v>600</v>
+      </c>
       <c r="U9" s="71"/>
       <c r="V9" s="71"/>
       <c r="W9" s="71">
         <f t="shared" si="0"/>
-        <v>2244.06</v>
+        <v>8889.41</v>
       </c>
       <c r="X9" s="64"/>
       <c r="Y9" s="65"/>
@@ -8445,12 +8718,12 @@
       <c r="B10" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="84">
-        <v>2500</v>
-      </c>
+      <c r="C10" s="72"/>
       <c r="D10" s="72"/>
       <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
+      <c r="F10" s="72">
+        <v>1245</v>
+      </c>
       <c r="G10" s="72"/>
       <c r="H10" s="72"/>
       <c r="I10" s="72"/>
@@ -8461,7 +8734,10 @@
       <c r="N10" s="72"/>
       <c r="O10" s="72"/>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <f>1000+1000</f>
+        <v>2000</v>
+      </c>
       <c r="R10" s="72"/>
       <c r="S10" s="72"/>
       <c r="T10" s="72"/>
@@ -8469,7 +8745,7 @@
       <c r="V10" s="72"/>
       <c r="W10" s="72">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>3245</v>
       </c>
       <c r="X10" s="68"/>
       <c r="Y10" s="69"/>
@@ -8486,7 +8762,10 @@
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <f>210+1009</f>
+        <v>1219</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
@@ -8494,16 +8773,20 @@
       <c r="M11" s="71"/>
       <c r="N11" s="71"/>
       <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
+      <c r="P11" s="71">
+        <v>340</v>
+      </c>
       <c r="Q11" s="71"/>
       <c r="R11" s="71"/>
       <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
+      <c r="T11" s="71">
+        <v>1479</v>
+      </c>
       <c r="U11" s="71"/>
       <c r="V11" s="71"/>
       <c r="W11" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3038</v>
       </c>
       <c r="X11" s="64"/>
       <c r="Y11" s="65"/>
@@ -8515,9 +8798,7 @@
       <c r="B12" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="84">
-        <v>2500</v>
-      </c>
+      <c r="C12" s="72"/>
       <c r="D12" s="72"/>
       <c r="E12" s="72"/>
       <c r="F12" s="72"/>
@@ -8529,17 +8810,23 @@
       <c r="L12" s="72"/>
       <c r="M12" s="72"/>
       <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
+      <c r="O12" s="72">
+        <v>367</v>
+      </c>
+      <c r="P12" s="72">
+        <v>285</v>
+      </c>
       <c r="Q12" s="72"/>
       <c r="R12" s="72"/>
       <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
+      <c r="T12" s="72">
+        <v>220</v>
+      </c>
       <c r="U12" s="72"/>
       <c r="V12" s="72"/>
       <c r="W12" s="72">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>872</v>
       </c>
       <c r="X12" s="68"/>
       <c r="Y12" s="69"/>
@@ -8556,7 +8843,9 @@
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="H13" s="71">
+        <v>1220</v>
+      </c>
       <c r="I13" s="71"/>
       <c r="J13" s="71"/>
       <c r="K13" s="71"/>
@@ -8564,8 +8853,12 @@
       <c r="M13" s="71"/>
       <c r="N13" s="71"/>
       <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
+      <c r="P13" s="71">
+        <v>131</v>
+      </c>
+      <c r="Q13" s="71">
+        <v>1012</v>
+      </c>
       <c r="R13" s="71"/>
       <c r="S13" s="71"/>
       <c r="T13" s="71"/>
@@ -8573,7 +8866,7 @@
       <c r="V13" s="71"/>
       <c r="W13" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2363</v>
       </c>
       <c r="X13" s="64"/>
       <c r="Y13" s="65"/>
@@ -8585,10 +8878,13 @@
       <c r="B14" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="84">
-        <v>2500</v>
-      </c>
-      <c r="D14" s="72"/>
+      <c r="C14" s="72">
+        <f>384+1318+1214</f>
+        <v>2916</v>
+      </c>
+      <c r="D14" s="72">
+        <v>1351.32</v>
+      </c>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
       <c r="G14" s="72"/>
@@ -8601,7 +8897,9 @@
       <c r="N14" s="72"/>
       <c r="O14" s="72"/>
       <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
+      <c r="Q14" s="72">
+        <v>450</v>
+      </c>
       <c r="R14" s="72"/>
       <c r="S14" s="72"/>
       <c r="T14" s="72"/>
@@ -8609,7 +8907,7 @@
       <c r="V14" s="72"/>
       <c r="W14" s="72">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>4717.32</v>
       </c>
       <c r="X14" s="68"/>
       <c r="Y14" s="69"/>
@@ -8621,7 +8919,9 @@
       <c r="B15" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="71"/>
+      <c r="C15" s="71">
+        <v>33</v>
+      </c>
       <c r="D15" s="71"/>
       <c r="E15" s="71"/>
       <c r="F15" s="71"/>
@@ -8643,7 +8943,7 @@
       <c r="V15" s="71"/>
       <c r="W15" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="X15" s="64"/>
       <c r="Y15" s="65"/>
@@ -8655,9 +8955,7 @@
       <c r="B16" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="84">
-        <v>2500</v>
-      </c>
+      <c r="C16" s="72"/>
       <c r="D16" s="72"/>
       <c r="E16" s="72"/>
       <c r="F16" s="72"/>
@@ -8670,7 +8968,9 @@
       <c r="M16" s="72"/>
       <c r="N16" s="72"/>
       <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
+      <c r="P16" s="72">
+        <v>280</v>
+      </c>
       <c r="Q16" s="72"/>
       <c r="R16" s="72"/>
       <c r="S16" s="72"/>
@@ -8679,7 +8979,7 @@
       <c r="V16" s="72"/>
       <c r="W16" s="72">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>280</v>
       </c>
       <c r="X16" s="68"/>
       <c r="Y16" s="69"/>
@@ -8725,11 +9025,11 @@
       <c r="B18" s="82"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
-        <v>14704</v>
+        <v>8428.35</v>
       </c>
       <c r="D18" s="73">
         <f t="shared" si="1"/>
-        <v>3040</v>
+        <v>8711.36</v>
       </c>
       <c r="E18" s="73">
         <f t="shared" si="1"/>
@@ -8737,7 +9037,7 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" si="1"/>
-        <v>189</v>
+        <v>1434</v>
       </c>
       <c r="G18" s="73">
         <f t="shared" si="1"/>
@@ -8745,7 +9045,7 @@
       </c>
       <c r="H18" s="73">
         <f t="shared" si="1"/>
-        <v>6465</v>
+        <v>8904</v>
       </c>
       <c r="I18" s="73">
         <f t="shared" si="1"/>
@@ -8773,15 +9073,15 @@
       </c>
       <c r="O18" s="73">
         <f t="shared" si="1"/>
-        <v>1964</v>
+        <v>2331</v>
       </c>
       <c r="P18" s="73">
         <f t="shared" si="1"/>
-        <v>1281</v>
+        <v>3317</v>
       </c>
       <c r="Q18" s="73">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3462</v>
       </c>
       <c r="R18" s="73">
         <f t="shared" si="1"/>
@@ -8793,7 +9093,7 @@
       </c>
       <c r="T18" s="73">
         <f t="shared" si="1"/>
-        <v>7000</v>
+        <v>9299</v>
       </c>
       <c r="U18" s="73">
         <f t="shared" si="1"/>
@@ -8805,7 +9105,7 @@
       </c>
       <c r="W18" s="73">
         <f t="shared" si="1"/>
-        <v>46957.52</v>
+        <v>58201.23</v>
       </c>
       <c r="X18" s="60">
         <f t="shared" si="1"/>
@@ -8813,7 +9113,7 @@
       </c>
       <c r="Y18" s="61">
         <f>X18-W18</f>
-        <v>10013.390000000007</v>
+        <v>-1230.3199999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15.75">
@@ -8823,8 +9123,12 @@
       <c r="B19" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
+      <c r="C19" s="71">
+        <v>953</v>
+      </c>
+      <c r="D19" s="71">
+        <v>1805.6</v>
+      </c>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
@@ -8837,14 +9141,23 @@
       <c r="N19" s="71"/>
       <c r="O19" s="71"/>
       <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
+      <c r="Q19" s="71">
+        <v>285</v>
+      </c>
       <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
+      <c r="S19" s="71">
+        <v>700</v>
+      </c>
       <c r="T19" s="71"/>
       <c r="U19" s="71"/>
       <c r="V19" s="71"/>
-      <c r="W19" s="71"/>
-      <c r="X19" s="64"/>
+      <c r="W19" s="71">
+        <f>SUM(C19:V19)</f>
+        <v>3743.6</v>
+      </c>
+      <c r="X19" s="64">
+        <v>32088.14</v>
+      </c>
       <c r="Y19" s="65"/>
     </row>
     <row r="20" spans="1:27" ht="15.75">
@@ -8855,7 +9168,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
+      <c r="D20" s="72">
+        <f>1303+346+262</f>
+        <v>1911</v>
+      </c>
       <c r="E20" s="72"/>
       <c r="F20" s="72"/>
       <c r="G20" s="72"/>
@@ -8866,15 +9182,25 @@
       <c r="L20" s="72"/>
       <c r="M20" s="72"/>
       <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
+      <c r="O20" s="72">
+        <f>553+689</f>
+        <v>1242</v>
+      </c>
       <c r="P20" s="72"/>
       <c r="Q20" s="72"/>
       <c r="R20" s="72"/>
       <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="72"/>
+      <c r="T20" s="72">
+        <v>849</v>
+      </c>
+      <c r="U20" s="72">
+        <v>2000</v>
+      </c>
       <c r="V20" s="72"/>
-      <c r="W20" s="72"/>
+      <c r="W20" s="72">
+        <f t="shared" ref="W20:W34" si="2">SUM(C20:V20)</f>
+        <v>6002</v>
+      </c>
       <c r="X20" s="68"/>
       <c r="Y20" s="69"/>
       <c r="AA20" s="44"/>
@@ -8886,28 +9212,47 @@
       <c r="B21" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>500</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
       <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
+      <c r="H21" s="71">
+        <f>1556+2900</f>
+        <v>4456</v>
+      </c>
+      <c r="I21" s="71">
+        <f>2101.91-500</f>
+        <v>1601.9099999999999</v>
+      </c>
       <c r="J21" s="71"/>
       <c r="K21" s="71"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="71"/>
       <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
+      <c r="P21" s="71">
+        <v>25.18</v>
+      </c>
       <c r="Q21" s="71"/>
       <c r="R21" s="71"/>
       <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
+      <c r="T21" s="71">
+        <v>800</v>
+      </c>
+      <c r="U21" s="71">
+        <v>316</v>
+      </c>
       <c r="V21" s="71"/>
-      <c r="W21" s="71"/>
-      <c r="X21" s="64"/>
+      <c r="W21" s="71">
+        <f t="shared" si="2"/>
+        <v>7699.09</v>
+      </c>
+      <c r="X21" s="64">
+        <v>1000</v>
+      </c>
       <c r="Y21" s="65"/>
     </row>
     <row r="22" spans="1:27" ht="15.75">
@@ -8917,7 +9262,9 @@
       <c r="B22" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="72"/>
+      <c r="C22" s="72">
+        <v>833</v>
+      </c>
       <c r="D22" s="72"/>
       <c r="E22" s="72"/>
       <c r="F22" s="72"/>
@@ -8929,7 +9276,9 @@
       <c r="L22" s="72"/>
       <c r="M22" s="72"/>
       <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
+      <c r="O22" s="72">
+        <v>332</v>
+      </c>
       <c r="P22" s="72"/>
       <c r="Q22" s="72"/>
       <c r="R22" s="72"/>
@@ -8937,7 +9286,10 @@
       <c r="T22" s="72"/>
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
-      <c r="W22" s="72"/>
+      <c r="W22" s="72">
+        <f t="shared" si="2"/>
+        <v>1165</v>
+      </c>
       <c r="X22" s="68"/>
       <c r="Y22" s="69"/>
     </row>
@@ -8948,7 +9300,10 @@
       <c r="B23" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <f>119+1463</f>
+        <v>1582</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -8968,7 +9323,10 @@
       <c r="T23" s="71"/>
       <c r="U23" s="71"/>
       <c r="V23" s="71"/>
-      <c r="W23" s="71"/>
+      <c r="W23" s="71">
+        <f t="shared" si="2"/>
+        <v>1582</v>
+      </c>
       <c r="X23" s="64"/>
       <c r="Y23" s="65"/>
     </row>
@@ -8986,20 +9344,29 @@
       <c r="G24" s="72"/>
       <c r="H24" s="72"/>
       <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
+      <c r="J24" s="72">
+        <v>3600</v>
+      </c>
       <c r="K24" s="72"/>
       <c r="L24" s="72"/>
       <c r="M24" s="72"/>
       <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
+      <c r="O24" s="72">
+        <v>397</v>
+      </c>
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
+      <c r="S24" s="72">
+        <v>700</v>
+      </c>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
-      <c r="W24" s="72"/>
+      <c r="W24" s="72">
+        <f t="shared" si="2"/>
+        <v>4697</v>
+      </c>
       <c r="X24" s="68"/>
       <c r="Y24" s="69"/>
     </row>
@@ -9030,7 +9397,10 @@
       <c r="T25" s="71"/>
       <c r="U25" s="71"/>
       <c r="V25" s="71"/>
-      <c r="W25" s="71"/>
+      <c r="W25" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X25" s="64"/>
       <c r="Y25" s="65"/>
     </row>
@@ -9061,7 +9431,10 @@
       <c r="T26" s="72"/>
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
-      <c r="W26" s="72"/>
+      <c r="W26" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X26" s="68"/>
       <c r="Y26" s="69"/>
     </row>
@@ -9092,7 +9465,10 @@
       <c r="T27" s="71"/>
       <c r="U27" s="71"/>
       <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
+      <c r="W27" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X27" s="64"/>
       <c r="Y27" s="65"/>
     </row>
@@ -9123,7 +9499,10 @@
       <c r="T28" s="72"/>
       <c r="U28" s="72"/>
       <c r="V28" s="72"/>
-      <c r="W28" s="72"/>
+      <c r="W28" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X28" s="68"/>
       <c r="Y28" s="69"/>
     </row>
@@ -9154,7 +9533,10 @@
       <c r="T29" s="71"/>
       <c r="U29" s="71"/>
       <c r="V29" s="71"/>
-      <c r="W29" s="71"/>
+      <c r="W29" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X29" s="64"/>
       <c r="Y29" s="65"/>
     </row>
@@ -9162,7 +9544,9 @@
       <c r="A30" s="66">
         <v>31</v>
       </c>
-      <c r="B30" s="67"/>
+      <c r="B30" s="67" t="s">
+        <v>6</v>
+      </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
       <c r="E30" s="72"/>
@@ -9183,7 +9567,10 @@
       <c r="T30" s="72"/>
       <c r="U30" s="72"/>
       <c r="V30" s="72"/>
-      <c r="W30" s="72"/>
+      <c r="W30" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X30" s="68"/>
       <c r="Y30" s="69"/>
     </row>
@@ -9192,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="71"/>
       <c r="D31" s="71"/>
@@ -9214,7 +9601,10 @@
       <c r="T31" s="71"/>
       <c r="U31" s="71"/>
       <c r="V31" s="71"/>
-      <c r="W31" s="71"/>
+      <c r="W31" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X31" s="64"/>
       <c r="Y31" s="65"/>
     </row>
@@ -9223,7 +9613,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -9245,7 +9635,10 @@
       <c r="T32" s="72"/>
       <c r="U32" s="72"/>
       <c r="V32" s="72"/>
-      <c r="W32" s="72"/>
+      <c r="W32" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X32" s="68"/>
       <c r="Y32" s="69"/>
     </row>
@@ -9254,7 +9647,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C33" s="71"/>
       <c r="D33" s="71"/>
@@ -9276,7 +9669,10 @@
       <c r="T33" s="71"/>
       <c r="U33" s="71"/>
       <c r="V33" s="71"/>
-      <c r="W33" s="71"/>
+      <c r="W33" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X33" s="64"/>
       <c r="Y33" s="65"/>
     </row>
@@ -9285,7 +9681,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="67" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -9307,7 +9703,10 @@
       <c r="T34" s="72"/>
       <c r="U34" s="72"/>
       <c r="V34" s="72"/>
-      <c r="W34" s="72"/>
+      <c r="W34" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="X34" s="68"/>
       <c r="Y34" s="69"/>
     </row>
@@ -9318,95 +9717,95 @@
       <c r="B35" s="82"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
+        <v>3868</v>
+      </c>
+      <c r="D35" s="73">
+        <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
+        <v>3716.6</v>
+      </c>
+      <c r="E35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D35" s="73">
-        <f t="shared" ref="D35:V35" si="2">SUM(D19:D34)</f>
+      <c r="F35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E35" s="73">
-        <f t="shared" si="2"/>
+      <c r="G35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="73">
-        <f t="shared" si="2"/>
+      <c r="H35" s="73">
+        <f t="shared" si="3"/>
+        <v>4456</v>
+      </c>
+      <c r="I35" s="73">
+        <f t="shared" si="3"/>
+        <v>1601.9099999999999</v>
+      </c>
+      <c r="J35" s="73">
+        <f t="shared" si="3"/>
+        <v>3600</v>
+      </c>
+      <c r="K35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="73">
-        <f t="shared" si="2"/>
+      <c r="L35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H35" s="73">
-        <f t="shared" si="2"/>
+      <c r="M35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I35" s="73">
-        <f t="shared" si="2"/>
+      <c r="N35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="73">
-        <f t="shared" si="2"/>
+      <c r="O35" s="73">
+        <f t="shared" si="3"/>
+        <v>1971</v>
+      </c>
+      <c r="P35" s="73">
+        <f t="shared" si="3"/>
+        <v>25.18</v>
+      </c>
+      <c r="Q35" s="73">
+        <f t="shared" si="3"/>
+        <v>285</v>
+      </c>
+      <c r="R35" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="S35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1400</v>
       </c>
       <c r="T35" s="73">
         <f>SUM(T19:T34)</f>
-        <v>0</v>
+        <v>1649</v>
       </c>
       <c r="U35" s="73">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>2316</v>
       </c>
       <c r="V35" s="73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W35" s="73">
         <f>SUM(W19:W34)</f>
-        <v>0</v>
+        <v>24888.690000000002</v>
       </c>
       <c r="X35" s="60">
         <f>SUM(X19:X34)</f>
-        <v>0</v>
+        <v>33088.14</v>
       </c>
       <c r="Y35" s="61">
         <f>X35-W35</f>
-        <v>0</v>
+        <v>8199.4499999999971</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
@@ -9416,95 +9815,95 @@
       <c r="B36" s="83"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
-        <v>14704</v>
+        <v>12296.35</v>
       </c>
       <c r="D36" s="70">
-        <f t="shared" ref="D36:W36" si="3">SUM(D18,D35)</f>
-        <v>3040</v>
+        <f t="shared" ref="D36:W36" si="4">SUM(D18,D35)</f>
+        <v>12427.960000000001</v>
       </c>
       <c r="E36" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F36" s="70">
-        <f t="shared" si="3"/>
-        <v>189</v>
+        <f t="shared" si="4"/>
+        <v>1434</v>
       </c>
       <c r="G36" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H36" s="70">
-        <f t="shared" si="3"/>
-        <v>6465</v>
+        <f t="shared" si="4"/>
+        <v>13360</v>
       </c>
       <c r="I36" s="70">
-        <f t="shared" si="3"/>
-        <v>750</v>
+        <f t="shared" si="4"/>
+        <v>2351.91</v>
       </c>
       <c r="J36" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>3600</v>
+      </c>
+      <c r="K36" s="70">
+        <f t="shared" si="4"/>
+        <v>5015.5200000000004</v>
+      </c>
+      <c r="L36" s="70">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K36" s="70">
-        <f t="shared" si="3"/>
-        <v>5015.5200000000004</v>
-      </c>
-      <c r="L36" s="70">
-        <f t="shared" si="3"/>
+      <c r="M36" s="70">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M36" s="70">
-        <f t="shared" si="3"/>
+      <c r="N36" s="70">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N36" s="70">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="O36" s="70">
-        <f t="shared" si="3"/>
-        <v>1964</v>
+        <f t="shared" si="4"/>
+        <v>4302</v>
       </c>
       <c r="P36" s="70">
-        <f t="shared" si="3"/>
-        <v>1281</v>
+        <f t="shared" si="4"/>
+        <v>3342.18</v>
       </c>
       <c r="Q36" s="70">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3747</v>
       </c>
       <c r="R36" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S36" s="70">
         <f>SUM(S18,S35)</f>
-        <v>6549</v>
+        <v>7949</v>
       </c>
       <c r="T36" s="70">
-        <f t="shared" si="3"/>
-        <v>7000</v>
+        <f t="shared" si="4"/>
+        <v>10948</v>
       </c>
       <c r="U36" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>2316</v>
+      </c>
+      <c r="V36" s="70">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V36" s="70">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="W36" s="70">
-        <f t="shared" si="3"/>
-        <v>46957.52</v>
+        <f t="shared" si="4"/>
+        <v>83089.920000000013</v>
       </c>
       <c r="X36" s="70">
         <f>SUM(X18,X35)</f>
-        <v>56970.91</v>
+        <v>90059.05</v>
       </c>
       <c r="Y36" s="70">
         <f>SUM(Y18,Y35)</f>
-        <v>10013.390000000007</v>
+        <v>6969.1299999999974</v>
       </c>
     </row>
     <row r="40" spans="1:25">

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная" sheetId="5" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Март 2026" sheetId="1" r:id="rId3"/>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
+    <sheet name=" Июнь 2026" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -2345,12 +2346,336 @@
         </r>
       </text>
     </comment>
+    <comment ref="V25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Журнальчики</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Поход в кино
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Додо пицца</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама дала в долг</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс + доля за орнамент</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама перевела на бензин, впн, кинопоиск
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КФЦ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ВК музыка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Журнал ЧТИВО</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="58">
   <si>
     <t>Число</t>
   </si>
@@ -2534,7 +2859,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2722,6 +3047,30 @@
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Algerian"/>
       <family val="5"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B050"/>
+      <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="18">
@@ -3004,7 +3353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3209,11 +3558,34 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -3526,7 +3898,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3742,18 +4114,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9337,7 +9709,10 @@
       <c r="B24" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="72"/>
+      <c r="C24" s="72">
+        <f>440</f>
+        <v>440</v>
+      </c>
       <c r="D24" s="72"/>
       <c r="E24" s="72"/>
       <c r="F24" s="72"/>
@@ -9352,7 +9727,8 @@
       <c r="M24" s="72"/>
       <c r="N24" s="72"/>
       <c r="O24" s="72">
-        <v>397</v>
+        <f>397+401</f>
+        <v>798</v>
       </c>
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
@@ -9360,12 +9736,1605 @@
       <c r="S24" s="72">
         <v>700</v>
       </c>
+      <c r="T24" s="72">
+        <v>200</v>
+      </c>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72">
+        <f t="shared" si="2"/>
+        <v>5738</v>
+      </c>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="69"/>
+    </row>
+    <row r="25" spans="1:27" ht="15.75">
+      <c r="A25" s="62">
+        <v>26</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71">
+        <f>637</f>
+        <v>637</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71">
+        <f>249+309</f>
+        <v>558</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71">
+        <v>598</v>
+      </c>
+      <c r="U25" s="71"/>
+      <c r="V25" s="71">
+        <f>1555+50</f>
+        <v>1605</v>
+      </c>
+      <c r="W25" s="71">
+        <f t="shared" si="2"/>
+        <v>3398</v>
+      </c>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="65"/>
+    </row>
+    <row r="26" spans="1:27" ht="15.75">
+      <c r="A26" s="66">
+        <v>27</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="69"/>
+    </row>
+    <row r="27" spans="1:27" ht="15.75">
+      <c r="A27" s="62">
+        <v>28</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71">
+        <v>158</v>
+      </c>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71">
+        <f>273+500</f>
+        <v>773</v>
+      </c>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="71">
+        <f>249</f>
+        <v>249</v>
+      </c>
+      <c r="T27" s="71"/>
+      <c r="U27" s="71"/>
+      <c r="V27" s="71"/>
+      <c r="W27" s="71">
+        <f t="shared" si="2"/>
+        <v>1180</v>
+      </c>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="65"/>
+    </row>
+    <row r="28" spans="1:27" ht="15.75">
+      <c r="A28" s="66">
+        <v>29</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="72">
+        <v>1121</v>
+      </c>
+      <c r="D28" s="72">
+        <v>661</v>
+      </c>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72">
+        <f>220+726</f>
+        <v>946</v>
+      </c>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72">
+        <f>204+233</f>
+        <v>437</v>
+      </c>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72">
+        <f>390+1100</f>
+        <v>1490</v>
+      </c>
+      <c r="W28" s="72">
+        <f t="shared" si="2"/>
+        <v>4655</v>
+      </c>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="69"/>
+    </row>
+    <row r="29" spans="1:27" ht="15.75">
+      <c r="A29" s="62">
+        <v>30</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="71">
+        <f>2136</f>
+        <v>2136</v>
+      </c>
+      <c r="D29" s="71">
+        <v>1318.68</v>
+      </c>
+      <c r="E29" s="71">
+        <v>1330</v>
+      </c>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+      <c r="T29" s="71"/>
+      <c r="U29" s="71"/>
+      <c r="V29" s="71"/>
+      <c r="W29" s="71">
+        <f t="shared" si="2"/>
+        <v>4784.68</v>
+      </c>
+      <c r="X29" s="64">
+        <v>5000</v>
+      </c>
+      <c r="Y29" s="65"/>
+    </row>
+    <row r="30" spans="1:27" ht="15.75">
+      <c r="A30" s="66">
+        <v>31</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="72">
+        <f>493.95+190+90+150+1613.51</f>
+        <v>2537.46</v>
+      </c>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72">
+        <v>500</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72">
+        <f t="shared" si="2"/>
+        <v>3037.46</v>
+      </c>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="69"/>
+    </row>
+    <row r="31" spans="1:27" ht="15.75">
+      <c r="A31" s="62">
+        <v>1</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71">
+        <f>500+2720</f>
+        <v>3220</v>
+      </c>
+      <c r="O31" s="71">
+        <v>241</v>
+      </c>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71">
+        <f>300+841</f>
+        <v>1141</v>
+      </c>
+      <c r="T31" s="71"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="71"/>
+      <c r="W31" s="71">
+        <f t="shared" si="2"/>
+        <v>4602</v>
+      </c>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="65"/>
+    </row>
+    <row r="32" spans="1:27" ht="15.75">
+      <c r="A32" s="66">
+        <v>2</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="69"/>
+    </row>
+    <row r="33" spans="1:25" ht="15.75">
+      <c r="A33" s="62">
+        <v>3</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="71"/>
+      <c r="U33" s="71"/>
+      <c r="V33" s="71"/>
+      <c r="W33" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="65"/>
+    </row>
+    <row r="34" spans="1:25" ht="15.75">
+      <c r="A34" s="66">
+        <v>4</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="68">
+        <v>3000</v>
+      </c>
+      <c r="Y34" s="69"/>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="82"/>
+      <c r="C35" s="73">
+        <f>SUM(C19:C34)</f>
+        <v>10739.46</v>
+      </c>
+      <c r="D35" s="73">
+        <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
+        <v>5696.2800000000007</v>
+      </c>
+      <c r="E35" s="73">
+        <f t="shared" si="3"/>
+        <v>1330</v>
+      </c>
+      <c r="F35" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="73">
+        <f t="shared" si="3"/>
+        <v>5560</v>
+      </c>
+      <c r="I35" s="73">
+        <f t="shared" si="3"/>
+        <v>1601.9099999999999</v>
+      </c>
+      <c r="J35" s="73">
+        <f t="shared" si="3"/>
+        <v>3600</v>
+      </c>
+      <c r="K35" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="73">
+        <f t="shared" si="3"/>
+        <v>437</v>
+      </c>
+      <c r="M35" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="73">
+        <f t="shared" si="3"/>
+        <v>3220</v>
+      </c>
+      <c r="O35" s="73">
+        <f t="shared" si="3"/>
+        <v>3944</v>
+      </c>
+      <c r="P35" s="73">
+        <f t="shared" si="3"/>
+        <v>25.18</v>
+      </c>
+      <c r="Q35" s="73">
+        <f t="shared" si="3"/>
+        <v>785</v>
+      </c>
+      <c r="R35" s="73">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="73">
+        <f t="shared" si="3"/>
+        <v>2790</v>
+      </c>
+      <c r="T35" s="73">
+        <f>SUM(T19:T34)</f>
+        <v>2447</v>
+      </c>
+      <c r="U35" s="73">
+        <f t="shared" si="3"/>
+        <v>2316</v>
+      </c>
+      <c r="V35" s="73">
+        <f t="shared" si="3"/>
+        <v>3095</v>
+      </c>
+      <c r="W35" s="73">
+        <f>SUM(W19:W34)</f>
+        <v>47586.83</v>
+      </c>
+      <c r="X35" s="60">
+        <f>SUM(X19:X34)</f>
+        <v>41088.14</v>
+      </c>
+      <c r="Y35" s="61">
+        <f>X35-W35</f>
+        <v>-6498.6900000000023</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="31.5" customHeight="1">
+      <c r="A36" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="83"/>
+      <c r="C36" s="70">
+        <f>SUM(C18,C35)</f>
+        <v>19167.809999999998</v>
+      </c>
+      <c r="D36" s="70">
+        <f t="shared" ref="D36:W36" si="4">SUM(D18,D35)</f>
+        <v>14407.640000000001</v>
+      </c>
+      <c r="E36" s="70">
+        <f t="shared" si="4"/>
+        <v>1330</v>
+      </c>
+      <c r="F36" s="70">
+        <f t="shared" si="4"/>
+        <v>1434</v>
+      </c>
+      <c r="G36" s="70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="70">
+        <f t="shared" si="4"/>
+        <v>14464</v>
+      </c>
+      <c r="I36" s="70">
+        <f t="shared" si="4"/>
+        <v>2351.91</v>
+      </c>
+      <c r="J36" s="70">
+        <f t="shared" si="4"/>
+        <v>3600</v>
+      </c>
+      <c r="K36" s="70">
+        <f t="shared" si="4"/>
+        <v>5015.5200000000004</v>
+      </c>
+      <c r="L36" s="70">
+        <f t="shared" si="4"/>
+        <v>437</v>
+      </c>
+      <c r="M36" s="70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="70">
+        <f t="shared" si="4"/>
+        <v>3220</v>
+      </c>
+      <c r="O36" s="70">
+        <f t="shared" si="4"/>
+        <v>6275</v>
+      </c>
+      <c r="P36" s="70">
+        <f t="shared" si="4"/>
+        <v>3342.18</v>
+      </c>
+      <c r="Q36" s="70">
+        <f t="shared" si="4"/>
+        <v>4247</v>
+      </c>
+      <c r="R36" s="70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="70">
+        <f>SUM(S18,S35)</f>
+        <v>9339</v>
+      </c>
+      <c r="T36" s="70">
+        <f t="shared" si="4"/>
+        <v>11746</v>
+      </c>
+      <c r="U36" s="70">
+        <f t="shared" si="4"/>
+        <v>2316</v>
+      </c>
+      <c r="V36" s="70">
+        <f t="shared" si="4"/>
+        <v>3095</v>
+      </c>
+      <c r="W36" s="70">
+        <f t="shared" si="4"/>
+        <v>105788.06</v>
+      </c>
+      <c r="X36" s="70">
+        <f>SUM(X18,X35)</f>
+        <v>98059.05</v>
+      </c>
+      <c r="Y36" s="70">
+        <f>SUM(Y18,Y35)</f>
+        <v>-7729.010000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+  </mergeCells>
+  <conditionalFormatting sqref="Y18:Y36">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>Y18&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>Y18&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AU40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" ht="60.75" customHeight="1">
+      <c r="A1" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="84"/>
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="84"/>
+    </row>
+    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="A2" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="87" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="87" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="87" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+    </row>
+    <row r="3" spans="1:47" ht="15.75">
+      <c r="A3" s="62">
+        <v>5</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71">
+        <v>596</v>
+      </c>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71">
+        <v>271</v>
+      </c>
+      <c r="P3" s="71">
+        <v>1000</v>
+      </c>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71">
+        <f>199</f>
+        <v>199</v>
+      </c>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71">
+        <f>850</f>
+        <v>850</v>
+      </c>
+      <c r="W3" s="71">
+        <f>SUM(C3:V3)</f>
+        <v>2916</v>
+      </c>
+      <c r="X3" s="64">
+        <f>35654.26+22580</f>
+        <v>58234.26</v>
+      </c>
+      <c r="Y3" s="65"/>
+    </row>
+    <row r="4" spans="1:47" ht="15.75">
+      <c r="A4" s="66">
+        <v>6</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72">
+        <f>SUM(C4:V4)</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="69"/>
+    </row>
+    <row r="5" spans="1:47" ht="15.75">
+      <c r="A5" s="62">
+        <v>7</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71">
+        <f t="shared" ref="W5:W17" si="0">SUM(C5:V5)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="65"/>
+    </row>
+    <row r="6" spans="1:47" ht="15.75">
+      <c r="A6" s="66">
+        <v>8</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="69"/>
+    </row>
+    <row r="7" spans="1:47" ht="15.75">
+      <c r="A7" s="62">
+        <v>9</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="65"/>
+    </row>
+    <row r="8" spans="1:47" ht="15.75">
+      <c r="A8" s="66">
+        <v>10</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="69"/>
+    </row>
+    <row r="9" spans="1:47" ht="15.75">
+      <c r="A9" s="62">
+        <v>11</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="65"/>
+    </row>
+    <row r="10" spans="1:47" ht="15.75">
+      <c r="A10" s="66">
+        <v>12</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="69"/>
+    </row>
+    <row r="11" spans="1:47" ht="15.75">
+      <c r="A11" s="62">
+        <v>13</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="65"/>
+    </row>
+    <row r="12" spans="1:47" ht="15.75">
+      <c r="A12" s="66">
+        <v>14</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="69"/>
+    </row>
+    <row r="13" spans="1:47" ht="15.75">
+      <c r="A13" s="62">
+        <v>15</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="65"/>
+    </row>
+    <row r="14" spans="1:47" ht="15.75">
+      <c r="A14" s="66">
+        <v>16</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="68"/>
+      <c r="Y14" s="69"/>
+    </row>
+    <row r="15" spans="1:47" ht="15.75">
+      <c r="A15" s="62">
+        <v>17</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="65"/>
+    </row>
+    <row r="16" spans="1:47" ht="15.75">
+      <c r="A16" s="66">
+        <v>18</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="68"/>
+      <c r="Y16" s="69"/>
+    </row>
+    <row r="17" spans="1:27" ht="15.75">
+      <c r="A17" s="62">
+        <v>19</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="65"/>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="85" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="85"/>
+      <c r="C18" s="86">
+        <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="86">
+        <f t="shared" si="1"/>
+        <v>596</v>
+      </c>
+      <c r="G18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="86">
+        <f t="shared" si="1"/>
+        <v>271</v>
+      </c>
+      <c r="P18" s="86">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="Q18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="86">
+        <f t="shared" si="1"/>
+        <v>199</v>
+      </c>
+      <c r="T18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="86">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="W18" s="86">
+        <f t="shared" si="1"/>
+        <v>2916</v>
+      </c>
+      <c r="X18" s="88">
+        <f t="shared" si="1"/>
+        <v>58234.26</v>
+      </c>
+      <c r="Y18" s="61">
+        <f>X18-W18</f>
+        <v>55318.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="15.75">
+      <c r="A19" s="62">
+        <v>20</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="71">
+        <f>SUM(C19:V19)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="65"/>
+    </row>
+    <row r="20" spans="1:27" ht="15.75">
+      <c r="A20" s="66">
+        <v>21</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="72">
+        <f t="shared" ref="W20:W34" si="2">SUM(C20:V20)</f>
+        <v>0</v>
+      </c>
+      <c r="X20" s="68"/>
+      <c r="Y20" s="69"/>
+      <c r="AA20" s="44"/>
+    </row>
+    <row r="21" spans="1:27" ht="15.75">
+      <c r="A21" s="62">
+        <v>22</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
+      <c r="U21" s="71"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="65"/>
+    </row>
+    <row r="22" spans="1:27" ht="15.75">
+      <c r="A22" s="66">
+        <v>23</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="69"/>
+    </row>
+    <row r="23" spans="1:27" ht="15.75">
+      <c r="A23" s="62">
+        <v>24</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="65"/>
+    </row>
+    <row r="24" spans="1:27" ht="15.75">
+      <c r="A24" s="66">
+        <v>25</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
       <c r="W24" s="72">
         <f t="shared" si="2"/>
-        <v>4697</v>
+        <v>0</v>
       </c>
       <c r="X24" s="68"/>
       <c r="Y24" s="69"/>
@@ -9375,7 +11344,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" s="71"/>
       <c r="D25" s="71"/>
@@ -9409,7 +11378,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" s="72"/>
       <c r="D26" s="72"/>
@@ -9443,7 +11412,7 @@
         <v>28</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C27" s="71"/>
       <c r="D27" s="71"/>
@@ -9477,7 +11446,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="72"/>
@@ -9511,7 +11480,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C29" s="71"/>
       <c r="D29" s="71"/>
@@ -9545,7 +11514,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
@@ -9579,7 +11548,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C31" s="71"/>
       <c r="D31" s="71"/>
@@ -9613,7 +11582,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -9647,7 +11616,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" s="71"/>
       <c r="D33" s="71"/>
@@ -9681,7 +11650,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="67" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -9711,199 +11680,199 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="82"/>
-      <c r="C35" s="73">
+      <c r="B35" s="85"/>
+      <c r="C35" s="86">
         <f>SUM(C19:C34)</f>
-        <v>3868</v>
-      </c>
-      <c r="D35" s="73">
+        <v>0</v>
+      </c>
+      <c r="D35" s="86">
         <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
-        <v>3716.6</v>
-      </c>
-      <c r="E35" s="73">
+        <v>0</v>
+      </c>
+      <c r="E35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="73">
+      <c r="F35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="73">
+      <c r="G35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H35" s="73">
+      <c r="H35" s="86">
         <f t="shared" si="3"/>
-        <v>4456</v>
-      </c>
-      <c r="I35" s="73">
+        <v>0</v>
+      </c>
+      <c r="I35" s="86">
         <f t="shared" si="3"/>
-        <v>1601.9099999999999</v>
-      </c>
-      <c r="J35" s="73">
+        <v>0</v>
+      </c>
+      <c r="J35" s="86">
         <f t="shared" si="3"/>
-        <v>3600</v>
-      </c>
-      <c r="K35" s="73">
+        <v>0</v>
+      </c>
+      <c r="K35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="73">
+      <c r="L35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="73">
+      <c r="M35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="73">
+      <c r="N35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O35" s="73">
+      <c r="O35" s="86">
         <f t="shared" si="3"/>
-        <v>1971</v>
-      </c>
-      <c r="P35" s="73">
+        <v>0</v>
+      </c>
+      <c r="P35" s="86">
         <f t="shared" si="3"/>
-        <v>25.18</v>
-      </c>
-      <c r="Q35" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="86">
         <f t="shared" si="3"/>
-        <v>285</v>
-      </c>
-      <c r="R35" s="73">
+        <v>0</v>
+      </c>
+      <c r="R35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S35" s="73">
+      <c r="S35" s="86">
         <f t="shared" si="3"/>
-        <v>1400</v>
-      </c>
-      <c r="T35" s="73">
+        <v>0</v>
+      </c>
+      <c r="T35" s="86">
         <f>SUM(T19:T34)</f>
-        <v>1649</v>
-      </c>
-      <c r="U35" s="73">
+        <v>0</v>
+      </c>
+      <c r="U35" s="86">
         <f t="shared" si="3"/>
-        <v>2316</v>
-      </c>
-      <c r="V35" s="73">
+        <v>0</v>
+      </c>
+      <c r="V35" s="86">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W35" s="73">
+      <c r="W35" s="86">
         <f>SUM(W19:W34)</f>
-        <v>24888.690000000002</v>
-      </c>
-      <c r="X35" s="60">
+        <v>0</v>
+      </c>
+      <c r="X35" s="88">
         <f>SUM(X19:X34)</f>
-        <v>33088.14</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="61">
         <f>X35-W35</f>
-        <v>8199.4499999999971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="83"/>
-      <c r="C36" s="70">
+      <c r="B36" s="82"/>
+      <c r="C36" s="73">
         <f>SUM(C18,C35)</f>
-        <v>12296.35</v>
-      </c>
-      <c r="D36" s="70">
+        <v>0</v>
+      </c>
+      <c r="D36" s="73">
         <f t="shared" ref="D36:W36" si="4">SUM(D18,D35)</f>
-        <v>12427.960000000001</v>
-      </c>
-      <c r="E36" s="70">
+        <v>0</v>
+      </c>
+      <c r="E36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F36" s="70">
+      <c r="F36" s="73">
         <f t="shared" si="4"/>
-        <v>1434</v>
-      </c>
-      <c r="G36" s="70">
+        <v>596</v>
+      </c>
+      <c r="G36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H36" s="70">
+      <c r="H36" s="73">
         <f t="shared" si="4"/>
-        <v>13360</v>
-      </c>
-      <c r="I36" s="70">
+        <v>0</v>
+      </c>
+      <c r="I36" s="73">
         <f t="shared" si="4"/>
-        <v>2351.91</v>
-      </c>
-      <c r="J36" s="70">
+        <v>0</v>
+      </c>
+      <c r="J36" s="73">
         <f t="shared" si="4"/>
-        <v>3600</v>
-      </c>
-      <c r="K36" s="70">
+        <v>0</v>
+      </c>
+      <c r="K36" s="73">
         <f t="shared" si="4"/>
-        <v>5015.5200000000004</v>
-      </c>
-      <c r="L36" s="70">
+        <v>0</v>
+      </c>
+      <c r="L36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M36" s="70">
+      <c r="M36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N36" s="70">
+      <c r="N36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O36" s="70">
+      <c r="O36" s="73">
         <f t="shared" si="4"/>
-        <v>4302</v>
-      </c>
-      <c r="P36" s="70">
+        <v>271</v>
+      </c>
+      <c r="P36" s="73">
         <f t="shared" si="4"/>
-        <v>3342.18</v>
-      </c>
-      <c r="Q36" s="70">
+        <v>1000</v>
+      </c>
+      <c r="Q36" s="73">
         <f t="shared" si="4"/>
-        <v>3747</v>
-      </c>
-      <c r="R36" s="70">
+        <v>0</v>
+      </c>
+      <c r="R36" s="73">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S36" s="70">
+      <c r="S36" s="73">
         <f>SUM(S18,S35)</f>
-        <v>7949</v>
-      </c>
-      <c r="T36" s="70">
+        <v>199</v>
+      </c>
+      <c r="T36" s="73">
         <f t="shared" si="4"/>
-        <v>10948</v>
-      </c>
-      <c r="U36" s="70">
+        <v>0</v>
+      </c>
+      <c r="U36" s="73">
         <f t="shared" si="4"/>
-        <v>2316</v>
-      </c>
-      <c r="V36" s="70">
+        <v>0</v>
+      </c>
+      <c r="V36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="70">
+        <v>850</v>
+      </c>
+      <c r="W36" s="73">
         <f t="shared" si="4"/>
-        <v>83089.920000000013</v>
-      </c>
-      <c r="X36" s="70">
+        <v>2916</v>
+      </c>
+      <c r="X36" s="73">
         <f>SUM(X18,X35)</f>
-        <v>90059.05</v>
+        <v>58234.26</v>
       </c>
       <c r="Y36" s="70">
         <f>SUM(Y18,Y35)</f>
-        <v>6969.1299999999974</v>
+        <v>55318.26</v>
       </c>
     </row>
     <row r="40" spans="1:25">

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5"/>
   </bookViews>
@@ -14,9 +14,9 @@
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
     <sheet name=" Июнь 2026" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -162,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -215,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -267,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -329,7 +329,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -355,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -381,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -408,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -460,7 +460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -486,7 +486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -512,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -539,7 +539,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -565,7 +565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -591,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -644,7 +644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -671,7 +671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -697,7 +697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -749,7 +749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -775,7 +775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -811,7 +811,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -827,7 +827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -854,7 +854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -881,7 +881,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -907,7 +907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -933,7 +933,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -959,7 +959,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -985,7 +985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1012,7 +1012,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1039,7 +1039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1066,7 +1066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1092,7 +1092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1119,7 +1119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1145,7 +1145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0">
+    <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1172,7 +1172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0">
+    <comment ref="S6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1199,7 +1199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0">
+    <comment ref="H8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1215,7 +1215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1242,7 +1242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0">
+    <comment ref="X11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1269,7 +1269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0">
+    <comment ref="X12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1295,7 +1295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1322,7 +1322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1338,7 +1338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0">
+    <comment ref="T15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1353,7 +1353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1379,7 +1379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1405,7 +1405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1431,7 +1431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1458,7 +1458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1484,7 +1484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1510,7 +1510,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1535,7 +1535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0">
+    <comment ref="T22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1560,7 +1560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="E24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1586,7 +1586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0">
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1612,7 +1612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1638,7 +1638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0">
+    <comment ref="H29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1663,7 +1663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1688,7 +1688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1713,7 +1713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0">
+    <comment ref="X30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1737,7 +1737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1761,7 +1761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1787,7 +1787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0">
+    <comment ref="X35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1823,7 +1823,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1847,7 +1847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1872,7 +1872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1896,7 +1896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
+    <comment ref="F5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1922,7 +1922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1948,7 +1948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1974,7 +1974,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0">
+    <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2000,7 +2000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0">
+    <comment ref="X7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2026,7 +2026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2052,7 +2052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0">
+    <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2078,7 +2078,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0">
+    <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2103,7 +2103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0">
+    <comment ref="H11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2127,7 +2127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2152,7 +2152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0">
+    <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2176,7 +2176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2200,7 +2200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2225,7 +2225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2249,7 +2249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2274,7 +2274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0">
+    <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2298,7 +2298,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0">
+    <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2322,7 +2322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2346,7 +2346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0">
+    <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2372,7 +2372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0">
+    <comment ref="H27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2398,7 +2398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0">
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2424,7 +2424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0">
+    <comment ref="H28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2450,7 +2450,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0">
+    <comment ref="V28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2477,7 +2477,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0">
+    <comment ref="X28" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама дала в долг</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2503,7 +2529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0">
+    <comment ref="X29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2529,7 +2555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0">
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2555,7 +2581,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2592,7 +2644,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2618,7 +2670,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+БК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2644,7 +2722,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Чурсанову на шары на др</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2667,6 +2771,733 @@
           </rPr>
           <t xml:space="preserve">
 Журнал ЧТИВО</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Бабл ти и поке</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Поход к Паньшину</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Снял в банкомате и отдал Ане</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Теле2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+1/2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Не помню, что это</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Бабл ти</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вкусно и Точка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Не помню на что</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевод Ане</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Про мясо и бабл ти</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Цветы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S8" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Доля ми за журнальчик</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевод Ане</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Батя дал на таблетки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Додо Пицца</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Игристое для посиделок с Гогой и Владой</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевод от Ани
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевод от Ани</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Долямми за журнальчик</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X14" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама дала в долг</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама перевела Ане (дала в долг)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Кофе</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Удаление кондиломы</t>
         </r>
       </text>
     </comment>
@@ -2675,7 +3506,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="59">
   <si>
     <t>Число</t>
   </si>
@@ -2851,11 +3682,14 @@
   <si>
     <t>Доходы - Расходы Май 2026</t>
   </si>
+  <si>
+    <t>Доходы - Расходы Июнь 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -3067,13 +3901,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Franklin Gothic Demi"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3173,6 +4007,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3353,7 +4193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3528,6 +4368,10 @@
     <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3564,13 +4408,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3898,14 +4740,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3939,7 +4781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="16.5">
+    <row r="5" spans="3:8" ht="15.75">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -3959,7 +4801,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="16.5">
+    <row r="6" spans="3:8" ht="15.75">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -3980,7 +4822,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="16.5">
+    <row r="7" spans="3:8" ht="15.75">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -4001,7 +4843,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="16.5">
+    <row r="8" spans="3:8" ht="15.75">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -4022,7 +4864,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="16.5">
+    <row r="9" spans="3:8" ht="15.75">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -4032,7 +4874,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="16.5">
+    <row r="10" spans="3:8" ht="15.75">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -4042,7 +4884,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="16.5">
+    <row r="11" spans="3:8" ht="15.75">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -4052,7 +4894,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="16.5">
+    <row r="12" spans="3:8" ht="15.75">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -4062,7 +4904,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="16.5">
+    <row r="13" spans="3:8" ht="15.75">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -4072,7 +4914,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="16.5">
+    <row r="14" spans="3:8" ht="15.75">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -4082,7 +4924,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="16.5">
+    <row r="15" spans="3:8" ht="15.75">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -4092,7 +4934,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="17.25" thickBot="1">
+    <row r="16" spans="3:8" ht="16.5" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -4102,7 +4944,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="17.25" thickBot="1">
+    <row r="17" spans="3:8" ht="16.5" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -4135,7 +4977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4145,32 +4987,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -5369,10 +6211,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="75"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -5485,7 +6327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5495,32 +6337,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -6731,10 +7573,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="76"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -6847,7 +7689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6857,33 +7699,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -7701,10 +8543,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="80"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -8213,7 +9055,7 @@
         <f t="shared" si="0"/>
         <v>821</v>
       </c>
-      <c r="X30" s="42">
+      <c r="X30" s="90">
         <v>10000</v>
       </c>
       <c r="Y30" s="43"/>
@@ -8424,10 +9266,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="79" t="s">
+      <c r="A36" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="80"/>
+      <c r="B36" s="82"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -8522,10 +9364,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="78"/>
+      <c r="B37" s="80"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -8645,7 +9487,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8655,33 +9497,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -9391,10 +10233,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="82" t="s">
+      <c r="A18" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="82"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -9913,7 +10755,9 @@
         <f t="shared" si="2"/>
         <v>4655</v>
       </c>
-      <c r="X28" s="68"/>
+      <c r="X28" s="88">
+        <v>5000</v>
+      </c>
       <c r="Y28" s="69"/>
     </row>
     <row r="29" spans="1:27" ht="15.75">
@@ -9954,7 +10798,7 @@
         <f t="shared" si="2"/>
         <v>4784.68</v>
       </c>
-      <c r="X29" s="64">
+      <c r="X29" s="88">
         <v>5000</v>
       </c>
       <c r="Y29" s="65"/>
@@ -10145,10 +10989,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="82"/>
+      <c r="B35" s="84"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -10235,18 +11079,18 @@
       </c>
       <c r="X35" s="60">
         <f>SUM(X19:X34)</f>
-        <v>41088.14</v>
+        <v>46088.14</v>
       </c>
       <c r="Y35" s="61">
         <f>X35-W35</f>
-        <v>-6498.6900000000023</v>
+        <v>-1498.6900000000023</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="83"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -10333,11 +11177,11 @@
       </c>
       <c r="X36" s="70">
         <f>SUM(X18,X35)</f>
-        <v>98059.05</v>
+        <v>103059.05</v>
       </c>
       <c r="Y36" s="70">
         <f>SUM(Y18,Y35)</f>
-        <v>-7729.010000000002</v>
+        <v>-2729.010000000002</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -10374,7 +11218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10384,108 +11228,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
+      <c r="A1" s="86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
+      <c r="V1" s="86"/>
+      <c r="W1" s="86"/>
+      <c r="X1" s="86"/>
+      <c r="Y1" s="86"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="87" t="s">
+      <c r="G2" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="87" t="s">
+      <c r="H2" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="87" t="s">
+      <c r="J2" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="87" t="s">
+      <c r="K2" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="87" t="s">
+      <c r="L2" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="87" t="s">
+      <c r="M2" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="87" t="s">
+      <c r="O2" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="87" t="s">
+      <c r="P2" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="87" t="s">
+      <c r="Q2" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="87" t="s">
+      <c r="R2" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="87" t="s">
+      <c r="S2" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="87" t="s">
+      <c r="T2" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="87" t="s">
+      <c r="U2" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="87" t="s">
+      <c r="V2" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="87" t="s">
+      <c r="W2" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="87" t="s">
+      <c r="X2" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="87" t="s">
+      <c r="Y2" s="89" t="s">
         <v>21</v>
       </c>
       <c r="Z2" s="1"/>
@@ -10518,14 +11362,22 @@
       <c r="B3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
+      <c r="C3" s="71">
+        <f>310+1963+195</f>
+        <v>2468</v>
+      </c>
+      <c r="D3" s="71">
+        <v>2091</v>
+      </c>
       <c r="E3" s="71"/>
       <c r="F3" s="71">
         <v>596</v>
       </c>
       <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="H3" s="71">
+        <f>209</f>
+        <v>209</v>
+      </c>
       <c r="I3" s="71"/>
       <c r="J3" s="71"/>
       <c r="K3" s="71"/>
@@ -10544,7 +11396,9 @@
         <f>199</f>
         <v>199</v>
       </c>
-      <c r="T3" s="71"/>
+      <c r="T3" s="71">
+        <v>2300</v>
+      </c>
       <c r="U3" s="71"/>
       <c r="V3" s="71">
         <f>850</f>
@@ -10552,7 +11406,7 @@
       </c>
       <c r="W3" s="71">
         <f>SUM(C3:V3)</f>
-        <v>2916</v>
+        <v>9984</v>
       </c>
       <c r="X3" s="64">
         <f>35654.26+22580</f>
@@ -10568,28 +11422,39 @@
         <v>5</v>
       </c>
       <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
+      <c r="D4" s="72">
+        <f>5183+98</f>
+        <v>5281</v>
+      </c>
       <c r="E4" s="72"/>
       <c r="F4" s="72"/>
       <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
+      <c r="H4" s="72">
+        <v>1450</v>
+      </c>
       <c r="I4" s="72"/>
       <c r="J4" s="72"/>
       <c r="K4" s="72"/>
       <c r="L4" s="72"/>
       <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
+      <c r="N4" s="72">
+        <v>2000</v>
+      </c>
       <c r="O4" s="72"/>
       <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
+      <c r="Q4" s="72">
+        <v>5700</v>
+      </c>
       <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
+      <c r="S4" s="72">
+        <v>700</v>
+      </c>
       <c r="T4" s="72"/>
       <c r="U4" s="72"/>
       <c r="V4" s="72"/>
       <c r="W4" s="72">
         <f>SUM(C4:V4)</f>
-        <v>0</v>
+        <v>15131</v>
       </c>
       <c r="X4" s="68"/>
       <c r="Y4" s="69"/>
@@ -10601,12 +11466,17 @@
       <c r="B5" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="71"/>
+      <c r="C5" s="71">
+        <f>280+1103</f>
+        <v>1383</v>
+      </c>
       <c r="D5" s="71"/>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
+      <c r="H5" s="71">
+        <v>1280</v>
+      </c>
       <c r="I5" s="71"/>
       <c r="J5" s="71"/>
       <c r="K5" s="71"/>
@@ -10618,12 +11488,14 @@
       <c r="Q5" s="71"/>
       <c r="R5" s="71"/>
       <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
+      <c r="T5" s="71">
+        <v>1075</v>
+      </c>
       <c r="U5" s="71"/>
       <c r="V5" s="71"/>
       <c r="W5" s="71">
         <f t="shared" ref="W5:W17" si="0">SUM(C5:V5)</f>
-        <v>0</v>
+        <v>3738</v>
       </c>
       <c r="X5" s="64"/>
       <c r="Y5" s="65"/>
@@ -10635,12 +11507,20 @@
       <c r="B6" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="72"/>
+      <c r="C6" s="72">
+        <f>155</f>
+        <v>155</v>
+      </c>
       <c r="D6" s="72"/>
       <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
+      <c r="F6" s="72">
+        <f>700</f>
+        <v>700</v>
+      </c>
       <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
+      <c r="H6" s="72">
+        <v>1734</v>
+      </c>
       <c r="I6" s="72"/>
       <c r="J6" s="72"/>
       <c r="K6" s="72"/>
@@ -10648,16 +11528,20 @@
       <c r="M6" s="72"/>
       <c r="N6" s="72"/>
       <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
+      <c r="P6" s="72">
+        <v>336</v>
+      </c>
       <c r="Q6" s="72"/>
       <c r="R6" s="72"/>
       <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
+      <c r="T6" s="72">
+        <v>990</v>
+      </c>
       <c r="U6" s="72"/>
       <c r="V6" s="72"/>
       <c r="W6" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="X6" s="68"/>
       <c r="Y6" s="69"/>
@@ -10669,7 +11553,9 @@
       <c r="B7" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="71"/>
+      <c r="C7" s="71">
+        <v>1707</v>
+      </c>
       <c r="D7" s="71"/>
       <c r="E7" s="71"/>
       <c r="F7" s="71"/>
@@ -10682,8 +11568,13 @@
       <c r="M7" s="71"/>
       <c r="N7" s="71"/>
       <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
+      <c r="P7" s="71">
+        <f>1000+297</f>
+        <v>1297</v>
+      </c>
+      <c r="Q7" s="71">
+        <v>400</v>
+      </c>
       <c r="R7" s="71"/>
       <c r="S7" s="71"/>
       <c r="T7" s="71"/>
@@ -10691,7 +11582,7 @@
       <c r="V7" s="71"/>
       <c r="W7" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3404</v>
       </c>
       <c r="X7" s="64"/>
       <c r="Y7" s="65"/>
@@ -10704,9 +11595,14 @@
         <v>2</v>
       </c>
       <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
+      <c r="D8" s="72">
+        <v>1261</v>
+      </c>
       <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
+      <c r="F8" s="72">
+        <f>1080+740</f>
+        <v>1820</v>
+      </c>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
       <c r="I8" s="72"/>
@@ -10714,18 +11610,25 @@
       <c r="K8" s="72"/>
       <c r="L8" s="72"/>
       <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
+      <c r="N8" s="72">
+        <f>15454</f>
+        <v>15454</v>
+      </c>
       <c r="O8" s="72"/>
       <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
+      <c r="Q8" s="72">
+        <v>2630</v>
+      </c>
       <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
+      <c r="S8" s="72">
+        <v>841</v>
+      </c>
       <c r="T8" s="72"/>
       <c r="U8" s="72"/>
       <c r="V8" s="72"/>
       <c r="W8" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22006</v>
       </c>
       <c r="X8" s="68"/>
       <c r="Y8" s="69"/>
@@ -10737,7 +11640,9 @@
       <c r="B9" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>1198</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -10749,9 +11654,14 @@
       <c r="L9" s="71"/>
       <c r="M9" s="71"/>
       <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <f>201+203+153</f>
+        <v>557</v>
+      </c>
       <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="Q9" s="71">
+        <v>2600</v>
+      </c>
       <c r="R9" s="71"/>
       <c r="S9" s="71"/>
       <c r="T9" s="71"/>
@@ -10759,9 +11669,11 @@
       <c r="V9" s="71"/>
       <c r="W9" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="64"/>
+        <v>4355</v>
+      </c>
+      <c r="X9" s="64">
+        <v>15000</v>
+      </c>
       <c r="Y9" s="65"/>
     </row>
     <row r="10" spans="1:47" ht="15.75">
@@ -10772,8 +11684,12 @@
         <v>4</v>
       </c>
       <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
+      <c r="D10" s="72">
+        <v>1951.75</v>
+      </c>
+      <c r="E10" s="72">
+        <v>1310</v>
+      </c>
       <c r="F10" s="72"/>
       <c r="G10" s="72"/>
       <c r="H10" s="72"/>
@@ -10793,7 +11709,7 @@
       <c r="V10" s="72"/>
       <c r="W10" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3261.75</v>
       </c>
       <c r="X10" s="68"/>
       <c r="Y10" s="69"/>
@@ -10805,19 +11721,30 @@
       <c r="B11" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
+      <c r="C11" s="71">
+        <f>391+602</f>
+        <v>993</v>
+      </c>
+      <c r="D11" s="71">
+        <v>1090.32</v>
+      </c>
+      <c r="E11" s="71">
+        <v>4180</v>
+      </c>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
       <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
+      <c r="I11" s="71">
+        <v>1413</v>
+      </c>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
       <c r="L11" s="71"/>
       <c r="M11" s="71"/>
       <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="71">
+        <v>340</v>
+      </c>
       <c r="P11" s="71"/>
       <c r="Q11" s="71"/>
       <c r="R11" s="71"/>
@@ -10827,7 +11754,7 @@
       <c r="V11" s="71"/>
       <c r="W11" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8016.32</v>
       </c>
       <c r="X11" s="64"/>
       <c r="Y11" s="65"/>
@@ -10840,7 +11767,9 @@
         <v>6</v>
       </c>
       <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
+      <c r="D12" s="72">
+        <v>1743</v>
+      </c>
       <c r="E12" s="72"/>
       <c r="F12" s="72"/>
       <c r="G12" s="72"/>
@@ -10851,9 +11780,13 @@
       <c r="L12" s="72"/>
       <c r="M12" s="72"/>
       <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
+      <c r="O12" s="72">
+        <v>385</v>
+      </c>
       <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
+      <c r="Q12" s="72">
+        <v>-1000</v>
+      </c>
       <c r="R12" s="72"/>
       <c r="S12" s="72"/>
       <c r="T12" s="72"/>
@@ -10861,7 +11794,7 @@
       <c r="V12" s="72"/>
       <c r="W12" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="X12" s="68"/>
       <c r="Y12" s="69"/>
@@ -10874,7 +11807,9 @@
         <v>7</v>
       </c>
       <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
+      <c r="D13" s="71">
+        <v>152</v>
+      </c>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
@@ -10885,17 +11820,23 @@
       <c r="L13" s="71"/>
       <c r="M13" s="71"/>
       <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="71">
+        <v>358</v>
+      </c>
       <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
+      <c r="Q13" s="71">
+        <v>-300</v>
+      </c>
       <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
+      <c r="S13" s="71">
+        <v>842</v>
+      </c>
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
       <c r="V13" s="71"/>
       <c r="W13" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="X13" s="64"/>
       <c r="Y13" s="65"/>
@@ -10931,7 +11872,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X14" s="68"/>
+      <c r="X14" s="88">
+        <v>5000</v>
+      </c>
       <c r="Y14" s="69"/>
     </row>
     <row r="15" spans="1:47" ht="15.75">
@@ -10999,7 +11942,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X16" s="68"/>
+      <c r="X16" s="88">
+        <v>2000</v>
+      </c>
       <c r="Y16" s="69"/>
     </row>
     <row r="17" spans="1:27" ht="15.75">
@@ -11010,11 +11955,15 @@
         <v>4</v>
       </c>
       <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
+      <c r="D17" s="71">
+        <v>2587</v>
+      </c>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
       <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
+      <c r="H17" s="71">
+        <v>1836</v>
+      </c>
       <c r="I17" s="71"/>
       <c r="J17" s="71"/>
       <c r="K17" s="71"/>
@@ -11022,116 +11971,123 @@
       <c r="M17" s="71"/>
       <c r="N17" s="71"/>
       <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
+      <c r="P17" s="71">
+        <f>280+13</f>
+        <v>293</v>
+      </c>
       <c r="Q17" s="71"/>
       <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
+      <c r="S17" s="71">
+        <v>499</v>
+      </c>
+      <c r="T17" s="71">
+        <v>640</v>
+      </c>
       <c r="U17" s="71"/>
       <c r="V17" s="71"/>
       <c r="W17" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="X17" s="64"/>
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86">
+      <c r="B18" s="87"/>
+      <c r="C18" s="74">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="86">
+        <v>7904</v>
+      </c>
+      <c r="D18" s="74">
+        <f t="shared" si="1"/>
+        <v>16157.07</v>
+      </c>
+      <c r="E18" s="74">
+        <f t="shared" si="1"/>
+        <v>5490</v>
+      </c>
+      <c r="F18" s="74">
+        <f t="shared" si="1"/>
+        <v>3116</v>
+      </c>
+      <c r="G18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E18" s="86">
+      <c r="H18" s="74">
+        <f t="shared" si="1"/>
+        <v>6509</v>
+      </c>
+      <c r="I18" s="74">
+        <f t="shared" si="1"/>
+        <v>1413</v>
+      </c>
+      <c r="J18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F18" s="86">
-        <f t="shared" si="1"/>
-        <v>596</v>
-      </c>
-      <c r="G18" s="86">
+      <c r="K18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="86">
+      <c r="L18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="86">
+      <c r="M18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="86">
+      <c r="N18" s="74">
+        <f t="shared" si="1"/>
+        <v>17454</v>
+      </c>
+      <c r="O18" s="74">
+        <f t="shared" si="1"/>
+        <v>1911</v>
+      </c>
+      <c r="P18" s="74">
+        <f t="shared" si="1"/>
+        <v>2926</v>
+      </c>
+      <c r="Q18" s="74">
+        <f t="shared" si="1"/>
+        <v>10030</v>
+      </c>
+      <c r="R18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="86">
+      <c r="S18" s="74">
+        <f t="shared" si="1"/>
+        <v>3081</v>
+      </c>
+      <c r="T18" s="74">
+        <f t="shared" si="1"/>
+        <v>5005</v>
+      </c>
+      <c r="U18" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="86">
-        <f t="shared" si="1"/>
-        <v>271</v>
-      </c>
-      <c r="P18" s="86">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="Q18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="86">
-        <f t="shared" si="1"/>
-        <v>199</v>
-      </c>
-      <c r="T18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="86">
+      <c r="V18" s="74">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="W18" s="86">
+      <c r="W18" s="74">
         <f t="shared" si="1"/>
-        <v>2916</v>
-      </c>
-      <c r="X18" s="88">
+        <v>81846.070000000007</v>
+      </c>
+      <c r="X18" s="75">
         <f t="shared" si="1"/>
-        <v>58234.26</v>
+        <v>80234.260000000009</v>
       </c>
       <c r="Y18" s="61">
         <f>X18-W18</f>
-        <v>55318.26</v>
+        <v>-1611.8099999999977</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15.75">
@@ -11146,14 +12102,20 @@
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="H19" s="71">
+        <v>351</v>
+      </c>
       <c r="I19" s="71"/>
       <c r="J19" s="71"/>
       <c r="K19" s="71"/>
       <c r="L19" s="71"/>
       <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
+      <c r="N19" s="71">
+        <v>7500</v>
+      </c>
+      <c r="O19" s="71">
+        <v>556</v>
+      </c>
       <c r="P19" s="71"/>
       <c r="Q19" s="71"/>
       <c r="R19" s="71"/>
@@ -11163,9 +12125,11 @@
       <c r="V19" s="71"/>
       <c r="W19" s="71">
         <f>SUM(C19:V19)</f>
-        <v>0</v>
-      </c>
-      <c r="X19" s="64"/>
+        <v>8407</v>
+      </c>
+      <c r="X19" s="64">
+        <v>32257.279999999999</v>
+      </c>
       <c r="Y19" s="65"/>
     </row>
     <row r="20" spans="1:27" ht="15.75">
@@ -11680,123 +12644,123 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="86">
+      <c r="B35" s="87"/>
+      <c r="C35" s="74">
         <f>SUM(C19:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="86">
+      <c r="D35" s="74">
         <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="86">
+      <c r="E35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="86">
+      <c r="F35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="86">
+      <c r="G35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H35" s="86">
+      <c r="H35" s="74">
+        <f t="shared" si="3"/>
+        <v>351</v>
+      </c>
+      <c r="I35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I35" s="86">
+      <c r="J35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="86">
+      <c r="K35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="86">
+      <c r="L35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="86">
+      <c r="M35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="86">
+      <c r="N35" s="74">
+        <f t="shared" si="3"/>
+        <v>7500</v>
+      </c>
+      <c r="O35" s="74">
+        <f t="shared" si="3"/>
+        <v>556</v>
+      </c>
+      <c r="P35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="86">
+      <c r="Q35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O35" s="86">
+      <c r="R35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P35" s="86">
+      <c r="S35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="86">
+      <c r="T35" s="74">
+        <f>SUM(T19:T34)</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R35" s="86">
+      <c r="V35" s="74">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S35" s="86">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T35" s="86">
-        <f>SUM(T19:T34)</f>
-        <v>0</v>
-      </c>
-      <c r="U35" s="86">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="86">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="86">
+      <c r="W35" s="74">
         <f>SUM(W19:W34)</f>
-        <v>0</v>
-      </c>
-      <c r="X35" s="88">
+        <v>8407</v>
+      </c>
+      <c r="X35" s="75">
         <f>SUM(X19:X34)</f>
-        <v>0</v>
+        <v>32257.279999999999</v>
       </c>
       <c r="Y35" s="61">
         <f>X35-W35</f>
-        <v>0</v>
+        <v>23850.28</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="82" t="s">
+      <c r="A36" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="84"/>
       <c r="C36" s="73">
         <f>SUM(C18,C35)</f>
-        <v>0</v>
+        <v>7904</v>
       </c>
       <c r="D36" s="73">
         <f t="shared" ref="D36:W36" si="4">SUM(D18,D35)</f>
-        <v>0</v>
+        <v>16157.07</v>
       </c>
       <c r="E36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5490</v>
       </c>
       <c r="F36" s="73">
         <f t="shared" si="4"/>
-        <v>596</v>
+        <v>3116</v>
       </c>
       <c r="G36" s="73">
         <f t="shared" si="4"/>
@@ -11804,11 +12768,11 @@
       </c>
       <c r="H36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6860</v>
       </c>
       <c r="I36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="J36" s="73">
         <f t="shared" si="4"/>
@@ -11828,19 +12792,19 @@
       </c>
       <c r="N36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24954</v>
       </c>
       <c r="O36" s="73">
         <f t="shared" si="4"/>
-        <v>271</v>
+        <v>2467</v>
       </c>
       <c r="P36" s="73">
         <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>2926</v>
       </c>
       <c r="Q36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="R36" s="73">
         <f t="shared" si="4"/>
@@ -11848,11 +12812,11 @@
       </c>
       <c r="S36" s="73">
         <f>SUM(S18,S35)</f>
-        <v>199</v>
+        <v>3081</v>
       </c>
       <c r="T36" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5005</v>
       </c>
       <c r="U36" s="73">
         <f t="shared" si="4"/>
@@ -11864,15 +12828,15 @@
       </c>
       <c r="W36" s="73">
         <f t="shared" si="4"/>
-        <v>2916</v>
+        <v>90253.07</v>
       </c>
       <c r="X36" s="73">
         <f>SUM(X18,X35)</f>
-        <v>58234.26</v>
+        <v>112491.54000000001</v>
       </c>
       <c r="Y36" s="70">
         <f>SUM(Y18,Y35)</f>
-        <v>55318.26</v>
+        <v>22238.47</v>
       </c>
     </row>
     <row r="40" spans="1:25">

--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная" sheetId="5" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Апрель 2026" sheetId="4" r:id="rId4"/>
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
     <sheet name=" Июнь 2026" sheetId="7" r:id="rId6"/>
+    <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3506,7 +3507,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="60">
   <si>
     <t>Число</t>
   </si>
@@ -3685,6 +3686,9 @@
   <si>
     <t>Доходы - Расходы Июнь 2026</t>
   </si>
+  <si>
+    <t>Доходы - Расходы Июль 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -3693,7 +3697,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3905,6 +3909,32 @@
       <name val="Franklin Gothic Demi"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFD5DA08"/>
+      <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFD5DA08"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -4193,7 +4223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4371,7 +4401,11 @@
     <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4408,16 +4442,40 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -4450,18 +4508,19 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFEC1606"/>
+        <color rgb="FF57B418"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF57B418"/>
+        <color rgb="FFEC1606"/>
       </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD5DA08"/>
       <color rgb="FF57B418"/>
       <color rgb="FFFF8585"/>
       <color rgb="FF6C0000"/>
@@ -4471,7 +4530,6 @@
       <color rgb="FF094679"/>
       <color rgb="FF7BB7E9"/>
       <color rgb="FF3179E3"/>
-      <color rgb="FF134873"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4528,7 +4586,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -4563,7 +4621,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4956,18 +5014,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>H5&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>H5&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>H5&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4987,32 +5045,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -6211,10 +6269,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="77"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -6337,32 +6395,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -7573,10 +7631,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="78" t="s">
+      <c r="A32" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="80"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -7699,33 +7757,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -8543,10 +8601,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="82"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -9055,7 +9113,7 @@
         <f t="shared" si="0"/>
         <v>821</v>
       </c>
-      <c r="X30" s="90">
+      <c r="X30" s="77">
         <v>10000</v>
       </c>
       <c r="Y30" s="43"/>
@@ -9266,10 +9324,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="81" t="s">
+      <c r="A36" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="82"/>
+      <c r="B36" s="84"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -9364,10 +9422,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="80"/>
+      <c r="B37" s="82"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -9497,33 +9555,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -10233,10 +10291,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="84"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -10755,7 +10813,7 @@
         <f t="shared" si="2"/>
         <v>4655</v>
       </c>
-      <c r="X28" s="88">
+      <c r="X28" s="75">
         <v>5000</v>
       </c>
       <c r="Y28" s="69"/>
@@ -10798,7 +10856,7 @@
         <f t="shared" si="2"/>
         <v>4784.68</v>
       </c>
-      <c r="X29" s="88">
+      <c r="X29" s="75">
         <v>5000</v>
       </c>
       <c r="Y29" s="65"/>
@@ -10989,10 +11047,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="84"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -11087,10 +11145,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="85" t="s">
+      <c r="A36" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="85"/>
+      <c r="B36" s="87"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -11204,10 +11262,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11228,108 +11286,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="86"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
-      <c r="A2" s="89" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="89" t="s">
+      <c r="A2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="89" t="s">
+      <c r="G2" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="89" t="s">
+      <c r="H2" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="89" t="s">
+      <c r="K2" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="89" t="s">
+      <c r="L2" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="89" t="s">
+      <c r="M2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="89" t="s">
+      <c r="N2" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="89" t="s">
+      <c r="O2" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="89" t="s">
+      <c r="P2" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="89" t="s">
+      <c r="Q2" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="89" t="s">
+      <c r="R2" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="89" t="s">
+      <c r="S2" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="89" t="s">
+      <c r="T2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="89" t="s">
+      <c r="U2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="89" t="s">
+      <c r="V2" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="89" t="s">
+      <c r="W2" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="89" t="s">
+      <c r="X2" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="89" t="s">
+      <c r="Y2" s="76" t="s">
         <v>21</v>
       </c>
       <c r="Z2" s="1"/>
@@ -11872,7 +11930,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X14" s="88">
+      <c r="X14" s="75">
         <v>5000</v>
       </c>
       <c r="Y14" s="69"/>
@@ -11942,7 +12000,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X16" s="88">
+      <c r="X16" s="75">
         <v>2000</v>
       </c>
       <c r="Y16" s="69"/>
@@ -11993,95 +12051,95 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="74">
+      <c r="B18" s="94"/>
+      <c r="C18" s="95">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="95">
         <f t="shared" si="1"/>
         <v>16157.07</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="95">
         <f t="shared" si="1"/>
         <v>5490</v>
       </c>
-      <c r="F18" s="74">
+      <c r="F18" s="95">
         <f t="shared" si="1"/>
         <v>3116</v>
       </c>
-      <c r="G18" s="74">
+      <c r="G18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="74">
+      <c r="H18" s="95">
         <f t="shared" si="1"/>
         <v>6509</v>
       </c>
-      <c r="I18" s="74">
+      <c r="I18" s="95">
         <f t="shared" si="1"/>
         <v>1413</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="74">
+      <c r="K18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="74">
+      <c r="L18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M18" s="74">
+      <c r="M18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="74">
+      <c r="N18" s="95">
         <f t="shared" si="1"/>
         <v>17454</v>
       </c>
-      <c r="O18" s="74">
+      <c r="O18" s="95">
         <f t="shared" si="1"/>
         <v>1911</v>
       </c>
-      <c r="P18" s="74">
+      <c r="P18" s="95">
         <f t="shared" si="1"/>
         <v>2926</v>
       </c>
-      <c r="Q18" s="74">
+      <c r="Q18" s="95">
         <f t="shared" si="1"/>
         <v>10030</v>
       </c>
-      <c r="R18" s="74">
+      <c r="R18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S18" s="74">
+      <c r="S18" s="95">
         <f t="shared" si="1"/>
         <v>3081</v>
       </c>
-      <c r="T18" s="74">
+      <c r="T18" s="95">
         <f t="shared" si="1"/>
         <v>5005</v>
       </c>
-      <c r="U18" s="74">
+      <c r="U18" s="95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V18" s="74">
+      <c r="V18" s="95">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="W18" s="74">
+      <c r="W18" s="95">
         <f t="shared" si="1"/>
         <v>81846.070000000007</v>
       </c>
-      <c r="X18" s="75">
+      <c r="X18" s="96">
         <f t="shared" si="1"/>
         <v>80234.260000000009</v>
       </c>
@@ -12644,95 +12702,95 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="87"/>
-      <c r="C35" s="74">
+      <c r="B35" s="94"/>
+      <c r="C35" s="95">
         <f>SUM(C19:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="74">
+      <c r="D35" s="95">
         <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="74">
+      <c r="E35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="74">
+      <c r="F35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="74">
+      <c r="G35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H35" s="74">
+      <c r="H35" s="95">
         <f t="shared" si="3"/>
         <v>351</v>
       </c>
-      <c r="I35" s="74">
+      <c r="I35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="74">
+      <c r="J35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="74">
+      <c r="K35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="74">
+      <c r="L35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="74">
+      <c r="M35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="74">
+      <c r="N35" s="95">
         <f t="shared" si="3"/>
         <v>7500</v>
       </c>
-      <c r="O35" s="74">
+      <c r="O35" s="95">
         <f t="shared" si="3"/>
         <v>556</v>
       </c>
-      <c r="P35" s="74">
+      <c r="P35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="74">
+      <c r="Q35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R35" s="74">
+      <c r="R35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S35" s="74">
+      <c r="S35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T35" s="74">
+      <c r="T35" s="95">
         <f>SUM(T19:T34)</f>
         <v>0</v>
       </c>
-      <c r="U35" s="74">
+      <c r="U35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V35" s="74">
+      <c r="V35" s="95">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W35" s="74">
+      <c r="W35" s="95">
         <f>SUM(W19:W34)</f>
         <v>8407</v>
       </c>
-      <c r="X35" s="75">
+      <c r="X35" s="96">
         <f>SUM(X19:X34)</f>
         <v>32257.279999999999</v>
       </c>
@@ -12742,95 +12800,95 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="84"/>
-      <c r="C36" s="73">
+      <c r="B36" s="89"/>
+      <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
       </c>
-      <c r="D36" s="73">
+      <c r="D36" s="74">
         <f t="shared" ref="D36:W36" si="4">SUM(D18,D35)</f>
         <v>16157.07</v>
       </c>
-      <c r="E36" s="73">
+      <c r="E36" s="74">
         <f t="shared" si="4"/>
         <v>5490</v>
       </c>
-      <c r="F36" s="73">
+      <c r="F36" s="74">
         <f t="shared" si="4"/>
         <v>3116</v>
       </c>
-      <c r="G36" s="73">
+      <c r="G36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H36" s="73">
+      <c r="H36" s="74">
         <f t="shared" si="4"/>
         <v>6860</v>
       </c>
-      <c r="I36" s="73">
+      <c r="I36" s="74">
         <f t="shared" si="4"/>
         <v>1413</v>
       </c>
-      <c r="J36" s="73">
+      <c r="J36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K36" s="73">
+      <c r="K36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L36" s="73">
+      <c r="L36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M36" s="73">
+      <c r="M36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N36" s="73">
+      <c r="N36" s="74">
         <f t="shared" si="4"/>
         <v>24954</v>
       </c>
-      <c r="O36" s="73">
+      <c r="O36" s="74">
         <f t="shared" si="4"/>
         <v>2467</v>
       </c>
-      <c r="P36" s="73">
+      <c r="P36" s="74">
         <f t="shared" si="4"/>
         <v>2926</v>
       </c>
-      <c r="Q36" s="73">
+      <c r="Q36" s="74">
         <f t="shared" si="4"/>
         <v>10030</v>
       </c>
-      <c r="R36" s="73">
+      <c r="R36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S36" s="73">
+      <c r="S36" s="74">
         <f>SUM(S18,S35)</f>
         <v>3081</v>
       </c>
-      <c r="T36" s="73">
+      <c r="T36" s="74">
         <f t="shared" si="4"/>
         <v>5005</v>
       </c>
-      <c r="U36" s="73">
+      <c r="U36" s="74">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V36" s="73">
+      <c r="V36" s="74">
         <f t="shared" si="4"/>
         <v>850</v>
       </c>
-      <c r="W36" s="73">
+      <c r="W36" s="74">
         <f t="shared" si="4"/>
         <v>90253.07</v>
       </c>
-      <c r="X36" s="73">
+      <c r="X36" s="74">
         <f>SUM(X18,X35)</f>
         <v>112491.54000000001</v>
       </c>
@@ -12859,10 +12917,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12870,4 +12928,1492 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AU42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
+    <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" ht="60.75" customHeight="1">
+      <c r="A1" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+    </row>
+    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="A2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+    </row>
+    <row r="3" spans="1:47" ht="15.75">
+      <c r="A3" s="62">
+        <v>3</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="65"/>
+    </row>
+    <row r="4" spans="1:47" ht="15.75">
+      <c r="A4" s="66">
+        <v>4</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="69"/>
+    </row>
+    <row r="5" spans="1:47" ht="15.75">
+      <c r="A5" s="62">
+        <v>5</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="65"/>
+    </row>
+    <row r="6" spans="1:47" ht="15.75">
+      <c r="A6" s="66">
+        <v>6</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="69"/>
+    </row>
+    <row r="7" spans="1:47" ht="15.75">
+      <c r="A7" s="62">
+        <v>7</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="65"/>
+    </row>
+    <row r="8" spans="1:47" ht="15.75">
+      <c r="A8" s="66">
+        <v>8</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="69"/>
+    </row>
+    <row r="9" spans="1:47" ht="15.75">
+      <c r="A9" s="62">
+        <v>9</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="65"/>
+    </row>
+    <row r="10" spans="1:47" ht="15.75">
+      <c r="A10" s="66">
+        <v>10</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="68"/>
+      <c r="Y10" s="69"/>
+    </row>
+    <row r="11" spans="1:47" ht="15.75">
+      <c r="A11" s="62">
+        <v>11</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="65"/>
+    </row>
+    <row r="12" spans="1:47" ht="15.75">
+      <c r="A12" s="66">
+        <v>12</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="69"/>
+    </row>
+    <row r="13" spans="1:47" ht="15.75">
+      <c r="A13" s="62">
+        <v>13</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="65"/>
+    </row>
+    <row r="14" spans="1:47" ht="15.75">
+      <c r="A14" s="66">
+        <v>14</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="69"/>
+    </row>
+    <row r="15" spans="1:47" ht="15.75">
+      <c r="A15" s="62">
+        <v>15</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="65"/>
+    </row>
+    <row r="16" spans="1:47" ht="15.75">
+      <c r="A16" s="66">
+        <v>16</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="69"/>
+    </row>
+    <row r="17" spans="1:27" ht="15.75">
+      <c r="A17" s="62">
+        <v>17</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="71"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="65"/>
+    </row>
+    <row r="18" spans="1:27" ht="15.75">
+      <c r="A18" s="66">
+        <v>18</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="69"/>
+    </row>
+    <row r="19" spans="1:27" ht="15.75">
+      <c r="A19" s="62">
+        <v>19</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="71"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="65"/>
+    </row>
+    <row r="20" spans="1:27" ht="14.25" customHeight="1">
+      <c r="A20" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="94"/>
+      <c r="C20" s="95">
+        <f t="shared" ref="C20:X20" si="0">SUM(C3:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="61">
+        <f>X20-W20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="15.75">
+      <c r="A21" s="62">
+        <v>20</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
+      <c r="U21" s="71"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="71"/>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="65"/>
+    </row>
+    <row r="22" spans="1:27" ht="15.75">
+      <c r="A22" s="66">
+        <v>21</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="68"/>
+      <c r="Y22" s="69"/>
+      <c r="AA22" s="44"/>
+    </row>
+    <row r="23" spans="1:27" ht="15.75">
+      <c r="A23" s="62">
+        <v>22</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="71"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="65"/>
+    </row>
+    <row r="24" spans="1:27" ht="15.75">
+      <c r="A24" s="66">
+        <v>23</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="68"/>
+      <c r="Y24" s="69"/>
+    </row>
+    <row r="25" spans="1:27" ht="15.75">
+      <c r="A25" s="62">
+        <v>24</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
+      <c r="U25" s="71"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="71"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="65"/>
+    </row>
+    <row r="26" spans="1:27" ht="15.75">
+      <c r="A26" s="66">
+        <v>25</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72"/>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="69"/>
+    </row>
+    <row r="27" spans="1:27" ht="15.75">
+      <c r="A27" s="62">
+        <v>26</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="71"/>
+      <c r="T27" s="71"/>
+      <c r="U27" s="71"/>
+      <c r="V27" s="71"/>
+      <c r="W27" s="71"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="65"/>
+    </row>
+    <row r="28" spans="1:27" ht="15.75">
+      <c r="A28" s="66">
+        <v>27</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="69"/>
+    </row>
+    <row r="29" spans="1:27" ht="15.75">
+      <c r="A29" s="62">
+        <v>28</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+      <c r="T29" s="71"/>
+      <c r="U29" s="71"/>
+      <c r="V29" s="71"/>
+      <c r="W29" s="71"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="65"/>
+    </row>
+    <row r="30" spans="1:27" ht="15.75">
+      <c r="A30" s="66">
+        <v>29</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="68"/>
+      <c r="Y30" s="69"/>
+    </row>
+    <row r="31" spans="1:27" ht="15.75">
+      <c r="A31" s="62">
+        <v>30</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="71"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="71"/>
+      <c r="W31" s="71"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="65"/>
+    </row>
+    <row r="32" spans="1:27" ht="15.75">
+      <c r="A32" s="66">
+        <v>31</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="68"/>
+      <c r="Y32" s="69"/>
+    </row>
+    <row r="33" spans="1:25" ht="15.75">
+      <c r="A33" s="62">
+        <v>1</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="71"/>
+      <c r="U33" s="71"/>
+      <c r="V33" s="71"/>
+      <c r="W33" s="71"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="65"/>
+    </row>
+    <row r="34" spans="1:25" ht="15.75">
+      <c r="A34" s="66">
+        <v>2</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72"/>
+      <c r="X34" s="68"/>
+      <c r="Y34" s="69"/>
+    </row>
+    <row r="35" spans="1:25" ht="15.75">
+      <c r="A35" s="62">
+        <v>3</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="71"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="71"/>
+      <c r="S35" s="71"/>
+      <c r="T35" s="71"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="71"/>
+      <c r="W35" s="71"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="65"/>
+    </row>
+    <row r="36" spans="1:25" ht="15.75">
+      <c r="A36" s="66">
+        <v>4</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="72"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="72"/>
+      <c r="X36" s="68"/>
+      <c r="Y36" s="69"/>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="94"/>
+      <c r="C37" s="95">
+        <f>SUM(C21:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="95">
+        <f t="shared" ref="D37:V37" si="1">SUM(D21:D36)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="95">
+        <f>SUM(T21:T36)</f>
+        <v>0</v>
+      </c>
+      <c r="U37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="95">
+        <f>SUM(W21:W36)</f>
+        <v>0</v>
+      </c>
+      <c r="X37" s="96">
+        <f>SUM(X21:X36)</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="93">
+        <f>X37-W37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="31.5" customHeight="1">
+      <c r="A38" s="91" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="91"/>
+      <c r="C38" s="92">
+        <f>SUM(C20,C37)</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="92">
+        <f t="shared" ref="D38:W38" si="2">SUM(D20,D37)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="92">
+        <f>SUM(S20,S37)</f>
+        <v>0</v>
+      </c>
+      <c r="T38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="92">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="92">
+        <f>SUM(X20,X37)</f>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="70">
+        <f>SUM(Y20,Y37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+  </mergeCells>
+  <conditionalFormatting sqref="Y20:Y38">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>Y20&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>Y20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Другое/2026/Доходы-Расходы.xlsx
+++ b/Другое/2026/Доходы-Расходы.xlsx
@@ -4406,6 +4406,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4439,6 +4449,9 @@
     <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4448,19 +4461,6 @@
     <xf numFmtId="0" fontId="31" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5045,32 +5045,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -6269,10 +6269,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="79"/>
+      <c r="B31" s="83"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -6395,32 +6395,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -7631,10 +7631,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="80"/>
+      <c r="B32" s="84"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -7757,33 +7757,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -8601,10 +8601,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="84"/>
+      <c r="B20" s="88"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -9324,10 +9324,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="84"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -9422,10 +9422,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="82" t="s">
+      <c r="A37" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="82"/>
+      <c r="B37" s="86"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -9555,33 +9555,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="89"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -10291,10 +10291,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="86"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -11047,10 +11047,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="86"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -11145,10 +11145,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="87"/>
+      <c r="B36" s="91"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -11286,33 +11286,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -12051,95 +12051,95 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="94"/>
-      <c r="C18" s="95">
+      <c r="B18" s="93"/>
+      <c r="C18" s="80">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
       </c>
-      <c r="D18" s="95">
+      <c r="D18" s="80">
         <f t="shared" si="1"/>
         <v>16157.07</v>
       </c>
-      <c r="E18" s="95">
+      <c r="E18" s="80">
         <f t="shared" si="1"/>
         <v>5490</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="80">
         <f t="shared" si="1"/>
         <v>3116</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="95">
+      <c r="H18" s="80">
         <f t="shared" si="1"/>
         <v>6509</v>
       </c>
-      <c r="I18" s="95">
+      <c r="I18" s="80">
         <f t="shared" si="1"/>
         <v>1413</v>
       </c>
-      <c r="J18" s="95">
+      <c r="J18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="95">
+      <c r="K18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="95">
+      <c r="L18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M18" s="95">
+      <c r="M18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="95">
+      <c r="N18" s="80">
         <f t="shared" si="1"/>
         <v>17454</v>
       </c>
-      <c r="O18" s="95">
+      <c r="O18" s="80">
         <f t="shared" si="1"/>
         <v>1911</v>
       </c>
-      <c r="P18" s="95">
+      <c r="P18" s="80">
         <f t="shared" si="1"/>
         <v>2926</v>
       </c>
-      <c r="Q18" s="95">
+      <c r="Q18" s="80">
         <f t="shared" si="1"/>
         <v>10030</v>
       </c>
-      <c r="R18" s="95">
+      <c r="R18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S18" s="95">
+      <c r="S18" s="80">
         <f t="shared" si="1"/>
         <v>3081</v>
       </c>
-      <c r="T18" s="95">
+      <c r="T18" s="80">
         <f t="shared" si="1"/>
         <v>5005</v>
       </c>
-      <c r="U18" s="95">
+      <c r="U18" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V18" s="95">
+      <c r="V18" s="80">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="W18" s="95">
+      <c r="W18" s="80">
         <f t="shared" si="1"/>
         <v>81846.070000000007</v>
       </c>
-      <c r="X18" s="96">
+      <c r="X18" s="81">
         <f t="shared" si="1"/>
         <v>80234.260000000009</v>
       </c>
@@ -12702,95 +12702,95 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="94"/>
-      <c r="C35" s="95">
+      <c r="B35" s="93"/>
+      <c r="C35" s="80">
         <f>SUM(C19:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="95">
+      <c r="D35" s="80">
         <f t="shared" ref="D35:V35" si="3">SUM(D19:D34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="95">
+      <c r="E35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="95">
+      <c r="F35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G35" s="95">
+      <c r="G35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H35" s="95">
+      <c r="H35" s="80">
         <f t="shared" si="3"/>
         <v>351</v>
       </c>
-      <c r="I35" s="95">
+      <c r="I35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="95">
+      <c r="J35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="95">
+      <c r="K35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L35" s="95">
+      <c r="L35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M35" s="95">
+      <c r="M35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="95">
+      <c r="N35" s="80">
         <f t="shared" si="3"/>
         <v>7500</v>
       </c>
-      <c r="O35" s="95">
+      <c r="O35" s="80">
         <f t="shared" si="3"/>
         <v>556</v>
       </c>
-      <c r="P35" s="95">
+      <c r="P35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="95">
+      <c r="Q35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R35" s="95">
+      <c r="R35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S35" s="95">
+      <c r="S35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T35" s="95">
+      <c r="T35" s="80">
         <f>SUM(T19:T34)</f>
         <v>0</v>
       </c>
-      <c r="U35" s="95">
+      <c r="U35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V35" s="95">
+      <c r="V35" s="80">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W35" s="95">
+      <c r="W35" s="80">
         <f>SUM(W19:W34)</f>
         <v>8407</v>
       </c>
-      <c r="X35" s="96">
+      <c r="X35" s="81">
         <f>SUM(X19:X34)</f>
         <v>32257.279999999999</v>
       </c>
@@ -12800,10 +12800,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="89" t="s">
+      <c r="A36" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="89"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -12941,33 +12941,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -13596,95 +13596,95 @@
       <c r="Y19" s="65"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="95">
+      <c r="B20" s="93"/>
+      <c r="C20" s="80">
         <f t="shared" ref="C20:X20" si="0">SUM(C3:C17)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="95">
+      <c r="D20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="95">
+      <c r="E20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="95">
+      <c r="G20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="95">
+      <c r="H20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="95">
+      <c r="I20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="95">
+      <c r="J20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K20" s="95">
+      <c r="K20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L20" s="95">
+      <c r="L20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M20" s="95">
+      <c r="M20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N20" s="95">
+      <c r="N20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O20" s="95">
+      <c r="O20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="95">
+      <c r="P20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="95">
+      <c r="Q20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R20" s="95">
+      <c r="R20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S20" s="95">
+      <c r="S20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T20" s="95">
+      <c r="T20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U20" s="95">
+      <c r="U20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V20" s="95">
+      <c r="V20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W20" s="95">
+      <c r="W20" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X20" s="96">
+      <c r="X20" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14191,193 +14191,193 @@
       <c r="Y36" s="69"/>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="94" t="s">
+      <c r="A37" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="94"/>
-      <c r="C37" s="95">
+      <c r="B37" s="93"/>
+      <c r="C37" s="80">
         <f>SUM(C21:C36)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="95">
+      <c r="D37" s="80">
         <f t="shared" ref="D37:V37" si="1">SUM(D21:D36)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="95">
+      <c r="E37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F37" s="95">
+      <c r="F37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G37" s="95">
+      <c r="G37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H37" s="95">
+      <c r="H37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="95">
+      <c r="I37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="95">
+      <c r="J37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K37" s="95">
+      <c r="K37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="95">
+      <c r="L37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="95">
+      <c r="M37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N37" s="95">
+      <c r="N37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O37" s="95">
+      <c r="O37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P37" s="95">
+      <c r="P37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="95">
+      <c r="Q37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R37" s="95">
+      <c r="R37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S37" s="95">
+      <c r="S37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T37" s="95">
+      <c r="T37" s="80">
         <f>SUM(T21:T36)</f>
         <v>0</v>
       </c>
-      <c r="U37" s="95">
+      <c r="U37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V37" s="95">
+      <c r="V37" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W37" s="95">
+      <c r="W37" s="80">
         <f>SUM(W21:W36)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="96">
+      <c r="X37" s="81">
         <f>SUM(X21:X36)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="93">
+      <c r="Y37" s="79">
         <f>X37-W37</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A38" s="91" t="s">
+      <c r="A38" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="91"/>
-      <c r="C38" s="92">
+      <c r="B38" s="96"/>
+      <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="92">
+      <c r="D38" s="78">
         <f t="shared" ref="D38:W38" si="2">SUM(D20,D37)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="92">
+      <c r="E38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F38" s="92">
+      <c r="F38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G38" s="92">
+      <c r="G38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H38" s="92">
+      <c r="H38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I38" s="92">
+      <c r="I38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J38" s="92">
+      <c r="J38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="92">
+      <c r="K38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L38" s="92">
+      <c r="L38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M38" s="92">
+      <c r="M38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N38" s="92">
+      <c r="N38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O38" s="92">
+      <c r="O38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P38" s="92">
+      <c r="P38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="92">
+      <c r="Q38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R38" s="92">
+      <c r="R38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S38" s="92">
+      <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="92">
+      <c r="T38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U38" s="92">
+      <c r="U38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V38" s="92">
+      <c r="V38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W38" s="92">
+      <c r="W38" s="78">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X38" s="92">
+      <c r="X38" s="78">
         <f>SUM(X20,X37)</f>
         <v>0</v>
       </c>
